--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -887,7 +887,7 @@
         <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
         <v>1.22</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
@@ -1897,13 +1897,13 @@
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q6" t="n">
         <v>1.23</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H9" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I9" t="n">
         <v>2.68</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
         <v>4</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
@@ -3155,7 +3155,7 @@
         <v>1.46</v>
       </c>
       <c r="J11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K11" t="n">
         <v>7</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 01:36:59</t>
+          <t>2026-07-18 03:58:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M2" t="n">
         <v>1.05</v>
       </c>
-      <c r="G2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.04</v>
-      </c>
       <c r="N2" t="n">
-        <v>1.28</v>
+        <v>4.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>1.21</v>
+        <v>2.72</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>2.84</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -1873,88 +1873,88 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.05</v>
+        <v>5.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>1.69</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="O6" t="n">
         <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
         <v>1.23</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>1.23</v>
+        <v>2.82</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC6" t="n">
         <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF6" t="n">
         <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AH6" t="n">
         <v>1000</v>
@@ -1963,130 +1963,130 @@
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>1.55</v>
       </c>
       <c r="J8" t="n">
         <v>4.5</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.18</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G9" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="H9" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="I9" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>2.12</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.79</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="I11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="J11" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q11" t="n">
         <v>1.54</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>1.91</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.05</v>
+        <v>1.81</v>
       </c>
       <c r="G14" t="n">
-        <v>2.56</v>
+        <v>1.97</v>
       </c>
       <c r="H14" t="n">
-        <v>1.72</v>
+        <v>4.4</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
-        <v>1.71</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J15" t="n">
-        <v>1.02</v>
+        <v>3.15</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>1.7</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
         <v>1.07</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>1.94</v>
       </c>
       <c r="H19" t="n">
-        <v>1.07</v>
+        <v>4.9</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="J19" t="n">
         <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>
@@ -5429,19 +5429,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.41</v>
+        <v>2.54</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="H20" t="n">
-        <v>1.41</v>
+        <v>2.9</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="K20" t="n">
         <v>3.5</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 03:58:50</t>
+          <t>2026-07-18 06:20:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="H2" t="n">
         <v>2.56</v>
       </c>
       <c r="I2" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="J2" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>4.2</v>
@@ -887,13 +887,13 @@
         <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q2" t="n">
         <v>1.69</v>
       </c>
       <c r="R2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
         <v>2.72</v>
@@ -902,13 +902,13 @@
         <v>1.59</v>
       </c>
       <c r="U2" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.52</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.48</v>
       </c>
       <c r="X2" t="n">
         <v>24</v>
@@ -947,19 +947,19 @@
         <v>42</v>
       </c>
       <c r="AJ2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK2" t="n">
         <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO2" t="n">
         <v>22</v>
@@ -974,7 +974,7 @@
         <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AT2" t="n">
         <v>10</v>
@@ -998,19 +998,19 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BE2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF2" t="n">
         <v>14</v>
@@ -1022,7 +1022,7 @@
         <v>4.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.199999999999999</v>
@@ -1046,10 +1046,10 @@
         <v>20</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS2" t="n">
         <v>7.2</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>5.5</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H6" t="n">
         <v>1.58</v>
@@ -1891,34 +1891,34 @@
         <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.23</v>
+        <v>1.72</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="U6" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
         <v>2.46</v>
@@ -1927,7 +1927,7 @@
         <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y6" t="n">
         <v>11</v>
@@ -1942,7 +1942,7 @@
         <v>26</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD6" t="n">
         <v>10.5</v>
@@ -1951,16 +1951,16 @@
         <v>19</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG6" t="n">
         <v>27</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ6" t="n">
         <v>180</v>
@@ -1972,13 +1972,13 @@
         <v>85</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN6" t="n">
         <v>100</v>
       </c>
       <c r="AO6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP6" t="n">
         <v>16.5</v>
@@ -2005,7 +2005,7 @@
         <v>13.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.48</v>
+        <v>5</v>
       </c>
       <c r="AY6" t="n">
         <v>19</v>
@@ -2014,22 +2014,22 @@
         <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.48</v>
+        <v>4.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.44</v>
+        <v>5.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.48</v>
+        <v>5.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.42</v>
+        <v>5.1</v>
       </c>
       <c r="BG6" t="n">
         <v>6.4</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>7.6</v>
       </c>
       <c r="G8" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H8" t="n">
         <v>1.46</v>
@@ -2396,7 +2396,7 @@
         <v>4.5</v>
       </c>
       <c r="K8" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="H9" t="n">
         <v>2.52</v>
       </c>
       <c r="I9" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
         <v>3.95</v>
@@ -2668,7 +2668,7 @@
         <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>2.12</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I10" t="n">
         <v>4.5</v>
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
         <v>1.76</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I11" t="n">
         <v>1.45</v>
@@ -3158,7 +3158,7 @@
         <v>5.3</v>
       </c>
       <c r="K11" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G13" t="n">
         <v>1.91</v>
@@ -3663,7 +3663,7 @@
         <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
         <v>4.3</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -4162,19 +4162,19 @@
         <v>2.22</v>
       </c>
       <c r="G15" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="H15" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J15" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>3.4</v>
       </c>
       <c r="J20" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
         <v>3.5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 06:20:25</t>
+          <t>2026-07-18 08:41:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -860,16 +860,16 @@
         <v>2.62</v>
       </c>
       <c r="G2" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="H2" t="n">
         <v>2.56</v>
       </c>
       <c r="I2" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
         <v>4.2</v>
@@ -887,13 +887,13 @@
         <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q2" t="n">
         <v>1.69</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S2" t="n">
         <v>2.72</v>
@@ -908,7 +908,7 @@
         <v>1.54</v>
       </c>
       <c r="W2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X2" t="n">
         <v>24</v>
@@ -953,7 +953,7 @@
         <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
         <v>80</v>
@@ -974,10 +974,10 @@
         <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU2" t="n">
         <v>7.6</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>2.16</v>
       </c>
       <c r="G4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>4.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="G6" t="n">
         <v>6.8</v>
@@ -1882,37 +1882,37 @@
         <v>1.58</v>
       </c>
       <c r="I6" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="J6" t="n">
         <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T6" t="n">
         <v>1.81</v>
@@ -1921,7 +1921,7 @@
         <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="W6" t="n">
         <v>1.17</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="G8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="I8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="J8" t="n">
         <v>4.5</v>
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
         <v>1.87</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G9" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="H9" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I9" t="n">
         <v>2.64</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
         <v>3.95</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G10" t="n">
         <v>2.12</v>
@@ -2904,7 +2904,7 @@
         <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>
@@ -3146,13 +3146,13 @@
         <v>7.6</v>
       </c>
       <c r="G11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="I11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="J11" t="n">
         <v>5.3</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>1.75</v>
       </c>
       <c r="G13" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H13" t="n">
         <v>4.6</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>1.81</v>
       </c>
       <c r="G14" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>4.4</v>
@@ -3917,7 +3917,7 @@
         <v>5.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
         <v>4.1</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J16" t="n">
         <v>4.2</v>
       </c>
       <c r="K16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
         <v>1.07</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="Q20" t="n">
         <v>2.4</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 08:41:26</t>
+          <t>2026-07-18 11:02:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -926,7 +926,7 @@
         <v>17</v>
       </c>
       <c r="AC2" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
         <v>15</v>
@@ -974,7 +974,7 @@
         <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -998,19 +998,19 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF2" t="n">
         <v>14</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>2.16</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
         <v>4.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R6" t="n">
         <v>1.45</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H8" t="n">
         <v>1.48</v>
       </c>
       <c r="I8" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="J8" t="n">
         <v>4.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="H9" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="I9" t="n">
         <v>2.64</v>
@@ -2650,7 +2650,7 @@
         <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q9" t="n">
         <v>1.69</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -3152,13 +3152,13 @@
         <v>1.42</v>
       </c>
       <c r="I11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="J11" t="n">
         <v>5.3</v>
       </c>
       <c r="K11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G15" t="n">
         <v>2.44</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J15" t="n">
         <v>3.4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="G16" t="n">
         <v>1.83</v>
       </c>
       <c r="H16" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="I16" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="K16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G19" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="H19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I19" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J19" t="n">
         <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>3.4</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K20" t="n">
         <v>3.5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 11:02:06</t>
+          <t>2026-07-18 11:58:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -875,7 +875,7 @@
         <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -1111,220 +1111,220 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -1371,28 +1371,28 @@
         <v>2.48</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="I4" t="n">
         <v>4.5</v>
       </c>
       <c r="J4" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
         <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P4" t="n">
         <v>1.71</v>
@@ -1401,194 +1401,194 @@
         <v>2.08</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -1637,202 +1637,202 @@
         <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>4.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -2035,31 +2035,31 @@
         <v>6.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BO6" t="n">
         <v>5</v>
       </c>
       <c r="BP6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BQ6" t="n">
         <v>8.4</v>
@@ -2068,7 +2068,7 @@
         <v>55</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT6" t="n">
         <v>4.5</v>
@@ -2080,13 +2080,13 @@
         <v>11</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BX6" t="n">
         <v>25</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -2145,212 +2145,212 @@
         <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -2399,16 +2399,16 @@
         <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
         <v>1.96</v>
@@ -2417,194 +2417,194 @@
         <v>1.87</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="G9" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="H9" t="n">
         <v>2.5</v>
       </c>
       <c r="I9" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="J9" t="n">
         <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="G10" t="n">
         <v>2.12</v>
       </c>
       <c r="H10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J10" t="n">
         <v>3.55</v>
@@ -2907,212 +2907,212 @@
         <v>3.95</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -3149,10 +3149,10 @@
         <v>8.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="J11" t="n">
         <v>5.3</v>
@@ -3161,16 +3161,16 @@
         <v>5.7</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P11" t="n">
         <v>2.8</v>
@@ -3179,194 +3179,194 @@
         <v>1.54</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>1.75</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H13" t="n">
         <v>4.6</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>1.81</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H14" t="n">
         <v>4.4</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G15" t="n">
         <v>2.44</v>
       </c>
       <c r="H15" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J15" t="n">
         <v>3.4</v>
@@ -4189,7 +4189,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q15" t="n">
         <v>2.02</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -4416,16 +4416,16 @@
         <v>1.74</v>
       </c>
       <c r="G16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H16" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I16" t="n">
         <v>4.5</v>
       </c>
       <c r="J16" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K16" t="n">
         <v>5.2</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.07</v>
+        <v>3.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G19" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H19" t="n">
         <v>4.8</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G20" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="H20" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J20" t="n">
         <v>3.05</v>
       </c>
       <c r="K20" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 11:58:18</t>
+          <t>2026-07-18 14:16:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -875,7 +875,7 @@
         <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1153,10 +1153,10 @@
         <v>1.16</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
         <v>1.02</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -1371,25 +1371,25 @@
         <v>2.48</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="O4" t="n">
         <v>1.38</v>
@@ -1401,130 +1401,130 @@
         <v>2.08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="V4" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
         <v>1.68</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK4" t="n">
         <v>34</v>
       </c>
-      <c r="AA4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>36</v>
-      </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.67</v>
+        <v>3.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.67</v>
+        <v>3.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.59</v>
+        <v>3.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.64</v>
+        <v>4</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.45</v>
+        <v>3.05</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.42</v>
+        <v>2.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.53</v>
+        <v>3.45</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.67</v>
+        <v>3.95</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.53</v>
+        <v>3.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.67</v>
+        <v>3.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.63</v>
+        <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.59</v>
+        <v>3.75</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.67</v>
+        <v>3.95</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.67</v>
+        <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.67</v>
+        <v>3.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.67</v>
+        <v>4</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="G6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H6" t="n">
         <v>1.58</v>
@@ -1924,7 +1924,7 @@
         <v>2.48</v>
       </c>
       <c r="W6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X6" t="n">
         <v>23</v>
@@ -1939,7 +1939,7 @@
         <v>18.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC6" t="n">
         <v>12</v>
@@ -1951,19 +1951,19 @@
         <v>19</v>
       </c>
       <c r="AF6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
         <v>38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AK6" t="n">
         <v>90</v>
@@ -1975,7 +1975,7 @@
         <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO6" t="n">
         <v>9.199999999999999</v>
@@ -2005,7 +2005,7 @@
         <v>13.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AY6" t="n">
         <v>19</v>
@@ -2014,52 +2014,52 @@
         <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BB6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD6" t="n">
         <v>5.3</v>
       </c>
-      <c r="BC6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BE6" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BG6" t="n">
         <v>6.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BJ6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO6" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BQ6" t="n">
         <v>8.4</v>
@@ -2068,25 +2068,25 @@
         <v>55</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT6" t="n">
         <v>4.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="BV6" t="n">
         <v>11</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BX6" t="n">
         <v>25</v>
       </c>
       <c r="BY6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,7 +2151,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O7" t="n">
         <v>1.35</v>
@@ -2175,10 +2175,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I8" t="n">
         <v>1.54</v>
@@ -2405,7 +2405,7 @@
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
         <v>1.3</v>
@@ -2459,7 +2459,7 @@
         <v>17.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AG8" t="n">
         <v>32</v>
@@ -2543,68 +2543,68 @@
         <v>7</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="BJ8" t="n">
         <v>14</v>
       </c>
       <c r="BK8" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="BM8" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BQ8" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BS8" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BU8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BV8" t="n">
         <v>11.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY8" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
         <v>22</v>
       </c>
       <c r="CA8" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
         <v>2.5</v>
       </c>
       <c r="I9" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J9" t="n">
         <v>3.7</v>
@@ -2659,10 +2659,10 @@
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P9" t="n">
         <v>2.32</v>
@@ -2671,130 +2671,130 @@
         <v>1.7</v>
       </c>
       <c r="R9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S9" t="n">
         <v>2.72</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z9" t="n">
         <v>19</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO9" t="n">
         <v>16.5</v>
       </c>
-      <c r="AC9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="AP9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG9" t="n">
+      <c r="AR9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT9" t="n">
         <v>14</v>
       </c>
-      <c r="AH9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK9" t="n">
+      <c r="AU9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD9" t="n">
         <v>30</v>
       </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>2.14</v>
-      </c>
       <c r="BE9" t="n">
-        <v>2.14</v>
+        <v>50</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.14</v>
+        <v>17</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.14</v>
+        <v>14.5</v>
       </c>
       <c r="BH9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G10" t="n">
         <v>2.12</v>
@@ -2904,37 +2904,37 @@
         <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="O10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
         <v>1.91</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
         <v>1.3</v>
@@ -2943,176 +2943,176 @@
         <v>1.89</v>
       </c>
       <c r="X10" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF10" t="n">
         <v>13.5</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AG10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP10" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AQ10" t="n">
-        <v>2.08</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.08</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.81</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.79</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.93</v>
+        <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.02</v>
+        <v>7</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.84</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.94</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.04</v>
+        <v>7</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.98</v>
+        <v>20</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.95</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.08</v>
+        <v>7.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.08</v>
+        <v>10.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.08</v>
+        <v>7</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK10" t="n">
         <v>1.01</v>
       </c>
       <c r="BL10" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM10" t="n">
         <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ10" t="n">
         <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS10" t="n">
         <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW10" t="n">
         <v>1.01</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY10" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA10" t="n">
         <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -3158,16 +3158,16 @@
         <v>5.3</v>
       </c>
       <c r="K11" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="M11" t="n">
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O11" t="n">
         <v>1.17</v>
@@ -3176,16 +3176,16 @@
         <v>2.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="S11" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="T11" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="U11" t="n">
         <v>2.22</v>
@@ -3197,52 +3197,52 @@
         <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN11" t="n">
         <v>85</v>
@@ -3251,122 +3251,122 @@
         <v>4.9</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.27</v>
+        <v>4.7</v>
       </c>
       <c r="AQ11" t="n">
         <v>10.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AS11" t="n">
         <v>11</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.27</v>
+        <v>4.8</v>
       </c>
       <c r="AU11" t="n">
         <v>11</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW11" t="n">
         <v>12.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.27</v>
+        <v>5.1</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.27</v>
+        <v>21</v>
       </c>
       <c r="AZ11" t="n">
         <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.27</v>
+        <v>4.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.27</v>
+        <v>5.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.27</v>
+        <v>5.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.27</v>
+        <v>5.1</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.27</v>
+        <v>5.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.25</v>
+        <v>5.1</v>
       </c>
       <c r="BG11" t="n">
         <v>4.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK11" t="n">
         <v>1.01</v>
       </c>
       <c r="BL11" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM11" t="n">
         <v>1.01</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BO11" t="n">
         <v>1.01</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ11" t="n">
         <v>1.01</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS11" t="n">
         <v>1.01</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BW11" t="n">
         <v>1.01</v>
       </c>
       <c r="BX11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY11" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="CA11" t="n">
         <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -3409,22 +3409,22 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K12" t="n">
         <v>3.3</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P12" t="n">
         <v>1.24</v>
@@ -3433,194 +3433,194 @@
         <v>1.01</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -3651,34 +3651,34 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="G13" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K13" t="n">
         <v>4.3</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
@@ -3687,194 +3687,194 @@
         <v>1.81</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -3917,22 +3917,22 @@
         <v>5.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
         <v>1.88</v>
@@ -3941,194 +3941,194 @@
         <v>1.92</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -4174,19 +4174,19 @@
         <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P15" t="n">
         <v>1.81</v>
@@ -4195,194 +4195,194 @@
         <v>2.02</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
         <v>1.84</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>4.5</v>
@@ -4428,19 +4428,19 @@
         <v>4.4</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="P16" t="n">
         <v>3.1</v>
@@ -4449,194 +4449,194 @@
         <v>1.39</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BM16" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BY16" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -4685,212 +4685,212 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -4939,212 +4939,212 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -5178,10 +5178,10 @@
         <v>1.8</v>
       </c>
       <c r="G19" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
         <v>5.7</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>
@@ -5432,13 +5432,13 @@
         <v>2.56</v>
       </c>
       <c r="G20" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H20" t="n">
         <v>2.92</v>
       </c>
       <c r="I20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>3.05</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 14:16:24</t>
+          <t>2026-07-18 16:34:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.15</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Q3" t="n">
         <v>1.15</v>
@@ -1159,10 +1159,10 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1276,55 +1276,55 @@
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -1530,65 +1530,65 @@
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,28 +1643,28 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
         <v>1.29</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.28</v>
+        <v>2.58</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1784,55 +1784,55 @@
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G6" t="n">
         <v>6.6</v>
@@ -1891,7 +1891,7 @@
         <v>4.9</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1930,19 +1930,19 @@
         <v>23</v>
       </c>
       <c r="Y6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z6" t="n">
         <v>11</v>
       </c>
-      <c r="Z6" t="n">
-        <v>12</v>
-      </c>
       <c r="AA6" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AB6" t="n">
         <v>25</v>
       </c>
       <c r="AC6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD6" t="n">
         <v>10.5</v>
@@ -1960,16 +1960,16 @@
         <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ6" t="n">
         <v>170</v>
       </c>
       <c r="AK6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM6" t="n">
         <v>120</v>
@@ -1978,7 +1978,7 @@
         <v>95</v>
       </c>
       <c r="AO6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AP6" t="n">
         <v>16.5</v>
@@ -2005,7 +2005,7 @@
         <v>13.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY6" t="n">
         <v>19</v>
@@ -2014,22 +2014,22 @@
         <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG6" t="n">
         <v>6.4</v>
@@ -2038,7 +2038,7 @@
         <v>4</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
@@ -2056,7 +2056,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BO6" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="BP6" t="n">
         <v>50</v>
@@ -2074,7 +2074,7 @@
         <v>4.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="BV6" t="n">
         <v>11</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2160,7 +2160,7 @@
         <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
@@ -2169,16 +2169,16 @@
         <v>1.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2292,65 +2292,65 @@
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -2417,10 +2417,10 @@
         <v>1.87</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
         <v>2.06</v>
@@ -2438,10 +2438,10 @@
         <v>19</v>
       </c>
       <c r="Y8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>14</v>
@@ -2513,31 +2513,31 @@
         <v>12</v>
       </c>
       <c r="AX8" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AZ8" t="n">
         <v>21</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF8" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG8" t="n">
         <v>7</v>
@@ -2552,31 +2552,31 @@
         <v>14</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BL8" t="n">
         <v>200</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BN8" t="n">
         <v>13.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP8" t="n">
         <v>90</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BR8" t="n">
         <v>90</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BT8" t="n">
         <v>4.6</v>
@@ -2588,23 +2588,23 @@
         <v>11.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BX8" t="n">
         <v>32</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BZ8" t="n">
         <v>22</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H9" t="n">
         <v>2.5</v>
@@ -2686,7 +2686,7 @@
         <v>1.63</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X9" t="n">
         <v>22</v>
@@ -2740,7 +2740,7 @@
         <v>23</v>
       </c>
       <c r="AO9" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AP9" t="n">
         <v>17.5</v>
@@ -2749,7 +2749,7 @@
         <v>12.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS9" t="n">
         <v>32</v>
@@ -2800,65 +2800,65 @@
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
         <v>3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
@@ -2943,7 +2943,7 @@
         <v>1.89</v>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y10" t="n">
         <v>16</v>
@@ -2955,7 +2955,7 @@
         <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>8.800000000000001</v>
@@ -2979,7 +2979,7 @@
         <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK10" t="n">
         <v>23</v>
@@ -2991,7 +2991,7 @@
         <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AO10" t="n">
         <v>65</v>
@@ -3006,7 +3006,7 @@
         <v>23</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -3018,7 +3018,7 @@
         <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
@@ -3030,7 +3030,7 @@
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB10" t="n">
         <v>20</v>
@@ -3042,77 +3042,77 @@
         <v>27</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF10" t="n">
         <v>10.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="BH10" t="n">
         <v>4.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="BJ10" t="n">
         <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL10" t="n">
         <v>150</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BN10" t="n">
         <v>5.7</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP10" t="n">
         <v>17.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BR10" t="n">
         <v>34</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BT10" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV10" t="n">
         <v>40</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BX10" t="n">
         <v>55</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BZ10" t="n">
         <v>29</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -3146,13 +3146,13 @@
         <v>7.6</v>
       </c>
       <c r="G11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="H11" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="I11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="J11" t="n">
         <v>5.3</v>
@@ -3173,7 +3173,7 @@
         <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q11" t="n">
         <v>1.5</v>
@@ -3182,7 +3182,7 @@
         <v>1.73</v>
       </c>
       <c r="S11" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="T11" t="n">
         <v>1.76</v>
@@ -3191,7 +3191,7 @@
         <v>2.22</v>
       </c>
       <c r="V11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="W11" t="n">
         <v>1.13</v>
@@ -3206,7 +3206,7 @@
         <v>13.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB11" t="n">
         <v>44</v>
@@ -3251,7 +3251,7 @@
         <v>4.9</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ11" t="n">
         <v>10.5</v>
@@ -3263,7 +3263,7 @@
         <v>11</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU11" t="n">
         <v>11</v>
@@ -3275,7 +3275,7 @@
         <v>12.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY11" t="n">
         <v>21</v>
@@ -3284,16 +3284,16 @@
         <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.7</v>
+        <v>19.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BC11" t="n">
         <v>5.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE11" t="n">
         <v>5.2</v>
@@ -3314,59 +3314,59 @@
         <v>12</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BL11" t="n">
         <v>120</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BN11" t="n">
         <v>13.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP11" t="n">
         <v>65</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BR11" t="n">
         <v>60</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BT11" t="n">
         <v>5.1</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BV11" t="n">
         <v>10.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BX11" t="n">
         <v>23</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BZ11" t="n">
         <v>13</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="K12" t="n">
         <v>3.3</v>
@@ -3418,37 +3418,37 @@
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="R12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S12" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3562,65 +3562,65 @@
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -3657,19 +3657,19 @@
         <v>1.9</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I13" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J13" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
@@ -3693,7 +3693,7 @@
         <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="U13" t="n">
         <v>2.06</v>
@@ -3705,16 +3705,16 @@
         <v>2.1</v>
       </c>
       <c r="X13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y13" t="n">
         <v>21</v>
       </c>
       <c r="Z13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA13" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB13" t="n">
         <v>11</v>
@@ -3723,10 +3723,10 @@
         <v>10.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF13" t="n">
         <v>13.5</v>
@@ -3735,10 +3735,10 @@
         <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ13" t="n">
         <v>21</v>
@@ -3750,13 +3750,13 @@
         <v>40</v>
       </c>
       <c r="AM13" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN13" t="n">
         <v>13</v>
       </c>
       <c r="AO13" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP13" t="n">
         <v>14</v>
@@ -3765,10 +3765,10 @@
         <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT13" t="n">
         <v>8</v>
@@ -3780,7 +3780,7 @@
         <v>16.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX13" t="n">
         <v>9.6</v>
@@ -3792,7 +3792,7 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB13" t="n">
         <v>16</v>
@@ -3801,80 +3801,80 @@
         <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF13" t="n">
         <v>8.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>1.88</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
         <v>1.31</v>
@@ -3941,16 +3941,16 @@
         <v>1.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
         <v>1.24</v>
@@ -3959,176 +3959,176 @@
         <v>2</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y14" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH14" t="n">
         <v>20</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AI14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL14" t="n">
         <v>40</v>
       </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>42</v>
-      </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.92</v>
+        <v>12</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.75</v>
+        <v>13.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.83</v>
+        <v>6</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.92</v>
+        <v>6.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.62</v>
+        <v>7.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.59</v>
+        <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.76</v>
+        <v>16</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.92</v>
+        <v>6.4</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.92</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.64</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.76</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.92</v>
+        <v>6.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.92</v>
+        <v>18</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.92</v>
+        <v>17</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.84</v>
+        <v>6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.92</v>
+        <v>6.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.92</v>
+        <v>10</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.92</v>
+        <v>6.4</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP14" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
         <v>3.65</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="U15" t="n">
         <v>1.92</v>
@@ -4279,10 +4279,10 @@
         <v>6</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AV15" t="n">
         <v>11.5</v>
@@ -4294,16 +4294,16 @@
         <v>11</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA15" t="n">
         <v>5.9</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.5</v>
+        <v>23</v>
       </c>
       <c r="BC15" t="n">
         <v>20</v>
@@ -4330,13 +4330,13 @@
         <v>11.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
         <v>150</v>
       </c>
       <c r="BM15" t="n">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
         <v>5.8</v>
@@ -4348,13 +4348,13 @@
         <v>20</v>
       </c>
       <c r="BQ15" t="n">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
         <v>38</v>
       </c>
       <c r="BS15" t="n">
-        <v>24</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
         <v>7.6</v>
@@ -4366,23 +4366,23 @@
         <v>34</v>
       </c>
       <c r="BW15" t="n">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
         <v>48</v>
       </c>
       <c r="BY15" t="n">
-        <v>30</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
         <v>34</v>
       </c>
       <c r="CA15" t="n">
-        <v>22</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
         <v>1.84</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I16" t="n">
         <v>4.5</v>
@@ -4437,10 +4437,10 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>7.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="P16" t="n">
         <v>3.1</v>
@@ -4449,82 +4449,82 @@
         <v>1.39</v>
       </c>
       <c r="R16" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="S16" t="n">
         <v>1.94</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="V16" t="n">
         <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP16" t="n">
         <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AR16" t="n">
         <v>1.01</v>
@@ -4533,46 +4533,46 @@
         <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW16" t="n">
         <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA16" t="n">
         <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BE16" t="n">
         <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH16" t="n">
         <v>6.4</v>
@@ -4584,13 +4584,13 @@
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
         <v>70</v>
       </c>
       <c r="BM16" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
         <v>6.4</v>
@@ -4602,41 +4602,41 @@
         <v>13.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR16" t="n">
         <v>21</v>
       </c>
       <c r="BS16" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
         <v>10.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
         <v>34</v>
       </c>
       <c r="BW16" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
         <v>34</v>
       </c>
       <c r="BY16" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
         <v>12.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -4688,10 +4688,10 @@
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O17" t="n">
         <v>1.11</v>
@@ -4703,7 +4703,7 @@
         <v>1.11</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
         <v>1.11</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -4942,10 +4942,10 @@
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O18" t="n">
         <v>1.08</v>
@@ -4957,7 +4957,7 @@
         <v>1.08</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
         <v>1.08</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G19" t="n">
         <v>1.97</v>
@@ -5184,7 +5184,7 @@
         <v>4.7</v>
       </c>
       <c r="I19" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J19" t="n">
         <v>3.5</v>
@@ -5193,16 +5193,16 @@
         <v>3.85</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P19" t="n">
         <v>1.73</v>
@@ -5211,194 +5211,194 @@
         <v>2.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL19" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="BM19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR19" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BS19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX19" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="BY19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 16:34:23</t>
+          <t>2026-07-18 18:49:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -872,10 +872,10 @@
         <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -917,7 +917,7 @@
         <v>16.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
         <v>46</v>
@@ -926,7 +926,7 @@
         <v>17</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AD2" t="n">
         <v>15</v>
@@ -941,10 +941,10 @@
         <v>15.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ2" t="n">
         <v>48</v>
@@ -953,7 +953,7 @@
         <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
         <v>80</v>
@@ -974,7 +974,7 @@
         <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -1001,7 +1001,7 @@
         <v>4.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
@@ -1010,7 +1010,7 @@
         <v>4.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF2" t="n">
         <v>14</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1159,10 +1159,10 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
@@ -1527,68 +1527,68 @@
         <v>4</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="BJ4" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BN4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BT4" t="n">
         <v>7</v>
       </c>
-      <c r="BO4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>26</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>50</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BV4" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BX4" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,16 +1643,16 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O5" t="n">
         <v>1.29</v>
       </c>
       <c r="P5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
         <v>10.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AF6" t="n">
         <v>55</v>
@@ -1966,16 +1966,16 @@
         <v>170</v>
       </c>
       <c r="AK6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AL6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM6" t="n">
         <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AO6" t="n">
         <v>8.6</v>
@@ -2005,7 +2005,7 @@
         <v>13.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY6" t="n">
         <v>19</v>
@@ -2014,22 +2014,22 @@
         <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE6" t="n">
         <v>7.2</v>
       </c>
-      <c r="BC6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE6" t="n">
+      <c r="BF6" t="n">
         <v>7</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6.8</v>
       </c>
       <c r="BG6" t="n">
         <v>6.4</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -2166,7 +2166,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2175,10 +2175,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
         <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
@@ -2522,7 +2522,7 @@
         <v>21</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BB8" t="n">
         <v>9</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="G9" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="I9" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J9" t="n">
         <v>3.7</v>
@@ -2653,7 +2653,7 @@
         <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
@@ -2665,7 +2665,7 @@
         <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
         <v>1.7</v>
@@ -2683,10 +2683,10 @@
         <v>2.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="X9" t="n">
         <v>22</v>
@@ -2695,10 +2695,10 @@
         <v>14</v>
       </c>
       <c r="Z9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB9" t="n">
         <v>16</v>
@@ -2710,10 +2710,10 @@
         <v>12</v>
       </c>
       <c r="AE9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG9" t="n">
         <v>13</v>
@@ -2725,10 +2725,10 @@
         <v>36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL9" t="n">
         <v>40</v>
@@ -2740,7 +2740,7 @@
         <v>23</v>
       </c>
       <c r="AO9" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AP9" t="n">
         <v>17.5</v>
@@ -2752,7 +2752,7 @@
         <v>16.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AT9" t="n">
         <v>14</v>
@@ -2791,74 +2791,74 @@
         <v>50</v>
       </c>
       <c r="BF9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BG9" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BJ9" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL9" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BN9" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BR9" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="BV9" t="n">
-        <v>26</v>
+        <v>17.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BZ9" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>2.12</v>
@@ -2919,10 +2919,10 @@
         <v>1.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="R10" t="n">
         <v>1.35</v>
@@ -2991,7 +2991,7 @@
         <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO10" t="n">
         <v>65</v>
@@ -3006,7 +3006,7 @@
         <v>23</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -3018,7 +3018,7 @@
         <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
@@ -3042,10 +3042,10 @@
         <v>27</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG10" t="n">
         <v>36</v>
@@ -3054,7 +3054,7 @@
         <v>4.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="BJ10" t="n">
         <v>11.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>8.6</v>
       </c>
       <c r="H11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I11" t="n">
         <v>1.45</v>
@@ -3167,13 +3167,13 @@
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O11" t="n">
         <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="Q11" t="n">
         <v>1.5</v>
@@ -3182,7 +3182,7 @@
         <v>1.73</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T11" t="n">
         <v>1.76</v>
@@ -3200,7 +3200,7 @@
         <v>38</v>
       </c>
       <c r="Y11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
         <v>13.5</v>
@@ -3218,7 +3218,7 @@
         <v>11</v>
       </c>
       <c r="AE11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AF11" t="n">
         <v>90</v>
@@ -3227,10 +3227,10 @@
         <v>36</v>
       </c>
       <c r="AH11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AJ11" t="n">
         <v>250</v>
@@ -3251,7 +3251,7 @@
         <v>4.9</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>10.5</v>
@@ -3263,7 +3263,7 @@
         <v>11</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU11" t="n">
         <v>11</v>
@@ -3275,7 +3275,7 @@
         <v>12.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AY11" t="n">
         <v>21</v>
@@ -3287,19 +3287,19 @@
         <v>19.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BG11" t="n">
         <v>4.4</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -3397,46 +3397,46 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R12" t="n">
         <v>1.12</v>
       </c>
-      <c r="N12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.13</v>
-      </c>
       <c r="S12" t="n">
-        <v>3.6</v>
+        <v>1.05</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
@@ -3681,16 +3681,16 @@
         <v>1.28</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R13" t="n">
         <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T13" t="n">
         <v>1.79</v>
@@ -3813,43 +3813,43 @@
         <v>5.1</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="BJ13" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL13" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BN13" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="BP13" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR13" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BU13" t="n">
         <v>5.4</v>
@@ -3858,23 +3858,23 @@
         <v>55</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BZ13" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
         <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
@@ -4067,68 +4067,68 @@
         <v>6.4</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BJ14" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BL14" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BN14" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="BP14" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BR14" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BT14" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY14" t="n">
         <v>5.3</v>
       </c>
-      <c r="BV14" t="n">
-        <v>55</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BZ14" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -4159,58 +4159,58 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J15" t="n">
         <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
         <v>1.36</v>
       </c>
       <c r="P15" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
         <v>2.02</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T15" t="n">
         <v>1.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="V15" t="n">
         <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X15" t="n">
         <v>15</v>
@@ -4252,16 +4252,16 @@
         <v>36</v>
       </c>
       <c r="AK15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM15" t="n">
         <v>120</v>
       </c>
       <c r="AN15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO15" t="n">
         <v>55</v>
@@ -4276,13 +4276,13 @@
         <v>18.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV15" t="n">
         <v>11.5</v>
@@ -4294,16 +4294,16 @@
         <v>11</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB15" t="n">
-        <v>23</v>
+        <v>5.7</v>
       </c>
       <c r="BC15" t="n">
         <v>20</v>
@@ -4312,77 +4312,77 @@
         <v>32</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF15" t="n">
         <v>16</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BH15" t="n">
         <v>3.65</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BJ15" t="n">
         <v>11.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BL15" t="n">
         <v>150</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BN15" t="n">
         <v>5.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BP15" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BR15" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BT15" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV15" t="n">
         <v>34</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BX15" t="n">
         <v>48</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BZ15" t="n">
         <v>34</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
         <v>4.4</v>
       </c>
       <c r="K16" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L16" t="n">
         <v>1.18</v>
@@ -4464,7 +4464,7 @@
         <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X16" t="n">
         <v>40</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O18" t="n">
         <v>1.08</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -5193,19 +5193,19 @@
         <v>3.85</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O19" t="n">
         <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q19" t="n">
         <v>2.1</v>
@@ -5244,7 +5244,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD19" t="n">
         <v>23</v>
@@ -5265,7 +5265,7 @@
         <v>95</v>
       </c>
       <c r="AJ19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK19" t="n">
         <v>26</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
         <v>2.92</v>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J20" t="n">
         <v>3.05</v>
@@ -5447,16 +5447,16 @@
         <v>3.45</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P20" t="n">
         <v>1.58</v>
@@ -5465,194 +5465,194 @@
         <v>2.4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 18:49:17</t>
+          <t>2026-07-18 21:03:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -884,25 +884,25 @@
         <v>4.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
         <v>2.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R2" t="n">
         <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V2" t="n">
         <v>1.54</v>
@@ -914,16 +914,16 @@
         <v>24</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
         <v>46</v>
       </c>
       <c r="AB2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC2" t="n">
         <v>11</v>
@@ -941,10 +941,10 @@
         <v>15.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AI2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AJ2" t="n">
         <v>48</v>
@@ -953,7 +953,7 @@
         <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
         <v>80</v>
@@ -968,16 +968,16 @@
         <v>16.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR2" t="n">
         <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="AT2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AU2" t="n">
         <v>7.6</v>
@@ -986,37 +986,37 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>19</v>
+        <v>3.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BC2" t="n">
-        <v>20</v>
+        <v>3.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH2" t="n">
         <v>4.1</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>
@@ -1111,217 +1111,217 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.16</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="H3" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>1.32</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.22</v>
+        <v>5.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>1.22</v>
+        <v>2.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.63</v>
       </c>
       <c r="S3" t="n">
-        <v>1.16</v>
+        <v>2.34</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.06</v>
+        <v>4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>620</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI3" t="n">
         <v>1.04</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK3" t="n">
         <v>1.04</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM3" t="n">
         <v>1.04</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BO3" t="n">
         <v>1.04</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BQ3" t="n">
         <v>1.04</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BS3" t="n">
         <v>1.04</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BU3" t="n">
         <v>1.04</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BW3" t="n">
         <v>1.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY3" t="n">
         <v>1.04</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
         <v>2.16</v>
       </c>
       <c r="G4" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H4" t="n">
         <v>3.3</v>
@@ -1380,7 +1380,7 @@
         <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.44</v>
@@ -1404,7 +1404,7 @@
         <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T4" t="n">
         <v>1.83</v>
@@ -1536,59 +1536,59 @@
         <v>12</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="BL4" t="n">
         <v>180</v>
       </c>
       <c r="BM4" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BN4" t="n">
         <v>5.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="BP4" t="n">
         <v>22</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BR4" t="n">
         <v>42</v>
       </c>
       <c r="BS4" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BT4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BV4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BX4" t="n">
         <v>55</v>
       </c>
       <c r="BY4" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>40</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
         <v>1.29</v>
       </c>
       <c r="P5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>2.58</v>
+        <v>1.28</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="G6" t="n">
         <v>6.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="I6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="J6" t="n">
         <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1909,19 +1909,19 @@
         <v>1.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V6" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="W6" t="n">
         <v>1.18</v>
@@ -1930,13 +1930,13 @@
         <v>23</v>
       </c>
       <c r="Y6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z6" t="n">
         <v>11</v>
       </c>
       <c r="AA6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AB6" t="n">
         <v>25</v>
@@ -1966,10 +1966,10 @@
         <v>170</v>
       </c>
       <c r="AK6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL6" t="n">
         <v>80</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>75</v>
       </c>
       <c r="AM6" t="n">
         <v>120</v>
@@ -1987,13 +1987,13 @@
         <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AU6" t="n">
         <v>8.800000000000001</v>
@@ -2002,34 +2002,34 @@
         <v>8.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE6" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE6" t="n">
+      <c r="BF6" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7</v>
       </c>
       <c r="BG6" t="n">
         <v>6.4</v>
@@ -2038,7 +2038,7 @@
         <v>4</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="O7" t="n">
         <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q7" t="n">
         <v>1.34</v>
@@ -2166,7 +2166,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="G8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="I8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="J8" t="n">
         <v>4.5</v>
@@ -2399,7 +2399,7 @@
         <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
@@ -2408,40 +2408,40 @@
         <v>3.75</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
         <v>1.87</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U8" t="n">
         <v>1.81</v>
       </c>
       <c r="V8" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="W8" t="n">
         <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA8" t="n">
         <v>14</v>
@@ -2498,7 +2498,7 @@
         <v>7.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
         <v>20</v>
@@ -2510,7 +2510,7 @@
         <v>8.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX8" t="n">
         <v>8.199999999999999</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G9" t="n">
         <v>3.05</v>
@@ -2665,7 +2665,7 @@
         <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
         <v>1.7</v>
@@ -2689,19 +2689,19 @@
         <v>1.48</v>
       </c>
       <c r="X9" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z9" t="n">
         <v>18.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AB9" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AC9" t="n">
         <v>8.800000000000001</v>
@@ -2722,7 +2722,7 @@
         <v>15</v>
       </c>
       <c r="AI9" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ9" t="n">
         <v>46</v>
@@ -2731,16 +2731,16 @@
         <v>30</v>
       </c>
       <c r="AL9" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM9" t="n">
         <v>65</v>
       </c>
       <c r="AN9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO9" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP9" t="n">
         <v>17.5</v>
@@ -2749,7 +2749,7 @@
         <v>12.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS9" t="n">
         <v>30</v>
@@ -2767,7 +2767,7 @@
         <v>21</v>
       </c>
       <c r="AX9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY9" t="n">
         <v>12</v>
@@ -2779,10 +2779,10 @@
         <v>28</v>
       </c>
       <c r="BB9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BC9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD9" t="n">
         <v>30</v>
@@ -2803,19 +2803,19 @@
         <v>3.15</v>
       </c>
       <c r="BJ9" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.4</v>
+        <v>3.25</v>
       </c>
       <c r="BL9" t="n">
         <v>100</v>
       </c>
       <c r="BM9" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BO9" t="n">
         <v>5.5</v>
@@ -2824,41 +2824,41 @@
         <v>24</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.9</v>
+        <v>3.95</v>
       </c>
       <c r="BR9" t="n">
         <v>34</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BU9" t="n">
         <v>5.2</v>
       </c>
       <c r="BV9" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.4</v>
+        <v>3.85</v>
       </c>
       <c r="BX9" t="n">
         <v>32</v>
       </c>
       <c r="BY9" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="BZ9" t="n">
         <v>23</v>
       </c>
       <c r="CA9" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
         <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
         <v>1.38</v>
@@ -2919,10 +2919,10 @@
         <v>1.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R10" t="n">
         <v>1.35</v>
@@ -2934,7 +2934,7 @@
         <v>1.76</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V10" t="n">
         <v>1.3</v>
@@ -2943,7 +2943,7 @@
         <v>1.89</v>
       </c>
       <c r="X10" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y10" t="n">
         <v>16</v>
@@ -2955,7 +2955,7 @@
         <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC10" t="n">
         <v>8.800000000000001</v>
@@ -2994,7 +2994,7 @@
         <v>15</v>
       </c>
       <c r="AO10" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP10" t="n">
         <v>12.5</v>
@@ -3003,10 +3003,10 @@
         <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>23</v>
+        <v>6.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -3018,7 +3018,7 @@
         <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>36</v>
+        <v>7.4</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
@@ -3030,7 +3030,7 @@
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BB10" t="n">
         <v>20</v>
@@ -3039,13 +3039,13 @@
         <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>27</v>
+        <v>6.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BG10" t="n">
         <v>36</v>
@@ -3054,7 +3054,7 @@
         <v>4.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="BJ10" t="n">
         <v>11.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
         <v>2.24</v>
       </c>
       <c r="T11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U11" t="n">
         <v>2.22</v>
@@ -3197,13 +3197,13 @@
         <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="Y11" t="n">
         <v>13</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AA11" t="n">
         <v>16</v>
@@ -3215,7 +3215,7 @@
         <v>16</v>
       </c>
       <c r="AD11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE11" t="n">
         <v>15</v>
@@ -3224,7 +3224,7 @@
         <v>90</v>
       </c>
       <c r="AG11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AH11" t="n">
         <v>23</v>
@@ -3245,37 +3245,37 @@
         <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AO11" t="n">
         <v>4.9</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
         <v>9.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU11" t="n">
         <v>11</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW11" t="n">
         <v>12.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AY11" t="n">
         <v>21</v>
@@ -3284,22 +3284,22 @@
         <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>19.5</v>
+        <v>6</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BG11" t="n">
         <v>4.4</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3421,13 +3421,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O12" t="n">
         <v>1.01</v>
       </c>
       <c r="P12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Q12" t="n">
         <v>1.54</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>
@@ -3660,10 +3660,10 @@
         <v>4.6</v>
       </c>
       <c r="I13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K13" t="n">
         <v>4.2</v>
@@ -3675,7 +3675,7 @@
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
         <v>1.28</v>
@@ -3684,7 +3684,7 @@
         <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R13" t="n">
         <v>1.38</v>
@@ -3720,13 +3720,13 @@
         <v>11</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD13" t="n">
         <v>22</v>
       </c>
       <c r="AE13" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF13" t="n">
         <v>13.5</v>
@@ -3735,13 +3735,13 @@
         <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK13" t="n">
         <v>22</v>
@@ -3750,16 +3750,16 @@
         <v>40</v>
       </c>
       <c r="AM13" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN13" t="n">
         <v>13</v>
       </c>
       <c r="AO13" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
         <v>15</v>
@@ -3777,16 +3777,16 @@
         <v>7.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW13" t="n">
         <v>5.1</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ13" t="n">
         <v>16</v>
@@ -3795,19 +3795,19 @@
         <v>5.1</v>
       </c>
       <c r="BB13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC13" t="n">
         <v>16</v>
       </c>
-      <c r="BC13" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BD13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BE13" t="n">
         <v>5.3</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG13" t="n">
         <v>5.1</v>
@@ -3819,62 +3819,62 @@
         <v>2.96</v>
       </c>
       <c r="BJ13" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="BL13" t="n">
         <v>140</v>
       </c>
       <c r="BM13" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="BP13" t="n">
         <v>14</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BR13" t="n">
         <v>30</v>
       </c>
       <c r="BS13" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BT13" t="n">
         <v>9.6</v>
       </c>
       <c r="BU13" t="n">
-        <v>5.4</v>
+        <v>3.55</v>
       </c>
       <c r="BV13" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BX13" t="n">
         <v>55</v>
       </c>
       <c r="BY13" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BZ13" t="n">
         <v>24</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G14" t="n">
         <v>1.99</v>
@@ -3944,7 +3944,7 @@
         <v>1.34</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T14" t="n">
         <v>1.81</v>
@@ -3959,13 +3959,13 @@
         <v>2</v>
       </c>
       <c r="X14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Z14" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AA14" t="n">
         <v>130</v>
@@ -3974,10 +3974,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AE14" t="n">
         <v>75</v>
@@ -3986,10 +3986,10 @@
         <v>13.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AI14" t="n">
         <v>80</v>
@@ -4001,7 +4001,7 @@
         <v>24</v>
       </c>
       <c r="AL14" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM14" t="n">
         <v>130</v>
@@ -4019,10 +4019,10 @@
         <v>13.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="AT14" t="n">
         <v>7.4</v>
@@ -4034,7 +4034,7 @@
         <v>16</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="AX14" t="n">
         <v>9.800000000000001</v>
@@ -4046,7 +4046,7 @@
         <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
         <v>18</v>
@@ -4055,16 +4055,16 @@
         <v>17</v>
       </c>
       <c r="BD14" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF14" t="n">
         <v>10</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="BH14" t="n">
         <v>3.8</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>3.8</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
         <v>3.75</v>
@@ -4180,7 +4180,7 @@
         <v>1.37</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
         <v>3.4</v>
@@ -4192,7 +4192,7 @@
         <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
         <v>1.32</v>
@@ -4213,22 +4213,22 @@
         <v>1.71</v>
       </c>
       <c r="X15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y15" t="n">
         <v>15</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>14.5</v>
       </c>
       <c r="Z15" t="n">
         <v>29</v>
       </c>
       <c r="AA15" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AC15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD15" t="n">
         <v>17.5</v>
@@ -4237,7 +4237,7 @@
         <v>55</v>
       </c>
       <c r="AF15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG15" t="n">
         <v>13</v>
@@ -4252,10 +4252,10 @@
         <v>36</v>
       </c>
       <c r="AK15" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AL15" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM15" t="n">
         <v>120</v>
@@ -4267,16 +4267,16 @@
         <v>55</v>
       </c>
       <c r="AP15" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AR15" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="AT15" t="n">
         <v>8.199999999999999</v>
@@ -4285,13 +4285,13 @@
         <v>6.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW15" t="n">
-        <v>34</v>
+        <v>4.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY15" t="n">
         <v>9.800000000000001</v>
@@ -4300,43 +4300,43 @@
         <v>15.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="BD15" t="n">
-        <v>32</v>
+        <v>4.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.72</v>
+        <v>2.98</v>
       </c>
       <c r="BJ15" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BL15" t="n">
         <v>150</v>
       </c>
       <c r="BM15" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BN15" t="n">
         <v>5.8</v>
@@ -4348,41 +4348,41 @@
         <v>19.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BR15" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV15" t="n">
         <v>32</v>
       </c>
-      <c r="BS15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>34</v>
-      </c>
       <c r="BW15" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BX15" t="n">
         <v>48</v>
       </c>
       <c r="BY15" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ15" t="n">
         <v>34</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G16" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="H16" t="n">
         <v>3.9</v>
       </c>
       <c r="I16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J16" t="n">
         <v>4.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.4</v>
       </c>
       <c r="K16" t="n">
         <v>5.1</v>
@@ -4446,13 +4446,13 @@
         <v>3.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="R16" t="n">
         <v>1.87</v>
       </c>
       <c r="S16" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="T16" t="n">
         <v>1.45</v>
@@ -4464,10 +4464,10 @@
         <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X16" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Y16" t="n">
         <v>36</v>
@@ -4476,10 +4476,10 @@
         <v>50</v>
       </c>
       <c r="AA16" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AB16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AC16" t="n">
         <v>15.5</v>
@@ -4488,16 +4488,16 @@
         <v>23</v>
       </c>
       <c r="AE16" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AF16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AG16" t="n">
         <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
         <v>44</v>
@@ -4506,7 +4506,7 @@
         <v>26</v>
       </c>
       <c r="AK16" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AL16" t="n">
         <v>27</v>
@@ -4554,7 +4554,7 @@
         <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BB16" t="n">
         <v>15.5</v>
@@ -4569,7 +4569,7 @@
         <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BG16" t="n">
         <v>16</v>
@@ -4584,13 +4584,13 @@
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BL16" t="n">
         <v>70</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BN16" t="n">
         <v>6.4</v>
@@ -4602,41 +4602,41 @@
         <v>13.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>8.199999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="BR16" t="n">
         <v>21</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BT16" t="n">
         <v>10.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BV16" t="n">
         <v>34</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BX16" t="n">
         <v>34</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BZ16" t="n">
         <v>12.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>
@@ -4709,10 +4709,10 @@
         <v>1.11</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
@@ -4832,65 +4832,65 @@
         <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
         <v>1.08</v>
@@ -4963,10 +4963,10 @@
         <v>1.08</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
@@ -5086,65 +5086,65 @@
         <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18" t="n">
         <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN18" t="n">
         <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT18" t="n">
         <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
         <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L19" t="n">
         <v>1.44</v>
@@ -5214,7 +5214,7 @@
         <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T19" t="n">
         <v>1.93</v>
@@ -5223,22 +5223,22 @@
         <v>1.87</v>
       </c>
       <c r="V19" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W19" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X19" t="n">
         <v>14</v>
       </c>
       <c r="Y19" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z19" t="n">
         <v>44</v>
       </c>
       <c r="AA19" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB19" t="n">
         <v>8.800000000000001</v>
@@ -5247,13 +5247,13 @@
         <v>8.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE19" t="n">
         <v>90</v>
       </c>
       <c r="AF19" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG19" t="n">
         <v>12</v>
@@ -5289,13 +5289,13 @@
         <v>11.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT19" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AU19" t="n">
         <v>6.4</v>
@@ -5304,7 +5304,7 @@
         <v>15.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX19" t="n">
         <v>8.4</v>
@@ -5313,10 +5313,10 @@
         <v>8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB19" t="n">
         <v>16</v>
@@ -5325,16 +5325,16 @@
         <v>16.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF19" t="n">
         <v>12</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH19" t="n">
         <v>3.5</v>
@@ -5346,59 +5346,59 @@
         <v>12.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL19" t="n">
         <v>190</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BN19" t="n">
         <v>4.9</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BP19" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR19" t="n">
         <v>36</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BT19" t="n">
         <v>9.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BV19" t="n">
         <v>55</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BX19" t="n">
         <v>70</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BZ19" t="n">
         <v>34</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>
@@ -5432,31 +5432,31 @@
         <v>2.56</v>
       </c>
       <c r="G20" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="H20" t="n">
         <v>2.92</v>
       </c>
       <c r="I20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="K20" t="n">
         <v>3.45</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>1.58</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="P20" t="n">
         <v>1.58</v>
@@ -5465,194 +5465,194 @@
         <v>2.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S20" t="n">
         <v>4.5</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W20" t="n">
         <v>1.52</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 21:03:51</t>
+          <t>2026-07-18 23:17:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="G2" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="H2" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I2" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="J2" t="n">
         <v>3.7</v>
@@ -884,31 +884,31 @@
         <v>4.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q2" t="n">
         <v>1.71</v>
       </c>
       <c r="R2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S2" t="n">
         <v>2.76</v>
       </c>
       <c r="T2" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="U2" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.54</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.53</v>
       </c>
       <c r="X2" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO2" t="n">
         <v>22</v>
@@ -968,46 +968,46 @@
         <v>16.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
         <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU2" t="n">
         <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AX2" t="n">
         <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>10.5</v>
+        <v>3.45</v>
       </c>
       <c r="AZ2" t="n">
         <v>13</v>
       </c>
       <c r="BA2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC2" t="n">
         <v>3.9</v>
       </c>
-      <c r="BB2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BD2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BE2" t="n">
         <v>4.1</v>
@@ -1016,7 +1016,7 @@
         <v>13.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH2" t="n">
         <v>4.1</v>
@@ -1028,13 +1028,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN2" t="n">
         <v>6.4</v>
@@ -1052,7 +1052,7 @@
         <v>29</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
@@ -1064,13 +1064,13 @@
         <v>19.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX2" t="n">
         <v>29</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>
@@ -1111,64 +1111,64 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X3" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y3" t="n">
         <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V3" t="n">
-        <v>4</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X3" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
         <v>8.800000000000001</v>
@@ -1177,22 +1177,22 @@
         <v>10.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AC3" t="n">
         <v>15.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
         <v>14.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AG3" t="n">
-        <v>950</v>
+        <v>48</v>
       </c>
       <c r="AH3" t="n">
         <v>950</v>
@@ -1201,130 +1201,130 @@
         <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>620</v>
+        <v>490</v>
       </c>
       <c r="AK3" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="AL3" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AM3" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AP3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>160</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>16</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>110</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>90</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BV3" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>170</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>120</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>100</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>8</v>
-      </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BX3" t="n">
         <v>26</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>
@@ -1377,13 +1377,13 @@
         <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
         <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
@@ -1395,19 +1395,19 @@
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
         <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U4" t="n">
         <v>1.95</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>
@@ -1619,220 +1619,220 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>1.83</v>
       </c>
       <c r="H5" t="n">
-        <v>1.11</v>
+        <v>5.5</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J5" t="n">
-        <v>1.24</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.29</v>
+        <v>2.12</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>1.28</v>
+        <v>3.95</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="G6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="J6" t="n">
         <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.3</v>
@@ -1903,28 +1903,28 @@
         <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q6" t="n">
         <v>1.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
         <v>2.46</v>
       </c>
       <c r="W6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X6" t="n">
         <v>23</v>
@@ -1978,16 +1978,16 @@
         <v>85</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AP6" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS6" t="n">
         <v>13.5</v>
@@ -1996,10 +1996,10 @@
         <v>18</v>
       </c>
       <c r="AU6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV6" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>8.4</v>
       </c>
       <c r="AW6" t="n">
         <v>14</v>
@@ -2014,25 +2014,25 @@
         <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE6" t="n">
         <v>7.6</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BF6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG6" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>6.4</v>
       </c>
       <c r="BH6" t="n">
         <v>4</v>
@@ -2074,7 +2074,7 @@
         <v>4.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="BV6" t="n">
         <v>11</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O7" t="n">
         <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q7" t="n">
         <v>1.34</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>7.6</v>
       </c>
       <c r="G8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H8" t="n">
         <v>1.48</v>
@@ -2399,25 +2399,25 @@
         <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O8" t="n">
         <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
         <v>1.87</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
         <v>3.2</v>
@@ -2426,7 +2426,7 @@
         <v>2.02</v>
       </c>
       <c r="U8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V8" t="n">
         <v>2.82</v>
@@ -2471,19 +2471,19 @@
         <v>42</v>
       </c>
       <c r="AJ8" t="n">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AK8" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AL8" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AM8" t="n">
         <v>190</v>
       </c>
       <c r="AN8" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AO8" t="n">
         <v>8.800000000000001</v>
@@ -2513,7 +2513,7 @@
         <v>14</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY8" t="n">
         <v>7.2</v>
@@ -2522,10 +2522,10 @@
         <v>21</v>
       </c>
       <c r="BA8" t="n">
-        <v>32</v>
+        <v>7.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC8" t="n">
         <v>8.800000000000001</v>
@@ -2534,7 +2534,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF8" t="n">
         <v>9</v>
@@ -2543,68 +2543,68 @@
         <v>7</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="BJ8" t="n">
         <v>14</v>
       </c>
       <c r="BK8" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BL8" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="BM8" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BN8" t="n">
         <v>13.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BP8" t="n">
         <v>90</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BR8" t="n">
         <v>90</v>
       </c>
       <c r="BS8" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BT8" t="n">
         <v>4.6</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BV8" t="n">
         <v>11.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BX8" t="n">
         <v>32</v>
       </c>
       <c r="BY8" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>22</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G9" t="n">
         <v>3.05</v>
@@ -2644,7 +2644,7 @@
         <v>2.46</v>
       </c>
       <c r="I9" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J9" t="n">
         <v>3.7</v>
@@ -2653,43 +2653,43 @@
         <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
         <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
         <v>1.6</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W9" t="n">
         <v>1.48</v>
       </c>
       <c r="X9" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y9" t="n">
         <v>13.5</v>
@@ -2701,7 +2701,7 @@
         <v>34</v>
       </c>
       <c r="AB9" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC9" t="n">
         <v>8.800000000000001</v>
@@ -2734,28 +2734,28 @@
         <v>36</v>
       </c>
       <c r="AM9" t="n">
-        <v>65</v>
+        <v>650</v>
       </c>
       <c r="AN9" t="n">
         <v>21</v>
       </c>
       <c r="AO9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ9" t="n">
         <v>12.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS9" t="n">
         <v>30</v>
       </c>
       <c r="AT9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU9" t="n">
         <v>8</v>
@@ -2776,7 +2776,7 @@
         <v>13.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB9" t="n">
         <v>40</v>
@@ -2803,16 +2803,16 @@
         <v>3.15</v>
       </c>
       <c r="BJ9" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="BL9" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="BM9" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BN9" t="n">
         <v>7.4</v>
@@ -2821,44 +2821,44 @@
         <v>5.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="BR9" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BS9" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU9" t="n">
         <v>5.2</v>
       </c>
       <c r="BV9" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="BX9" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>
@@ -2919,10 +2919,10 @@
         <v>1.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R10" t="n">
         <v>1.35</v>
@@ -3060,7 +3060,7 @@
         <v>11.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>7</v>
+        <v>3.35</v>
       </c>
       <c r="BL10" t="n">
         <v>150</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="K12" t="n">
         <v>3.2</v>
@@ -3424,7 +3424,7 @@
         <v>1.29</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="P12" t="n">
         <v>1.29</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="H13" t="n">
         <v>4.6</v>
@@ -3669,7 +3669,7 @@
         <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
@@ -3681,7 +3681,7 @@
         <v>1.28</v>
       </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
         <v>1.83</v>
@@ -3693,19 +3693,19 @@
         <v>3.15</v>
       </c>
       <c r="T13" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="U13" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V13" t="n">
         <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y13" t="n">
         <v>21</v>
@@ -3726,7 +3726,7 @@
         <v>22</v>
       </c>
       <c r="AE13" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
         <v>13.5</v>
@@ -3765,10 +3765,10 @@
         <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT13" t="n">
         <v>8</v>
@@ -3780,7 +3780,7 @@
         <v>16</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX13" t="n">
         <v>9.800000000000001</v>
@@ -3792,7 +3792,7 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB13" t="n">
         <v>16.5</v>
@@ -3801,16 +3801,16 @@
         <v>16</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH13" t="n">
         <v>4.1</v>
@@ -3828,25 +3828,25 @@
         <v>140</v>
       </c>
       <c r="BM13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BN13" t="n">
         <v>5.1</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BP13" t="n">
         <v>14</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="BR13" t="n">
         <v>30</v>
       </c>
       <c r="BS13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BT13" t="n">
         <v>9.6</v>
@@ -3855,7 +3855,7 @@
         <v>3.55</v>
       </c>
       <c r="BV13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW13" t="n">
         <v>5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G14" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H14" t="n">
         <v>4.4</v>
@@ -3956,7 +3956,7 @@
         <v>1.24</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X14" t="n">
         <v>17</v>
@@ -4088,7 +4088,7 @@
         <v>5.1</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BP14" t="n">
         <v>15.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
         <v>2.4</v>
       </c>
       <c r="H15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
         <v>3.8</v>
@@ -4177,7 +4177,7 @@
         <v>3.75</v>
       </c>
       <c r="L15" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
@@ -4210,10 +4210,10 @@
         <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y15" t="n">
         <v>15</v>
@@ -4225,7 +4225,7 @@
         <v>80</v>
       </c>
       <c r="AB15" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC15" t="n">
         <v>9</v>
@@ -4237,7 +4237,7 @@
         <v>55</v>
       </c>
       <c r="AF15" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG15" t="n">
         <v>13</v>
@@ -4276,7 +4276,7 @@
         <v>21</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT15" t="n">
         <v>8.199999999999999</v>
@@ -4288,7 +4288,7 @@
         <v>13</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AX15" t="n">
         <v>12.5</v>
@@ -4300,25 +4300,25 @@
         <v>15.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF15" t="n">
         <v>15.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BH15" t="n">
         <v>3.35</v>
@@ -4330,16 +4330,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL15" t="n">
         <v>150</v>
       </c>
       <c r="BM15" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BO15" t="n">
         <v>4.5</v>
@@ -4348,16 +4348,16 @@
         <v>19.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BR15" t="n">
         <v>36</v>
       </c>
       <c r="BS15" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU15" t="n">
         <v>5.4</v>
@@ -4366,23 +4366,23 @@
         <v>32</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BX15" t="n">
         <v>48</v>
       </c>
       <c r="BY15" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BZ15" t="n">
         <v>34</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I16" t="n">
         <v>4.6</v>
@@ -4428,16 +4428,16 @@
         <v>4.5</v>
       </c>
       <c r="K16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O16" t="n">
         <v>1.12</v>
@@ -4449,10 +4449,10 @@
         <v>1.37</v>
       </c>
       <c r="R16" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="S16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="T16" t="n">
         <v>1.45</v>
@@ -4464,7 +4464,7 @@
         <v>1.28</v>
       </c>
       <c r="W16" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X16" t="n">
         <v>44</v>
@@ -4521,7 +4521,7 @@
         <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AQ16" t="n">
         <v>21</v>
@@ -4536,7 +4536,7 @@
         <v>13</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV16" t="n">
         <v>13.5</v>
@@ -4560,7 +4560,7 @@
         <v>15.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD16" t="n">
         <v>16</v>
@@ -4569,7 +4569,7 @@
         <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG16" t="n">
         <v>16</v>
@@ -4584,59 +4584,59 @@
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>3.15</v>
+        <v>6.2</v>
       </c>
       <c r="BL16" t="n">
         <v>70</v>
       </c>
       <c r="BM16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BN16" t="n">
         <v>6.4</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BP16" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>3.35</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS16" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BT16" t="n">
         <v>10.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.15</v>
+        <v>6.2</v>
       </c>
       <c r="BV16" t="n">
         <v>34</v>
       </c>
       <c r="BW16" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BX16" t="n">
         <v>34</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BZ16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.3</v>
+        <v>7.8</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
         <v>190</v>
       </c>
       <c r="BM19" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BN19" t="n">
         <v>4.9</v>
@@ -5370,13 +5370,13 @@
         <v>36</v>
       </c>
       <c r="BS19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BT19" t="n">
         <v>9.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV19" t="n">
         <v>55</v>
@@ -5391,14 +5391,14 @@
         <v>5.5</v>
       </c>
       <c r="BZ19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA19" t="n">
         <v>5.1</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>
@@ -5438,10 +5438,10 @@
         <v>2.92</v>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J20" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="K20" t="n">
         <v>3.45</v>
@@ -5468,16 +5468,16 @@
         <v>1.21</v>
       </c>
       <c r="S20" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
         <v>1.97</v>
       </c>
       <c r="U20" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="V20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
         <v>1.52</v>
@@ -5600,34 +5600,34 @@
         <v>13</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL20" t="n">
         <v>220</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BN20" t="n">
         <v>6.6</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP20" t="n">
         <v>29</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BR20" t="n">
         <v>55</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU20" t="n">
         <v>4.5</v>
@@ -5636,23 +5636,23 @@
         <v>34</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BX20" t="n">
         <v>60</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ20" t="n">
         <v>55</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-18 23:17:34</t>
+          <t>2026-07-19 01:31:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="I3" t="n">
         <v>1.36</v>
@@ -1129,13 +1129,13 @@
         <v>6.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.19</v>
@@ -1144,37 +1144,37 @@
         <v>2.52</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="R3" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="S3" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="U3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X3" t="n">
         <v>30</v>
       </c>
       <c r="Y3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AB3" t="n">
         <v>46</v>
@@ -1201,130 +1201,130 @@
         <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="AK3" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AL3" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AM3" t="n">
         <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AP3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT3" t="n">
         <v>7.8</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV3" t="n">
         <v>5.1</v>
       </c>
-      <c r="AR3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AW3" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD3" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BF3" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BH3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="BJ3" t="n">
         <v>13.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BL3" t="n">
         <v>160</v>
       </c>
       <c r="BM3" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN3" t="n">
         <v>16</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BP3" t="n">
         <v>110</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BR3" t="n">
         <v>90</v>
       </c>
       <c r="BS3" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BT3" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BU3" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BV3" t="n">
         <v>7.4</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="BX3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BY3" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
         <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
@@ -1416,7 +1416,7 @@
         <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X4" t="n">
         <v>14.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -1628,34 +1628,34 @@
         <v>5.5</v>
       </c>
       <c r="I5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="O5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q5" t="n">
         <v>2.12</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="S5" t="n">
         <v>3.95</v>
@@ -1664,10 +1664,10 @@
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="V5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
         <v>2.2</v>
@@ -1676,7 +1676,7 @@
         <v>15</v>
       </c>
       <c r="Y5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z5" t="n">
         <v>55</v>
@@ -1733,34 +1733,34 @@
         <v>4.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AV5" t="n">
         <v>4.3</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AZ5" t="n">
         <v>4.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB5" t="n">
         <v>4.1</v>
@@ -1769,49 +1769,49 @@
         <v>4.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BJ5" t="n">
         <v>13.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BL5" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="BM5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BN5" t="n">
         <v>4.9</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BR5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BS5" t="n">
         <v>4.3</v>
@@ -1820,19 +1820,19 @@
         <v>11</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BV5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BW5" t="n">
         <v>4.5</v>
       </c>
       <c r="BX5" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -1882,10 +1882,10 @@
         <v>1.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
         <v>4.6</v>
@@ -1900,49 +1900,49 @@
         <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P6" t="n">
         <v>2.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
         <v>2.88</v>
       </c>
       <c r="T6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.19</v>
       </c>
       <c r="X6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB6" t="n">
         <v>25</v>
       </c>
       <c r="AC6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
         <v>10.5</v>
@@ -1978,7 +1978,7 @@
         <v>85</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP6" t="n">
         <v>16.5</v>
@@ -2002,10 +2002,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AY6" t="n">
         <v>18.5</v>
@@ -2014,22 +2014,22 @@
         <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG6" t="n">
         <v>7.2</v>
@@ -2044,7 +2044,7 @@
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2056,7 +2056,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BO6" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BP6" t="n">
         <v>50</v>
@@ -2080,7 +2080,7 @@
         <v>11</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX6" t="n">
         <v>25</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2175,10 +2175,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -2396,37 +2396,37 @@
         <v>4.5</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T8" t="n">
         <v>2.02</v>
       </c>
       <c r="U8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V8" t="n">
         <v>2.82</v>
@@ -2435,13 +2435,13 @@
         <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>14</v>
@@ -2492,7 +2492,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR8" t="n">
         <v>7.4</v>
@@ -2513,70 +2513,70 @@
         <v>14</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AY8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AZ8" t="n">
         <v>21</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG8" t="n">
         <v>7</v>
       </c>
       <c r="BH8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="BJ8" t="n">
         <v>14</v>
       </c>
       <c r="BK8" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BL8" t="n">
         <v>190</v>
       </c>
       <c r="BM8" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BN8" t="n">
         <v>13.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="BP8" t="n">
         <v>90</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BR8" t="n">
         <v>90</v>
       </c>
       <c r="BS8" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BT8" t="n">
         <v>4.6</v>
@@ -2588,23 +2588,23 @@
         <v>11.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BX8" t="n">
         <v>32</v>
       </c>
       <c r="BY8" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BZ8" t="n">
         <v>22</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H9" t="n">
         <v>2.46</v>
       </c>
       <c r="I9" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
         <v>1.32</v>
@@ -2659,7 +2659,7 @@
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.23</v>
@@ -2668,25 +2668,25 @@
         <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T9" t="n">
         <v>1.6</v>
       </c>
       <c r="U9" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W9" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X9" t="n">
         <v>20</v>
@@ -2734,7 +2734,7 @@
         <v>36</v>
       </c>
       <c r="AM9" t="n">
-        <v>650</v>
+        <v>730</v>
       </c>
       <c r="AN9" t="n">
         <v>21</v>
@@ -2776,7 +2776,7 @@
         <v>13.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB9" t="n">
         <v>40</v>
@@ -2785,7 +2785,7 @@
         <v>26</v>
       </c>
       <c r="BD9" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BE9" t="n">
         <v>50</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G10" t="n">
         <v>2.12</v>
@@ -2904,7 +2904,7 @@
         <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
         <v>1.38</v>
@@ -2919,7 +2919,7 @@
         <v>1.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q10" t="n">
         <v>1.89</v>
@@ -2943,7 +2943,7 @@
         <v>1.89</v>
       </c>
       <c r="X10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y10" t="n">
         <v>16</v>
@@ -2955,7 +2955,7 @@
         <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>8.800000000000001</v>
@@ -3003,10 +3003,10 @@
         <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT10" t="n">
         <v>8.199999999999999</v>
@@ -3018,7 +3018,7 @@
         <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
@@ -3030,7 +3030,7 @@
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB10" t="n">
         <v>20</v>
@@ -3039,10 +3039,10 @@
         <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF10" t="n">
         <v>10.5</v>
@@ -3057,62 +3057,62 @@
         <v>2.78</v>
       </c>
       <c r="BJ10" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BK10" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="BL10" t="n">
         <v>150</v>
       </c>
       <c r="BM10" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BO10" t="n">
         <v>4.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="BR10" t="n">
         <v>34</v>
       </c>
       <c r="BS10" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BU10" t="n">
         <v>5.6</v>
       </c>
       <c r="BV10" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BX10" t="n">
         <v>55</v>
       </c>
       <c r="BY10" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BZ10" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>7.6</v>
       </c>
       <c r="G11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="H11" t="n">
         <v>1.42</v>
@@ -3155,7 +3155,7 @@
         <v>1.45</v>
       </c>
       <c r="J11" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K11" t="n">
         <v>5.8</v>
@@ -3167,25 +3167,25 @@
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P11" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q11" t="n">
         <v>1.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S11" t="n">
         <v>2.24</v>
       </c>
       <c r="T11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U11" t="n">
         <v>2.22</v>
@@ -3197,7 +3197,7 @@
         <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y11" t="n">
         <v>13</v>
@@ -3206,19 +3206,19 @@
         <v>11</v>
       </c>
       <c r="AA11" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AC11" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AD11" t="n">
         <v>10.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AF11" t="n">
         <v>90</v>
@@ -3230,7 +3230,7 @@
         <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ11" t="n">
         <v>250</v>
@@ -3248,10 +3248,10 @@
         <v>110</v>
       </c>
       <c r="AO11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AP11" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ11" t="n">
         <v>11</v>
@@ -3260,22 +3260,22 @@
         <v>9.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU11" t="n">
         <v>11</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW11" t="n">
         <v>12.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="AY11" t="n">
         <v>21</v>
@@ -3284,28 +3284,28 @@
         <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BG11" t="n">
         <v>4.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BI11" t="n">
         <v>3.7</v>
@@ -3314,31 +3314,31 @@
         <v>12</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="BL11" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM11" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BN11" t="n">
         <v>13.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="BP11" t="n">
         <v>65</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BR11" t="n">
         <v>60</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BT11" t="n">
         <v>5.1</v>
@@ -3347,26 +3347,26 @@
         <v>3.4</v>
       </c>
       <c r="BV11" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BW11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BX11" t="n">
         <v>23</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BZ11" t="n">
         <v>13</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="K12" t="n">
         <v>3.2</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>1.87</v>
       </c>
       <c r="H13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
         <v>5.2</v>
@@ -3669,19 +3669,19 @@
         <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O13" t="n">
         <v>1.28</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
         <v>1.83</v>
@@ -3693,10 +3693,10 @@
         <v>3.15</v>
       </c>
       <c r="T13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U13" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V13" t="n">
         <v>1.25</v>
@@ -3732,7 +3732,7 @@
         <v>13.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH13" t="n">
         <v>22</v>
@@ -3747,7 +3747,7 @@
         <v>22</v>
       </c>
       <c r="AL13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM13" t="n">
         <v>120</v>
@@ -3759,16 +3759,16 @@
         <v>80</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
         <v>8</v>
@@ -3780,7 +3780,7 @@
         <v>16</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AX13" t="n">
         <v>9.800000000000001</v>
@@ -3792,7 +3792,7 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BB13" t="n">
         <v>16.5</v>
@@ -3801,16 +3801,16 @@
         <v>16</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BF13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BH13" t="n">
         <v>4.1</v>
@@ -3828,7 +3828,7 @@
         <v>140</v>
       </c>
       <c r="BM13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BN13" t="n">
         <v>5.1</v>
@@ -3846,7 +3846,7 @@
         <v>30</v>
       </c>
       <c r="BS13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BT13" t="n">
         <v>9.6</v>
@@ -3855,7 +3855,7 @@
         <v>3.55</v>
       </c>
       <c r="BV13" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BW13" t="n">
         <v>5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -3917,13 +3917,13 @@
         <v>5.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
         <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
@@ -3932,22 +3932,22 @@
         <v>3.55</v>
       </c>
       <c r="O14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R14" t="n">
         <v>1.34</v>
       </c>
       <c r="S14" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T14" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U14" t="n">
         <v>2</v>
@@ -3959,7 +3959,7 @@
         <v>2.02</v>
       </c>
       <c r="X14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y14" t="n">
         <v>19</v>
@@ -3971,7 +3971,7 @@
         <v>130</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC14" t="n">
         <v>9.800000000000001</v>
@@ -3986,7 +3986,7 @@
         <v>13.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH14" t="n">
         <v>23</v>
@@ -3998,10 +3998,10 @@
         <v>25</v>
       </c>
       <c r="AK14" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM14" t="n">
         <v>130</v>
@@ -4019,10 +4019,10 @@
         <v>13.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT14" t="n">
         <v>7.4</v>
@@ -4034,7 +4034,7 @@
         <v>16</v>
       </c>
       <c r="AW14" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX14" t="n">
         <v>9.800000000000001</v>
@@ -4046,7 +4046,7 @@
         <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BB14" t="n">
         <v>18</v>
@@ -4055,16 +4055,16 @@
         <v>17</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF14" t="n">
         <v>10</v>
       </c>
       <c r="BG14" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BH14" t="n">
         <v>3.8</v>
@@ -4088,10 +4088,10 @@
         <v>5.1</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="BP14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ14" t="n">
         <v>4.2</v>
@@ -4106,29 +4106,29 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV14" t="n">
         <v>46</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BX14" t="n">
         <v>60</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BZ14" t="n">
         <v>28</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
         <v>3.75</v>
       </c>
       <c r="L15" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
@@ -4186,7 +4186,7 @@
         <v>3.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P15" t="n">
         <v>1.83</v>
@@ -4201,13 +4201,13 @@
         <v>3.6</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U15" t="n">
         <v>2.06</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
         <v>1.72</v>
@@ -4330,13 +4330,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL15" t="n">
         <v>150</v>
       </c>
       <c r="BM15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN15" t="n">
         <v>5.2</v>
@@ -4351,7 +4351,7 @@
         <v>6.8</v>
       </c>
       <c r="BR15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS15" t="n">
         <v>8.199999999999999</v>
@@ -4366,7 +4366,7 @@
         <v>32</v>
       </c>
       <c r="BW15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX15" t="n">
         <v>48</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G16" t="n">
         <v>1.89</v>
@@ -4428,7 +4428,7 @@
         <v>4.5</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L16" t="n">
         <v>1.21</v>
@@ -4521,28 +4521,28 @@
         <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.05</v>
+        <v>4</v>
       </c>
       <c r="AQ16" t="n">
         <v>21</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT16" t="n">
         <v>13</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="AV16" t="n">
         <v>13.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX16" t="n">
         <v>12.5</v>
@@ -4554,7 +4554,7 @@
         <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.05</v>
+        <v>4.1</v>
       </c>
       <c r="BB16" t="n">
         <v>15.5</v>
@@ -4566,7 +4566,7 @@
         <v>16</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF16" t="n">
         <v>4.6</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
         <v>190</v>
       </c>
       <c r="BM19" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BN19" t="n">
         <v>4.9</v>
@@ -5370,10 +5370,10 @@
         <v>36</v>
       </c>
       <c r="BS19" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BT19" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU19" t="n">
         <v>6.4</v>
@@ -5382,23 +5382,23 @@
         <v>55</v>
       </c>
       <c r="BW19" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BX19" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY19" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BZ19" t="n">
         <v>32</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>
@@ -5429,19 +5429,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G20" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="H20" t="n">
         <v>2.92</v>
       </c>
       <c r="I20" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J20" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="K20" t="n">
         <v>3.45</v>
@@ -5450,7 +5450,7 @@
         <v>1.52</v>
       </c>
       <c r="M20" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N20" t="n">
         <v>2.7</v>
@@ -5477,10 +5477,10 @@
         <v>1.84</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X20" t="n">
         <v>12</v>
@@ -5489,7 +5489,7 @@
         <v>11.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA20" t="n">
         <v>70</v>
@@ -5507,7 +5507,7 @@
         <v>55</v>
       </c>
       <c r="AF20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="n">
         <v>15.5</v>
@@ -5546,19 +5546,19 @@
         <v>14.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT20" t="n">
         <v>6.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AV20" t="n">
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX20" t="n">
         <v>12</v>
@@ -5570,25 +5570,25 @@
         <v>15.5</v>
       </c>
       <c r="BA20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB20" t="n">
         <v>4</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BC20" t="n">
         <v>3.95</v>
       </c>
-      <c r="BC20" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BD20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE20" t="n">
         <v>4.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH20" t="n">
         <v>3.25</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-19 01:31:12</t>
+          <t>2026-07-19 03:44:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB20"/>
+  <dimension ref="A1:CB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -941,7 +941,7 @@
         <v>15.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI2" t="n">
         <v>42</v>
@@ -1004,7 +1004,7 @@
         <v>4</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BD2" t="n">
         <v>4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
@@ -1276,55 +1276,55 @@
         <v>5.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BJ3" t="n">
         <v>13.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BL3" t="n">
         <v>160</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BN3" t="n">
         <v>16</v>
       </c>
       <c r="BO3" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BP3" t="n">
         <v>110</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BR3" t="n">
         <v>90</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT3" t="n">
         <v>3.95</v>
       </c>
       <c r="BU3" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BV3" t="n">
         <v>7.4</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="BX3" t="n">
         <v>24</v>
       </c>
       <c r="BY3" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G4" t="n">
         <v>2.46</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>1.72</v>
       </c>
       <c r="G5" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="H5" t="n">
         <v>5.5</v>
@@ -1631,31 +1631,31 @@
         <v>6.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="O5" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="Q5" t="n">
         <v>2.12</v>
       </c>
       <c r="R5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
         <v>3.95</v>
@@ -1664,19 +1664,19 @@
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V5" t="n">
         <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="X5" t="n">
         <v>15</v>
       </c>
       <c r="Y5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z5" t="n">
         <v>55</v>
@@ -1727,7 +1727,7 @@
         <v>160</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AQ5" t="n">
         <v>4.1</v>
@@ -1763,10 +1763,10 @@
         <v>4.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BD5" t="n">
         <v>4.7</v>
@@ -1775,25 +1775,25 @@
         <v>5</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BG5" t="n">
         <v>5</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BJ5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BL5" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="BM5" t="n">
         <v>4.8</v>
@@ -1808,13 +1808,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BR5" t="n">
         <v>40</v>
       </c>
       <c r="BS5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BT5" t="n">
         <v>11</v>
@@ -1823,16 +1823,16 @@
         <v>3.4</v>
       </c>
       <c r="BV5" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BX5" t="n">
         <v>85</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         <v>1.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="J6" t="n">
         <v>4.4</v>
@@ -1903,7 +1903,7 @@
         <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
         <v>1.75</v>
@@ -1921,7 +1921,7 @@
         <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="W6" t="n">
         <v>1.19</v>
@@ -1936,7 +1936,7 @@
         <v>10.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AB6" t="n">
         <v>25</v>
@@ -1948,7 +1948,7 @@
         <v>10.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF6" t="n">
         <v>55</v>
@@ -1978,7 +1978,7 @@
         <v>85</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AP6" t="n">
         <v>16.5</v>
@@ -1990,7 +1990,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT6" t="n">
         <v>18</v>
@@ -2005,31 +2005,31 @@
         <v>14.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY6" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AZ6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA6" t="n">
         <v>7.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF6" t="n">
         <v>8.6</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="BG6" t="n">
         <v>7.2</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2175,10 +2175,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
         <v>4.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
@@ -2432,7 +2432,7 @@
         <v>2.82</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
         <v>16.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
@@ -2641,13 +2641,13 @@
         <v>2.96</v>
       </c>
       <c r="H9" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I9" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
         <v>3.9</v>
@@ -2659,7 +2659,7 @@
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
         <v>1.23</v>
@@ -2683,7 +2683,7 @@
         <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W9" t="n">
         <v>1.51</v>
@@ -2692,13 +2692,13 @@
         <v>20</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB9" t="n">
         <v>16.5</v>
@@ -2725,25 +2725,25 @@
         <v>32</v>
       </c>
       <c r="AJ9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AK9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL9" t="n">
         <v>36</v>
       </c>
       <c r="AM9" t="n">
-        <v>730</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>12.5</v>
@@ -2779,19 +2779,19 @@
         <v>28</v>
       </c>
       <c r="BB9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BC9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD9" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BE9" t="n">
         <v>50</v>
       </c>
       <c r="BF9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BG9" t="n">
         <v>13.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>1.98</v>
       </c>
       <c r="G10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H10" t="n">
         <v>3.9</v>
@@ -2940,7 +2940,7 @@
         <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X10" t="n">
         <v>18</v>
@@ -3054,7 +3054,7 @@
         <v>4.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="BJ10" t="n">
         <v>10</v>
@@ -3066,7 +3066,7 @@
         <v>150</v>
       </c>
       <c r="BM10" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BN10" t="n">
         <v>5</v>
@@ -3078,13 +3078,13 @@
         <v>15</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BR10" t="n">
         <v>34</v>
       </c>
       <c r="BS10" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BT10" t="n">
         <v>7.8</v>
@@ -3096,23 +3096,23 @@
         <v>36</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BX10" t="n">
         <v>55</v>
       </c>
       <c r="BY10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="CA10" t="n">
         <v>5.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="G11" t="n">
         <v>8.4</v>
@@ -3155,13 +3155,13 @@
         <v>1.45</v>
       </c>
       <c r="J11" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="K11" t="n">
         <v>5.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M11" t="n">
         <v>1.03</v>
@@ -3173,22 +3173,22 @@
         <v>1.16</v>
       </c>
       <c r="P11" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="Q11" t="n">
         <v>1.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U11" t="n">
         <v>2.24</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.22</v>
       </c>
       <c r="V11" t="n">
         <v>3.2</v>
@@ -3224,10 +3224,10 @@
         <v>90</v>
       </c>
       <c r="AG11" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AH11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
         <v>28</v>
@@ -3236,22 +3236,22 @@
         <v>250</v>
       </c>
       <c r="AK11" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AL11" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM11" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN11" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO11" t="n">
         <v>4.8</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ11" t="n">
         <v>11</v>
@@ -3263,7 +3263,7 @@
         <v>11</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU11" t="n">
         <v>11</v>
@@ -3275,7 +3275,7 @@
         <v>12.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
         <v>21</v>
@@ -3284,22 +3284,22 @@
         <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BC11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BD11" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG11" t="n">
         <v>4.4</v>
@@ -3308,37 +3308,37 @@
         <v>5.7</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ11" t="n">
         <v>12</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BL11" t="n">
         <v>110</v>
       </c>
       <c r="BM11" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BN11" t="n">
         <v>13.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BP11" t="n">
         <v>65</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BR11" t="n">
         <v>60</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="BT11" t="n">
         <v>5.1</v>
@@ -3347,26 +3347,26 @@
         <v>3.4</v>
       </c>
       <c r="BV11" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BW11" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BX11" t="n">
         <v>23</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BZ11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="K12" t="n">
         <v>3.2</v>
@@ -3424,16 +3424,16 @@
         <v>1.29</v>
       </c>
       <c r="O12" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="P12" t="n">
         <v>1.29</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="R12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S12" t="n">
         <v>1.05</v>
@@ -3445,10 +3445,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G14" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H14" t="n">
         <v>4.4</v>
@@ -3956,7 +3956,7 @@
         <v>1.24</v>
       </c>
       <c r="W14" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X14" t="n">
         <v>16.5</v>
@@ -3995,7 +3995,7 @@
         <v>80</v>
       </c>
       <c r="AJ14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK14" t="n">
         <v>21</v>
@@ -4019,10 +4019,10 @@
         <v>13.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT14" t="n">
         <v>7.4</v>
@@ -4034,7 +4034,7 @@
         <v>16</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX14" t="n">
         <v>9.800000000000001</v>
@@ -4055,16 +4055,16 @@
         <v>17</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF14" t="n">
         <v>10</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH14" t="n">
         <v>3.8</v>
@@ -4106,7 +4106,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU14" t="n">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="BV14" t="n">
         <v>46</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,246 +4150,246 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Academia de Balompie Boli</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4</v>
+        <v>110</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="K15" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
         <v>1.37</v>
       </c>
-      <c r="M15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O15" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>11.5</v>
+        <v>26</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.1</v>
+        <v>40</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="AX15" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB15" t="n">
         <v>15.5</v>
       </c>
-      <c r="BA15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BC15" t="n">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.9</v>
+        <v>17</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.2</v>
+        <v>32</v>
       </c>
       <c r="BF15" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,251 +4399,251 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IF Vestri</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.73</v>
       </c>
-      <c r="G16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="I16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X16" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="Y16" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="Z16" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AA16" t="n">
         <v>80</v>
       </c>
       <c r="AB16" t="n">
-        <v>22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>15.5</v>
+        <v>8</v>
       </c>
       <c r="AD16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN16" t="n">
         <v>23</v>
       </c>
-      <c r="AE16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF16" t="n">
+      <c r="AO16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR16" t="n">
         <v>21</v>
       </c>
-      <c r="AG16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AS16" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AT16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV16" t="n">
         <v>13</v>
       </c>
-      <c r="AU16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AW16" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AX16" t="n">
         <v>12.5</v>
       </c>
       <c r="AY16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>48</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>34</v>
+      </c>
+      <c r="CA16" t="n">
         <v>8.6</v>
       </c>
-      <c r="AZ16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>16</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>70</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>22</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>34</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>13</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>7.8</v>
-      </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,239 +4658,239 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Keflavik</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.26</v>
+        <v>7.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P17" t="n">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="S17" t="n">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>2.78</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL17" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BN17" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP17" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR17" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BT17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BV17" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BX17" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
@@ -4912,12 +4912,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>Keflavik</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>IA Akranes</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4945,22 +4945,22 @@
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O18" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="P18" t="n">
         <v>1.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="R18" t="n">
         <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,244 +5161,244 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Torque</t>
+          <t>Hafnarfjordur</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O19" t="n">
         <v>1.08</v>
       </c>
-      <c r="N19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.37</v>
-      </c>
       <c r="P19" t="n">
-        <v>1.74</v>
+        <v>1.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1</v>
+        <v>1.08</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.85</v>
+        <v>1.08</v>
       </c>
       <c r="T19" t="n">
-        <v>1.93</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
-        <v>1.87</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL19" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP19" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BR19" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT19" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV19" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-19 03:44:22</t>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>
@@ -5415,244 +5415,498 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X20" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>190</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>32</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-07-19 05:58:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Defensor Sporting</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Liverpool Montevideo</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
         <v>2.58</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>2.88</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>2.92</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>3.3</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>3.15</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>3.45</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>1.52</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>1.11</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N21" t="n">
         <v>2.7</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O21" t="n">
         <v>1.47</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P21" t="n">
         <v>1.58</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>2.4</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>1.21</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S21" t="n">
         <v>4.2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>1.97</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>1.84</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V21" t="n">
         <v>1.43</v>
       </c>
-      <c r="W20" t="n">
+      <c r="W21" t="n">
         <v>1.53</v>
       </c>
-      <c r="X20" t="n">
+      <c r="X21" t="n">
         <v>12</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Y21" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="Z21" t="n">
         <v>24</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AA21" t="n">
         <v>70</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AB21" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AC21" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AD21" t="n">
         <v>17</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AE21" t="n">
         <v>55</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AF21" t="n">
         <v>20</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AG21" t="n">
         <v>15.5</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AH21" t="n">
         <v>26</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AI21" t="n">
         <v>80</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AJ21" t="n">
         <v>55</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AK21" t="n">
         <v>46</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AL21" t="n">
         <v>75</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AM21" t="n">
         <v>190</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AN21" t="n">
         <v>50</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AO21" t="n">
         <v>65</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AP21" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AQ21" t="n">
         <v>7</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="AR21" t="n">
         <v>14.5</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="AS21" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="AT21" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="AU21" t="n">
         <v>5.6</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="AV21" t="n">
         <v>10</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="AW21" t="n">
         <v>4</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="AX21" t="n">
         <v>12</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="AY21" t="n">
         <v>9.4</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="AZ21" t="n">
         <v>15.5</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BA21" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BB21" t="n">
         <v>4</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BC21" t="n">
         <v>3.95</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BD21" t="n">
         <v>4.1</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BE21" t="n">
         <v>4.2</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BF21" t="n">
         <v>4</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BG21" t="n">
         <v>4.1</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BH21" t="n">
         <v>3.25</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BI21" t="n">
         <v>2.32</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BJ21" t="n">
         <v>13</v>
       </c>
-      <c r="BK20" t="n">
+      <c r="BK21" t="n">
         <v>3.55</v>
       </c>
-      <c r="BL20" t="n">
+      <c r="BL21" t="n">
         <v>220</v>
       </c>
-      <c r="BM20" t="n">
+      <c r="BM21" t="n">
         <v>4.8</v>
       </c>
-      <c r="BN20" t="n">
+      <c r="BN21" t="n">
         <v>6.6</v>
       </c>
-      <c r="BO20" t="n">
+      <c r="BO21" t="n">
         <v>4.2</v>
       </c>
-      <c r="BP20" t="n">
+      <c r="BP21" t="n">
         <v>29</v>
       </c>
-      <c r="BQ20" t="n">
+      <c r="BQ21" t="n">
         <v>4.2</v>
       </c>
-      <c r="BR20" t="n">
+      <c r="BR21" t="n">
         <v>55</v>
       </c>
-      <c r="BS20" t="n">
+      <c r="BS21" t="n">
         <v>4.5</v>
       </c>
-      <c r="BT20" t="n">
+      <c r="BT21" t="n">
         <v>7.2</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="BU21" t="n">
         <v>4.5</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="BV21" t="n">
         <v>34</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="BW21" t="n">
         <v>4.2</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="BX21" t="n">
         <v>60</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="BY21" t="n">
         <v>4.5</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="BZ21" t="n">
         <v>55</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CA21" t="n">
         <v>4.5</v>
       </c>
-      <c r="CB20" t="inlineStr">
-        <is>
-          <t>2026-07-19 03:44:22</t>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-07-19 05:58:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB21"/>
+  <dimension ref="A1:CB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,7 +866,7 @@
         <v>2.6</v>
       </c>
       <c r="I2" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J2" t="n">
         <v>3.7</v>
@@ -893,7 +893,7 @@
         <v>1.71</v>
       </c>
       <c r="R2" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S2" t="n">
         <v>2.76</v>
@@ -926,7 +926,7 @@
         <v>17.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
         <v>15</v>
@@ -941,7 +941,7 @@
         <v>15.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI2" t="n">
         <v>42</v>
@@ -974,7 +974,7 @@
         <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AT2" t="n">
         <v>12.5</v>
@@ -986,31 +986,31 @@
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AX2" t="n">
         <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AZ2" t="n">
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BF2" t="n">
         <v>13.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="I3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="J3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K3" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.24</v>
@@ -1135,34 +1135,34 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T3" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
         <v>30</v>
@@ -1174,7 +1174,7 @@
         <v>9</v>
       </c>
       <c r="AA3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AB3" t="n">
         <v>46</v>
@@ -1183,7 +1183,7 @@
         <v>15.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
         <v>14.5</v>
@@ -1198,10 +1198,10 @@
         <v>950</v>
       </c>
       <c r="AI3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>470</v>
+        <v>560</v>
       </c>
       <c r="AK3" t="n">
         <v>200</v>
@@ -1213,118 +1213,118 @@
         <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BA3" t="n">
         <v>7.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.55</v>
+        <v>2.94</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="BJ3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK3" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BL3" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="BM3" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BO3" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP3" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="BV3" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="BX3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY3" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>2.46</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I4" t="n">
         <v>4</v>
@@ -1380,10 +1380,10 @@
         <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="G5" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H5" t="n">
         <v>5.5</v>
@@ -1631,31 +1631,31 @@
         <v>6.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="L5" t="n">
         <v>1.48</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="Q5" t="n">
         <v>2.12</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
         <v>3.95</v>
@@ -1670,7 +1670,7 @@
         <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X5" t="n">
         <v>15</v>
@@ -1685,10 +1685,10 @@
         <v>200</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD5" t="n">
         <v>28</v>
@@ -1697,7 +1697,7 @@
         <v>120</v>
       </c>
       <c r="AF5" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AG5" t="n">
         <v>12.5</v>
@@ -1727,58 +1727,58 @@
         <v>160</v>
       </c>
       <c r="AP5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX5" t="n">
         <v>3.85</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR5" t="n">
+      <c r="AY5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BA5" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BB5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF5" t="n">
         <v>4.2</v>
       </c>
-      <c r="BC5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BH5" t="n">
         <v>3.5</v>
@@ -1787,7 +1787,7 @@
         <v>2.46</v>
       </c>
       <c r="BJ5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK5" t="n">
         <v>3.65</v>
@@ -1796,7 +1796,7 @@
         <v>230</v>
       </c>
       <c r="BM5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN5" t="n">
         <v>4.9</v>
@@ -1808,7 +1808,7 @@
         <v>15.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BR5" t="n">
         <v>40</v>
@@ -1820,13 +1820,13 @@
         <v>11</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV5" t="n">
         <v>70</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BX5" t="n">
         <v>85</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="I6" t="n">
         <v>1.67</v>
@@ -1888,7 +1888,7 @@
         <v>4.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L6" t="n">
         <v>1.3</v>
@@ -1927,7 +1927,7 @@
         <v>1.19</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y6" t="n">
         <v>9.6</v>
@@ -1966,10 +1966,10 @@
         <v>170</v>
       </c>
       <c r="AK6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AL6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM6" t="n">
         <v>120</v>
@@ -1978,7 +1978,7 @@
         <v>85</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP6" t="n">
         <v>16.5</v>
@@ -2014,22 +2014,22 @@
         <v>18</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC6" t="n">
         <v>8.4</v>
       </c>
       <c r="BD6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF6" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>8.6</v>
       </c>
       <c r="BG6" t="n">
         <v>7.2</v>
@@ -2044,7 +2044,7 @@
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2056,7 +2056,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BO6" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="BP6" t="n">
         <v>50</v>
@@ -2074,13 +2074,13 @@
         <v>4.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="BV6" t="n">
         <v>11</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="BX6" t="n">
         <v>25</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>1.94</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.19</v>
+        <v>1.94</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="O7" t="n">
         <v>1.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
         <v>1.34</v>
@@ -2166,7 +2166,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2175,10 +2175,10 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -2396,10 +2396,10 @@
         <v>4.5</v>
       </c>
       <c r="K8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
@@ -2522,7 +2522,7 @@
         <v>21</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BB8" t="n">
         <v>9.800000000000001</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -2626,246 +2626,246 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Djurgardens</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.92</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>2.96</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="I9" t="n">
-        <v>2.52</v>
+        <v>1.45</v>
       </c>
       <c r="J9" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="O9" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>2.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="S9" t="n">
-        <v>2.72</v>
+        <v>2.22</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="U9" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.65</v>
+        <v>3.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.51</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="Y9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE9" t="n">
         <v>14</v>
       </c>
-      <c r="Z9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="AF9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>250</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC9" t="n">
         <v>36</v>
       </c>
-      <c r="AB9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="BD9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BJ9" t="n">
         <v>12</v>
       </c>
-      <c r="AE9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF9" t="n">
+      <c r="BK9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>110</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>65</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>60</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BX9" t="n">
         <v>23</v>
       </c>
-      <c r="AG9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ9" t="n">
+      <c r="BY9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BZ9" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>38</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>85</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>26</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>18.5</v>
-      </c>
       <c r="CA9" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Norrby IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.98</v>
+        <v>2.96</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>2.98</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4</v>
+        <v>2.52</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="T10" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>2.54</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="W10" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Y10" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB10" t="n">
         <v>16</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP10" t="n">
         <v>17.5</v>
       </c>
-      <c r="AE10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF10" t="n">
+      <c r="AQ10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>13.5</v>
       </c>
-      <c r="AG10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL10" t="n">
+      <c r="BA10" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB10" t="n">
         <v>38</v>
       </c>
-      <c r="AM10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR10" t="n">
+      <c r="BC10" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>85</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BT10" t="n">
         <v>6.8</v>
       </c>
-      <c r="AS10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>150</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BN10" t="n">
+      <c r="BU10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>26</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="CA10" t="n">
         <v>5</v>
       </c>
-      <c r="BO10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>55</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>28</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>5.5</v>
-      </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,239 +3134,239 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Orgryte</t>
+          <t>Norrby IF</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Djurgardens</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>7.8</v>
+        <v>1.98</v>
       </c>
       <c r="G11" t="n">
-        <v>8.4</v>
+        <v>2.1</v>
       </c>
       <c r="H11" t="n">
-        <v>1.42</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1.45</v>
+        <v>4.4</v>
       </c>
       <c r="J11" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="M11" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="O11" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.86</v>
+        <v>1.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="R11" t="n">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>2.22</v>
+        <v>3.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U11" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="V11" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.9</v>
       </c>
       <c r="X11" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z11" t="n">
         <v>32</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>13</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AR11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX11" t="n">
         <v>11</v>
       </c>
-      <c r="AA11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD11" t="n">
+      <c r="AY11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF11" t="n">
         <v>10.5</v>
       </c>
-      <c r="AE11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>250</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX11" t="n">
+      <c r="BG11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ11" t="n">
         <v>10</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>12</v>
       </c>
       <c r="BK11" t="n">
         <v>3.45</v>
       </c>
       <c r="BL11" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="BM11" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BN11" t="n">
-        <v>13.5</v>
+        <v>5.7</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>65</v>
+        <v>17.5</v>
       </c>
       <c r="BQ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS11" t="n">
         <v>4.5</v>
       </c>
-      <c r="BR11" t="n">
-        <v>60</v>
-      </c>
-      <c r="BS11" t="n">
+      <c r="BT11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>29</v>
+      </c>
+      <c r="CA11" t="n">
         <v>4.4</v>
       </c>
-      <c r="BT11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>23</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>3.45</v>
-      </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -3430,13 +3430,13 @@
         <v>1.29</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="R12" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S12" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3445,10 +3445,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -3651,25 +3651,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G13" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="H13" t="n">
         <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
@@ -3681,10 +3681,10 @@
         <v>1.28</v>
       </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R13" t="n">
         <v>1.38</v>
@@ -3696,13 +3696,13 @@
         <v>1.77</v>
       </c>
       <c r="U13" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V13" t="n">
         <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X13" t="n">
         <v>17.5</v>
@@ -3747,7 +3747,7 @@
         <v>22</v>
       </c>
       <c r="AL13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM13" t="n">
         <v>120</v>
@@ -3822,59 +3822,59 @@
         <v>11.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BL13" t="n">
         <v>140</v>
       </c>
       <c r="BM13" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BN13" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="BP13" t="n">
         <v>14</v>
       </c>
       <c r="BQ13" t="n">
-        <v>9.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR13" t="n">
         <v>30</v>
       </c>
       <c r="BS13" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="BV13" t="n">
         <v>48</v>
       </c>
       <c r="BW13" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BX13" t="n">
         <v>55</v>
       </c>
       <c r="BY13" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BZ13" t="n">
         <v>24</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G14" t="n">
         <v>1.96</v>
@@ -3920,7 +3920,7 @@
         <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L14" t="n">
         <v>1.4</v>
@@ -4061,7 +4061,7 @@
         <v>5.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG14" t="n">
         <v>5.6</v>
@@ -4076,13 +4076,13 @@
         <v>11.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BL14" t="n">
         <v>150</v>
       </c>
       <c r="BM14" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BN14" t="n">
         <v>5.1</v>
@@ -4094,10 +4094,10 @@
         <v>15</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BR14" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BS14" t="n">
         <v>5</v>
@@ -4106,29 +4106,29 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV14" t="n">
         <v>46</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BX14" t="n">
         <v>60</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BZ14" t="n">
         <v>28</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="G15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
         <v>1.04</v>
@@ -4171,13 +4171,13 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
       </c>
       <c r="L15" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
         <v>1.01</v>
@@ -4189,7 +4189,7 @@
         <v>1.1</v>
       </c>
       <c r="P15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Q15" t="n">
         <v>1.1</v>
@@ -4198,7 +4198,7 @@
         <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -4267,52 +4267,52 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
         <v>1.01</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -4413,25 +4413,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G16" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="H16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" t="n">
         <v>3.4</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.35</v>
       </c>
       <c r="K16" t="n">
         <v>3.65</v>
       </c>
       <c r="L16" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
@@ -4443,7 +4443,7 @@
         <v>1.35</v>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q16" t="n">
         <v>2.04</v>
@@ -4455,16 +4455,16 @@
         <v>3.65</v>
       </c>
       <c r="T16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U16" t="n">
         <v>2.06</v>
       </c>
       <c r="V16" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W16" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="X16" t="n">
         <v>15</v>
@@ -4482,7 +4482,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
         <v>17.5</v>
@@ -4491,31 +4491,31 @@
         <v>55</v>
       </c>
       <c r="AF16" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH16" t="n">
         <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ16" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK16" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL16" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM16" t="n">
         <v>120</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>55</v>
@@ -4530,10 +4530,10 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU16" t="n">
         <v>6.8</v>
@@ -4542,37 +4542,37 @@
         <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
         <v>15.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.1</v>
+        <v>20</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF16" t="n">
         <v>15.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BH16" t="n">
         <v>3.3</v>
@@ -4584,59 +4584,59 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BL16" t="n">
         <v>150</v>
       </c>
       <c r="BM16" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BR16" t="n">
         <v>38</v>
       </c>
       <c r="BS16" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BT16" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BU16" t="n">
         <v>5.4</v>
       </c>
       <c r="BV16" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BX16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY16" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ16" t="n">
         <v>34</v>
       </c>
       <c r="CA16" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="G17" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="H17" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J17" t="n">
         <v>4.5</v>
       </c>
       <c r="K17" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.21</v>
@@ -4691,19 +4691,19 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O17" t="n">
         <v>1.12</v>
       </c>
       <c r="P17" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q17" t="n">
         <v>1.37</v>
       </c>
       <c r="R17" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="S17" t="n">
         <v>1.93</v>
@@ -4715,10 +4715,10 @@
         <v>2.78</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W17" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="X17" t="n">
         <v>44</v>
@@ -4730,7 +4730,7 @@
         <v>50</v>
       </c>
       <c r="AA17" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AB17" t="n">
         <v>22</v>
@@ -4769,19 +4769,19 @@
         <v>60</v>
       </c>
       <c r="AN17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO17" t="n">
         <v>27</v>
       </c>
       <c r="AP17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ17" t="n">
         <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS17" t="n">
         <v>4.3</v>
@@ -4790,31 +4790,31 @@
         <v>13</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.5</v>
+        <v>9.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>13.5</v>
+        <v>3.8</v>
       </c>
       <c r="AW17" t="n">
         <v>4.1</v>
       </c>
       <c r="AX17" t="n">
-        <v>12.5</v>
+        <v>3.75</v>
       </c>
       <c r="AY17" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>11</v>
+        <v>3.65</v>
       </c>
       <c r="BA17" t="n">
         <v>4.1</v>
       </c>
       <c r="BB17" t="n">
-        <v>15.5</v>
+        <v>3.9</v>
       </c>
       <c r="BC17" t="n">
-        <v>12</v>
+        <v>3.7</v>
       </c>
       <c r="BD17" t="n">
         <v>16</v>
@@ -4823,10 +4823,10 @@
         <v>4.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.6</v>
+        <v>2.74</v>
       </c>
       <c r="BG17" t="n">
-        <v>16</v>
+        <v>3.9</v>
       </c>
       <c r="BH17" t="n">
         <v>6.4</v>
@@ -4844,7 +4844,7 @@
         <v>70</v>
       </c>
       <c r="BM17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BN17" t="n">
         <v>6.4</v>
@@ -4853,16 +4853,16 @@
         <v>4.6</v>
       </c>
       <c r="BP17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BR17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS17" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BT17" t="n">
         <v>10.5</v>
@@ -4874,23 +4874,23 @@
         <v>34</v>
       </c>
       <c r="BW17" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BX17" t="n">
         <v>34</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BZ17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA17" t="n">
         <v>7.8</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
         <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L20" t="n">
         <v>1.45</v>
@@ -5459,7 +5459,7 @@
         <v>1.38</v>
       </c>
       <c r="P20" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" t="n">
         <v>2.1</v>
@@ -5567,16 +5567,16 @@
         <v>8</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA20" t="n">
         <v>5.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD20" t="n">
         <v>5.1</v>
@@ -5597,7 +5597,7 @@
         <v>2.62</v>
       </c>
       <c r="BJ20" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BK20" t="n">
         <v>8.4</v>
@@ -5606,16 +5606,16 @@
         <v>190</v>
       </c>
       <c r="BM20" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BO20" t="n">
         <v>3.8</v>
       </c>
       <c r="BP20" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ20" t="n">
         <v>10</v>
@@ -5624,7 +5624,7 @@
         <v>36</v>
       </c>
       <c r="BS20" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BT20" t="n">
         <v>8.6</v>
@@ -5636,277 +5636,531 @@
         <v>60</v>
       </c>
       <c r="BW20" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BX20" t="n">
         <v>65</v>
       </c>
       <c r="BY20" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BZ20" t="n">
         <v>32</v>
       </c>
       <c r="CA20" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-19 05:58:00</t>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Nacional Potosi</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>CDT Real Oruro</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-07-19 08:11:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Uruguayan Primera Division</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Defensor Sporting</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Liverpool Montevideo</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="G21" t="n">
+      <c r="F22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G22" t="n">
         <v>2.88</v>
       </c>
-      <c r="H21" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="H22" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I22" t="n">
         <v>3.3</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>3.15</v>
       </c>
-      <c r="K21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="K22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M22" t="n">
         <v>1.11</v>
       </c>
-      <c r="N21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="N22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P22" t="n">
         <v>1.58</v>
       </c>
-      <c r="Q21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="Q22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.21</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S22" t="n">
         <v>4.2</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>1.97</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>1.84</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V22" t="n">
         <v>1.43</v>
       </c>
-      <c r="W21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X21" t="n">
+      <c r="W22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX22" t="n">
         <v>12</v>
       </c>
-      <c r="Y21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE21" t="n">
+      <c r="AY22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>220</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>29</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BR22" t="n">
         <v>55</v>
       </c>
-      <c r="AF21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ21" t="n">
+      <c r="BS22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BZ22" t="n">
         <v>55</v>
       </c>
-      <c r="AK21" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>220</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>29</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>55</v>
-      </c>
-      <c r="BS21" t="n">
+      <c r="CA22" t="n">
         <v>4.5</v>
       </c>
-      <c r="BT21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BZ21" t="n">
-        <v>55</v>
-      </c>
-      <c r="CA21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="CB21" t="inlineStr">
-        <is>
-          <t>2026-07-19 05:58:00</t>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-07-19 08:11:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB22"/>
+  <dimension ref="A1:CB23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G2" t="n">
         <v>2.82</v>
@@ -887,16 +887,16 @@
         <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="R2" t="n">
         <v>1.51</v>
       </c>
       <c r="S2" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T2" t="n">
         <v>1.62</v>
@@ -926,13 +926,13 @@
         <v>17.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
         <v>15</v>
       </c>
       <c r="AE2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF2" t="n">
         <v>25</v>
@@ -953,13 +953,13 @@
         <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
         <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO2" t="n">
         <v>22</v>
@@ -968,13 +968,13 @@
         <v>16.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>3.95</v>
       </c>
       <c r="AR2" t="n">
         <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT2" t="n">
         <v>12.5</v>
@@ -983,40 +983,40 @@
         <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX2" t="n">
         <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AZ2" t="n">
         <v>13</v>
       </c>
       <c r="BA2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC2" t="n">
         <v>4.4</v>
       </c>
-      <c r="BB2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BD2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BH2" t="n">
         <v>4.1</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="H3" t="n">
         <v>1.27</v>
@@ -1123,7 +1123,7 @@
         <v>1.32</v>
       </c>
       <c r="J3" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
         <v>7.2</v>
@@ -1132,22 +1132,22 @@
         <v>1.24</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q3" t="n">
         <v>1.53</v>
       </c>
       <c r="R3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="S3" t="n">
         <v>2.32</v>
@@ -1162,121 +1162,121 @@
         <v>4.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y3" t="n">
         <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>10.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD3" t="n">
         <v>13</v>
       </c>
       <c r="AE3" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AG3" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AH3" t="n">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AI3" t="n">
         <v>44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="AK3" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AL3" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AM3" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN3" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AO3" t="n">
         <v>4.4</v>
       </c>
       <c r="AP3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR3" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AS3" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.6</v>
+        <v>13</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="BH3" t="n">
         <v>5.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.72</v>
+        <v>3.7</v>
       </c>
       <c r="BJ3" t="n">
         <v>14</v>
@@ -1288,37 +1288,37 @@
         <v>170</v>
       </c>
       <c r="BM3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BN3" t="n">
         <v>17</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP3" t="n">
         <v>120</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR3" t="n">
         <v>95</v>
       </c>
       <c r="BS3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BT3" t="n">
         <v>4.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>2.48</v>
+        <v>3.15</v>
       </c>
       <c r="BV3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.35</v>
+        <v>5.6</v>
       </c>
       <c r="BX3" t="n">
         <v>25</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
@@ -1383,13 +1383,13 @@
         <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.38</v>
@@ -1404,7 +1404,7 @@
         <v>1.27</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
         <v>1.84</v>
@@ -1437,7 +1437,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE4" t="n">
         <v>60</v>
@@ -1473,13 +1473,13 @@
         <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AQ4" t="n">
         <v>3.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AS4" t="n">
         <v>4</v>
@@ -1497,13 +1497,13 @@
         <v>3.95</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AY4" t="n">
         <v>3.25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BA4" t="n">
         <v>4</v>
@@ -1515,13 +1515,13 @@
         <v>3.75</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BE4" t="n">
         <v>4.1</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BG4" t="n">
         <v>4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
@@ -1625,43 +1625,43 @@
         <v>1.84</v>
       </c>
       <c r="H5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
         <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
         <v>1.8</v>
@@ -1673,16 +1673,16 @@
         <v>2.18</v>
       </c>
       <c r="X5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA5" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AB5" t="n">
         <v>7.2</v>
@@ -1691,10 +1691,10 @@
         <v>8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE5" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF5" t="n">
         <v>12</v>
@@ -1703,100 +1703,100 @@
         <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI5" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AN5" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.3</v>
+        <v>14</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD5" t="n">
         <v>4.7</v>
       </c>
-      <c r="AW5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BE5" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BJ5" t="n">
         <v>13.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BL5" t="n">
         <v>230</v>
       </c>
       <c r="BM5" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BN5" t="n">
         <v>4.9</v>
@@ -1808,31 +1808,31 @@
         <v>15.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BR5" t="n">
         <v>40</v>
       </c>
       <c r="BS5" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BT5" t="n">
         <v>11</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="BV5" t="n">
         <v>70</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BX5" t="n">
         <v>85</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G6" t="n">
         <v>6.4</v>
@@ -1882,10 +1882,10 @@
         <v>1.62</v>
       </c>
       <c r="I6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K6" t="n">
         <v>4.7</v>
@@ -1906,7 +1906,7 @@
         <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R6" t="n">
         <v>1.47</v>
@@ -1915,13 +1915,13 @@
         <v>2.88</v>
       </c>
       <c r="T6" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U6" t="n">
         <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.19</v>
@@ -1936,22 +1936,22 @@
         <v>10.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC6" t="n">
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AG6" t="n">
         <v>26</v>
@@ -1963,22 +1963,22 @@
         <v>34</v>
       </c>
       <c r="AJ6" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AK6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL6" t="n">
         <v>80</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>75</v>
       </c>
       <c r="AM6" t="n">
         <v>120</v>
       </c>
       <c r="AN6" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AP6" t="n">
         <v>16.5</v>
@@ -1993,7 +1993,7 @@
         <v>14</v>
       </c>
       <c r="AT6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AU6" t="n">
         <v>9</v>
@@ -2005,13 +2005,13 @@
         <v>14.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA6" t="n">
         <v>7.4</v>
@@ -2020,7 +2020,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BC6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD6" t="n">
         <v>8.199999999999999</v>
@@ -2044,7 +2044,7 @@
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
@@ -2127,237 +2127,237 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H7" t="n">
-        <v>1.94</v>
+        <v>3.05</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J7" t="n">
-        <v>1.59</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
         <v>3.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.24</v>
+        <v>2.76</v>
       </c>
       <c r="O7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.34</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>1.34</v>
+        <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BL7" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Peruvian Segunda Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:15:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Pirata FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Uni San Martin</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>1.55</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>1.24</v>
       </c>
       <c r="O8" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.89</v>
+        <v>1.35</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>1.34</v>
       </c>
       <c r="T8" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,195 +2621,195 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:15:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Orgryte</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Djurgardens</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X9" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>330</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>160</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>230</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX9" t="n">
         <v>8</v>
       </c>
-      <c r="G9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="AY9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI9" t="n">
         <v>2.86</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X9" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE9" t="n">
+      <c r="BJ9" t="n">
         <v>14</v>
       </c>
-      <c r="AF9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>250</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>48</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>36</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>34</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>12</v>
-      </c>
       <c r="BK9" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BL9" t="n">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="BM9" t="n">
         <v>4.6</v>
@@ -2818,47 +2818,47 @@
         <v>13.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="BQ9" t="n">
         <v>4.5</v>
       </c>
       <c r="BR9" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="BS9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="BV9" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BX9" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BY9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BZ9" t="n">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G10" t="n">
         <v>2.96</v>
       </c>
-      <c r="G10" t="n">
-        <v>2.98</v>
-      </c>
       <c r="H10" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I10" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
         <v>3.85</v>
@@ -2913,7 +2913,7 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
@@ -2934,16 +2934,16 @@
         <v>1.61</v>
       </c>
       <c r="U10" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V10" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y10" t="n">
         <v>14</v>
@@ -2955,7 +2955,7 @@
         <v>36</v>
       </c>
       <c r="AB10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC10" t="n">
         <v>8.800000000000001</v>
@@ -2964,16 +2964,16 @@
         <v>12</v>
       </c>
       <c r="AE10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG10" t="n">
         <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI10" t="n">
         <v>32</v>
@@ -3045,10 +3045,10 @@
         <v>50</v>
       </c>
       <c r="BF10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH10" t="n">
         <v>4.7</v>
@@ -3063,10 +3063,10 @@
         <v>6.4</v>
       </c>
       <c r="BL10" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="BM10" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BN10" t="n">
         <v>7.4</v>
@@ -3078,16 +3078,16 @@
         <v>20</v>
       </c>
       <c r="BQ10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS10" t="n">
         <v>5.1</v>
       </c>
-      <c r="BR10" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BT10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU10" t="n">
         <v>5.2</v>
@@ -3096,23 +3096,23 @@
         <v>17.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BX10" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BY10" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BZ10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA10" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
         <v>1.38</v>
@@ -3173,7 +3173,7 @@
         <v>1.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q11" t="n">
         <v>1.89</v>
@@ -3188,7 +3188,7 @@
         <v>1.76</v>
       </c>
       <c r="U11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="n">
         <v>1.3</v>
@@ -3197,10 +3197,10 @@
         <v>1.9</v>
       </c>
       <c r="X11" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Z11" t="n">
         <v>32</v>
@@ -3209,13 +3209,13 @@
         <v>110</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AE11" t="n">
         <v>55</v>
@@ -3227,13 +3227,13 @@
         <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
         <v>60</v>
       </c>
       <c r="AJ11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK11" t="n">
         <v>23</v>
@@ -3245,10 +3245,10 @@
         <v>120</v>
       </c>
       <c r="AN11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP11" t="n">
         <v>12.5</v>
@@ -3257,10 +3257,10 @@
         <v>13</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="AS11" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AT11" t="n">
         <v>8.199999999999999</v>
@@ -3272,7 +3272,7 @@
         <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -3284,7 +3284,7 @@
         <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.6</v>
+        <v>46</v>
       </c>
       <c r="BB11" t="n">
         <v>20</v>
@@ -3293,16 +3293,16 @@
         <v>18</v>
       </c>
       <c r="BD11" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BF11" t="n">
         <v>10.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH11" t="n">
         <v>4.1</v>
@@ -3314,13 +3314,13 @@
         <v>10</v>
       </c>
       <c r="BK11" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="BL11" t="n">
         <v>150</v>
       </c>
       <c r="BM11" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BN11" t="n">
         <v>5.7</v>
@@ -3329,51 +3329,51 @@
         <v>4.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BR11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BS11" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BT11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV11" t="n">
         <v>36</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BX11" t="n">
         <v>55</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BZ11" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AD Berazategui</t>
+          <t>Orgryte</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Central Cordoba</t>
+          <t>Djurgardens</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.91</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>1.94</v>
+        <v>1.43</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>1.45</v>
       </c>
       <c r="J12" t="n">
-        <v>1.53</v>
+        <v>5.3</v>
       </c>
       <c r="K12" t="n">
-        <v>3.15</v>
+        <v>5.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>1.29</v>
+        <v>6.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="P12" t="n">
-        <v>1.29</v>
+        <v>2.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.12</v>
+        <v>1.76</v>
       </c>
       <c r="S12" t="n">
-        <v>1.55</v>
+        <v>2.24</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="V12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.13</v>
       </c>
-      <c r="W12" t="n">
-        <v>1.2</v>
-      </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ12" t="n">
         <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BL12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,251 +3637,251 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>AD Berazategui</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Central Cordoba</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7</v>
+        <v>2.02</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>1.63</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>3.9</v>
+        <v>1.29</v>
       </c>
       <c r="O13" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="S13" t="n">
-        <v>3.15</v>
+        <v>1.55</v>
       </c>
       <c r="T13" t="n">
-        <v>1.77</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL13" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP13" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV13" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,246 +3896,246 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ACS Sepsi OSK</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G14" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K14" t="n">
         <v>3.95</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="O14" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="R14" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="T14" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="X14" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Y14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Z14" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AA14" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF14" t="n">
         <v>13.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>23</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AK14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO14" t="n">
         <v>80</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>75</v>
-      </c>
       <c r="AP14" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV14" t="n">
         <v>16</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AX14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB14" t="n">
         <v>16.5</v>
       </c>
-      <c r="BA14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>18</v>
-      </c>
       <c r="BC14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG14" t="n">
         <v>5.3</v>
       </c>
-      <c r="BE14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BH14" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="BJ14" t="n">
         <v>11.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="BL14" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="BM14" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BN14" t="n">
         <v>5.1</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BR14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS14" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BT14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BV14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BX14" t="n">
         <v>60</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BZ14" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="CA14" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,251 +4145,251 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Rapid Bucharest</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Academia de Balompie Boli</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.31</v>
+        <v>1.84</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>1.96</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>1.37</v>
+        <v>3.55</v>
       </c>
       <c r="O15" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="P15" t="n">
-        <v>1.37</v>
+        <v>1.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.1</v>
+        <v>1.93</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>1.54</v>
+        <v>3.45</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BL15" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BX15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Academia de Balompie Boli</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.1</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>2.22</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>1.06</v>
       </c>
       <c r="K16" t="n">
-        <v>3.65</v>
+        <v>500</v>
       </c>
       <c r="L16" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4</v>
+        <v>1.37</v>
       </c>
       <c r="O16" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="P16" t="n">
-        <v>1.85</v>
+        <v>1.37</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.04</v>
+        <v>1.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>3.65</v>
+        <v>1.54</v>
       </c>
       <c r="T16" t="n">
-        <v>1.82</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.82</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.98</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV16" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IF Vestri</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
-        <v>1.84</v>
+        <v>2.22</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="I17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR17" t="n">
         <v>4.7</v>
       </c>
-      <c r="J17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="AS17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE17" t="n">
         <v>5.3</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="BF17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>29</v>
+      </c>
+      <c r="CA17" t="n">
         <v>7.4</v>
       </c>
-      <c r="O17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="X17" t="n">
-        <v>44</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>70</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>13</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>21</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BX17" t="n">
-        <v>34</v>
-      </c>
-      <c r="BY17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BZ17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>7.8</v>
-      </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,239 +4912,239 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Keflavik</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M18" t="n">
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>1.26</v>
+        <v>7.8</v>
       </c>
       <c r="O18" t="n">
         <v>1.11</v>
       </c>
       <c r="P18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP18" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
@@ -5166,12 +5166,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>Keflavik</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>IA Akranes</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -5199,22 +5199,22 @@
         <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O19" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="P19" t="n">
         <v>1.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="R19" t="n">
         <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="T19" t="n">
         <v>1.11</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,251 +5415,251 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Torque</t>
+          <t>Hafnarfjordur</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O20" t="n">
         <v>1.08</v>
       </c>
-      <c r="N20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.38</v>
-      </c>
       <c r="P20" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.1</v>
+        <v>1.08</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>3.9</v>
+        <v>1.08</v>
       </c>
       <c r="T20" t="n">
-        <v>1.95</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV20" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,498 +5669,752 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nacional Potosi</t>
+          <t>Torque</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CDT Real Oruro</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="G21" t="n">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="J21" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>1.41</v>
+        <v>3.15</v>
       </c>
       <c r="O21" t="n">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="P21" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.09</v>
+        <v>2.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>1.09</v>
+        <v>3.75</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL21" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX21" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-19 08:11:46</t>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Nacional Potosi</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>CDT Real Oruro</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Uruguayan Primera Division</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Defensor Sporting</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Liverpool Montevideo</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="F23" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
         <v>2.88</v>
       </c>
-      <c r="H22" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K23" t="n">
         <v>3.3</v>
       </c>
-      <c r="J22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>1.53</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>1.11</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>2.72</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>1.48</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>1.58</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>2.42</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>1.21</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>220</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>30</v>
+      </c>
+      <c r="BQ23" t="n">
         <v>4.2</v>
       </c>
-      <c r="T22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE22" t="n">
+      <c r="BR23" t="n">
         <v>55</v>
       </c>
-      <c r="AF22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ22" t="n">
+      <c r="BS23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BZ23" t="n">
         <v>55</v>
       </c>
-      <c r="AK22" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>220</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>29</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>55</v>
-      </c>
-      <c r="BS22" t="n">
+      <c r="CA23" t="n">
         <v>4.5</v>
       </c>
-      <c r="BT22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>55</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="CB22" t="inlineStr">
-        <is>
-          <t>2026-07-19 08:11:46</t>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-07-19 10:24:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CB27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="G2" t="n">
         <v>2.82</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I2" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J2" t="n">
         <v>3.7</v>
@@ -884,10 +884,10 @@
         <v>4.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q2" t="n">
         <v>1.68</v>
@@ -896,7 +896,7 @@
         <v>1.51</v>
       </c>
       <c r="S2" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="T2" t="n">
         <v>1.62</v>
@@ -905,7 +905,7 @@
         <v>2.46</v>
       </c>
       <c r="V2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W2" t="n">
         <v>1.54</v>
@@ -935,13 +935,13 @@
         <v>28</v>
       </c>
       <c r="AF2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG2" t="n">
         <v>15.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI2" t="n">
         <v>42</v>
@@ -959,7 +959,7 @@
         <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO2" t="n">
         <v>22</v>
@@ -968,13 +968,13 @@
         <v>16.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.95</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
         <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT2" t="n">
         <v>12.5</v>
@@ -986,31 +986,31 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX2" t="n">
         <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AZ2" t="n">
         <v>13</v>
       </c>
       <c r="BA2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC2" t="n">
         <v>4.6</v>
       </c>
-      <c r="BB2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF2" t="n">
         <v>15.5</v>
@@ -1028,31 +1028,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
         <v>29</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
@@ -1064,13 +1064,13 @@
         <v>19.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX2" t="n">
         <v>29</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="H3" t="n">
         <v>1.27</v>
@@ -1126,7 +1126,7 @@
         <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.24</v>
@@ -1141,7 +1141,7 @@
         <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q3" t="n">
         <v>1.53</v>
@@ -1150,7 +1150,7 @@
         <v>1.63</v>
       </c>
       <c r="S3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T3" t="n">
         <v>2.02</v>
@@ -1162,7 +1162,7 @@
         <v>4.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
         <v>32</v>
@@ -1186,7 +1186,7 @@
         <v>13</v>
       </c>
       <c r="AE3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF3" t="n">
         <v>140</v>
@@ -1198,7 +1198,7 @@
         <v>34</v>
       </c>
       <c r="AI3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="n">
         <v>550</v>
@@ -1228,49 +1228,49 @@
         <v>6.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AZ3" t="n">
         <v>6</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC3" t="n">
         <v>7.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BH3" t="n">
         <v>5.2</v>
@@ -1282,31 +1282,31 @@
         <v>14</v>
       </c>
       <c r="BK3" t="n">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="BL3" t="n">
         <v>170</v>
       </c>
       <c r="BM3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BN3" t="n">
         <v>17</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP3" t="n">
         <v>120</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR3" t="n">
         <v>95</v>
       </c>
       <c r="BS3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BT3" t="n">
         <v>4.4</v>
@@ -1315,10 +1315,10 @@
         <v>3.15</v>
       </c>
       <c r="BV3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BX3" t="n">
         <v>25</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
@@ -1380,16 +1380,16 @@
         <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.43</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="O4" t="n">
         <v>1.38</v>
@@ -1407,10 +1407,10 @@
         <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V4" t="n">
         <v>1.33</v>
@@ -1431,7 +1431,7 @@
         <v>90</v>
       </c>
       <c r="AB4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
         <v>9.199999999999999</v>
@@ -1473,55 +1473,55 @@
         <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT4" t="n">
         <v>3.05</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BA4" t="n">
         <v>4</v>
       </c>
       <c r="BB4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC4" t="n">
         <v>3.8</v>
       </c>
-      <c r="BC4" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BD4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BG4" t="n">
         <v>4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         <v>190</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR5" t="n">
         <v>4.7</v>
@@ -1742,10 +1742,10 @@
         <v>5.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AW5" t="n">
         <v>5</v>
@@ -1754,19 +1754,19 @@
         <v>8.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.4</v>
+        <v>17.5</v>
       </c>
       <c r="BA5" t="n">
         <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD5" t="n">
         <v>4.7</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="I6" t="n">
         <v>1.66</v>
@@ -1891,34 +1891,34 @@
         <v>4.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T6" t="n">
         <v>1.81</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
         <v>2.5</v>
@@ -1927,10 +1927,10 @@
         <v>1.19</v>
       </c>
       <c r="X6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z6" t="n">
         <v>10.5</v>
@@ -1948,7 +1948,7 @@
         <v>10</v>
       </c>
       <c r="AE6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF6" t="n">
         <v>60</v>
@@ -1984,7 +1984,7 @@
         <v>16.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AR6" t="n">
         <v>9.199999999999999</v>
@@ -2005,31 +2005,31 @@
         <v>14.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY6" t="n">
         <v>19</v>
       </c>
       <c r="AZ6" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF6" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>8.4</v>
       </c>
       <c r="BG6" t="n">
         <v>7.2</v>
@@ -2038,7 +2038,7 @@
         <v>4</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
@@ -2053,10 +2053,10 @@
         <v>9.4</v>
       </c>
       <c r="BN6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BO6" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BP6" t="n">
         <v>50</v>
@@ -2074,13 +2074,13 @@
         <v>4.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="BV6" t="n">
         <v>11</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BX6" t="n">
         <v>25</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
         <v>1.43</v>
@@ -2202,7 +2202,7 @@
         <v>15.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF7" t="n">
         <v>17</v>
@@ -2214,7 +2214,7 @@
         <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="n">
         <v>50</v>
@@ -2295,62 +2295,62 @@
         <v>2.52</v>
       </c>
       <c r="BJ7" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="BL7" t="n">
         <v>170</v>
       </c>
       <c r="BM7" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>2.74</v>
+        <v>3.45</v>
       </c>
       <c r="BP7" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BR7" t="n">
         <v>42</v>
       </c>
       <c r="BS7" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BT7" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>2.98</v>
+        <v>4.1</v>
       </c>
       <c r="BV7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BX7" t="n">
         <v>55</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BZ7" t="n">
         <v>40</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2405,13 +2405,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
         <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
         <v>1.35</v>
@@ -2420,7 +2420,7 @@
         <v>1.16</v>
       </c>
       <c r="S8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
@@ -2638,70 +2638,70 @@
         <v>7.6</v>
       </c>
       <c r="G9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H9" t="n">
         <v>1.47</v>
       </c>
       <c r="I9" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="J9" t="n">
         <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O9" t="n">
         <v>1.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
         <v>2.04</v>
       </c>
       <c r="U9" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="V9" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>14</v>
       </c>
       <c r="AB9" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AC9" t="n">
         <v>11</v>
@@ -2713,19 +2713,19 @@
         <v>18</v>
       </c>
       <c r="AF9" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AG9" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AH9" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
         <v>42</v>
       </c>
       <c r="AJ9" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
         <v>160</v>
@@ -2737,10 +2737,10 @@
         <v>190</v>
       </c>
       <c r="AN9" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP9" t="n">
         <v>14</v>
@@ -2752,13 +2752,13 @@
         <v>7.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>11.5</v>
+        <v>4.4</v>
       </c>
       <c r="AT9" t="n">
         <v>20</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV9" t="n">
         <v>8.6</v>
@@ -2767,10 +2767,10 @@
         <v>14</v>
       </c>
       <c r="AX9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY9" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>21</v>
@@ -2779,67 +2779,67 @@
         <v>32</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH9" t="n">
         <v>4.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ9" t="n">
         <v>14</v>
       </c>
       <c r="BK9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BL9" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="BM9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>100</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>4.6</v>
       </c>
-      <c r="BN9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>90</v>
-      </c>
-      <c r="BQ9" t="n">
+      <c r="BR9" t="n">
+        <v>95</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BT9" t="n">
         <v>4.5</v>
       </c>
-      <c r="BR9" t="n">
-        <v>90</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BU9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BW9" t="n">
         <v>3.35</v>
@@ -2848,17 +2848,17 @@
         <v>32</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BZ9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Djurgardens</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.92</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>2.96</v>
+        <v>8.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.52</v>
+        <v>1.43</v>
       </c>
       <c r="I10" t="n">
-        <v>2.54</v>
+        <v>1.45</v>
       </c>
       <c r="J10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X10" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI10" t="n">
         <v>3.75</v>
       </c>
-      <c r="K10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="BJ10" t="n">
         <v>12</v>
       </c>
-      <c r="AE10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="BK10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>110</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>65</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>60</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>23</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BZ10" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>38</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>100</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>19</v>
-      </c>
       <c r="CA10" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,246 +3134,246 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Norrby IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.98</v>
+        <v>2.92</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1</v>
+        <v>2.96</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="I11" t="n">
-        <v>4.4</v>
+        <v>2.54</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="T11" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="U11" t="n">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="W11" t="n">
-        <v>1.9</v>
+        <v>1.51</v>
       </c>
       <c r="X11" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z11" t="n">
         <v>18.5</v>
       </c>
-      <c r="Y11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>32</v>
-      </c>
       <c r="AA11" t="n">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="AC11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX11" t="n">
         <v>20</v>
       </c>
-      <c r="AE11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF11" t="n">
+      <c r="AY11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>13.5</v>
       </c>
-      <c r="AG11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ11" t="n">
+      <c r="BA11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC11" t="n">
         <v>26</v>
       </c>
-      <c r="AK11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV11" t="n">
+      <c r="BD11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG11" t="n">
         <v>14</v>
       </c>
-      <c r="AW11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB11" t="n">
+      <c r="BH11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>100</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP11" t="n">
         <v>20</v>
       </c>
-      <c r="BC11" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>38</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>150</v>
-      </c>
-      <c r="BM11" t="n">
+      <c r="BQ11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS11" t="n">
         <v>5.5</v>
       </c>
-      <c r="BN11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BT11" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BV11" t="n">
-        <v>36</v>
+        <v>17.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BX11" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="BY11" t="n">
         <v>5.2</v>
       </c>
       <c r="BZ11" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,239 +3388,239 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Orgryte</t>
+          <t>Norrby IF</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Djurgardens</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>1.98</v>
       </c>
       <c r="G12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X12" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT12" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X12" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z12" t="n">
+      <c r="AU12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX12" t="n">
         <v>11</v>
       </c>
-      <c r="AA12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AY12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG12" t="n">
         <v>38</v>
       </c>
-      <c r="AC12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>95</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>22</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>19</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>48</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>34</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BH12" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.75</v>
+        <v>2.78</v>
       </c>
       <c r="BJ12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BK12" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="BL12" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="BM12" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BN12" t="n">
-        <v>13.5</v>
+        <v>5</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BP12" t="n">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="BQ12" t="n">
         <v>4.5</v>
       </c>
       <c r="BR12" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="BS12" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BT12" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="BV12" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BW12" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="BX12" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="BY12" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="BZ12" t="n">
-        <v>12.5</v>
+        <v>29</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="K13" t="n">
         <v>3.15</v>
@@ -3699,10 +3699,10 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,251 +3891,251 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>CA Atlas</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia</t>
+          <t>Sacachispas</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.65</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>3.15</v>
+        <v>1.55</v>
       </c>
       <c r="T14" t="n">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,251 +4145,251 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Rapid Bucharest</t>
+          <t>CA Deportivo Paraguayo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ACS Sepsi OSK</t>
+          <t>CSD Central Ballester</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="G15" t="n">
-        <v>1.96</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="I15" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>3.55</v>
+        <v>1.02</v>
       </c>
       <c r="K15" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>3.55</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="P15" t="n">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="S15" t="n">
-        <v>3.45</v>
+        <v>1.57</v>
       </c>
       <c r="T15" t="n">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV15" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,36 +4399,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Estrella del Sur</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Academia de Balompie Boli</t>
+          <t>Club Lujan</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="G16" t="n">
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="K16" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4437,22 +4437,22 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="P16" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="S16" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4464,7 +4464,7 @@
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,251 +4653,251 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>CSR Espanol BA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Leones de Rosario</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="G17" t="n">
-        <v>2.22</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="I17" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L17" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>3.4</v>
+        <v>1.25</v>
       </c>
       <c r="O17" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="S17" t="n">
-        <v>3.65</v>
+        <v>1.57</v>
       </c>
       <c r="T17" t="n">
-        <v>1.82</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,251 +4907,251 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IF Vestri</t>
+          <t>Lokomotiv Sofia</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="G18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T18" t="n">
         <v>1.79</v>
       </c>
-      <c r="H18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.46</v>
-      </c>
       <c r="U18" t="n">
-        <v>2.78</v>
+        <v>2.04</v>
       </c>
       <c r="V18" t="n">
         <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="X18" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="Y18" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AA18" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AB18" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AC18" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
         <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF18" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AH18" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK18" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AL18" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AM18" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AN18" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AO18" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="AU18" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX18" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB18" t="n">
         <v>16.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
-        <v>15.5</v>
+        <v>5</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>140</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ18" t="n">
         <v>4</v>
       </c>
-      <c r="BG18" t="n">
-        <v>20</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>70</v>
-      </c>
-      <c r="BM18" t="n">
+      <c r="BR18" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>24</v>
+      </c>
+      <c r="CA18" t="n">
         <v>4.6</v>
       </c>
-      <c r="BN18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>21</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>12</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>34</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>12</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>7.4</v>
-      </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,251 +5161,251 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Keflavik</t>
+          <t>Rapid Bucharest</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>ACS Sepsi OSK</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.26</v>
       </c>
-      <c r="O19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BL19" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,60 +5415,60 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hafnarfjordur</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Academia de Balompie Boli</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="P20" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>1.08</v>
+        <v>1.54</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -5480,7 +5480,7 @@
         <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,251 +5669,251 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Torque</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="G21" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="H21" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="I21" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L21" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="M21" t="n">
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="P21" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="U21" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="V21" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="X21" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z21" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AA21" t="n">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AF21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG21" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG21" t="n">
-        <v>12</v>
-      </c>
       <c r="AH21" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI21" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AJ21" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AK21" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL21" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM21" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AN21" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AO21" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AP21" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>12</v>
       </c>
       <c r="AR21" t="n">
-        <v>32</v>
+        <v>4.8</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT21" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>16</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BA21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD21" t="n">
         <v>5</v>
       </c>
-      <c r="AX21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE21" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BG21" t="n">
         <v>5.1</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="BJ21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>19</v>
+      </c>
+      <c r="BQ21" t="n">
         <v>12.5</v>
       </c>
-      <c r="BK21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>190</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>10</v>
-      </c>
       <c r="BR21" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BS21" t="n">
         <v>6.2</v>
       </c>
       <c r="BT21" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BU21" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BV21" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BW21" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BX21" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="BY21" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ21" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="CA21" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,498 +5923,1514 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Nacional Potosi</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CDT Real Oruro</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="G22" t="n">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="J22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M22" t="n">
         <v>1.02</v>
       </c>
-      <c r="K22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N22" t="n">
-        <v>1.41</v>
+        <v>7.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="P22" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="R22" t="n">
-        <v>1.41</v>
+        <v>1.94</v>
       </c>
       <c r="S22" t="n">
-        <v>1.09</v>
+        <v>1.89</v>
       </c>
       <c r="T22" t="n">
-        <v>1.11</v>
+        <v>1.46</v>
       </c>
       <c r="U22" t="n">
-        <v>1.11</v>
+        <v>2.8</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL22" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BV22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BX22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-19 10:24:45</t>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Keflavik</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>IA Akranes</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X23" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>65</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>22</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>7</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-07-19 12:37:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Hafnarfjordur</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Breidablik</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-07-19 12:37:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Uruguayan Primera Division</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X25" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>190</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>60</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>32</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-07-19 12:37:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Nacional Potosi</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CDT Real Oruro</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-07-19 12:37:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Defensor Sporting</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Liverpool Montevideo</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="G23" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="F27" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH27" t="n">
         <v>3.25</v>
       </c>
-      <c r="J23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="BI27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>220</v>
+      </c>
+      <c r="BM27" t="n">
         <v>4.8</v>
       </c>
-      <c r="T23" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE23" t="n">
+      <c r="BN27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>30</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BR27" t="n">
         <v>55</v>
       </c>
-      <c r="AF23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ23" t="n">
+      <c r="BS27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BX27" t="n">
         <v>60</v>
       </c>
-      <c r="AK23" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN23" t="n">
+      <c r="BY27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BZ27" t="n">
         <v>55</v>
       </c>
-      <c r="AO23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>220</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>30</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>55</v>
-      </c>
-      <c r="BS23" t="n">
+      <c r="CA27" t="n">
         <v>4.5</v>
       </c>
-      <c r="BT23" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>34</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>55</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="CB23" t="inlineStr">
-        <is>
-          <t>2026-07-19 10:24:45</t>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-07-19 12:37:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H2" t="n">
         <v>2.66</v>
       </c>
-      <c r="G2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.62</v>
-      </c>
       <c r="I2" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="J2" t="n">
         <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>1.27</v>
@@ -887,16 +887,16 @@
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R2" t="n">
         <v>1.51</v>
       </c>
       <c r="S2" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="T2" t="n">
         <v>1.62</v>
@@ -908,7 +908,7 @@
         <v>1.56</v>
       </c>
       <c r="W2" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X2" t="n">
         <v>24</v>
@@ -974,43 +974,43 @@
         <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
         <v>12.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX2" t="n">
         <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AZ2" t="n">
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BC2" t="n">
         <v>4.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
         <v>15.5</v>
@@ -1022,7 +1022,7 @@
         <v>4.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.199999999999999</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -1123,13 +1123,13 @@
         <v>1.32</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
@@ -1150,7 +1150,7 @@
         <v>1.63</v>
       </c>
       <c r="S3" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T3" t="n">
         <v>2.02</v>
@@ -1168,7 +1168,7 @@
         <v>32</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
         <v>8.800000000000001</v>
@@ -1231,7 +1231,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
         <v>11.5</v>
@@ -1243,37 +1243,37 @@
         <v>10.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA3" t="n">
         <v>6.6</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BB3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BI3" t="n">
         <v>3.7</v>
@@ -1285,46 +1285,46 @@
         <v>9.4</v>
       </c>
       <c r="BL3" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="BN3" t="n">
         <v>17</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BP3" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BV3" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX3" t="n">
         <v>25</v>
       </c>
       <c r="BY3" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -1365,40 +1365,40 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G4" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J4" t="n">
         <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R4" t="n">
         <v>1.27</v>
@@ -1410,19 +1410,19 @@
         <v>1.85</v>
       </c>
       <c r="U4" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V4" t="n">
         <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z4" t="n">
         <v>32</v>
@@ -1437,7 +1437,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE4" t="n">
         <v>60</v>
@@ -1446,7 +1446,7 @@
         <v>17</v>
       </c>
       <c r="AG4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH4" t="n">
         <v>23</v>
@@ -1473,122 +1473,122 @@
         <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AS4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB4" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BC4" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BG4" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="BI4" t="n">
         <v>2.52</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="BL4" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>4.8</v>
+        <v>2.38</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="BR4" t="n">
         <v>42</v>
       </c>
       <c r="BS4" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="BV4" t="n">
         <v>38</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="BZ4" t="n">
         <v>40</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -1646,13 +1646,13 @@
         <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P5" t="n">
         <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R5" t="n">
         <v>1.26</v>
@@ -1739,7 +1739,7 @@
         <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AU5" t="n">
         <v>7.4</v>
@@ -1751,10 +1751,10 @@
         <v>5</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AZ5" t="n">
         <v>17.5</v>
@@ -1790,16 +1790,16 @@
         <v>13.5</v>
       </c>
       <c r="BK5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BN5" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>230</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>4.9</v>
       </c>
       <c r="BO5" t="n">
         <v>3.25</v>
@@ -1808,31 +1808,31 @@
         <v>15.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BR5" t="n">
         <v>40</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BT5" t="n">
         <v>11</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BX5" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="G6" t="n">
         <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="I6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="J6" t="n">
         <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1906,13 +1906,13 @@
         <v>2.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R6" t="n">
         <v>1.46</v>
       </c>
       <c r="S6" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="T6" t="n">
         <v>1.81</v>
@@ -1921,13 +1921,13 @@
         <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="W6" t="n">
         <v>1.19</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Y6" t="n">
         <v>9.4</v>
@@ -1939,25 +1939,25 @@
         <v>16</v>
       </c>
       <c r="AB6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AC6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD6" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>10</v>
       </c>
       <c r="AE6" t="n">
         <v>17</v>
       </c>
       <c r="AF6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG6" t="n">
         <v>26</v>
       </c>
       <c r="AH6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
         <v>34</v>
@@ -1978,10 +1978,10 @@
         <v>100</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP6" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>8</v>
@@ -1993,10 +1993,10 @@
         <v>14</v>
       </c>
       <c r="AT6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AU6" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AV6" t="n">
         <v>8.800000000000001</v>
@@ -2005,40 +2005,40 @@
         <v>14.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY6" t="n">
         <v>19</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BC6" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG6" t="n">
         <v>7.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN6" t="n">
         <v>10</v>
@@ -2062,31 +2062,31 @@
         <v>50</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR6" t="n">
         <v>55</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BV6" t="n">
         <v>11</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX6" t="n">
         <v>25</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -2127,100 +2127,100 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="H7" t="n">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
         <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U7" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="n">
         <v>12.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AB7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG7" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AH7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI7" t="n">
         <v>60</v>
       </c>
-      <c r="AF7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>80</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK7" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AL7" t="n">
         <v>60</v>
@@ -2229,67 +2229,67 @@
         <v>140</v>
       </c>
       <c r="AN7" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AO7" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AP7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF7" t="n">
         <v>4.8</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BG7" t="n">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="BI7" t="n">
         <v>2.52</v>
@@ -2298,59 +2298,59 @@
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="BL7" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="BP7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BR7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BV7" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BX7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BZ7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -2635,25 +2635,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="G9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="I9" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
@@ -2665,25 +2665,25 @@
         <v>1.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
         <v>1.88</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V9" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="W9" t="n">
         <v>1.11</v>
@@ -2692,16 +2692,16 @@
         <v>16.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AB9" t="n">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="AC9" t="n">
         <v>11</v>
@@ -2713,22 +2713,22 @@
         <v>18</v>
       </c>
       <c r="AF9" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AG9" t="n">
         <v>36</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI9" t="n">
         <v>42</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AK9" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AL9" t="n">
         <v>140</v>
@@ -2737,7 +2737,7 @@
         <v>190</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AO9" t="n">
         <v>8.199999999999999</v>
@@ -2746,13 +2746,13 @@
         <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT9" t="n">
         <v>20</v>
@@ -2767,10 +2767,10 @@
         <v>14</v>
       </c>
       <c r="AX9" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ9" t="n">
         <v>21</v>
@@ -2779,86 +2779,86 @@
         <v>32</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BI9" t="n">
         <v>2.88</v>
       </c>
       <c r="BJ9" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL9" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="BN9" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.65</v>
+        <v>5.8</v>
       </c>
       <c r="BP9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="BT9" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BU9" t="n">
         <v>3</v>
       </c>
       <c r="BV9" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="BX9" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -2898,10 +2898,10 @@
         <v>1.43</v>
       </c>
       <c r="I10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="J10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K10" t="n">
         <v>5.6</v>
@@ -2928,22 +2928,22 @@
         <v>1.76</v>
       </c>
       <c r="S10" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U10" t="n">
         <v>2.32</v>
       </c>
       <c r="V10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="W10" t="n">
         <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y10" t="n">
         <v>13</v>
@@ -2952,7 +2952,7 @@
         <v>11</v>
       </c>
       <c r="AA10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AB10" t="n">
         <v>38</v>
@@ -2964,7 +2964,7 @@
         <v>10.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AF10" t="n">
         <v>80</v>
@@ -2973,10 +2973,10 @@
         <v>30</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ10" t="n">
         <v>1000</v>
@@ -2991,25 +2991,25 @@
         <v>85</v>
       </c>
       <c r="AN10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AO10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AP10" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AQ10" t="n">
         <v>11.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS10" t="n">
         <v>12</v>
       </c>
       <c r="AT10" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AU10" t="n">
         <v>11.5</v>
@@ -3024,13 +3024,13 @@
         <v>34</v>
       </c>
       <c r="AY10" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BB10" t="n">
         <v>48</v>
@@ -3042,77 +3042,77 @@
         <v>34</v>
       </c>
       <c r="BE10" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="BF10" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH10" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BI10" t="n">
         <v>3.75</v>
       </c>
       <c r="BJ10" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="BL10" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="BM10" t="n">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="BN10" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="BP10" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BQ10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>50</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT10" t="n">
         <v>4.5</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>60</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>5.1</v>
       </c>
       <c r="BU10" t="n">
         <v>3.4</v>
       </c>
       <c r="BV10" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BW10" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="BX10" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BY10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BZ10" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G11" t="n">
         <v>2.96</v>
@@ -3191,7 +3191,7 @@
         <v>2.52</v>
       </c>
       <c r="V11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W11" t="n">
         <v>1.51</v>
@@ -3206,7 +3206,7 @@
         <v>18.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB11" t="n">
         <v>15.5</v>
@@ -3218,10 +3218,10 @@
         <v>12</v>
       </c>
       <c r="AE11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
@@ -3245,7 +3245,7 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO11" t="n">
         <v>15.5</v>
@@ -3305,10 +3305,10 @@
         <v>14</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BJ11" t="n">
         <v>8.800000000000001</v>
@@ -3317,13 +3317,13 @@
         <v>6.4</v>
       </c>
       <c r="BL11" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="BM11" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO11" t="n">
         <v>5.5</v>
@@ -3332,16 +3332,16 @@
         <v>20</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="BR11" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BS11" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BU11" t="n">
         <v>5.2</v>
@@ -3350,23 +3350,23 @@
         <v>17.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX11" t="n">
         <v>26</v>
       </c>
       <c r="BY11" t="n">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>18.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -3403,13 +3403,13 @@
         <v>2.1</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I12" t="n">
         <v>4.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
         <v>3.9</v>
@@ -3559,7 +3559,7 @@
         <v>38</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BI12" t="n">
         <v>2.78</v>
@@ -3568,13 +3568,13 @@
         <v>10</v>
       </c>
       <c r="BK12" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="BL12" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN12" t="n">
         <v>5</v>
@@ -3586,16 +3586,16 @@
         <v>15</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BR12" t="n">
         <v>29</v>
       </c>
       <c r="BS12" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT12" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BU12" t="n">
         <v>5.7</v>
@@ -3604,23 +3604,23 @@
         <v>36</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX12" t="n">
         <v>55</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ12" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="CA12" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1</v>
+        <v>1.02</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="K13" t="n">
         <v>3.15</v>
@@ -3699,10 +3699,10 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="W13" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -3929,22 +3929,22 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R14" t="n">
         <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
         <v>1.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R15" t="n">
         <v>1.12</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R16" t="n">
         <v>1.12</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4700,7 @@
         <v>1.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R17" t="n">
         <v>1.12</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G18" t="n">
         <v>1.9</v>
@@ -4930,22 +4930,22 @@
         <v>4.7</v>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O18" t="n">
         <v>1.28</v>
@@ -4978,7 +4978,7 @@
         <v>18</v>
       </c>
       <c r="Y18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z18" t="n">
         <v>44</v>
@@ -4996,7 +4996,7 @@
         <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF18" t="n">
         <v>13.5</v>
@@ -5032,13 +5032,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AR18" t="n">
         <v>5.1</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT18" t="n">
         <v>8</v>
@@ -5047,13 +5047,13 @@
         <v>7.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY18" t="n">
         <v>9</v>
@@ -5062,19 +5062,19 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BC18" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BD18" t="n">
         <v>5</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF18" t="n">
         <v>8.6</v>
@@ -5083,68 +5083,68 @@
         <v>5.4</v>
       </c>
       <c r="BH18" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="BI18" t="n">
         <v>2.96</v>
       </c>
       <c r="BJ18" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="BL18" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BP18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4</v>
+        <v>9.4</v>
       </c>
       <c r="BR18" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT18" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU18" t="n">
-        <v>3.55</v>
+        <v>6.6</v>
       </c>
       <c r="BV18" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BX18" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="G19" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H19" t="n">
         <v>4.4</v>
       </c>
       <c r="I19" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J19" t="n">
         <v>3.6</v>
@@ -5337,25 +5337,25 @@
         <v>5.2</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="BI19" t="n">
         <v>2.82</v>
       </c>
       <c r="BJ19" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="BL19" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="BN19" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BO19" t="n">
         <v>3.65</v>
@@ -5364,41 +5364,41 @@
         <v>15</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BR19" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BT19" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV19" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BX19" t="n">
         <v>60</v>
       </c>
       <c r="BY19" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ19" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -5429,230 +5429,230 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.32</v>
+        <v>1.72</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>1.82</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1.08</v>
+        <v>3.85</v>
       </c>
       <c r="K20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT20" t="n">
         <v>4.4</v>
       </c>
-      <c r="L20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
         <v>3.65</v>
       </c>
       <c r="T21" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U21" t="n">
         <v>2.06</v>
@@ -5845,7 +5845,7 @@
         <v>5.1</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="BI21" t="n">
         <v>2.72</v>
@@ -5857,10 +5857,10 @@
         <v>7.8</v>
       </c>
       <c r="BL21" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BN21" t="n">
         <v>5</v>
@@ -5878,10 +5878,10 @@
         <v>32</v>
       </c>
       <c r="BS21" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BU21" t="n">
         <v>6</v>
@@ -5890,23 +5890,23 @@
         <v>36</v>
       </c>
       <c r="BW21" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BX21" t="n">
         <v>50</v>
       </c>
       <c r="BY21" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ21" t="n">
         <v>29</v>
       </c>
       <c r="CA21" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -6057,22 +6057,22 @@
         <v>4.4</v>
       </c>
       <c r="AT22" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AW22" t="n">
         <v>4.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY22" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
         <v>11.5</v>
@@ -6081,13 +6081,13 @@
         <v>4.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BC22" t="n">
         <v>11</v>
       </c>
       <c r="BD22" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BE22" t="n">
         <v>4.2</v>
@@ -6096,7 +6096,7 @@
         <v>4.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BH22" t="n">
         <v>5.8</v>
@@ -6105,19 +6105,19 @@
         <v>4.3</v>
       </c>
       <c r="BJ22" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BK22" t="n">
         <v>6.6</v>
       </c>
       <c r="BL22" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BN22" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO22" t="n">
         <v>4.6</v>
@@ -6132,7 +6132,7 @@
         <v>21</v>
       </c>
       <c r="BS22" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="BT22" t="n">
         <v>11</v>
@@ -6144,23 +6144,23 @@
         <v>36</v>
       </c>
       <c r="BW22" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BX22" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BZ22" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="CA22" t="n">
         <v>7.4</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
         <v>2.38</v>
       </c>
       <c r="G23" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="H23" t="n">
         <v>2.7</v>
@@ -6203,16 +6203,16 @@
         <v>2.86</v>
       </c>
       <c r="J23" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K23" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L23" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="M23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N23" t="n">
         <v>6.8</v>
@@ -6221,28 +6221,28 @@
         <v>1.14</v>
       </c>
       <c r="P23" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
         <v>1.43</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S23" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T23" t="n">
         <v>1.44</v>
       </c>
       <c r="U23" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="V23" t="n">
         <v>1.53</v>
       </c>
       <c r="W23" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="X23" t="n">
         <v>40</v>
@@ -6254,7 +6254,7 @@
         <v>29</v>
       </c>
       <c r="AA23" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB23" t="n">
         <v>23</v>
@@ -6272,7 +6272,7 @@
         <v>26</v>
       </c>
       <c r="AG23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH23" t="n">
         <v>16.5</v>
@@ -6299,7 +6299,7 @@
         <v>14</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.05</v>
+        <v>4.6</v>
       </c>
       <c r="AQ23" t="n">
         <v>16</v>
@@ -6308,7 +6308,7 @@
         <v>19</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT23" t="n">
         <v>15</v>
@@ -6335,7 +6335,7 @@
         <v>20</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.05</v>
+        <v>4.6</v>
       </c>
       <c r="BC23" t="n">
         <v>17</v>
@@ -6344,7 +6344,7 @@
         <v>19.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF23" t="n">
         <v>8</v>
@@ -6353,19 +6353,19 @@
         <v>9.4</v>
       </c>
       <c r="BH23" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BI23" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BJ23" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BL23" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM23" t="n">
         <v>8.800000000000001</v>
@@ -6374,7 +6374,7 @@
         <v>6.4</v>
       </c>
       <c r="BO23" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BP23" t="n">
         <v>16</v>
@@ -6383,38 +6383,38 @@
         <v>6.2</v>
       </c>
       <c r="BR23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BS23" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BT23" t="n">
         <v>6.8</v>
       </c>
       <c r="BU23" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BW23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX23" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BY23" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BZ23" t="n">
         <v>12.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
         <v>5.7</v>
       </c>
       <c r="J25" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K25" t="n">
         <v>3.8</v>
@@ -6861,22 +6861,22 @@
         <v>5.1</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="BI25" t="n">
         <v>2.62</v>
       </c>
       <c r="BJ25" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BK25" t="n">
         <v>8.4</v>
       </c>
       <c r="BL25" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BN25" t="n">
         <v>4.4</v>
@@ -6885,7 +6885,7 @@
         <v>3.8</v>
       </c>
       <c r="BP25" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ25" t="n">
         <v>10</v>
@@ -6894,7 +6894,7 @@
         <v>36</v>
       </c>
       <c r="BS25" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BT25" t="n">
         <v>8.6</v>
@@ -6906,23 +6906,23 @@
         <v>60</v>
       </c>
       <c r="BW25" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BX25" t="n">
         <v>65</v>
       </c>
       <c r="BY25" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BZ25" t="n">
         <v>32</v>
       </c>
       <c r="CA25" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -6953,220 +6953,220 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="G26" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="J26" t="n">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M26" t="n">
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="P26" t="n">
-        <v>1.4</v>
+        <v>2.84</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="S26" t="n">
-        <v>1.09</v>
+        <v>1.9</v>
       </c>
       <c r="T26" t="n">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="U26" t="n">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH26" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BN26" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BP26" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR26" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BT26" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX26" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G27" t="n">
         <v>3.05</v>
       </c>
       <c r="H27" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="I27" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J27" t="n">
         <v>3.05</v>
       </c>
       <c r="K27" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L27" t="n">
         <v>1.53</v>
@@ -7369,7 +7369,7 @@
         <v>4.1</v>
       </c>
       <c r="BH27" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="BI27" t="n">
         <v>2.3</v>
@@ -7378,16 +7378,16 @@
         <v>13</v>
       </c>
       <c r="BK27" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="BL27" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN27" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BO27" t="n">
         <v>4.3</v>
@@ -7396,16 +7396,16 @@
         <v>30</v>
       </c>
       <c r="BQ27" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR27" t="n">
         <v>55</v>
       </c>
       <c r="BS27" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="BT27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BU27" t="n">
         <v>4.4</v>
@@ -7414,23 +7414,23 @@
         <v>32</v>
       </c>
       <c r="BW27" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX27" t="n">
         <v>60</v>
       </c>
       <c r="BY27" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="BZ27" t="n">
         <v>55</v>
       </c>
       <c r="CA27" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-19 12:37:19</t>
+          <t>2026-07-19 14:48:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G2" t="n">
         <v>2.78</v>
@@ -866,43 +866,43 @@
         <v>2.66</v>
       </c>
       <c r="I2" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q2" t="n">
         <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S2" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U2" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V2" t="n">
         <v>1.56</v>
@@ -983,16 +983,16 @@
         <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX2" t="n">
         <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
         <v>13</v>
@@ -1022,7 +1022,7 @@
         <v>4.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.199999999999999</v>
@@ -1064,7 +1064,7 @@
         <v>19.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BX2" t="n">
         <v>29</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="H3" t="n">
         <v>1.27</v>
@@ -1135,19 +1135,19 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q3" t="n">
         <v>1.53</v>
       </c>
       <c r="R3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S3" t="n">
         <v>2.32</v>
@@ -1162,13 +1162,13 @@
         <v>4.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
         <v>32</v>
       </c>
       <c r="Y3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
         <v>8.800000000000001</v>
@@ -1216,7 +1216,7 @@
         <v>280</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AP3" t="n">
         <v>21</v>
@@ -1231,7 +1231,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU3" t="n">
         <v>11.5</v>
@@ -1243,31 +1243,31 @@
         <v>10.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG3" t="n">
         <v>3.8</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -1365,49 +1365,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G4" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H4" t="n">
         <v>3.45</v>
       </c>
       <c r="I4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
         <v>2.12</v>
       </c>
       <c r="R4" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U4" t="n">
         <v>1.97</v>
@@ -1419,10 +1419,10 @@
         <v>1.7</v>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="Z4" t="n">
         <v>32</v>
@@ -1431,10 +1431,10 @@
         <v>90</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
         <v>18.5</v>
@@ -1473,58 +1473,58 @@
         <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AQ4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX4" t="n">
         <v>3.4</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AY4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA4" t="n">
         <v>4</v>
       </c>
-      <c r="AS4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV4" t="n">
+      <c r="BB4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF4" t="n">
         <v>3.7</v>
       </c>
-      <c r="AW4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BG4" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
@@ -1536,59 +1536,59 @@
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.38</v>
+        <v>4.1</v>
       </c>
       <c r="BN4" t="n">
         <v>5.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BP4" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BR4" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.8</v>
+        <v>3.8</v>
       </c>
       <c r="BT4" t="n">
         <v>7</v>
       </c>
       <c r="BU4" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BV4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.8</v>
+        <v>3.8</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8</v>
+        <v>3.85</v>
       </c>
       <c r="BZ4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.8</v>
+        <v>3.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="G5" t="n">
         <v>1.84</v>
@@ -1634,10 +1634,10 @@
         <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
@@ -1646,13 +1646,13 @@
         <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
         <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.26</v>
@@ -1664,7 +1664,7 @@
         <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V5" t="n">
         <v>1.18</v>
@@ -1688,7 +1688,7 @@
         <v>7.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
         <v>29</v>
@@ -1733,10 +1733,10 @@
         <v>12</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT5" t="n">
         <v>6.2</v>
@@ -1769,16 +1769,16 @@
         <v>15.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF5" t="n">
         <v>11</v>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH5" t="n">
         <v>3.1</v>
@@ -1790,7 +1790,7 @@
         <v>13.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1814,13 +1814,13 @@
         <v>40</v>
       </c>
       <c r="BS5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT5" t="n">
         <v>11</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -1873,64 +1873,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="I6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="J6" t="n">
         <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="T6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.19</v>
       </c>
       <c r="X6" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z6" t="n">
         <v>10.5</v>
@@ -1978,13 +1978,13 @@
         <v>100</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP6" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR6" t="n">
         <v>9.199999999999999</v>
@@ -1996,25 +1996,25 @@
         <v>18</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW6" t="n">
         <v>14.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB6" t="n">
         <v>10</v>
@@ -2023,16 +2023,16 @@
         <v>9.4</v>
       </c>
       <c r="BD6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE6" t="n">
         <v>9.6</v>
       </c>
-      <c r="BE6" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BF6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH6" t="n">
         <v>3.95</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN6" t="n">
         <v>10</v>
@@ -2068,7 +2068,7 @@
         <v>55</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT6" t="n">
         <v>4.4</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>2.76</v>
       </c>
       <c r="I7" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J7" t="n">
         <v>3.1</v>
@@ -2145,13 +2145,13 @@
         <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.38</v>
@@ -2175,7 +2175,7 @@
         <v>1.99</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
         <v>1.5</v>
@@ -2196,7 +2196,7 @@
         <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7" t="n">
         <v>13.5</v>
@@ -2220,7 +2220,7 @@
         <v>55</v>
       </c>
       <c r="AK7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL7" t="n">
         <v>60</v>
@@ -2274,16 +2274,16 @@
         <v>30</v>
       </c>
       <c r="BC7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BD7" t="n">
         <v>34</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BG7" t="n">
         <v>26</v>
@@ -2304,7 +2304,7 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN7" t="n">
         <v>5.9</v>
@@ -2313,7 +2313,7 @@
         <v>4.9</v>
       </c>
       <c r="BP7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ7" t="n">
         <v>7</v>
@@ -2322,7 +2322,7 @@
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT7" t="n">
         <v>6.2</v>
@@ -2334,13 +2334,13 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -2677,10 +2677,10 @@
         <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V9" t="n">
         <v>3</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H10" t="n">
         <v>1.43</v>
@@ -2913,28 +2913,28 @@
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="O10" t="n">
         <v>1.16</v>
       </c>
       <c r="P10" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="R10" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="S10" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="U10" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V10" t="n">
         <v>3.25</v>
@@ -2943,22 +2943,22 @@
         <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA10" t="n">
         <v>13</v>
       </c>
       <c r="AB10" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AC10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD10" t="n">
         <v>10.5</v>
@@ -2991,34 +2991,34 @@
         <v>85</v>
       </c>
       <c r="AN10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO10" t="n">
         <v>4.6</v>
       </c>
       <c r="AP10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
         <v>12</v>
       </c>
       <c r="AT10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AU10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV10" t="n">
         <v>9.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX10" t="n">
         <v>34</v>
@@ -3030,7 +3030,7 @@
         <v>18.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB10" t="n">
         <v>48</v>
@@ -3039,22 +3039,22 @@
         <v>36</v>
       </c>
       <c r="BD10" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE10" t="n">
         <v>34</v>
       </c>
-      <c r="BE10" t="n">
-        <v>70</v>
-      </c>
       <c r="BF10" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH10" t="n">
         <v>5</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="G11" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I11" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
         <v>1.33</v>
@@ -3173,7 +3173,7 @@
         <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
         <v>1.7</v>
@@ -3185,16 +3185,16 @@
         <v>2.74</v>
       </c>
       <c r="T11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U11" t="n">
         <v>2.52</v>
       </c>
       <c r="V11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
         <v>20</v>
@@ -3203,7 +3203,7 @@
         <v>14</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
         <v>36</v>
@@ -3215,10 +3215,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF11" t="n">
         <v>22</v>
@@ -3227,13 +3227,13 @@
         <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
         <v>32</v>
       </c>
       <c r="AJ11" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK11" t="n">
         <v>29</v>
@@ -3245,7 +3245,7 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO11" t="n">
         <v>15.5</v>
@@ -3278,7 +3278,7 @@
         <v>20</v>
       </c>
       <c r="AY11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>13.5</v>
@@ -3287,10 +3287,10 @@
         <v>28</v>
       </c>
       <c r="BB11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BC11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD11" t="n">
         <v>30</v>
@@ -3299,7 +3299,7 @@
         <v>50</v>
       </c>
       <c r="BF11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BG11" t="n">
         <v>14</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G12" t="n">
         <v>2.1</v>
       </c>
       <c r="H12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I12" t="n">
         <v>4.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K12" t="n">
         <v>3.9</v>
@@ -3427,7 +3427,7 @@
         <v>1.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q12" t="n">
         <v>1.89</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.14</v>
+        <v>1.53</v>
       </c>
       <c r="G13" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.02</v>
+        <v>2.24</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="K13" t="n">
         <v>3.15</v>
@@ -3699,10 +3699,10 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3929,13 +3929,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
         <v>1.02</v>
       </c>
       <c r="P14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
         <v>1.02</v>
@@ -3944,7 +3944,7 @@
         <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -3953,10 +3953,10 @@
         <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -4159,19 +4159,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4207,10 +4207,10 @@
         <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4413,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G16" t="n">
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4461,10 +4461,10 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -4667,19 +4667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G17" t="n">
         <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4715,10 +4715,10 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
         <v>4.7</v>
       </c>
       <c r="I18" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J18" t="n">
         <v>3.7</v>
@@ -4939,13 +4939,13 @@
         <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
         <v>1.28</v>
@@ -4966,7 +4966,7 @@
         <v>1.79</v>
       </c>
       <c r="U18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V18" t="n">
         <v>1.25</v>
@@ -4996,7 +4996,7 @@
         <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF18" t="n">
         <v>13.5</v>
@@ -5086,7 +5086,7 @@
         <v>3.75</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BJ18" t="n">
         <v>10.5</v>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN18" t="n">
         <v>4.7</v>
@@ -5107,7 +5107,7 @@
         <v>3.9</v>
       </c>
       <c r="BP18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ18" t="n">
         <v>9.4</v>
@@ -5116,7 +5116,7 @@
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT18" t="n">
         <v>8.800000000000001</v>
@@ -5128,13 +5128,13 @@
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ18" t="n">
         <v>22</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="G19" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="H19" t="n">
         <v>4.4</v>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
         <v>1.4</v>
@@ -5199,7 +5199,7 @@
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O19" t="n">
         <v>1.32</v>
@@ -5208,25 +5208,25 @@
         <v>1.89</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S19" t="n">
         <v>3.45</v>
       </c>
       <c r="T19" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U19" t="n">
         <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X19" t="n">
         <v>16.5</v>
@@ -5253,7 +5253,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
         <v>10.5</v>
@@ -5286,13 +5286,13 @@
         <v>12</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT19" t="n">
         <v>7.6</v>
@@ -5304,7 +5304,7 @@
         <v>16</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX19" t="n">
         <v>9.800000000000001</v>
@@ -5313,28 +5313,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB19" t="n">
         <v>17.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF19" t="n">
         <v>10.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH19" t="n">
         <v>3.5</v>
@@ -5346,59 +5346,59 @@
         <v>10.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO19" t="n">
         <v>3.65</v>
       </c>
       <c r="BP19" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT19" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BX19" t="n">
         <v>60</v>
       </c>
       <c r="BY19" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
         <v>25</v>
       </c>
       <c r="CA19" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -5435,49 +5435,49 @@
         <v>1.82</v>
       </c>
       <c r="H20" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="I20" t="n">
         <v>5.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="K20" t="n">
-        <v>5.4</v>
+        <v>29</v>
       </c>
       <c r="L20" t="n">
         <v>1.2</v>
       </c>
       <c r="M20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>2.92</v>
+        <v>1.1</v>
       </c>
       <c r="O20" t="n">
         <v>1.15</v>
       </c>
       <c r="P20" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="R20" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>1.97</v>
+        <v>1.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U20" t="n">
         <v>2.6</v>
       </c>
       <c r="V20" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W20" t="n">
         <v>2.2</v>
@@ -5486,7 +5486,7 @@
         <v>42</v>
       </c>
       <c r="Y20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z20" t="n">
         <v>55</v>
@@ -5495,34 +5495,34 @@
         <v>110</v>
       </c>
       <c r="AB20" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AC20" t="n">
         <v>14.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE20" t="n">
         <v>55</v>
       </c>
       <c r="AF20" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AG20" t="n">
         <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AI20" t="n">
         <v>48</v>
       </c>
       <c r="AJ20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL20" t="n">
         <v>27</v>
@@ -5537,58 +5537,58 @@
         <v>34</v>
       </c>
       <c r="AP20" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG20" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>5.1</v>
       </c>
       <c r="BH20" t="n">
         <v>5.5</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -5683,19 +5683,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="H21" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
         <v>3.65</v>
@@ -5707,7 +5707,7 @@
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O21" t="n">
         <v>1.35</v>
@@ -5731,10 +5731,10 @@
         <v>2.06</v>
       </c>
       <c r="V21" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="X21" t="n">
         <v>15.5</v>
@@ -5761,10 +5761,10 @@
         <v>60</v>
       </c>
       <c r="AF21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH21" t="n">
         <v>22</v>
@@ -5797,10 +5797,10 @@
         <v>12</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT21" t="n">
         <v>7.8</v>
@@ -5812,7 +5812,7 @@
         <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX21" t="n">
         <v>11.5</v>
@@ -5824,25 +5824,25 @@
         <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC21" t="n">
         <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF21" t="n">
         <v>14</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH21" t="n">
         <v>3.3</v>
@@ -5851,7 +5851,7 @@
         <v>2.72</v>
       </c>
       <c r="BJ21" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK21" t="n">
         <v>7.8</v>
@@ -5860,10 +5860,10 @@
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO21" t="n">
         <v>4.4</v>
@@ -5878,35 +5878,35 @@
         <v>32</v>
       </c>
       <c r="BS21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU21" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BV21" t="n">
         <v>36</v>
       </c>
       <c r="BW21" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX21" t="n">
         <v>50</v>
       </c>
       <c r="BY21" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ21" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
         <v>3.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R22" t="n">
         <v>1.94</v>
@@ -6075,7 +6075,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA22" t="n">
         <v>4.2</v>
@@ -6084,7 +6084,7 @@
         <v>17</v>
       </c>
       <c r="BC22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD22" t="n">
         <v>18</v>
@@ -6102,7 +6102,7 @@
         <v>5.8</v>
       </c>
       <c r="BI22" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BJ22" t="n">
         <v>9</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
         <v>2.38</v>
       </c>
       <c r="G23" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="H23" t="n">
         <v>2.7</v>
@@ -6206,10 +6206,10 @@
         <v>4.1</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M23" t="n">
         <v>1.03</v>
@@ -6230,7 +6230,7 @@
         <v>1.81</v>
       </c>
       <c r="S23" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T23" t="n">
         <v>1.44</v>
@@ -6239,13 +6239,13 @@
         <v>2.94</v>
       </c>
       <c r="V23" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W23" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="X23" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y23" t="n">
         <v>25</v>
@@ -6344,7 +6344,7 @@
         <v>19.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF23" t="n">
         <v>8</v>
@@ -6362,31 +6362,31 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK23" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN23" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO23" t="n">
         <v>4.9</v>
       </c>
       <c r="BP23" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR23" t="n">
         <v>24</v>
       </c>
       <c r="BS23" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT23" t="n">
         <v>6.8</v>
@@ -6398,23 +6398,23 @@
         <v>21</v>
       </c>
       <c r="BW23" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX23" t="n">
         <v>26</v>
       </c>
       <c r="BY23" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ23" t="n">
         <v>12.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -6469,34 +6469,34 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>1.25</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
         <v>1.08</v>
       </c>
       <c r="P24" t="n">
-        <v>1.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>1.08</v>
+        <v>1.84</v>
       </c>
       <c r="T24" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="U24" t="n">
         <v>1.11</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
         <v>5.7</v>
       </c>
       <c r="J25" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K25" t="n">
         <v>3.8</v>
@@ -6774,7 +6774,7 @@
         <v>24</v>
       </c>
       <c r="AE25" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF25" t="n">
         <v>12.5</v>
@@ -6813,7 +6813,7 @@
         <v>12</v>
       </c>
       <c r="AR25" t="n">
-        <v>32</v>
+        <v>4.7</v>
       </c>
       <c r="AS25" t="n">
         <v>5.1</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -6953,46 +6953,46 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="G26" t="n">
-        <v>1.57</v>
+        <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>5.3</v>
+        <v>1.23</v>
       </c>
       <c r="I26" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>4.4</v>
+        <v>1.02</v>
       </c>
       <c r="K26" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.1</v>
+        <v>1.56</v>
       </c>
       <c r="O26" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="P26" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="R26" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="S26" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="T26" t="n">
         <v>1.55</v>
@@ -7004,10 +7004,10 @@
         <v>1.13</v>
       </c>
       <c r="W26" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="X26" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
         <v>46</v>
@@ -7016,13 +7016,13 @@
         <v>80</v>
       </c>
       <c r="AA26" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AC26" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AD26" t="n">
         <v>32</v>
@@ -7031,13 +7031,13 @@
         <v>85</v>
       </c>
       <c r="AF26" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI26" t="n">
         <v>70</v>
@@ -7046,7 +7046,7 @@
         <v>18.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL26" t="n">
         <v>29</v>
@@ -7058,61 +7058,61 @@
         <v>5.1</v>
       </c>
       <c r="AO26" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP26" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="AS26" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="AT26" t="n">
-        <v>4</v>
+        <v>2.78</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.85</v>
+        <v>2.74</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.4</v>
+        <v>2.96</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="AX26" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="AY26" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.2</v>
+        <v>2.86</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="BB26" t="n">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="BC26" t="n">
-        <v>3.85</v>
+        <v>2.74</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.4</v>
+        <v>2.92</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="BF26" t="n">
-        <v>2.58</v>
+        <v>1.99</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="BH26" t="n">
         <v>5.8</v>
@@ -7124,7 +7124,7 @@
         <v>10</v>
       </c>
       <c r="BK26" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
@@ -7142,7 +7142,7 @@
         <v>9</v>
       </c>
       <c r="BQ26" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR26" t="n">
         <v>18</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G27" t="n">
         <v>3.05</v>
@@ -7372,19 +7372,19 @@
         <v>2.88</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="BJ27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BK27" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BN27" t="n">
         <v>5.8</v>
@@ -7393,16 +7393,16 @@
         <v>4.3</v>
       </c>
       <c r="BP27" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BR27" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BT27" t="n">
         <v>6</v>
@@ -7411,26 +7411,26 @@
         <v>4.4</v>
       </c>
       <c r="BV27" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BX27" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BZ27" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-19 14:48:40</t>
+          <t>2026-07-19 16:59:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G2" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H2" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I2" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="J2" t="n">
         <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>1.32</v>
@@ -881,103 +881,103 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S2" t="n">
         <v>2.78</v>
       </c>
       <c r="T2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U2" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V2" t="n">
         <v>1.56</v>
       </c>
       <c r="W2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR2" t="n">
         <v>17.5</v>
       </c>
-      <c r="AC2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>26</v>
       </c>
       <c r="AT2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU2" t="n">
         <v>8</v>
@@ -986,7 +986,7 @@
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX2" t="n">
         <v>17</v>
@@ -998,25 +998,25 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.8</v>
+        <v>24</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.6</v>
+        <v>19</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.7</v>
+        <v>24</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="BF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG2" t="n">
         <v>15.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>15</v>
       </c>
       <c r="BH2" t="n">
         <v>4.1</v>
@@ -1064,7 +1064,7 @@
         <v>19.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="BX2" t="n">
         <v>29</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>1.27</v>
       </c>
       <c r="I3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="J3" t="n">
         <v>6.2</v>
@@ -1129,7 +1129,7 @@
         <v>7.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
@@ -1162,7 +1162,7 @@
         <v>4.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
         <v>32</v>
@@ -1177,7 +1177,7 @@
         <v>10.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AC3" t="n">
         <v>17.5</v>
@@ -1186,10 +1186,10 @@
         <v>13</v>
       </c>
       <c r="AE3" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="AG3" t="n">
         <v>55</v>
@@ -1207,10 +1207,10 @@
         <v>230</v>
       </c>
       <c r="AL3" t="n">
-        <v>170</v>
+        <v>460</v>
       </c>
       <c r="AM3" t="n">
-        <v>180</v>
+        <v>380</v>
       </c>
       <c r="AN3" t="n">
         <v>280</v>
@@ -1231,7 +1231,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU3" t="n">
         <v>11.5</v>
@@ -1243,31 +1243,31 @@
         <v>10.5</v>
       </c>
       <c r="AX3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AY3" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="BG3" t="n">
         <v>3.8</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -1371,46 +1371,46 @@
         <v>2.42</v>
       </c>
       <c r="H4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.38</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
         <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="U4" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
         <v>1.33</v>
@@ -1419,118 +1419,118 @@
         <v>1.7</v>
       </c>
       <c r="X4" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
         <v>32</v>
       </c>
       <c r="AA4" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
         <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AJ4" t="n">
         <v>38</v>
       </c>
       <c r="AK4" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AL4" t="n">
         <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.92</v>
+        <v>4.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AW4" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="AY4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH4" t="n">
         <v>3.25</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BI4" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BN4" t="n">
         <v>5.2</v>
@@ -1551,16 +1551,16 @@
         <v>3.55</v>
       </c>
       <c r="BP4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BT4" t="n">
         <v>7</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
         <v>60</v>
       </c>
       <c r="AA5" t="n">
-        <v>220</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
         <v>7.2</v>
@@ -1694,7 +1694,7 @@
         <v>29</v>
       </c>
       <c r="AE5" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AF5" t="n">
         <v>12</v>
@@ -1706,7 +1706,7 @@
         <v>29</v>
       </c>
       <c r="AI5" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AJ5" t="n">
         <v>23</v>
@@ -1718,13 +1718,13 @@
         <v>60</v>
       </c>
       <c r="AM5" t="n">
-        <v>210</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
         <v>18.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AP5" t="n">
         <v>8.4</v>
@@ -1733,7 +1733,7 @@
         <v>12</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS5" t="n">
         <v>5.1</v>
@@ -1769,7 +1769,7 @@
         <v>15.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE5" t="n">
         <v>5.1</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="I6" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
         <v>4.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1903,25 +1903,25 @@
         <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q6" t="n">
         <v>1.76</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
         <v>2.94</v>
       </c>
       <c r="T6" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U6" t="n">
         <v>2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="W6" t="n">
         <v>1.19</v>
@@ -1942,7 +1942,7 @@
         <v>24</v>
       </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
         <v>10.5</v>
@@ -1954,7 +1954,7 @@
         <v>55</v>
       </c>
       <c r="AG6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AH6" t="n">
         <v>23</v>
@@ -1963,22 +1963,22 @@
         <v>34</v>
       </c>
       <c r="AJ6" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AK6" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AL6" t="n">
         <v>80</v>
       </c>
       <c r="AM6" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
         <v>100</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AP6" t="n">
         <v>15.5</v>
@@ -1990,7 +1990,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AT6" t="n">
         <v>18</v>
@@ -1999,7 +1999,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW6" t="n">
         <v>14.5</v>
@@ -2011,10 +2011,10 @@
         <v>18.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BB6" t="n">
         <v>10</v>
@@ -2023,13 +2023,13 @@
         <v>9.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG6" t="n">
         <v>7.4</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G7" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="H7" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I7" t="n">
         <v>3.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
         <v>1.5</v>
@@ -2151,13 +2151,13 @@
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q7" t="n">
         <v>2.2</v>
@@ -2178,13 +2178,13 @@
         <v>1.47</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X7" t="n">
         <v>14</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z7" t="n">
         <v>20</v>
@@ -2208,25 +2208,25 @@
         <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI7" t="n">
         <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AK7" t="n">
         <v>40</v>
       </c>
       <c r="AL7" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AM7" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
         <v>38</v>
@@ -2247,7 +2247,7 @@
         <v>36</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU7" t="n">
         <v>6.4</v>
@@ -2271,19 +2271,19 @@
         <v>36</v>
       </c>
       <c r="BB7" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="BD7" t="n">
         <v>34</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.1</v>
+        <v>20</v>
       </c>
       <c r="BG7" t="n">
         <v>26</v>
@@ -2298,13 +2298,13 @@
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN7" t="n">
         <v>5.9</v>
@@ -2313,7 +2313,7 @@
         <v>4.9</v>
       </c>
       <c r="BP7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ7" t="n">
         <v>7</v>
@@ -2322,7 +2322,7 @@
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT7" t="n">
         <v>6.2</v>
@@ -2334,13 +2334,13 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2405,13 +2405,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
         <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q8" t="n">
         <v>1.35</v>
@@ -2429,7 +2429,7 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
         <v>9.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="I9" t="n">
         <v>1.5</v>
@@ -2665,13 +2665,13 @@
         <v>1.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q9" t="n">
         <v>1.88</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
         <v>3.25</v>
@@ -2710,7 +2710,7 @@
         <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF9" t="n">
         <v>95</v>
@@ -2767,7 +2767,7 @@
         <v>14</v>
       </c>
       <c r="AX9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY9" t="n">
         <v>7.6</v>
@@ -2779,16 +2779,16 @@
         <v>32</v>
       </c>
       <c r="BB9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC9" t="n">
         <v>9.4</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BD9" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BD9" t="n">
-        <v>9</v>
-      </c>
       <c r="BE9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF9" t="n">
         <v>9.4</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="H10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I10" t="n">
         <v>1.43</v>
       </c>
-      <c r="I10" t="n">
-        <v>1.44</v>
-      </c>
       <c r="J10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L10" t="n">
         <v>1.25</v>
@@ -2916,19 +2916,19 @@
         <v>7</v>
       </c>
       <c r="O10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P10" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R10" t="n">
         <v>1.8</v>
       </c>
       <c r="S10" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T10" t="n">
         <v>1.7</v>
@@ -2937,7 +2937,7 @@
         <v>2.34</v>
       </c>
       <c r="V10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="W10" t="n">
         <v>1.13</v>
@@ -2946,7 +2946,7 @@
         <v>32</v>
       </c>
       <c r="Y10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z10" t="n">
         <v>11.5</v>
@@ -2991,16 +2991,16 @@
         <v>85</v>
       </c>
       <c r="AN10" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AO10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AP10" t="n">
         <v>27</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR10" t="n">
         <v>10</v>
@@ -3009,7 +3009,7 @@
         <v>12</v>
       </c>
       <c r="AT10" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AU10" t="n">
         <v>12</v>
@@ -3048,7 +3048,7 @@
         <v>34</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH10" t="n">
         <v>5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="G11" t="n">
         <v>2.9</v>
       </c>
       <c r="H11" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J11" t="n">
         <v>3.8</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L11" t="n">
         <v>1.33</v>
@@ -3176,13 +3176,13 @@
         <v>2.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R11" t="n">
         <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T11" t="n">
         <v>1.6</v>
@@ -3191,19 +3191,19 @@
         <v>2.52</v>
       </c>
       <c r="V11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W11" t="n">
         <v>1.52</v>
       </c>
       <c r="X11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="n">
         <v>14</v>
       </c>
       <c r="Z11" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA11" t="n">
         <v>36</v>
@@ -3212,10 +3212,10 @@
         <v>15.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
         <v>25</v>
@@ -3242,13 +3242,13 @@
         <v>36</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN11" t="n">
         <v>19.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AP11" t="n">
         <v>17.5</v>
@@ -3257,25 +3257,25 @@
         <v>12.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS11" t="n">
         <v>30</v>
       </c>
       <c r="AT11" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU11" t="n">
         <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW11" t="n">
         <v>21</v>
       </c>
       <c r="AX11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AY11" t="n">
         <v>11.5</v>
@@ -3287,7 +3287,7 @@
         <v>28</v>
       </c>
       <c r="BB11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC11" t="n">
         <v>25</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G12" t="n">
         <v>2.1</v>
@@ -3412,28 +3412,28 @@
         <v>3.65</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
         <v>1.38</v>
       </c>
       <c r="M12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O12" t="n">
         <v>1.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
         <v>1.89</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
         <v>3.3</v>
@@ -3442,7 +3442,7 @@
         <v>1.76</v>
       </c>
       <c r="U12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V12" t="n">
         <v>1.3</v>
@@ -3502,7 +3502,7 @@
         <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP12" t="n">
         <v>12.5</v>
@@ -3511,10 +3511,10 @@
         <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
         <v>8.199999999999999</v>
@@ -3526,7 +3526,7 @@
         <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -3547,7 +3547,7 @@
         <v>18</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE12" t="n">
         <v>7</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="H13" t="n">
-        <v>2.24</v>
+        <v>3.5</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.85</v>
+        <v>2.46</v>
       </c>
       <c r="K13" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3675,13 +3675,13 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="O13" t="n">
         <v>1.01</v>
       </c>
       <c r="P13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Q13" t="n">
         <v>1.55</v>
@@ -3699,10 +3699,10 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="W13" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3717,10 +3717,10 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD13" t="n">
         <v>1000</v>
@@ -3729,10 +3729,10 @@
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH13" t="n">
         <v>1000</v>
@@ -3741,76 +3741,76 @@
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.02</v>
+        <v>2.08</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.02</v>
+        <v>2.08</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3932,7 +3932,7 @@
         <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P14" t="n">
         <v>1.25</v>
@@ -3953,118 +3953,118 @@
         <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.02</v>
+        <v>2.14</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.02</v>
+        <v>2.06</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -4207,118 +4207,118 @@
         <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="G17" t="n">
         <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>1.02</v>
+        <v>2.1</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4715,13 +4715,13 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y17" t="n">
         <v>1000</v>
@@ -4778,55 +4778,55 @@
         <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -4975,16 +4975,16 @@
         <v>2.1</v>
       </c>
       <c r="X18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y18" t="n">
         <v>20</v>
       </c>
       <c r="Z18" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="AA18" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AB18" t="n">
         <v>11</v>
@@ -4993,40 +4993,40 @@
         <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AF18" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG18" t="n">
         <v>10</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AJ18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL18" t="n">
         <v>38</v>
       </c>
       <c r="AM18" t="n">
-        <v>120</v>
+        <v>320</v>
       </c>
       <c r="AN18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO18" t="n">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="AP18" t="n">
         <v>13.5</v>
@@ -5035,10 +5035,10 @@
         <v>13.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT18" t="n">
         <v>8</v>
@@ -5050,7 +5050,7 @@
         <v>14.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
@@ -5062,7 +5062,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BB18" t="n">
         <v>15</v>
@@ -5071,16 +5071,16 @@
         <v>14.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF18" t="n">
         <v>8.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="BH18" t="n">
         <v>3.75</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G19" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H19" t="n">
         <v>4.4</v>
@@ -5199,13 +5199,13 @@
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
         <v>1.32</v>
       </c>
       <c r="P19" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q19" t="n">
         <v>1.95</v>
@@ -5220,28 +5220,28 @@
         <v>1.84</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V19" t="n">
         <v>1.25</v>
       </c>
       <c r="W19" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X19" t="n">
         <v>16.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z19" t="n">
         <v>42</v>
       </c>
       <c r="AA19" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC19" t="n">
         <v>9.800000000000001</v>
@@ -5250,7 +5250,7 @@
         <v>22</v>
       </c>
       <c r="AE19" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF19" t="n">
         <v>13</v>
@@ -5259,28 +5259,28 @@
         <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AJ19" t="n">
         <v>24</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="n">
         <v>44</v>
       </c>
       <c r="AM19" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO19" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
         <v>12</v>
@@ -5289,10 +5289,10 @@
         <v>12.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT19" t="n">
         <v>7.6</v>
@@ -5304,7 +5304,7 @@
         <v>16</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AX19" t="n">
         <v>9.800000000000001</v>
@@ -5316,7 +5316,7 @@
         <v>17</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BB19" t="n">
         <v>17.5</v>
@@ -5325,16 +5325,16 @@
         <v>15.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BF19" t="n">
         <v>10.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BH19" t="n">
         <v>3.5</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="G20" t="n">
         <v>1.82</v>
       </c>
       <c r="H20" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="I20" t="n">
         <v>5.2</v>
@@ -5444,7 +5444,7 @@
         <v>4.2</v>
       </c>
       <c r="K20" t="n">
-        <v>29</v>
+        <v>5.4</v>
       </c>
       <c r="L20" t="n">
         <v>1.2</v>
@@ -5453,31 +5453,31 @@
         <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>1.1</v>
+        <v>2.92</v>
       </c>
       <c r="O20" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="P20" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="Q20" t="n">
         <v>1.39</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1</v>
+        <v>1.97</v>
       </c>
       <c r="T20" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U20" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V20" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W20" t="n">
         <v>2.2</v>
@@ -5492,13 +5492,13 @@
         <v>55</v>
       </c>
       <c r="AA20" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AB20" t="n">
         <v>19</v>
       </c>
       <c r="AC20" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD20" t="n">
         <v>23</v>
@@ -5507,22 +5507,22 @@
         <v>55</v>
       </c>
       <c r="AF20" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI20" t="n">
         <v>48</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL20" t="n">
         <v>27</v>
@@ -5531,70 +5531,70 @@
         <v>60</v>
       </c>
       <c r="AN20" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AO20" t="n">
         <v>34</v>
       </c>
       <c r="AP20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX20" t="n">
         <v>4.5</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR20" t="n">
+      <c r="AY20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>4</v>
-      </c>
       <c r="BA20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC20" t="n">
         <v>4.6</v>
       </c>
-      <c r="BB20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>4</v>
-      </c>
       <c r="BD20" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BH20" t="n">
         <v>5.5</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="BJ20" t="n">
         <v>9.199999999999999</v>
@@ -5630,7 +5630,7 @@
         <v>9.4</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -5698,10 +5698,10 @@
         <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
         <v>1.08</v>
@@ -5746,7 +5746,7 @@
         <v>32</v>
       </c>
       <c r="AA21" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB21" t="n">
         <v>10.5</v>
@@ -5758,7 +5758,7 @@
         <v>19</v>
       </c>
       <c r="AE21" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF21" t="n">
         <v>15</v>
@@ -5779,7 +5779,7 @@
         <v>27</v>
       </c>
       <c r="AL21" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM21" t="n">
         <v>130</v>
@@ -5797,10 +5797,10 @@
         <v>12</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT21" t="n">
         <v>7.8</v>
@@ -5812,7 +5812,7 @@
         <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX21" t="n">
         <v>11.5</v>
@@ -5824,89 +5824,89 @@
         <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="BC21" t="n">
         <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF21" t="n">
         <v>14</v>
       </c>
       <c r="BG21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
         <v>5.3</v>
       </c>
-      <c r="BH21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>9</v>
-      </c>
       <c r="BT21" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="BV21" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>9.4</v>
+        <v>4.8</v>
       </c>
       <c r="BX21" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -5940,10 +5940,10 @@
         <v>1.64</v>
       </c>
       <c r="G22" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I22" t="n">
         <v>5</v>
@@ -5970,7 +5970,7 @@
         <v>3.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R22" t="n">
         <v>1.94</v>
@@ -5988,34 +5988,34 @@
         <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X22" t="n">
         <v>55</v>
       </c>
       <c r="Y22" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="Z22" t="n">
         <v>60</v>
       </c>
       <c r="AA22" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AB22" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AE22" t="n">
         <v>55</v>
       </c>
       <c r="AF22" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG22" t="n">
         <v>14</v>
@@ -6027,10 +6027,10 @@
         <v>46</v>
       </c>
       <c r="AJ22" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK22" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AL22" t="n">
         <v>27</v>
@@ -6045,16 +6045,16 @@
         <v>30</v>
       </c>
       <c r="AP22" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.1</v>
+        <v>14.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AT22" t="n">
         <v>15.5</v>
@@ -6066,7 +6066,7 @@
         <v>17</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AX22" t="n">
         <v>14</v>
@@ -6078,7 +6078,7 @@
         <v>13.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB22" t="n">
         <v>17</v>
@@ -6090,7 +6090,7 @@
         <v>18</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BF22" t="n">
         <v>4.5</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
         <v>2.38</v>
       </c>
       <c r="G23" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H23" t="n">
         <v>2.7</v>
@@ -6227,7 +6227,7 @@
         <v>1.43</v>
       </c>
       <c r="R23" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="S23" t="n">
         <v>2.06</v>
@@ -6236,13 +6236,13 @@
         <v>1.44</v>
       </c>
       <c r="U23" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="V23" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W23" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X23" t="n">
         <v>38</v>
@@ -6281,7 +6281,7 @@
         <v>32</v>
       </c>
       <c r="AJ23" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK23" t="n">
         <v>26</v>
@@ -6299,7 +6299,7 @@
         <v>14</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ23" t="n">
         <v>16</v>
@@ -6308,7 +6308,7 @@
         <v>19</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT23" t="n">
         <v>15</v>
@@ -6335,7 +6335,7 @@
         <v>20</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="BC23" t="n">
         <v>17</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -6448,13 +6448,13 @@
         <v>2.84</v>
       </c>
       <c r="G24" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H24" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I24" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J24" t="n">
         <v>4.2</v>
@@ -6481,13 +6481,13 @@
         <v>1.33</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S24" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="T24" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="U24" t="n">
         <v>1.11</v>
@@ -6496,115 +6496,115 @@
         <v>1.74</v>
       </c>
       <c r="W24" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -6702,10 +6702,10 @@
         <v>1.8</v>
       </c>
       <c r="G25" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I25" t="n">
         <v>5.7</v>
@@ -6723,28 +6723,28 @@
         <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
         <v>1.38</v>
       </c>
       <c r="P25" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R25" t="n">
         <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="T25" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U25" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V25" t="n">
         <v>1.21</v>
@@ -6756,22 +6756,22 @@
         <v>14</v>
       </c>
       <c r="Y25" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA25" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB25" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE25" t="n">
         <v>90</v>
@@ -6780,7 +6780,7 @@
         <v>12.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
         <v>25</v>
@@ -6798,13 +6798,13 @@
         <v>50</v>
       </c>
       <c r="AM25" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
         <v>18</v>
       </c>
       <c r="AO25" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AP25" t="n">
         <v>9.199999999999999</v>
@@ -6813,10 +6813,10 @@
         <v>12</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.7</v>
+        <v>32</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AT25" t="n">
         <v>6</v>
@@ -6828,7 +6828,7 @@
         <v>16</v>
       </c>
       <c r="AW25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX25" t="n">
         <v>8.199999999999999</v>
@@ -6840,7 +6840,7 @@
         <v>16.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB25" t="n">
         <v>17.5</v>
@@ -6849,16 +6849,16 @@
         <v>16.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE25" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BF25" t="n">
         <v>11.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BH25" t="n">
         <v>3.2</v>
@@ -6876,13 +6876,13 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN25" t="n">
         <v>4.4</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP25" t="n">
         <v>13.5</v>
@@ -6894,7 +6894,7 @@
         <v>36</v>
       </c>
       <c r="BS25" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT25" t="n">
         <v>8.6</v>
@@ -6909,7 +6909,7 @@
         <v>10</v>
       </c>
       <c r="BX25" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BY25" t="n">
         <v>10</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -6953,46 +6953,46 @@
         </is>
       </c>
       <c r="F26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L26" t="n">
         <v>1.18</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.01</v>
       </c>
       <c r="M26" t="n">
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.56</v>
+        <v>1.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="P26" t="n">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="R26" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="S26" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="T26" t="n">
         <v>1.55</v>
@@ -7004,25 +7004,25 @@
         <v>1.13</v>
       </c>
       <c r="W26" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Y26" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Z26" t="n">
         <v>80</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB26" t="n">
         <v>19</v>
       </c>
       <c r="AC26" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AD26" t="n">
         <v>32</v>
@@ -7031,13 +7031,13 @@
         <v>85</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG26" t="n">
         <v>13.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
         <v>70</v>
@@ -7058,61 +7058,61 @@
         <v>5.1</v>
       </c>
       <c r="AO26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.78</v>
+        <v>3.9</v>
       </c>
       <c r="AU26" t="n">
-        <v>2.74</v>
+        <v>3.7</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.96</v>
+        <v>4.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="AX26" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AY26" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2.86</v>
+        <v>4</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>2.76</v>
+        <v>3.9</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.74</v>
+        <v>3.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="BH26" t="n">
         <v>5.8</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G27" t="n">
         <v>3.05</v>
@@ -7216,7 +7216,7 @@
         <v>2.8</v>
       </c>
       <c r="I27" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J27" t="n">
         <v>3.05</v>
@@ -7255,7 +7255,7 @@
         <v>1.85</v>
       </c>
       <c r="V27" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W27" t="n">
         <v>1.49</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-19 16:59:08</t>
+          <t>2026-07-19 19:08:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="G2" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="H2" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="J2" t="n">
         <v>3.75</v>
@@ -884,7 +884,7 @@
         <v>4.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
         <v>2.34</v>
@@ -896,31 +896,31 @@
         <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U2" t="n">
         <v>2.5</v>
       </c>
       <c r="V2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.56</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.57</v>
       </c>
       <c r="X2" t="n">
         <v>21</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AA2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="n">
         <v>15</v>
@@ -929,34 +929,34 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AF2" t="n">
         <v>21</v>
       </c>
       <c r="AG2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI2" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
         <v>90</v>
       </c>
       <c r="AK2" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AL2" t="n">
         <v>65</v>
       </c>
       <c r="AM2" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN2" t="n">
         <v>18.5</v>
@@ -965,16 +965,16 @@
         <v>21</v>
       </c>
       <c r="AP2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ2" t="n">
         <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AS2" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AT2" t="n">
         <v>13</v>
@@ -986,10 +986,10 @@
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
@@ -998,22 +998,22 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC2" t="n">
         <v>19</v>
       </c>
       <c r="BD2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BE2" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BF2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG2" t="n">
         <v>15.5</v>
@@ -1022,19 +1022,19 @@
         <v>4.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK2" t="n">
         <v>4.9</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>6.2</v>
@@ -1046,31 +1046,31 @@
         <v>19.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR2" t="n">
         <v>29</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV2" t="n">
         <v>19.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX2" t="n">
         <v>29</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -1120,13 +1120,13 @@
         <v>1.27</v>
       </c>
       <c r="I3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="J3" t="n">
         <v>6.2</v>
       </c>
       <c r="K3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
         <v>1.24</v>
@@ -1135,22 +1135,22 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P3" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R3" t="n">
         <v>1.65</v>
       </c>
       <c r="S3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T3" t="n">
         <v>2.02</v>
@@ -1177,13 +1177,13 @@
         <v>10.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>120</v>
+        <v>950</v>
       </c>
       <c r="AC3" t="n">
         <v>17.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE3" t="n">
         <v>14.5</v>
@@ -1201,7 +1201,7 @@
         <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="AK3" t="n">
         <v>230</v>
@@ -1216,7 +1216,7 @@
         <v>280</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AP3" t="n">
         <v>21</v>
@@ -1231,7 +1231,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3" t="n">
         <v>11.5</v>
@@ -1243,10 +1243,10 @@
         <v>10.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
         <v>14.5</v>
@@ -1255,16 +1255,16 @@
         <v>16</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD3" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF3" t="n">
         <v>15</v>
@@ -1276,7 +1276,7 @@
         <v>4.7</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ3" t="n">
         <v>14</v>
@@ -1288,25 +1288,25 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BO3" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
         <v>3.9</v>
@@ -1324,7 +1324,7 @@
         <v>25</v>
       </c>
       <c r="BY3" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -1365,112 +1365,112 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="G4" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="I4" t="n">
         <v>3.95</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X4" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AA4" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE4" t="n">
         <v>500</v>
       </c>
-      <c r="AB4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>60</v>
-      </c>
       <c r="AF4" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AI4" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>38</v>
+        <v>900</v>
       </c>
       <c r="AK4" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AO4" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AP4" t="n">
         <v>6.2</v>
@@ -1479,10 +1479,10 @@
         <v>6.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>6</v>
+        <v>2.28</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.8</v>
+        <v>2.06</v>
       </c>
       <c r="AT4" t="n">
         <v>4.9</v>
@@ -1491,10 +1491,10 @@
         <v>4.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>5</v>
+        <v>2.42</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.6</v>
+        <v>2.06</v>
       </c>
       <c r="AX4" t="n">
         <v>7</v>
@@ -1503,92 +1503,92 @@
         <v>6.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.4</v>
+        <v>1.89</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.6</v>
+        <v>2.06</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.2</v>
+        <v>2.04</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.9</v>
+        <v>2.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.4</v>
+        <v>2.04</v>
       </c>
       <c r="BE4" t="n">
-        <v>7</v>
+        <v>2.08</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.6</v>
+        <v>2.58</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.56</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="G5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H5" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="I5" t="n">
         <v>6.6</v>
       </c>
       <c r="J5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.9</v>
       </c>
       <c r="L5" t="n">
         <v>1.5</v>
@@ -1652,7 +1652,7 @@
         <v>1.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R5" t="n">
         <v>1.26</v>
@@ -1664,13 +1664,13 @@
         <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X5" t="n">
         <v>14</v>
@@ -1685,7 +1685,7 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC5" t="n">
         <v>8.4</v>
@@ -1733,10 +1733,10 @@
         <v>12</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT5" t="n">
         <v>6.2</v>
@@ -1748,7 +1748,7 @@
         <v>17</v>
       </c>
       <c r="AW5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX5" t="n">
         <v>8.6</v>
@@ -1760,7 +1760,7 @@
         <v>17.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB5" t="n">
         <v>13.5</v>
@@ -1769,16 +1769,16 @@
         <v>15.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
         <v>11</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH5" t="n">
         <v>3.1</v>
@@ -1790,7 +1790,7 @@
         <v>13.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1820,7 +1820,7 @@
         <v>11</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="G6" t="n">
         <v>6.4</v>
@@ -1885,7 +1885,7 @@
         <v>1.63</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K6" t="n">
         <v>4.7</v>
@@ -1903,13 +1903,13 @@
         <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
         <v>2.94</v>
@@ -1918,7 +1918,7 @@
         <v>1.84</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
         <v>2.58</v>
@@ -1927,109 +1927,109 @@
         <v>1.19</v>
       </c>
       <c r="X6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y6" t="n">
         <v>9.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA6" t="n">
         <v>16</v>
       </c>
       <c r="AB6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF6" t="n">
         <v>55</v>
       </c>
       <c r="AG6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
         <v>34</v>
       </c>
       <c r="AJ6" t="n">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="AK6" t="n">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AL6" t="n">
         <v>80</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>380</v>
       </c>
       <c r="AN6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP6" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW6" t="n">
         <v>14.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="AY6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>18.5</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>17</v>
-      </c>
       <c r="BA6" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="BC6" t="n">
-        <v>9.4</v>
+        <v>55</v>
       </c>
       <c r="BD6" t="n">
-        <v>9.4</v>
+        <v>34</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="BF6" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="BG6" t="n">
         <v>7.4</v>
@@ -2074,7 +2074,7 @@
         <v>4.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV6" t="n">
         <v>11</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -2127,43 +2127,43 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H7" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J7" t="n">
         <v>3.15</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
         <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
         <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
         <v>3.9</v>
@@ -2172,16 +2172,16 @@
         <v>1.82</v>
       </c>
       <c r="U7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y7" t="n">
         <v>11.5</v>
@@ -2199,28 +2199,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
         <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AJ7" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AK7" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="AL7" t="n">
         <v>120</v>
@@ -2268,7 +2268,7 @@
         <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB7" t="n">
         <v>24</v>
@@ -2280,13 +2280,13 @@
         <v>34</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF7" t="n">
         <v>20</v>
       </c>
       <c r="BG7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BH7" t="n">
         <v>3.25</v>
@@ -2298,19 +2298,19 @@
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP7" t="n">
         <v>23</v>
@@ -2322,13 +2322,13 @@
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT7" t="n">
         <v>6.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2340,17 +2340,17 @@
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
         <v>8</v>
       </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>7.8</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>2.06</v>
+        <v>2.52</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2411,7 +2411,7 @@
         <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q8" t="n">
         <v>1.35</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2537,7 +2537,7 @@
         <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="H9" t="n">
         <v>1.45</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L9" t="n">
         <v>1.31</v>
@@ -2659,19 +2659,19 @@
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O9" t="n">
         <v>1.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="Q9" t="n">
         <v>1.88</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
         <v>3.25</v>
@@ -2683,10 +2683,10 @@
         <v>1.76</v>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
         <v>16.5</v>
@@ -2713,13 +2713,13 @@
         <v>17.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="AG9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AH9" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI9" t="n">
         <v>42</v>
@@ -2767,10 +2767,10 @@
         <v>14</v>
       </c>
       <c r="AX9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AZ9" t="n">
         <v>21</v>
@@ -2779,19 +2779,19 @@
         <v>32</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BD9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BG9" t="n">
         <v>6.6</v>
@@ -2806,7 +2806,7 @@
         <v>12.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2818,19 +2818,19 @@
         <v>12.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT9" t="n">
         <v>3.95</v>
@@ -2848,17 +2848,17 @@
         <v>28</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="CA9" t="n">
         <v>6.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="I10" t="n">
         <v>1.43</v>
@@ -2919,22 +2919,22 @@
         <v>1.15</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="S10" t="n">
         <v>2.16</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U10" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V10" t="n">
         <v>3.3</v>
@@ -2955,7 +2955,7 @@
         <v>13</v>
       </c>
       <c r="AB10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC10" t="n">
         <v>13.5</v>
@@ -2979,7 +2979,7 @@
         <v>27</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AK10" t="n">
         <v>95</v>
@@ -3000,7 +3000,7 @@
         <v>27</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR10" t="n">
         <v>10</v>
@@ -3009,7 +3009,7 @@
         <v>12</v>
       </c>
       <c r="AT10" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AU10" t="n">
         <v>12</v>
@@ -3030,7 +3030,7 @@
         <v>18.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB10" t="n">
         <v>48</v>
@@ -3039,13 +3039,13 @@
         <v>36</v>
       </c>
       <c r="BD10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE10" t="n">
         <v>34</v>
       </c>
       <c r="BF10" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BG10" t="n">
         <v>4.2</v>
@@ -3060,31 +3060,31 @@
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL10" t="n">
         <v>95</v>
       </c>
       <c r="BM10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN10" t="n">
         <v>11.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP10" t="n">
         <v>55</v>
       </c>
       <c r="BQ10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR10" t="n">
         <v>50</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT10" t="n">
         <v>4.5</v>
@@ -3096,23 +3096,23 @@
         <v>8.6</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BX10" t="n">
         <v>19.5</v>
       </c>
       <c r="BY10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CA10" t="n">
         <v>5.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="G11" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="H11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I11" t="n">
         <v>2.54</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.58</v>
       </c>
       <c r="J11" t="n">
         <v>3.8</v>
@@ -3167,34 +3167,34 @@
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
         <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T11" t="n">
         <v>1.6</v>
       </c>
       <c r="U11" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="V11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X11" t="n">
         <v>21</v>
@@ -3209,7 +3209,7 @@
         <v>36</v>
       </c>
       <c r="AB11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC11" t="n">
         <v>9</v>
@@ -3218,13 +3218,13 @@
         <v>12</v>
       </c>
       <c r="AE11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF11" t="n">
         <v>22</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
         <v>15</v>
@@ -3236,10 +3236,10 @@
         <v>44</v>
       </c>
       <c r="AK11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM11" t="n">
         <v>65</v>
@@ -3248,34 +3248,34 @@
         <v>19.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>12.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT11" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU11" t="n">
         <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW11" t="n">
         <v>21</v>
       </c>
       <c r="AX11" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY11" t="n">
         <v>11.5</v>
@@ -3317,7 +3317,7 @@
         <v>6.4</v>
       </c>
       <c r="BL11" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
         <v>14.5</v>
@@ -3338,7 +3338,7 @@
         <v>28</v>
       </c>
       <c r="BS11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT11" t="n">
         <v>5.8</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>1.99</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H12" t="n">
         <v>3.9</v>
@@ -3409,7 +3409,7 @@
         <v>4.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
         <v>3.95</v>
@@ -3421,19 +3421,19 @@
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
         <v>3.3</v>
@@ -3442,25 +3442,25 @@
         <v>1.76</v>
       </c>
       <c r="U12" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V12" t="n">
         <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X12" t="n">
         <v>18</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Z12" t="n">
         <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
         <v>9.800000000000001</v>
@@ -3481,7 +3481,7 @@
         <v>11</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
         <v>60</v>
@@ -3490,13 +3490,13 @@
         <v>25</v>
       </c>
       <c r="AK12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
         <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>120</v>
+        <v>320</v>
       </c>
       <c r="AN12" t="n">
         <v>15</v>
@@ -3514,7 +3514,7 @@
         <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT12" t="n">
         <v>8.199999999999999</v>
@@ -3538,7 +3538,7 @@
         <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="BB12" t="n">
         <v>20</v>
@@ -3547,10 +3547,10 @@
         <v>18</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF12" t="n">
         <v>10.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="G13" t="n">
-        <v>3.65</v>
+        <v>100</v>
       </c>
       <c r="H13" t="n">
         <v>3.5</v>
@@ -3663,10 +3663,10 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="K13" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -3675,22 +3675,22 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
         <v>1.01</v>
       </c>
       <c r="P13" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="R13" t="n">
         <v>1.12</v>
       </c>
       <c r="S13" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -3702,7 +3702,7 @@
         <v>1.12</v>
       </c>
       <c r="W13" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H14" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J14" t="n">
         <v>2.4</v>
@@ -3932,7 +3932,7 @@
         <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P14" t="n">
         <v>1.25</v>
@@ -3944,7 +3944,7 @@
         <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J15" t="n">
         <v>2.32</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -4667,19 +4667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J17" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="K17" t="n">
         <v>7</v>
@@ -4724,109 +4724,109 @@
         <v>970</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I18" t="n">
         <v>5.3</v>
@@ -4939,7 +4939,7 @@
         <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
@@ -4966,13 +4966,13 @@
         <v>1.79</v>
       </c>
       <c r="U18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V18" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="X18" t="n">
         <v>16</v>
@@ -5020,7 +5020,7 @@
         <v>38</v>
       </c>
       <c r="AM18" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
         <v>12</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -5178,40 +5178,40 @@
         <v>1.83</v>
       </c>
       <c r="G19" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H19" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O19" t="n">
         <v>1.32</v>
       </c>
       <c r="P19" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
         <v>1.95</v>
       </c>
       <c r="R19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
         <v>3.45</v>
@@ -5223,7 +5223,7 @@
         <v>2.02</v>
       </c>
       <c r="V19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W19" t="n">
         <v>2.08</v>
@@ -5235,13 +5235,13 @@
         <v>18.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AA19" t="n">
         <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AC19" t="n">
         <v>9.800000000000001</v>
@@ -5253,10 +5253,10 @@
         <v>500</v>
       </c>
       <c r="AF19" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH19" t="n">
         <v>21</v>
@@ -5265,22 +5265,22 @@
         <v>500</v>
       </c>
       <c r="AJ19" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK19" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="AL19" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AM19" t="n">
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP19" t="n">
         <v>12</v>
@@ -5289,22 +5289,22 @@
         <v>12.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT19" t="n">
         <v>7.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV19" t="n">
         <v>16</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AX19" t="n">
         <v>9.800000000000001</v>
@@ -5316,7 +5316,7 @@
         <v>17</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB19" t="n">
         <v>17.5</v>
@@ -5325,80 +5325,80 @@
         <v>15.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BE19" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF19" t="n">
         <v>10.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BH19" t="n">
         <v>3.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="BJ19" t="n">
         <v>10.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BN19" t="n">
         <v>4.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA19" t="n">
         <v>8.4</v>
       </c>
-      <c r="BX19" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BZ19" t="n">
-        <v>25</v>
-      </c>
-      <c r="CA19" t="n">
-        <v>7.4</v>
-      </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>1.64</v>
       </c>
       <c r="G20" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H20" t="n">
         <v>4.2</v>
@@ -5441,7 +5441,7 @@
         <v>5.2</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="K20" t="n">
         <v>5.4</v>
@@ -5459,22 +5459,22 @@
         <v>1.13</v>
       </c>
       <c r="P20" t="n">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="Q20" t="n">
         <v>1.39</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="S20" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="T20" t="n">
         <v>1.48</v>
       </c>
       <c r="U20" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V20" t="n">
         <v>1.23</v>
@@ -5483,28 +5483,28 @@
         <v>2.2</v>
       </c>
       <c r="X20" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="Y20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z20" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AA20" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB20" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AC20" t="n">
         <v>13.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF20" t="n">
         <v>16.5</v>
@@ -5513,82 +5513,82 @@
         <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI20" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AJ20" t="n">
         <v>21</v>
       </c>
       <c r="AK20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AM20" t="n">
-        <v>60</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
         <v>6.2</v>
       </c>
       <c r="AO20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX20" t="n">
         <v>5.4</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AY20" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BH20" t="n">
         <v>5.5</v>
@@ -5630,7 +5630,7 @@
         <v>9.4</v>
       </c>
       <c r="BU20" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G21" t="n">
         <v>2.16</v>
@@ -5692,16 +5692,16 @@
         <v>3.85</v>
       </c>
       <c r="I21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J21" t="n">
         <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="M21" t="n">
         <v>1.08</v>
@@ -5722,16 +5722,16 @@
         <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T21" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U21" t="n">
         <v>2.06</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W21" t="n">
         <v>1.86</v>
@@ -5746,7 +5746,7 @@
         <v>32</v>
       </c>
       <c r="AA21" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB21" t="n">
         <v>10.5</v>
@@ -5764,22 +5764,22 @@
         <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH21" t="n">
         <v>22</v>
       </c>
       <c r="AI21" t="n">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="AJ21" t="n">
         <v>32</v>
       </c>
       <c r="AK21" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="AM21" t="n">
         <v>130</v>
@@ -5788,7 +5788,7 @@
         <v>21</v>
       </c>
       <c r="AO21" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AP21" t="n">
         <v>11.5</v>
@@ -5800,7 +5800,7 @@
         <v>14.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT21" t="n">
         <v>7.8</v>
@@ -5812,7 +5812,7 @@
         <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AX21" t="n">
         <v>11.5</v>
@@ -5824,7 +5824,7 @@
         <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB21" t="n">
         <v>10.5</v>
@@ -5833,16 +5833,16 @@
         <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF21" t="n">
         <v>14</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BH21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -5937,34 +5937,34 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="G22" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="J22" t="n">
         <v>4.7</v>
       </c>
       <c r="K22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="O22" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P22" t="n">
         <v>3.3</v>
@@ -5973,49 +5973,49 @@
         <v>1.36</v>
       </c>
       <c r="R22" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S22" t="n">
         <v>1.89</v>
       </c>
       <c r="T22" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U22" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="V22" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W22" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X22" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="Y22" t="n">
         <v>80</v>
       </c>
       <c r="Z22" t="n">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="AA22" t="n">
         <v>500</v>
       </c>
       <c r="AB22" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC22" t="n">
         <v>14.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AE22" t="n">
         <v>55</v>
       </c>
       <c r="AF22" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG22" t="n">
         <v>14</v>
@@ -6024,10 +6024,10 @@
         <v>19.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AJ22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK22" t="n">
         <v>16</v>
@@ -6036,7 +6036,7 @@
         <v>27</v>
       </c>
       <c r="AM22" t="n">
-        <v>60</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
         <v>6.2</v>
@@ -6045,19 +6045,19 @@
         <v>30</v>
       </c>
       <c r="AP22" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ22" t="n">
         <v>14.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU22" t="n">
         <v>11.5</v>
@@ -6066,10 +6066,10 @@
         <v>17</v>
       </c>
       <c r="AW22" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY22" t="n">
         <v>9.800000000000001</v>
@@ -6078,7 +6078,7 @@
         <v>13.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BB22" t="n">
         <v>17</v>
@@ -6090,7 +6090,7 @@
         <v>18</v>
       </c>
       <c r="BE22" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BF22" t="n">
         <v>4.5</v>
@@ -6102,65 +6102,65 @@
         <v>5.8</v>
       </c>
       <c r="BI22" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BJ22" t="n">
         <v>9</v>
       </c>
       <c r="BK22" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BN22" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BP22" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="BR22" t="n">
         <v>21</v>
       </c>
       <c r="BS22" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BT22" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BU22" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="BV22" t="n">
         <v>36</v>
       </c>
       <c r="BW22" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BX22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY22" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ22" t="n">
         <v>10.5</v>
       </c>
       <c r="CA22" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G23" t="n">
         <v>2.54</v>
@@ -6200,13 +6200,13 @@
         <v>2.7</v>
       </c>
       <c r="I23" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
         <v>4.1</v>
       </c>
       <c r="K23" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L23" t="n">
         <v>1.21</v>
@@ -6239,10 +6239,10 @@
         <v>2.96</v>
       </c>
       <c r="V23" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W23" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X23" t="n">
         <v>38</v>
@@ -6281,7 +6281,7 @@
         <v>32</v>
       </c>
       <c r="AJ23" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AK23" t="n">
         <v>26</v>
@@ -6290,7 +6290,7 @@
         <v>30</v>
       </c>
       <c r="AM23" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AN23" t="n">
         <v>12</v>
@@ -6299,7 +6299,7 @@
         <v>14</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ23" t="n">
         <v>16</v>
@@ -6308,13 +6308,13 @@
         <v>19</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT23" t="n">
         <v>15</v>
       </c>
       <c r="AU23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV23" t="n">
         <v>10.5</v>
@@ -6344,7 +6344,7 @@
         <v>19.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF23" t="n">
         <v>8</v>
@@ -6353,7 +6353,7 @@
         <v>9.4</v>
       </c>
       <c r="BH23" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BI23" t="n">
         <v>4.6</v>
@@ -6362,13 +6362,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN23" t="n">
         <v>6.2</v>
@@ -6380,13 +6380,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR23" t="n">
         <v>24</v>
       </c>
       <c r="BS23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT23" t="n">
         <v>6.8</v>
@@ -6398,23 +6398,23 @@
         <v>21</v>
       </c>
       <c r="BW23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX23" t="n">
         <v>26</v>
       </c>
       <c r="BY23" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ23" t="n">
         <v>12.5</v>
       </c>
       <c r="CA23" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G24" t="n">
         <v>3.4</v>
@@ -6460,7 +6460,7 @@
         <v>4.2</v>
       </c>
       <c r="K24" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -6478,19 +6478,19 @@
         <v>3.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R24" t="n">
         <v>1.96</v>
       </c>
       <c r="S24" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="T24" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="U24" t="n">
-        <v>1.11</v>
+        <v>2.66</v>
       </c>
       <c r="V24" t="n">
         <v>1.74</v>
@@ -6568,7 +6568,7 @@
         <v>1.74</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="AV24" t="n">
         <v>1.62</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6756,7 @@
         <v>14</v>
       </c>
       <c r="Y25" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z25" t="n">
         <v>42</v>
@@ -6786,7 +6786,7 @@
         <v>25</v>
       </c>
       <c r="AI25" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AJ25" t="n">
         <v>24</v>
@@ -6837,10 +6837,10 @@
         <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB25" t="n">
         <v>17.5</v>
@@ -6849,7 +6849,7 @@
         <v>16.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE25" t="n">
         <v>6.2</v>
@@ -6858,7 +6858,7 @@
         <v>11.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH25" t="n">
         <v>3.2</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -6956,10 +6956,10 @@
         <v>1.42</v>
       </c>
       <c r="G26" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="H26" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I26" t="n">
         <v>8.6</v>
@@ -6974,25 +6974,25 @@
         <v>1.18</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="O26" t="n">
         <v>1.12</v>
       </c>
       <c r="P26" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R26" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="S26" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="T26" t="n">
         <v>1.55</v>
@@ -7001,58 +7001,58 @@
         <v>2.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W26" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="X26" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Y26" t="n">
         <v>40</v>
       </c>
       <c r="Z26" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AA26" t="n">
         <v>190</v>
       </c>
       <c r="AB26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AC26" t="n">
         <v>15</v>
       </c>
       <c r="AD26" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AE26" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF26" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH26" t="n">
         <v>21</v>
       </c>
       <c r="AI26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM26" t="n">
         <v>70</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>80</v>
       </c>
       <c r="AN26" t="n">
         <v>5.1</v>
@@ -7061,58 +7061,58 @@
         <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AQ26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY26" t="n">
         <v>4.4</v>
       </c>
-      <c r="AR26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS26" t="n">
+      <c r="AZ26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB26" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BC26" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH26" t="n">
         <v>5.8</v>
@@ -7124,7 +7124,7 @@
         <v>10</v>
       </c>
       <c r="BK26" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
@@ -7142,7 +7142,7 @@
         <v>9</v>
       </c>
       <c r="BQ26" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BR26" t="n">
         <v>18</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G27" t="n">
         <v>3.05</v>
       </c>
       <c r="H27" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I27" t="n">
         <v>3.15</v>
@@ -7222,7 +7222,7 @@
         <v>3.05</v>
       </c>
       <c r="K27" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="L27" t="n">
         <v>1.53</v>
@@ -7231,28 +7231,28 @@
         <v>1.11</v>
       </c>
       <c r="N27" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O27" t="n">
         <v>1.48</v>
       </c>
       <c r="P27" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q27" t="n">
         <v>2.42</v>
       </c>
       <c r="R27" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S27" t="n">
         <v>4.8</v>
       </c>
       <c r="T27" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U27" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V27" t="n">
         <v>1.47</v>
@@ -7330,7 +7330,7 @@
         <v>6.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV27" t="n">
         <v>10</v>
@@ -7369,25 +7369,25 @@
         <v>4.1</v>
       </c>
       <c r="BH27" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="BJ27" t="n">
         <v>11</v>
       </c>
       <c r="BK27" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN27" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO27" t="n">
         <v>4.3</v>
@@ -7396,16 +7396,16 @@
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT27" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU27" t="n">
         <v>4.4</v>
@@ -7414,23 +7414,23 @@
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ27" t="n">
         <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-19 19:08:57</t>
+          <t>2026-07-19 23:28:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="G2" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H2" t="n">
         <v>2.66</v>
@@ -869,19 +869,19 @@
         <v>2.72</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
@@ -896,88 +896,88 @@
         <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U2" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V2" t="n">
         <v>1.58</v>
       </c>
       <c r="W2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X2" t="n">
         <v>21</v>
       </c>
       <c r="Y2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB2" t="n">
         <v>15.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>15</v>
       </c>
       <c r="AC2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AF2" t="n">
         <v>21</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
         <v>15</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AJ2" t="n">
         <v>90</v>
       </c>
       <c r="AK2" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AL2" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AM2" t="n">
         <v>190</v>
       </c>
       <c r="AN2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO2" t="n">
         <v>18.5</v>
       </c>
-      <c r="AO2" t="n">
-        <v>21</v>
-      </c>
       <c r="AP2" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AS2" t="n">
         <v>36</v>
       </c>
       <c r="AT2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU2" t="n">
         <v>8</v>
@@ -995,82 +995,82 @@
         <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BB2" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BC2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BD2" t="n">
         <v>27</v>
       </c>
       <c r="BE2" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BF2" t="n">
         <v>16</v>
       </c>
       <c r="BG2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL2" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BP2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS2" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BV2" t="n">
         <v>19.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2" t="n">
         <v>29</v>
       </c>
       <c r="BY2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -1111,61 +1111,61 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="G3" t="n">
         <v>14</v>
       </c>
       <c r="H3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="I3" t="n">
         <v>1.32</v>
       </c>
       <c r="J3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
         <v>7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q3" t="n">
         <v>1.54</v>
       </c>
       <c r="R3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S3" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V3" t="n">
         <v>4.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="Y3" t="n">
         <v>10.5</v>
@@ -1195,16 +1195,16 @@
         <v>55</v>
       </c>
       <c r="AH3" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AI3" t="n">
         <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>540</v>
+        <v>490</v>
       </c>
       <c r="AK3" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AL3" t="n">
         <v>460</v>
@@ -1216,61 +1216,61 @@
         <v>280</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AP3" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
         <v>9</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AX3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY3" t="n">
         <v>9.4</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF3" t="n">
         <v>15</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BH3" t="n">
         <v>4.7</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
         <v>15</v>
@@ -1300,16 +1300,16 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
         <v>10.5</v>
       </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>10</v>
-      </c>
       <c r="BT3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BU3" t="n">
         <v>3.45</v>
@@ -1324,7 +1324,7 @@
         <v>25</v>
       </c>
       <c r="BY3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -1368,55 +1368,55 @@
         <v>2.26</v>
       </c>
       <c r="G4" t="n">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="H4" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>2.08</v>
+        <v>4.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="U4" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1446,7 +1446,7 @@
         <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH4" t="n">
         <v>970</v>
@@ -1467,10 +1467,10 @@
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP4" t="n">
         <v>6.2</v>
@@ -1479,10 +1479,10 @@
         <v>6.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AT4" t="n">
         <v>4.9</v>
@@ -1491,10 +1491,10 @@
         <v>4.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.42</v>
+        <v>1.92</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AX4" t="n">
         <v>7</v>
@@ -1503,28 +1503,28 @@
         <v>6.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="BD4" t="n">
         <v>2.04</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BF4" t="n">
         <v>5</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.58</v>
+        <v>8</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I5" t="n">
         <v>6.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
         <v>1.5</v>
@@ -1643,37 +1643,37 @@
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T5" t="n">
         <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W5" t="n">
         <v>2.2</v>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y5" t="n">
         <v>20</v>
@@ -1727,25 +1727,25 @@
         <v>700</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.4</v>
+        <v>3.9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT5" t="n">
         <v>6.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>17</v>
+        <v>4.6</v>
       </c>
       <c r="AW5" t="n">
         <v>5.2</v>
@@ -1754,34 +1754,34 @@
         <v>8.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="BD5" t="n">
         <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI5" t="n">
         <v>2.48</v>
@@ -1790,13 +1790,13 @@
         <v>13.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BN5" t="n">
         <v>4.2</v>
@@ -1808,31 +1808,31 @@
         <v>15.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BR5" t="n">
         <v>40</v>
       </c>
       <c r="BS5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT5" t="n">
         <v>11</v>
       </c>
       <c r="BU5" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="I6" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.35</v>
@@ -1897,31 +1897,31 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
         <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R6" t="n">
         <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
         <v>1.84</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="W6" t="n">
         <v>1.19</v>
@@ -1942,7 +1942,7 @@
         <v>23</v>
       </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
         <v>16.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG6" t="n">
         <v>23</v>
@@ -1960,7 +1960,7 @@
         <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ6" t="n">
         <v>690</v>
@@ -1981,7 +1981,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AP6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ6" t="n">
         <v>8.800000000000001</v>
@@ -2005,7 +2005,7 @@
         <v>14.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AY6" t="n">
         <v>20</v>
@@ -2023,7 +2023,7 @@
         <v>55</v>
       </c>
       <c r="BD6" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BE6" t="n">
         <v>38</v>
@@ -2035,13 +2035,13 @@
         <v>7.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK6" t="n">
         <v>8</v>
@@ -2050,10 +2050,10 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BN6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BO6" t="n">
         <v>7.4</v>
@@ -2062,22 +2062,22 @@
         <v>50</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BR6" t="n">
         <v>55</v>
       </c>
       <c r="BS6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BV6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BW6" t="n">
         <v>8.199999999999999</v>
@@ -2086,7 +2086,7 @@
         <v>25</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="G7" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H7" t="n">
         <v>2.8</v>
       </c>
       <c r="I7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J7" t="n">
         <v>3.2</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.15</v>
-      </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.5</v>
@@ -2151,10 +2151,10 @@
         <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P7" t="n">
         <v>1.75</v>
@@ -2163,10 +2163,10 @@
         <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
         <v>1.82</v>
@@ -2175,7 +2175,7 @@
         <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
         <v>1.53</v>
@@ -2187,10 +2187,10 @@
         <v>11.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="n">
         <v>11</v>
@@ -2202,13 +2202,13 @@
         <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="AF7" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
         <v>19.5</v>
@@ -2217,7 +2217,7 @@
         <v>120</v>
       </c>
       <c r="AJ7" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AK7" t="n">
         <v>90</v>
@@ -2229,64 +2229,64 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AO7" t="n">
         <v>42</v>
       </c>
       <c r="AP7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR7" t="n">
         <v>16.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AT7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY7" t="n">
         <v>11</v>
       </c>
-      <c r="AW7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BB7" t="n">
         <v>24</v>
       </c>
       <c r="BC7" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="n">
         <v>34</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="BF7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG7" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BH7" t="n">
         <v>3.25</v>
@@ -2331,7 +2331,7 @@
         <v>5.1</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW7" t="n">
         <v>7.2</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.21</v>
+        <v>1.82</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2</v>
+        <v>2.96</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="J8" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
         <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Q8" t="n">
         <v>1.35</v>
       </c>
       <c r="R8" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>1.35</v>
+        <v>3.35</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2429,55 +2429,55 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC8" t="n">
         <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2486,61 +2486,61 @@
         <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BF8" t="n">
         <v>1.55</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -2635,61 +2635,61 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H9" t="n">
         <v>1.45</v>
       </c>
       <c r="I9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
         <v>5.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
         <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="U9" t="n">
         <v>1.76</v>
       </c>
       <c r="V9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y9" t="n">
         <v>7.8</v>
@@ -2698,25 +2698,25 @@
         <v>8.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC9" t="n">
         <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
         <v>170</v>
       </c>
       <c r="AG9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AH9" t="n">
         <v>29</v>
@@ -2725,82 +2725,82 @@
         <v>42</v>
       </c>
       <c r="AJ9" t="n">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="AK9" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AL9" t="n">
         <v>140</v>
       </c>
       <c r="AM9" t="n">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="AN9" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="AO9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AP9" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="AS9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX9" t="n">
         <v>10.5</v>
       </c>
-      <c r="AT9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AY9" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BA9" t="n">
-        <v>32</v>
+        <v>9.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BC9" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH9" t="n">
         <v>3.75</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BJ9" t="n">
         <v>12.5</v>
@@ -2824,7 +2824,7 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2851,14 +2851,14 @@
         <v>7.6</v>
       </c>
       <c r="BZ9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="CA9" t="n">
         <v>6.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="H10" t="n">
         <v>1.41</v>
@@ -2919,7 +2919,7 @@
         <v>1.15</v>
       </c>
       <c r="P10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q10" t="n">
         <v>1.46</v>
@@ -2928,13 +2928,13 @@
         <v>1.82</v>
       </c>
       <c r="S10" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T10" t="n">
         <v>1.71</v>
       </c>
       <c r="U10" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V10" t="n">
         <v>3.3</v>
@@ -2943,7 +2943,7 @@
         <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Y10" t="n">
         <v>14</v>
@@ -2952,7 +2952,7 @@
         <v>11.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AB10" t="n">
         <v>44</v>
@@ -2967,7 +2967,7 @@
         <v>13.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AG10" t="n">
         <v>30</v>
@@ -2976,10 +2976,10 @@
         <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ10" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
         <v>95</v>
@@ -2994,7 +2994,7 @@
         <v>85</v>
       </c>
       <c r="AO10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AP10" t="n">
         <v>27</v>
@@ -3021,7 +3021,7 @@
         <v>12</v>
       </c>
       <c r="AX10" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AY10" t="n">
         <v>27</v>
@@ -3039,10 +3039,10 @@
         <v>36</v>
       </c>
       <c r="BD10" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BE10" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BF10" t="n">
         <v>60</v>
@@ -3054,7 +3054,7 @@
         <v>5</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -3152,16 +3152,16 @@
         <v>2.5</v>
       </c>
       <c r="I11" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K11" t="n">
         <v>3.85</v>
       </c>
       <c r="L11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
@@ -3173,7 +3173,7 @@
         <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
         <v>1.7</v>
@@ -3182,10 +3182,10 @@
         <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U11" t="n">
         <v>2.58</v>
@@ -3206,13 +3206,13 @@
         <v>18.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
         <v>12</v>
@@ -3236,19 +3236,19 @@
         <v>44</v>
       </c>
       <c r="AK11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL11" t="n">
         <v>34</v>
       </c>
       <c r="AM11" t="n">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AO11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP11" t="n">
         <v>18.5</v>
@@ -3263,7 +3263,7 @@
         <v>32</v>
       </c>
       <c r="AT11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU11" t="n">
         <v>8</v>
@@ -3287,28 +3287,28 @@
         <v>28</v>
       </c>
       <c r="BB11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BC11" t="n">
         <v>25</v>
       </c>
       <c r="BD11" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BE11" t="n">
         <v>50</v>
       </c>
       <c r="BF11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BG11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH11" t="n">
         <v>4</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ11" t="n">
         <v>8.800000000000001</v>
@@ -3320,7 +3320,7 @@
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN11" t="n">
         <v>6.2</v>
@@ -3332,41 +3332,41 @@
         <v>20</v>
       </c>
       <c r="BQ11" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR11" t="n">
         <v>28</v>
       </c>
       <c r="BS11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU11" t="n">
         <v>5.2</v>
       </c>
       <c r="BV11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX11" t="n">
         <v>26</v>
       </c>
       <c r="BY11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ11" t="n">
         <v>18.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -3400,13 +3400,13 @@
         <v>1.99</v>
       </c>
       <c r="G12" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="n">
         <v>3.7</v>
@@ -3415,52 +3415,52 @@
         <v>3.95</v>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
         <v>1.31</v>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="R12" t="n">
         <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V12" t="n">
         <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X12" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z12" t="n">
         <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>90</v>
       </c>
       <c r="AB12" t="n">
         <v>9.800000000000001</v>
@@ -3499,37 +3499,37 @@
         <v>320</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ12" t="n">
         <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
         <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY12" t="n">
         <v>9</v>
@@ -3538,46 +3538,46 @@
         <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BB12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="BE12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF12" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BH12" t="n">
         <v>3.6</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ12" t="n">
         <v>10</v>
       </c>
       <c r="BK12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO12" t="n">
         <v>4.1</v>
@@ -3592,7 +3592,7 @@
         <v>29</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT12" t="n">
         <v>7.8</v>
@@ -3604,23 +3604,23 @@
         <v>36</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX12" t="n">
         <v>55</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ12" t="n">
         <v>25</v>
       </c>
       <c r="CA12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>600</v>
       </c>
       <c r="H14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I14" t="n">
         <v>870</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G18" t="n">
         <v>1.85</v>
@@ -4933,40 +4933,40 @@
         <v>5.3</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K18" t="n">
         <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
         <v>1.79</v>
       </c>
       <c r="U18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V18" t="n">
         <v>1.23</v>
@@ -4978,7 +4978,7 @@
         <v>16</v>
       </c>
       <c r="Y18" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z18" t="n">
         <v>140</v>
@@ -4987,10 +4987,10 @@
         <v>700</v>
       </c>
       <c r="AB18" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18" t="n">
         <v>20</v>
@@ -4999,7 +4999,7 @@
         <v>150</v>
       </c>
       <c r="AF18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG18" t="n">
         <v>10</v>
@@ -5032,13 +5032,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AR18" t="n">
-        <v>18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT18" t="n">
         <v>8</v>
@@ -5047,13 +5047,13 @@
         <v>7.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AW18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY18" t="n">
         <v>9</v>
@@ -5062,22 +5062,22 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BB18" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>16</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG18" t="n">
         <v>10</v>
@@ -5086,7 +5086,7 @@
         <v>3.75</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="BJ18" t="n">
         <v>10.5</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -5178,55 +5178,55 @@
         <v>1.83</v>
       </c>
       <c r="G19" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
         <v>5.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K19" t="n">
         <v>3.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="R19" t="n">
         <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="T19" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
         <v>1.24</v>
       </c>
       <c r="W19" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X19" t="n">
         <v>16.5</v>
@@ -5241,7 +5241,7 @@
         <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC19" t="n">
         <v>9.800000000000001</v>
@@ -5253,7 +5253,7 @@
         <v>500</v>
       </c>
       <c r="AF19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG19" t="n">
         <v>10</v>
@@ -5265,13 +5265,13 @@
         <v>500</v>
       </c>
       <c r="AJ19" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="AK19" t="n">
         <v>65</v>
       </c>
       <c r="AL19" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM19" t="n">
         <v>580</v>
@@ -5283,64 +5283,64 @@
         <v>100</v>
       </c>
       <c r="AP19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>12.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AU19" t="n">
         <v>7.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB19" t="n">
         <v>17</v>
       </c>
-      <c r="BA19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BC19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG19" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>8</v>
       </c>
       <c r="BH19" t="n">
         <v>3.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ19" t="n">
         <v>10.5</v>
@@ -5352,10 +5352,10 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO19" t="n">
         <v>3.6</v>
@@ -5364,13 +5364,13 @@
         <v>13</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT19" t="n">
         <v>8.4</v>
@@ -5382,23 +5382,23 @@
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -5429,230 +5429,230 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="G20" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="H20" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="K20" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T20" t="n">
         <v>1.2</v>
       </c>
-      <c r="M20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.48</v>
-      </c>
       <c r="U20" t="n">
-        <v>2.6</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="X20" t="n">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="Y20" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="Z20" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AA20" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB20" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AC20" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AE20" t="n">
         <v>500</v>
       </c>
       <c r="AF20" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AG20" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH20" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AI20" t="n">
         <v>500</v>
       </c>
       <c r="AJ20" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AK20" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AL20" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AM20" t="n">
         <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>6.2</v>
+        <v>29</v>
       </c>
       <c r="AO20" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.6</v>
+        <v>1.37</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.8</v>
+        <v>1.37</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.4</v>
+        <v>1.39</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.5</v>
+        <v>1.33</v>
       </c>
       <c r="AU20" t="n">
-        <v>5</v>
+        <v>1.35</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.8</v>
+        <v>1.34</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.8</v>
+        <v>1.37</v>
       </c>
       <c r="AX20" t="n">
-        <v>5.4</v>
+        <v>1.35</v>
       </c>
       <c r="AY20" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5.4</v>
+        <v>1.36</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.6</v>
+        <v>1.37</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.8</v>
+        <v>1.37</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.4</v>
+        <v>1.37</v>
       </c>
       <c r="BD20" t="n">
-        <v>6</v>
+        <v>1.38</v>
       </c>
       <c r="BE20" t="n">
-        <v>7</v>
+        <v>1.39</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.45</v>
+        <v>1.33</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.4</v>
+        <v>1.55</v>
       </c>
       <c r="BH20" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -5683,16 +5683,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="G21" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H21" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>3.45</v>
@@ -5701,28 +5701,28 @@
         <v>3.65</v>
       </c>
       <c r="L21" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="M21" t="n">
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P21" t="n">
         <v>1.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R21" t="n">
         <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T21" t="n">
         <v>1.84</v>
@@ -5731,28 +5731,28 @@
         <v>2.06</v>
       </c>
       <c r="V21" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="X21" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z21" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA21" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB21" t="n">
         <v>10.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD21" t="n">
         <v>19</v>
@@ -5764,7 +5764,7 @@
         <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH21" t="n">
         <v>22</v>
@@ -5776,34 +5776,34 @@
         <v>32</v>
       </c>
       <c r="AK21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
         <v>150</v>
       </c>
       <c r="AM21" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
         <v>21</v>
       </c>
       <c r="AO21" t="n">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="AP21" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR21" t="n">
         <v>14.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU21" t="n">
         <v>7</v>
@@ -5812,19 +5812,19 @@
         <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AX21" t="n">
         <v>11.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
         <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB21" t="n">
         <v>10.5</v>
@@ -5833,16 +5833,16 @@
         <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF21" t="n">
         <v>14</v>
       </c>
       <c r="BG21" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BH21" t="n">
         <v>1000</v>
@@ -5854,43 +5854,43 @@
         <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BT21" t="n">
         <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
@@ -5902,11 +5902,11 @@
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -5937,25 +5937,25 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G22" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="H22" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I22" t="n">
         <v>5.4</v>
       </c>
       <c r="J22" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K22" t="n">
         <v>5.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
@@ -5967,28 +5967,28 @@
         <v>1.12</v>
       </c>
       <c r="P22" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="R22" t="n">
         <v>1.95</v>
       </c>
       <c r="S22" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="T22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U22" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="V22" t="n">
         <v>1.23</v>
       </c>
       <c r="W22" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X22" t="n">
         <v>120</v>
@@ -6003,10 +6003,10 @@
         <v>500</v>
       </c>
       <c r="AB22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD22" t="n">
         <v>22</v>
@@ -6015,7 +6015,7 @@
         <v>55</v>
       </c>
       <c r="AF22" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG22" t="n">
         <v>14</v>
@@ -6027,34 +6027,34 @@
         <v>100</v>
       </c>
       <c r="AJ22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK22" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AM22" t="n">
         <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AO22" t="n">
         <v>30</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ22" t="n">
         <v>14.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="AT22" t="n">
         <v>14.5</v>
@@ -6066,7 +6066,7 @@
         <v>17</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="AX22" t="n">
         <v>13</v>
@@ -6078,10 +6078,10 @@
         <v>13.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC22" t="n">
         <v>13</v>
@@ -6090,7 +6090,7 @@
         <v>18</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BF22" t="n">
         <v>4.5</v>
@@ -6099,49 +6099,49 @@
         <v>20</v>
       </c>
       <c r="BH22" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BI22" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BJ22" t="n">
         <v>9</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BN22" t="n">
         <v>5.4</v>
       </c>
       <c r="BO22" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BP22" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BR22" t="n">
         <v>21</v>
       </c>
       <c r="BS22" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BT22" t="n">
         <v>9.6</v>
       </c>
       <c r="BU22" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV22" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
         <v>7</v>
@@ -6150,17 +6150,17 @@
         <v>32</v>
       </c>
       <c r="BY22" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ22" t="n">
         <v>10.5</v>
       </c>
       <c r="CA22" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -6191,64 +6191,64 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="G23" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H23" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="J23" t="n">
         <v>4.1</v>
       </c>
       <c r="K23" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M23" t="n">
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O23" t="n">
         <v>1.14</v>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R23" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="S23" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="T23" t="n">
         <v>1.44</v>
       </c>
       <c r="U23" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="V23" t="n">
         <v>1.52</v>
       </c>
       <c r="W23" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X23" t="n">
         <v>38</v>
       </c>
       <c r="Y23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z23" t="n">
         <v>29</v>
@@ -6257,7 +6257,7 @@
         <v>46</v>
       </c>
       <c r="AB23" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AC23" t="n">
         <v>13</v>
@@ -6284,13 +6284,13 @@
         <v>80</v>
       </c>
       <c r="AK23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
       </c>
       <c r="AM23" t="n">
-        <v>44</v>
+        <v>200</v>
       </c>
       <c r="AN23" t="n">
         <v>12</v>
@@ -6299,7 +6299,7 @@
         <v>14</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AQ23" t="n">
         <v>16</v>
@@ -6308,7 +6308,7 @@
         <v>19</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT23" t="n">
         <v>15</v>
@@ -6344,7 +6344,7 @@
         <v>19.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF23" t="n">
         <v>8</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G24" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="I24" t="n">
         <v>2.36</v>
@@ -6460,31 +6460,31 @@
         <v>4.2</v>
       </c>
       <c r="K24" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M24" t="n">
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>8.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="P24" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="R24" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="S24" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="T24" t="n">
         <v>1.37</v>
@@ -6493,10 +6493,10 @@
         <v>2.66</v>
       </c>
       <c r="V24" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W24" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="X24" t="n">
         <v>950</v>
@@ -6517,7 +6517,7 @@
         <v>950</v>
       </c>
       <c r="AD24" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE24" t="n">
         <v>500</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -6699,10 +6699,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G25" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H25" t="n">
         <v>5</v>
@@ -6717,22 +6717,22 @@
         <v>3.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M25" t="n">
         <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
         <v>1.38</v>
       </c>
       <c r="P25" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R25" t="n">
         <v>1.28</v>
@@ -6750,7 +6750,7 @@
         <v>1.21</v>
       </c>
       <c r="W25" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X25" t="n">
         <v>14</v>
@@ -6777,10 +6777,10 @@
         <v>90</v>
       </c>
       <c r="AF25" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH25" t="n">
         <v>25</v>
@@ -6789,7 +6789,7 @@
         <v>320</v>
       </c>
       <c r="AJ25" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK25" t="n">
         <v>25</v>
@@ -6813,10 +6813,10 @@
         <v>12</v>
       </c>
       <c r="AR25" t="n">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT25" t="n">
         <v>6</v>
@@ -6828,7 +6828,7 @@
         <v>16</v>
       </c>
       <c r="AW25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX25" t="n">
         <v>8.199999999999999</v>
@@ -6840,7 +6840,7 @@
         <v>18.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB25" t="n">
         <v>17.5</v>
@@ -6849,16 +6849,16 @@
         <v>16.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF25" t="n">
         <v>11.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH25" t="n">
         <v>3.2</v>
@@ -6870,13 +6870,13 @@
         <v>11</v>
       </c>
       <c r="BK25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN25" t="n">
         <v>4.4</v>
@@ -6891,7 +6891,7 @@
         <v>10</v>
       </c>
       <c r="BR25" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BS25" t="n">
         <v>9.199999999999999</v>
@@ -6906,23 +6906,23 @@
         <v>60</v>
       </c>
       <c r="BW25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX25" t="n">
         <v>70</v>
       </c>
       <c r="BY25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ25" t="n">
         <v>32</v>
       </c>
       <c r="CA25" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -6953,220 +6953,220 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="G26" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="H26" t="n">
-        <v>5.5</v>
+        <v>1.05</v>
       </c>
       <c r="I26" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K26" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="M26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>1.11</v>
+        <v>7.4</v>
       </c>
       <c r="O26" t="n">
         <v>1.12</v>
       </c>
       <c r="P26" t="n">
-        <v>3.15</v>
+        <v>1.56</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="R26" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S26" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="T26" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="U26" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W26" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X26" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="Z26" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AC26" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AD26" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>6</v>
+        <v>1.22</v>
       </c>
       <c r="AQ26" t="n">
-        <v>5.9</v>
+        <v>1.18</v>
       </c>
       <c r="AR26" t="n">
-        <v>6.2</v>
+        <v>1.22</v>
       </c>
       <c r="AS26" t="n">
-        <v>6.6</v>
+        <v>1.22</v>
       </c>
       <c r="AT26" t="n">
-        <v>4.9</v>
+        <v>1.12</v>
       </c>
       <c r="AU26" t="n">
-        <v>4.7</v>
+        <v>1.11</v>
       </c>
       <c r="AV26" t="n">
-        <v>5.6</v>
+        <v>1.22</v>
       </c>
       <c r="AW26" t="n">
-        <v>6.4</v>
+        <v>1.22</v>
       </c>
       <c r="AX26" t="n">
-        <v>4.7</v>
+        <v>1.22</v>
       </c>
       <c r="AY26" t="n">
-        <v>4.4</v>
+        <v>1.22</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5.2</v>
+        <v>1.22</v>
       </c>
       <c r="BA26" t="n">
-        <v>6.2</v>
+        <v>1.22</v>
       </c>
       <c r="BB26" t="n">
-        <v>4.8</v>
+        <v>1.22</v>
       </c>
       <c r="BC26" t="n">
-        <v>4.7</v>
+        <v>1.22</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.5</v>
+        <v>1.22</v>
       </c>
       <c r="BE26" t="n">
-        <v>6.2</v>
+        <v>1.22</v>
       </c>
       <c r="BF26" t="n">
-        <v>2.94</v>
+        <v>1.22</v>
       </c>
       <c r="BG26" t="n">
-        <v>6.2</v>
+        <v>1.22</v>
       </c>
       <c r="BH26" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BN26" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP26" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR26" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BT26" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV26" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX26" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="G27" t="n">
         <v>3.05</v>
@@ -7216,34 +7216,34 @@
         <v>2.82</v>
       </c>
       <c r="I27" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="J27" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K27" t="n">
         <v>3.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M27" t="n">
         <v>1.11</v>
       </c>
       <c r="N27" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="O27" t="n">
         <v>1.48</v>
       </c>
       <c r="P27" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R27" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S27" t="n">
         <v>4.8</v>
@@ -7252,13 +7252,13 @@
         <v>1.99</v>
       </c>
       <c r="U27" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V27" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W27" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X27" t="n">
         <v>11.5</v>
@@ -7282,16 +7282,16 @@
         <v>16.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG27" t="n">
         <v>16</v>
       </c>
       <c r="AH27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI27" t="n">
         <v>75</v>
@@ -7306,7 +7306,7 @@
         <v>75</v>
       </c>
       <c r="AM27" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN27" t="n">
         <v>55</v>
@@ -7315,16 +7315,16 @@
         <v>60</v>
       </c>
       <c r="AP27" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT27" t="n">
         <v>6.6</v>
@@ -7336,10 +7336,10 @@
         <v>10</v>
       </c>
       <c r="AW27" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX27" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY27" t="n">
         <v>9.800000000000001</v>
@@ -7348,46 +7348,46 @@
         <v>15</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC27" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH27" t="n">
         <v>2.86</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BJ27" t="n">
         <v>11</v>
       </c>
       <c r="BK27" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BN27" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BO27" t="n">
         <v>4.3</v>
@@ -7396,13 +7396,13 @@
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT27" t="n">
         <v>5.9</v>
@@ -7414,23 +7414,23 @@
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ27" t="n">
         <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-19 23:28:22</t>
+          <t>2026-07-20 01:38:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G2" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="H2" t="n">
         <v>2.66</v>
@@ -869,10 +869,10 @@
         <v>2.72</v>
       </c>
       <c r="J2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.8</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>1.34</v>
@@ -884,58 +884,58 @@
         <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S2" t="n">
         <v>2.82</v>
       </c>
       <c r="T2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U2" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V2" t="n">
         <v>1.58</v>
       </c>
       <c r="W2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X2" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y2" t="n">
         <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="n">
         <v>42</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
         <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF2" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG2" t="n">
         <v>12.5</v>
@@ -950,7 +950,7 @@
         <v>90</v>
       </c>
       <c r="AK2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL2" t="n">
         <v>34</v>
@@ -959,7 +959,7 @@
         <v>190</v>
       </c>
       <c r="AN2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO2" t="n">
         <v>18.5</v>
@@ -977,7 +977,7 @@
         <v>36</v>
       </c>
       <c r="AT2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU2" t="n">
         <v>8</v>
@@ -986,58 +986,58 @@
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BF2" t="n">
         <v>16</v>
       </c>
       <c r="BG2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM2" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO2" t="n">
         <v>5.3</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT2" t="n">
         <v>6</v>
@@ -1061,16 +1061,16 @@
         <v>5.4</v>
       </c>
       <c r="BV2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2" t="n">
         <v>29</v>
       </c>
       <c r="BY2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="G3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="I3" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.27</v>
@@ -1135,19 +1135,19 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="R3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S3" t="n">
         <v>2.38</v>
@@ -1159,19 +1159,19 @@
         <v>1.84</v>
       </c>
       <c r="V3" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
         <v>80</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA3" t="n">
         <v>10.5</v>
@@ -1180,10 +1180,10 @@
         <v>950</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AD3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
         <v>14.5</v>
@@ -1192,19 +1192,19 @@
         <v>540</v>
       </c>
       <c r="AG3" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AH3" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AI3" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AJ3" t="n">
-        <v>490</v>
+        <v>570</v>
       </c>
       <c r="AK3" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AL3" t="n">
         <v>460</v>
@@ -1216,49 +1216,49 @@
         <v>280</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AU3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
         <v>12</v>
       </c>
       <c r="AX3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY3" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BB3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC3" t="n">
         <v>11</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>10.5</v>
       </c>
       <c r="BD3" t="n">
         <v>10.5</v>
@@ -1267,64 +1267,64 @@
         <v>10.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BN3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BT3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BV3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BX3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G4" t="n">
         <v>2.32</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="J4" t="n">
         <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.47</v>
@@ -1389,13 +1389,13 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
         <v>1.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q4" t="n">
         <v>2.24</v>
@@ -1407,16 +1407,16 @@
         <v>4.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="U4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1479,10 +1479,10 @@
         <v>6.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AT4" t="n">
         <v>4.9</v>
@@ -1491,10 +1491,10 @@
         <v>4.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.92</v>
+        <v>6</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AX4" t="n">
         <v>7</v>
@@ -1503,22 +1503,22 @@
         <v>6.4</v>
       </c>
       <c r="AZ4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BB4" t="n">
         <v>2</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BC4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BE4" t="n">
         <v>2.04</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>2.06</v>
       </c>
       <c r="BF4" t="n">
         <v>5</v>
@@ -1527,68 +1527,68 @@
         <v>8</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="G5" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="H5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J5" t="n">
         <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>1.5</v>
@@ -1646,10 +1646,10 @@
         <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q5" t="n">
         <v>2.24</v>
@@ -1661,142 +1661,142 @@
         <v>4.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U5" t="n">
         <v>1.81</v>
       </c>
       <c r="V5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X5" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC5" t="n">
         <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AI5" t="n">
         <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AK5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.5</v>
+        <v>55</v>
       </c>
       <c r="AO5" t="n">
         <v>700</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="AT5" t="n">
         <v>6.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.6</v>
+        <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="BJ5" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BN5" t="n">
         <v>4.2</v>
@@ -1805,34 +1805,34 @@
         <v>3.25</v>
       </c>
       <c r="BP5" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR5" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BU5" t="n">
         <v>6.8</v>
       </c>
-      <c r="BT5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
         <v>6.2</v>
@@ -1930,10 +1930,10 @@
         <v>19</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA6" t="n">
         <v>16</v>
@@ -1957,25 +1957,25 @@
         <v>23</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
         <v>32</v>
       </c>
       <c r="AJ6" t="n">
-        <v>690</v>
+        <v>160</v>
       </c>
       <c r="AK6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN6" t="n">
         <v>85</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>380</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>90</v>
       </c>
       <c r="AO6" t="n">
         <v>8.199999999999999</v>
@@ -1987,7 +1987,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS6" t="n">
         <v>14</v>
@@ -2005,7 +2005,7 @@
         <v>14.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AY6" t="n">
         <v>20</v>
@@ -2020,16 +2020,16 @@
         <v>44</v>
       </c>
       <c r="BC6" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BD6" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BE6" t="n">
         <v>38</v>
       </c>
       <c r="BF6" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="BG6" t="n">
         <v>7.4</v>
@@ -2038,37 +2038,37 @@
         <v>3.8</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ6" t="n">
         <v>10</v>
       </c>
       <c r="BK6" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="BP6" t="n">
         <v>50</v>
       </c>
       <c r="BQ6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR6" t="n">
         <v>55</v>
       </c>
       <c r="BS6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT6" t="n">
         <v>4.3</v>
@@ -2080,13 +2080,13 @@
         <v>10.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BX6" t="n">
         <v>25</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I7" t="n">
         <v>3.15</v>
@@ -2142,7 +2142,7 @@
         <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
         <v>1.5</v>
@@ -2163,7 +2163,7 @@
         <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -2175,7 +2175,7 @@
         <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
         <v>1.53</v>
@@ -2184,19 +2184,19 @@
         <v>12.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
         <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="n">
         <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
         <v>14</v>
@@ -2205,10 +2205,10 @@
         <v>44</v>
       </c>
       <c r="AF7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
         <v>19.5</v>
@@ -2217,10 +2217,10 @@
         <v>120</v>
       </c>
       <c r="AJ7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK7" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="AL7" t="n">
         <v>120</v>
@@ -2229,7 +2229,7 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AO7" t="n">
         <v>42</v>
@@ -2238,13 +2238,13 @@
         <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR7" t="n">
         <v>16.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AT7" t="n">
         <v>8.800000000000001</v>
@@ -2253,13 +2253,13 @@
         <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AX7" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY7" t="n">
         <v>11</v>
@@ -2268,31 +2268,31 @@
         <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB7" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC7" t="n">
         <v>24</v>
       </c>
-      <c r="BC7" t="n">
-        <v>23</v>
-      </c>
       <c r="BD7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE7" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BF7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
@@ -2307,16 +2307,16 @@
         <v>9.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BP7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
@@ -2328,10 +2328,10 @@
         <v>6.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
         <v>7.2</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="G8" t="n">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="H8" t="n">
         <v>2.96</v>
@@ -2405,16 +2405,16 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="R8" t="n">
         <v>1.29</v>
@@ -2429,19 +2429,19 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y8" t="n">
         <v>950</v>
       </c>
       <c r="Z8" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
@@ -2450,16 +2450,16 @@
         <v>950</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD8" t="n">
         <v>950</v>
       </c>
       <c r="AE8" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AF8" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AG8" t="n">
         <v>950</v>
@@ -2468,73 +2468,73 @@
         <v>950</v>
       </c>
       <c r="AI8" t="n">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
         <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO8" t="n">
         <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AU8" t="n">
         <v>1.17</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="BF8" t="n">
         <v>1.55</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
         <v>1.38</v>
@@ -2662,7 +2662,7 @@
         <v>4.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P9" t="n">
         <v>2.04</v>
@@ -2671,19 +2671,19 @@
         <v>1.87</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
         <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="W9" t="n">
         <v>1.11</v>
@@ -2692,154 +2692,154 @@
         <v>17.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AB9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD9" t="n">
         <v>10.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="AG9" t="n">
         <v>36</v>
       </c>
       <c r="AH9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ9" t="n">
-        <v>420</v>
+        <v>470</v>
       </c>
       <c r="AK9" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="AL9" t="n">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="AM9" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN9" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AO9" t="n">
         <v>7.6</v>
       </c>
       <c r="AP9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS9" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS9" t="n">
+      <c r="AT9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB9" t="n">
         <v>9.6</v>
       </c>
-      <c r="AT9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>12</v>
-      </c>
       <c r="BC9" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>11.5</v>
+        <v>70</v>
       </c>
       <c r="BE9" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="BF9" t="n">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BH9" t="n">
         <v>3.75</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BJ9" t="n">
         <v>12.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BU9" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BV9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BW9" t="n">
         <v>5</v>
@@ -2848,17 +2848,17 @@
         <v>28</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CA9" t="n">
         <v>6.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="G10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="J10" t="n">
         <v>5.6</v>
       </c>
       <c r="K10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.25</v>
@@ -2913,43 +2913,43 @@
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q10" t="n">
         <v>1.46</v>
       </c>
       <c r="R10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S10" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T10" t="n">
         <v>1.71</v>
       </c>
       <c r="U10" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y10" t="n">
         <v>14</v>
       </c>
       <c r="Z10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA10" t="n">
         <v>12.5</v>
@@ -2976,16 +2976,16 @@
         <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AK10" t="n">
         <v>95</v>
       </c>
       <c r="AL10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM10" t="n">
         <v>85</v>
@@ -2997,7 +2997,7 @@
         <v>4.4</v>
       </c>
       <c r="AP10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AQ10" t="n">
         <v>12.5</v>
@@ -3036,10 +3036,10 @@
         <v>48</v>
       </c>
       <c r="BC10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BD10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BE10" t="n">
         <v>50</v>
@@ -3051,40 +3051,40 @@
         <v>4.2</v>
       </c>
       <c r="BH10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BL10" t="n">
         <v>95</v>
       </c>
       <c r="BM10" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BP10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BQ10" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BR10" t="n">
         <v>50</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT10" t="n">
         <v>4.5</v>
@@ -3096,23 +3096,23 @@
         <v>8.6</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BX10" t="n">
         <v>19.5</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BZ10" t="n">
         <v>10.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G11" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I11" t="n">
         <v>2.5</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.52</v>
       </c>
       <c r="J11" t="n">
         <v>3.75</v>
@@ -3167,7 +3167,7 @@
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.23</v>
@@ -3176,25 +3176,25 @@
         <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R11" t="n">
         <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U11" t="n">
         <v>2.58</v>
       </c>
       <c r="V11" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
         <v>21</v>
@@ -3209,7 +3209,7 @@
         <v>34</v>
       </c>
       <c r="AB11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC11" t="n">
         <v>8.800000000000001</v>
@@ -3221,10 +3221,10 @@
         <v>24</v>
       </c>
       <c r="AF11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
         <v>15</v>
@@ -3233,25 +3233,25 @@
         <v>32</v>
       </c>
       <c r="AJ11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM11" t="n">
-        <v>190</v>
+        <v>65</v>
       </c>
       <c r="AN11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO11" t="n">
         <v>15</v>
       </c>
       <c r="AP11" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ11" t="n">
         <v>12.5</v>
@@ -3266,7 +3266,7 @@
         <v>14</v>
       </c>
       <c r="AU11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV11" t="n">
         <v>10.5</v>
@@ -3278,7 +3278,7 @@
         <v>20</v>
       </c>
       <c r="AY11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ11" t="n">
         <v>13.5</v>
@@ -3290,10 +3290,10 @@
         <v>40</v>
       </c>
       <c r="BC11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD11" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BE11" t="n">
         <v>50</v>
@@ -3305,68 +3305,68 @@
         <v>13.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>85</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN11" t="n">
         <v>6.4</v>
       </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BO11" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BP11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS11" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>11.5</v>
       </c>
       <c r="BT11" t="n">
         <v>5.7</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="BV11" t="n">
         <v>17</v>
       </c>
       <c r="BW11" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BX11" t="n">
         <v>26</v>
       </c>
       <c r="BY11" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BZ11" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
         <v>2.04</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
         <v>4.3</v>
@@ -3424,7 +3424,7 @@
         <v>3.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P12" t="n">
         <v>1.98</v>
@@ -3436,13 +3436,13 @@
         <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="U12" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V12" t="n">
         <v>1.3</v>
@@ -3451,10 +3451,10 @@
         <v>1.96</v>
       </c>
       <c r="X12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z12" t="n">
         <v>32</v>
@@ -3463,31 +3463,31 @@
         <v>90</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE12" t="n">
         <v>55</v>
       </c>
       <c r="AF12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG12" t="n">
         <v>11</v>
       </c>
       <c r="AH12" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI12" t="n">
         <v>60</v>
       </c>
       <c r="AJ12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -3496,79 +3496,79 @@
         <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>320</v>
+        <v>190</v>
       </c>
       <c r="AN12" t="n">
         <v>14.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT12" t="n">
         <v>8.4</v>
       </c>
-      <c r="AT12" t="n">
-        <v>8</v>
-      </c>
       <c r="AU12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV12" t="n">
         <v>14.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AX12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BB12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BE12" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="BF12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BH12" t="n">
         <v>3.6</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ12" t="n">
         <v>10</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3577,7 +3577,7 @@
         <v>9.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO12" t="n">
         <v>4.1</v>
@@ -3586,7 +3586,7 @@
         <v>15</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BR12" t="n">
         <v>29</v>
@@ -3607,20 +3607,20 @@
         <v>8</v>
       </c>
       <c r="BX12" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ12" t="n">
         <v>25</v>
       </c>
       <c r="CA12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -3651,230 +3651,230 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="G13" t="n">
-        <v>100</v>
+        <v>2.02</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N13" t="n">
         <v>2.52</v>
       </c>
-      <c r="K13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1.25</v>
-      </c>
       <c r="O13" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.61</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.11</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>6.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>950</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF13" t="n">
-        <v>500</v>
+        <v>10.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ13" t="n">
-        <v>900</v>
+        <v>25</v>
       </c>
       <c r="AK13" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AL13" t="n">
         <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.29</v>
+        <v>4.3</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.29</v>
+        <v>5.3</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.29</v>
+        <v>7.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.29</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.18</v>
+        <v>4.1</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.25</v>
+        <v>4.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.29</v>
+        <v>6.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.29</v>
+        <v>8</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.23</v>
+        <v>4.7</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.23</v>
+        <v>5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.29</v>
+        <v>6.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.29</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.27</v>
+        <v>6.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.27</v>
+        <v>6.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.29</v>
+        <v>7.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.29</v>
+        <v>8.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.26</v>
+        <v>6.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -3905,46 +3905,46 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="G14" t="n">
-        <v>600</v>
+        <v>12</v>
       </c>
       <c r="H14" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="I14" t="n">
-        <v>870</v>
+        <v>12</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O14" t="n">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.02</v>
+        <v>2.14</v>
       </c>
       <c r="R14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S14" t="n">
-        <v>1.53</v>
+        <v>1.05</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -3974,7 +3974,7 @@
         <v>950</v>
       </c>
       <c r="AC14" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AD14" t="n">
         <v>950</v>
@@ -4007,58 +4007,58 @@
         <v>500</v>
       </c>
       <c r="AN14" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO14" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="BF14" t="n">
         <v>1.55</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -4159,46 +4159,46 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I15" t="n">
-        <v>870</v>
+        <v>4.6</v>
       </c>
       <c r="J15" t="n">
         <v>2.32</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="P15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.02</v>
+        <v>2.18</v>
       </c>
       <c r="R15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S15" t="n">
-        <v>1.57</v>
+        <v>3.85</v>
       </c>
       <c r="T15" t="n">
         <v>1.11</v>
@@ -4210,7 +4210,7 @@
         <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X15" t="n">
         <v>970</v>
@@ -4261,10 +4261,10 @@
         <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO15" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP15" t="n">
         <v>1.03</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.02</v>
+        <v>1.71</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="H16" t="n">
-        <v>1.02</v>
+        <v>1.92</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1.03</v>
+        <v>2.6</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4437,22 +4437,22 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O16" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.02</v>
+        <v>1.58</v>
       </c>
       <c r="R16" t="n">
         <v>1.12</v>
       </c>
       <c r="S16" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4461,118 +4461,118 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC16" t="n">
         <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AJ16" t="n">
         <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -4667,46 +4667,46 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="G17" t="n">
-        <v>600</v>
+        <v>11.5</v>
       </c>
       <c r="H17" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="I17" t="n">
-        <v>870</v>
+        <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>3.65</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N17" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O17" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.02</v>
+        <v>2.18</v>
       </c>
       <c r="R17" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S17" t="n">
-        <v>1.57</v>
+        <v>3.85</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4736,7 +4736,7 @@
         <v>950</v>
       </c>
       <c r="AC17" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AD17" t="n">
         <v>950</v>
@@ -4769,58 +4769,58 @@
         <v>500</v>
       </c>
       <c r="AN17" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO17" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="BF17" t="n">
         <v>1.55</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -4921,25 +4921,25 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I18" t="n">
         <v>5.3</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
@@ -4966,7 +4966,7 @@
         <v>1.79</v>
       </c>
       <c r="U18" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V18" t="n">
         <v>1.23</v>
@@ -4978,19 +4978,19 @@
         <v>16</v>
       </c>
       <c r="Y18" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z18" t="n">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="AA18" t="n">
         <v>700</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
         <v>20</v>
@@ -5008,7 +5008,7 @@
         <v>19.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="AJ18" t="n">
         <v>21</v>
@@ -5017,13 +5017,13 @@
         <v>20</v>
       </c>
       <c r="AL18" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM18" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO18" t="n">
         <v>280</v>
@@ -5035,70 +5035,70 @@
         <v>16</v>
       </c>
       <c r="AR18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT18" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>8</v>
       </c>
       <c r="AU18" t="n">
         <v>7.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="AX18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY18" t="n">
         <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="BB18" t="n">
         <v>16.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="BH18" t="n">
         <v>3.75</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="BJ18" t="n">
         <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN18" t="n">
         <v>4.7</v>
@@ -5113,10 +5113,10 @@
         <v>9.4</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT18" t="n">
         <v>8.800000000000001</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
         <v>5.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K19" t="n">
         <v>3.9</v>
@@ -5205,7 +5205,7 @@
         <v>1.33</v>
       </c>
       <c r="P19" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q19" t="n">
         <v>2.02</v>
@@ -5217,10 +5217,10 @@
         <v>3.6</v>
       </c>
       <c r="T19" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V19" t="n">
         <v>1.24</v>
@@ -5229,25 +5229,25 @@
         <v>2.12</v>
       </c>
       <c r="X19" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y19" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y19" t="n">
-        <v>18.5</v>
-      </c>
       <c r="Z19" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AA19" t="n">
         <v>900</v>
       </c>
       <c r="AB19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC19" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AC19" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AD19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE19" t="n">
         <v>500</v>
@@ -5256,149 +5256,149 @@
         <v>11</v>
       </c>
       <c r="AG19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
         <v>500</v>
       </c>
       <c r="AJ19" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="AK19" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AM19" t="n">
         <v>580</v>
       </c>
       <c r="AN19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>14</v>
       </c>
-      <c r="AO19" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AR19" t="n">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AU19" t="n">
         <v>7.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AW19" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="AX19" t="n">
         <v>9.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
         <v>17.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="BB19" t="n">
         <v>17</v>
       </c>
       <c r="BC19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.2</v>
+        <v>27</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BG19" t="n">
-        <v>8.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="BJ19" t="n">
         <v>10.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN19" t="n">
         <v>4.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP19" t="n">
         <v>13</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BT19" t="n">
         <v>8.4</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G20" t="n">
         <v>1.78</v>
@@ -5438,13 +5438,13 @@
         <v>4.4</v>
       </c>
       <c r="I20" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J20" t="n">
         <v>4.5</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L20" t="n">
         <v>1.24</v>
@@ -5459,22 +5459,22 @@
         <v>1.15</v>
       </c>
       <c r="P20" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S20" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>2.64</v>
       </c>
       <c r="V20" t="n">
         <v>1.25</v>
@@ -5483,176 +5483,176 @@
         <v>2.26</v>
       </c>
       <c r="X20" t="n">
-        <v>950</v>
+        <v>95</v>
       </c>
       <c r="Y20" t="n">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="Z20" t="n">
         <v>500</v>
       </c>
       <c r="AA20" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB20" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
         <v>500</v>
       </c>
       <c r="AF20" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AG20" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AI20" t="n">
         <v>500</v>
       </c>
       <c r="AJ20" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AL20" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AM20" t="n">
-        <v>580</v>
+        <v>55</v>
       </c>
       <c r="AN20" t="n">
-        <v>29</v>
+        <v>6.4</v>
       </c>
       <c r="AO20" t="n">
         <v>500</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.37</v>
+        <v>5.6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.36</v>
+        <v>5.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.37</v>
+        <v>5.9</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.39</v>
+        <v>6.2</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.33</v>
+        <v>4.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.35</v>
+        <v>4.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.34</v>
+        <v>5.1</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.37</v>
+        <v>5.9</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.35</v>
+        <v>4.8</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.36</v>
+        <v>4.8</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.37</v>
+        <v>6.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.37</v>
+        <v>5.1</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.37</v>
+        <v>4.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.38</v>
+        <v>5.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.39</v>
+        <v>6</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.33</v>
+        <v>3.3</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -5683,22 +5683,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="H21" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L21" t="n">
         <v>1.44</v>
@@ -5707,76 +5707,76 @@
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T21" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.84</v>
-      </c>
       <c r="U21" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V21" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W21" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="X21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA21" t="n">
         <v>900</v>
       </c>
       <c r="AB21" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC21" t="n">
         <v>8</v>
       </c>
       <c r="AD21" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>55</v>
+        <v>320</v>
       </c>
       <c r="AF21" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG21" t="n">
         <v>11</v>
       </c>
       <c r="AH21" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI21" t="n">
         <v>320</v>
       </c>
       <c r="AJ21" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
         <v>150</v>
@@ -5788,19 +5788,19 @@
         <v>21</v>
       </c>
       <c r="AO21" t="n">
-        <v>230</v>
+        <v>55</v>
       </c>
       <c r="AP21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ21" t="n">
         <v>11.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS21" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AT21" t="n">
         <v>8</v>
@@ -5809,10 +5809,10 @@
         <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="AX21" t="n">
         <v>11.5</v>
@@ -5821,92 +5821,92 @@
         <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BB21" t="n">
         <v>10.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.04</v>
+        <v>14.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="G22" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="I22" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J22" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="L22" t="n">
         <v>1.21</v>
@@ -5961,55 +5961,55 @@
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
         <v>1.12</v>
       </c>
       <c r="P22" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="Q22" t="n">
         <v>1.38</v>
       </c>
       <c r="R22" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S22" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="T22" t="n">
         <v>1.48</v>
       </c>
       <c r="U22" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V22" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W22" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="X22" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="Y22" t="n">
         <v>80</v>
       </c>
       <c r="Z22" t="n">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="AA22" t="n">
         <v>500</v>
       </c>
       <c r="AB22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE22" t="n">
         <v>55</v>
@@ -6018,149 +6018,149 @@
         <v>16</v>
       </c>
       <c r="AG22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH22" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI22" t="n">
         <v>100</v>
       </c>
       <c r="AJ22" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK22" t="n">
         <v>15.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM22" t="n">
-        <v>580</v>
+        <v>150</v>
       </c>
       <c r="AN22" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AO22" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="AP22" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="AS22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU22" t="n">
         <v>11.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX22" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY22" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.2</v>
+        <v>18.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG22" t="n">
         <v>7.4</v>
       </c>
-      <c r="BF22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>20</v>
-      </c>
       <c r="BH22" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BI22" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BJ22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BN22" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BP22" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BR22" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BS22" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BU22" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BX22" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BZ22" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA22" t="n">
         <v>4.9</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -6197,10 +6197,10 @@
         <v>2.52</v>
       </c>
       <c r="H23" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I23" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
         <v>4.1</v>
@@ -6212,31 +6212,31 @@
         <v>1.24</v>
       </c>
       <c r="M23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="R23" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="S23" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="T23" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="U23" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="V23" t="n">
         <v>1.52</v>
@@ -6245,176 +6245,176 @@
         <v>1.65</v>
       </c>
       <c r="X23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y23" t="n">
         <v>24</v>
       </c>
       <c r="Z23" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AA23" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AB23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC23" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AF23" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AG23" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AI23" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AJ23" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="AK23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL23" t="n">
         <v>25</v>
       </c>
-      <c r="AL23" t="n">
-        <v>30</v>
-      </c>
       <c r="AM23" t="n">
-        <v>200</v>
+        <v>42</v>
       </c>
       <c r="AN23" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO23" t="n">
         <v>14</v>
       </c>
       <c r="AP23" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ23" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AR23" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA23" t="n">
         <v>15</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>20</v>
       </c>
       <c r="BB23" t="n">
         <v>16</v>
       </c>
       <c r="BC23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD23" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF23" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BG23" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH23" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI23" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BJ23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BK23" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BN23" t="n">
         <v>6.2</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BP23" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BR23" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BS23" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT23" t="n">
         <v>6.8</v>
       </c>
       <c r="BU23" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BV23" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BW23" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX23" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BY23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BZ23" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CA23" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="G24" t="n">
         <v>3</v>
@@ -6457,7 +6457,7 @@
         <v>2.36</v>
       </c>
       <c r="J24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K24" t="n">
         <v>4.6</v>
@@ -6475,22 +6475,22 @@
         <v>1.11</v>
       </c>
       <c r="P24" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R24" t="n">
         <v>2.04</v>
       </c>
       <c r="S24" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="T24" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="U24" t="n">
-        <v>2.66</v>
+        <v>3.3</v>
       </c>
       <c r="V24" t="n">
         <v>1.73</v>
@@ -6499,176 +6499,176 @@
         <v>1.5</v>
       </c>
       <c r="X24" t="n">
-        <v>950</v>
+        <v>95</v>
       </c>
       <c r="Y24" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="Z24" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AA24" t="n">
-        <v>900</v>
+        <v>70</v>
       </c>
       <c r="AB24" t="n">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="AC24" t="n">
-        <v>950</v>
+        <v>12.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AF24" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AG24" t="n">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="AH24" t="n">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="AI24" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AJ24" t="n">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AK24" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AL24" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AM24" t="n">
-        <v>580</v>
+        <v>75</v>
       </c>
       <c r="AN24" t="n">
-        <v>500</v>
+        <v>11.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>500</v>
+        <v>8</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.76</v>
+        <v>27</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.73</v>
+        <v>20</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.73</v>
+        <v>17.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.76</v>
+        <v>28</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.74</v>
+        <v>18.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.62</v>
+        <v>11.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.72</v>
+        <v>16</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.75</v>
+        <v>22</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.65</v>
+        <v>13</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.63</v>
+        <v>12</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.71</v>
+        <v>17</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.77</v>
+        <v>32</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.73</v>
+        <v>18.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.73</v>
+        <v>18.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.75</v>
+        <v>24</v>
       </c>
       <c r="BF24" t="n">
-        <v>3</v>
+        <v>10.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>2.18</v>
+        <v>7.2</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -6699,31 +6699,31 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G25" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I25" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J25" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L25" t="n">
         <v>1.46</v>
       </c>
       <c r="M25" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
         <v>1.38</v>
@@ -6738,127 +6738,127 @@
         <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U25" t="n">
         <v>1.89</v>
       </c>
       <c r="V25" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W25" t="n">
         <v>2.1</v>
       </c>
       <c r="X25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Y25" t="n">
         <v>16</v>
       </c>
       <c r="Z25" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="AA25" t="n">
         <v>900</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE25" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="AF25" t="n">
         <v>11</v>
       </c>
       <c r="AG25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI25" t="n">
         <v>320</v>
       </c>
       <c r="AJ25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL25" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AM25" t="n">
         <v>580</v>
       </c>
       <c r="AN25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>540</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>18</v>
       </c>
-      <c r="AO25" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BA25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BB25" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC25" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BE25" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BH25" t="n">
         <v>3.2</v>
@@ -6876,7 +6876,7 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN25" t="n">
         <v>4.4</v>
@@ -6888,41 +6888,41 @@
         <v>13.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR25" t="n">
         <v>32</v>
       </c>
       <c r="BS25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT25" t="n">
         <v>8.6</v>
       </c>
       <c r="BU25" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BV25" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW25" t="n">
         <v>10.5</v>
       </c>
       <c r="BX25" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ25" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="CA25" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -6953,52 +6953,52 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="G26" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="H26" t="n">
-        <v>1.05</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J26" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O26" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P26" t="n">
-        <v>1.56</v>
+        <v>3.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S26" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="V26" t="n">
         <v>1.16</v>
@@ -7007,166 +7007,166 @@
         <v>2.88</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Y26" t="n">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB26" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.22</v>
+        <v>6.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.18</v>
+        <v>6.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.22</v>
+        <v>7</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.22</v>
+        <v>7.4</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.12</v>
+        <v>5.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.11</v>
+        <v>5.3</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.22</v>
+        <v>6</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.22</v>
+        <v>7</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.22</v>
+        <v>5</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.22</v>
+        <v>4.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.22</v>
+        <v>5.6</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.22</v>
+        <v>6.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.22</v>
+        <v>5.2</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.22</v>
+        <v>5.1</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.22</v>
+        <v>5.9</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.22</v>
+        <v>7</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.22</v>
+        <v>3.25</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.22</v>
+        <v>6.8</v>
       </c>
       <c r="BH26" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN26" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP26" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BR26" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BT26" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV26" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX26" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>
@@ -7207,16 +7207,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G27" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="I27" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J27" t="n">
         <v>3.1</v>
@@ -7231,40 +7231,40 @@
         <v>1.11</v>
       </c>
       <c r="N27" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P27" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R27" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S27" t="n">
         <v>4.8</v>
       </c>
       <c r="T27" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U27" t="n">
         <v>1.87</v>
       </c>
       <c r="V27" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W27" t="n">
         <v>1.5</v>
       </c>
       <c r="X27" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y27" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Z27" t="n">
         <v>23</v>
@@ -7279,13 +7279,13 @@
         <v>8.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AE27" t="n">
         <v>50</v>
       </c>
       <c r="AF27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG27" t="n">
         <v>16</v>
@@ -7306,7 +7306,7 @@
         <v>75</v>
       </c>
       <c r="AM27" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN27" t="n">
         <v>55</v>
@@ -7324,7 +7324,7 @@
         <v>13.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AT27" t="n">
         <v>6.6</v>
@@ -7336,7 +7336,7 @@
         <v>10</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AX27" t="n">
         <v>13</v>
@@ -7348,46 +7348,46 @@
         <v>15</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BC27" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH27" t="n">
         <v>2.86</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BJ27" t="n">
         <v>11</v>
       </c>
       <c r="BK27" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN27" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO27" t="n">
         <v>4.3</v>
@@ -7396,13 +7396,13 @@
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT27" t="n">
         <v>5.9</v>
@@ -7414,23 +7414,23 @@
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ27" t="n">
         <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-20 01:38:25</t>
+          <t>2026-07-20 03:48:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -857,88 +857,88 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G2" t="n">
         <v>2.7</v>
       </c>
-      <c r="G2" t="n">
-        <v>2.78</v>
-      </c>
       <c r="H2" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J2" t="n">
         <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R2" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="S2" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="T2" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="U2" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="V2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.58</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.56</v>
-      </c>
       <c r="X2" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
         <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AF2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>15</v>
@@ -947,46 +947,46 @@
         <v>34</v>
       </c>
       <c r="AJ2" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="AK2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM2" t="n">
-        <v>190</v>
+        <v>65</v>
       </c>
       <c r="AN2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR2" t="n">
         <v>18.5</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>18</v>
       </c>
       <c r="AS2" t="n">
         <v>36</v>
       </c>
       <c r="AT2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2" t="n">
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX2" t="n">
         <v>18</v>
@@ -995,43 +995,43 @@
         <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BB2" t="n">
         <v>34</v>
       </c>
       <c r="BC2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BE2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BG2" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BJ2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BM2" t="n">
         <v>13</v>
@@ -1043,13 +1043,13 @@
         <v>5.3</v>
       </c>
       <c r="BP2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BS2" t="n">
         <v>10</v>
@@ -1061,13 +1061,13 @@
         <v>5.4</v>
       </c>
       <c r="BV2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY2" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="I3" t="n">
         <v>1.28</v>
       </c>
       <c r="J3" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
         <v>7.2</v>
@@ -1135,28 +1135,28 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="O3" t="n">
         <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="S3" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="T3" t="n">
         <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V3" t="n">
         <v>4.5</v>
@@ -1165,7 +1165,7 @@
         <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="Y3" t="n">
         <v>11</v>
@@ -1174,37 +1174,37 @@
         <v>9</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AB3" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="AC3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AF3" t="n">
         <v>540</v>
       </c>
       <c r="AG3" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AH3" t="n">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="AI3" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AJ3" t="n">
-        <v>570</v>
+        <v>520</v>
       </c>
       <c r="AK3" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AL3" t="n">
         <v>460</v>
@@ -1213,16 +1213,16 @@
         <v>380</v>
       </c>
       <c r="AN3" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR3" t="n">
         <v>7.8</v>
@@ -1231,10 +1231,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="AU3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AV3" t="n">
         <v>10</v>
@@ -1243,37 +1243,37 @@
         <v>12</v>
       </c>
       <c r="AX3" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.4</v>
+        <v>42</v>
       </c>
       <c r="AZ3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC3" t="n">
         <v>14</v>
       </c>
-      <c r="BA3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>11</v>
-      </c>
       <c r="BD3" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BF3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BI3" t="n">
         <v>4.2</v>
@@ -1288,25 +1288,25 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>13</v>
       </c>
-      <c r="BN3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BT3" t="n">
         <v>3.9</v>
@@ -1324,7 +1324,7 @@
         <v>22</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G4" t="n">
         <v>2.32</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I4" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J4" t="n">
         <v>3.3</v>
@@ -1389,7 +1389,7 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
         <v>1.4</v>
@@ -1404,175 +1404,175 @@
         <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="U4" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
         <v>1.75</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AA4" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AC4" t="n">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>36</v>
       </c>
-      <c r="AH4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>900</v>
-      </c>
       <c r="AK4" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AM4" t="n">
         <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>600</v>
+        <v>29</v>
       </c>
       <c r="AO4" t="n">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.02</v>
+        <v>50</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV4" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.02</v>
+        <v>34</v>
       </c>
       <c r="AX4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.2</v>
+        <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.02</v>
+        <v>44</v>
       </c>
       <c r="BB4" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.99</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.02</v>
+        <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.04</v>
+        <v>60</v>
       </c>
       <c r="BF4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="BG4" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP4" t="n">
         <v>17.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.800000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="BT4" t="n">
         <v>7</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.800000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
@@ -1584,11 +1584,11 @@
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.800000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G5" t="n">
         <v>1.73</v>
       </c>
-      <c r="G5" t="n">
-        <v>1.81</v>
-      </c>
       <c r="H5" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>1.5</v>
@@ -1643,40 +1643,40 @@
         <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P5" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T5" t="n">
         <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="X5" t="n">
         <v>12</v>
       </c>
       <c r="Y5" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z5" t="n">
         <v>500</v>
@@ -1685,19 +1685,19 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
@@ -1709,22 +1709,22 @@
         <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AK5" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="AO5" t="n">
-        <v>700</v>
+        <v>220</v>
       </c>
       <c r="AP5" t="n">
         <v>10</v>
@@ -1733,25 +1733,25 @@
         <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT5" t="n">
         <v>6.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
         <v>9</v>
@@ -1760,64 +1760,64 @@
         <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="BC5" t="n">
         <v>18</v>
       </c>
       <c r="BD5" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF5" t="n">
         <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH5" t="n">
         <v>3.1</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="BJ5" t="n">
         <v>11.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BU5" t="n">
         <v>6.8</v>
@@ -1826,13 +1826,13 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -1879,19 +1879,19 @@
         <v>6.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="I6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="J6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K6" t="n">
         <v>4.4</v>
       </c>
-      <c r="K6" t="n">
-        <v>4.6</v>
-      </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1903,10 +1903,10 @@
         <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="R6" t="n">
         <v>1.48</v>
@@ -1921,7 +1921,7 @@
         <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.19</v>
@@ -1930,7 +1930,7 @@
         <v>19</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Z6" t="n">
         <v>10.5</v>
@@ -1939,7 +1939,7 @@
         <v>16</v>
       </c>
       <c r="AB6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC6" t="n">
         <v>9.800000000000001</v>
@@ -1963,7 +1963,7 @@
         <v>32</v>
       </c>
       <c r="AJ6" t="n">
-        <v>160</v>
+        <v>690</v>
       </c>
       <c r="AK6" t="n">
         <v>80</v>
@@ -1978,10 +1978,10 @@
         <v>85</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AP6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>8.800000000000001</v>
@@ -1993,7 +1993,7 @@
         <v>14</v>
       </c>
       <c r="AT6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU6" t="n">
         <v>9</v>
@@ -2005,7 +2005,7 @@
         <v>14.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AY6" t="n">
         <v>20</v>
@@ -2020,19 +2020,19 @@
         <v>44</v>
       </c>
       <c r="BC6" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE6" t="n">
         <v>65</v>
       </c>
-      <c r="BD6" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>38</v>
-      </c>
       <c r="BF6" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH6" t="n">
         <v>3.8</v>
@@ -2044,7 +2044,7 @@
         <v>10</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL6" t="n">
         <v>130</v>
@@ -2074,13 +2074,13 @@
         <v>4.3</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV6" t="n">
         <v>10.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX6" t="n">
         <v>25</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G7" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H7" t="n">
         <v>2.82</v>
       </c>
       <c r="I7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J7" t="n">
         <v>3.15</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.2</v>
       </c>
       <c r="K7" t="n">
         <v>3.45</v>
@@ -2148,16 +2148,16 @@
         <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O7" t="n">
         <v>1.39</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q7" t="n">
         <v>2.2</v>
@@ -2169,7 +2169,7 @@
         <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
         <v>2</v>
@@ -2181,7 +2181,7 @@
         <v>1.53</v>
       </c>
       <c r="X7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="n">
         <v>11</v>
@@ -2202,19 +2202,19 @@
         <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG7" t="n">
         <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="AI7" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AJ7" t="n">
         <v>48</v>
@@ -2229,7 +2229,7 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO7" t="n">
         <v>42</v>
@@ -2238,7 +2238,7 @@
         <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR7" t="n">
         <v>16.5</v>
@@ -2247,13 +2247,13 @@
         <v>38</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU7" t="n">
         <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW7" t="n">
         <v>30</v>
@@ -2274,7 +2274,7 @@
         <v>18</v>
       </c>
       <c r="BC7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD7" t="n">
         <v>38</v>
@@ -2283,31 +2283,31 @@
         <v>24</v>
       </c>
       <c r="BF7" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO7" t="n">
         <v>4.3</v>
@@ -2316,41 +2316,41 @@
         <v>24</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT7" t="n">
         <v>6.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BV7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>8</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -2381,64 +2381,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="G8" t="n">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="H8" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>4.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="K8" t="n">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
         <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="R8" t="n">
         <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="X8" t="n">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
         <v>500</v>
@@ -2447,154 +2447,154 @@
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>950</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>42</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>950</v>
+        <v>16.5</v>
       </c>
       <c r="AE8" t="n">
         <v>500</v>
       </c>
       <c r="AF8" t="n">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>950</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AK8" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AL8" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>600</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.28</v>
+        <v>3.65</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.26</v>
+        <v>3.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.27</v>
+        <v>4.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.28</v>
+        <v>4.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.24</v>
+        <v>3.3</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.17</v>
+        <v>3.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.26</v>
+        <v>3.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.28</v>
+        <v>4.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.26</v>
+        <v>3.75</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.25</v>
+        <v>3.55</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.26</v>
+        <v>4</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.28</v>
+        <v>4.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.27</v>
+        <v>4.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.27</v>
+        <v>4.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.27</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.28</v>
+        <v>4.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.55</v>
+        <v>4.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -2635,61 +2635,61 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="G9" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="I9" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="J9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="V9" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="n">
         <v>8</v>
@@ -2698,167 +2698,167 @@
         <v>8.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
         <v>10.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AG9" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AH9" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ9" t="n">
-        <v>470</v>
+        <v>340</v>
       </c>
       <c r="AK9" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="AL9" t="n">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="AM9" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AN9" t="n">
-        <v>310</v>
+        <v>230</v>
       </c>
       <c r="AO9" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AP9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>6.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS9" t="n">
         <v>10.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU9" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AW9" t="n">
         <v>14</v>
       </c>
       <c r="AX9" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AY9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ9" t="n">
         <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BC9" t="n">
-        <v>9.4</v>
+        <v>70</v>
       </c>
       <c r="BD9" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BE9" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="BF9" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BI9" t="n">
         <v>2.9</v>
       </c>
       <c r="BJ9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
         <v>12.5</v>
       </c>
-      <c r="BK9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BN9" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BU9" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="BV9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BW9" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BX9" t="n">
         <v>28</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -2889,61 +2889,61 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I10" t="n">
         <v>1.42</v>
       </c>
       <c r="J10" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="K10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L10" t="n">
         <v>1.25</v>
       </c>
       <c r="M10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.14</v>
       </c>
       <c r="P10" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="S10" t="n">
         <v>2.16</v>
       </c>
       <c r="T10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U10" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V10" t="n">
         <v>3.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y10" t="n">
         <v>14</v>
@@ -2955,7 +2955,7 @@
         <v>12.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC10" t="n">
         <v>13.5</v>
@@ -2967,7 +2967,7 @@
         <v>13.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AG10" t="n">
         <v>30</v>
@@ -2976,13 +2976,13 @@
         <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ10" t="n">
         <v>240</v>
       </c>
       <c r="AK10" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AL10" t="n">
         <v>75</v>
@@ -2997,7 +2997,7 @@
         <v>4.4</v>
       </c>
       <c r="AP10" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AQ10" t="n">
         <v>12.5</v>
@@ -3009,19 +3009,19 @@
         <v>12</v>
       </c>
       <c r="AT10" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AU10" t="n">
         <v>12</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW10" t="n">
         <v>12</v>
       </c>
       <c r="AX10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AY10" t="n">
         <v>27</v>
@@ -3033,28 +3033,28 @@
         <v>23</v>
       </c>
       <c r="BB10" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="BC10" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BD10" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BE10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF10" t="n">
         <v>60</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH10" t="n">
         <v>5.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3066,43 +3066,43 @@
         <v>95</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN10" t="n">
         <v>12</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BP10" t="n">
         <v>60</v>
       </c>
       <c r="BQ10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR10" t="n">
         <v>50</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT10" t="n">
         <v>4.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BV10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BW10" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BX10" t="n">
         <v>19.5</v>
       </c>
       <c r="BY10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ10" t="n">
         <v>10.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="H11" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="J11" t="n">
         <v>3.75</v>
@@ -3176,109 +3176,109 @@
         <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R11" t="n">
         <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T11" t="n">
         <v>1.6</v>
       </c>
       <c r="U11" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="X11" t="n">
         <v>21</v>
       </c>
       <c r="Y11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AB11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI11" t="n">
         <v>32</v>
       </c>
       <c r="AJ11" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AK11" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN11" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT11" t="n">
         <v>14</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>13.5</v>
@@ -3287,25 +3287,25 @@
         <v>28</v>
       </c>
       <c r="BB11" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BC11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BD11" t="n">
         <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BF11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BG11" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI11" t="n">
         <v>3.2</v>
@@ -3320,43 +3320,43 @@
         <v>85</v>
       </c>
       <c r="BM11" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO11" t="n">
         <v>4.8</v>
       </c>
       <c r="BP11" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>14.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT11" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BX11" t="n">
         <v>26</v>
       </c>
       <c r="BY11" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ11" t="n">
         <v>19</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K12" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.4</v>
@@ -3421,7 +3421,7 @@
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
         <v>1.32</v>
@@ -3430,49 +3430,49 @@
         <v>1.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
         <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U12" t="n">
         <v>2.12</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="X12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z12" t="n">
         <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC12" t="n">
         <v>8.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF12" t="n">
         <v>13</v>
@@ -3487,7 +3487,7 @@
         <v>60</v>
       </c>
       <c r="AJ12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -3499,28 +3499,28 @@
         <v>190</v>
       </c>
       <c r="AN12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
         <v>55</v>
       </c>
       <c r="AP12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AT12" t="n">
         <v>8.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV12" t="n">
         <v>14.5</v>
@@ -3532,10 +3532,10 @@
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA12" t="n">
         <v>44</v>
@@ -3547,7 +3547,7 @@
         <v>18</v>
       </c>
       <c r="BD12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE12" t="n">
         <v>70</v>
@@ -3556,7 +3556,7 @@
         <v>12</v>
       </c>
       <c r="BG12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BH12" t="n">
         <v>3.6</v>
@@ -3571,16 +3571,16 @@
         <v>7.2</v>
       </c>
       <c r="BL12" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM12" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN12" t="n">
         <v>5</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP12" t="n">
         <v>15</v>
@@ -3592,35 +3592,35 @@
         <v>29</v>
       </c>
       <c r="BS12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT12" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>7.8</v>
       </c>
       <c r="BU12" t="n">
         <v>5.7</v>
       </c>
       <c r="BV12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CA12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="G13" t="n">
         <v>2.02</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J13" t="n">
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L13" t="n">
         <v>1.52</v>
@@ -3678,13 +3678,13 @@
         <v>2.52</v>
       </c>
       <c r="O13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P13" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R13" t="n">
         <v>1.17</v>
@@ -3696,22 +3696,22 @@
         <v>2.26</v>
       </c>
       <c r="U13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
         <v>1.98</v>
       </c>
       <c r="X13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y13" t="n">
         <v>14</v>
       </c>
       <c r="Z13" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AA13" t="n">
         <v>900</v>
@@ -3747,7 +3747,7 @@
         <v>40</v>
       </c>
       <c r="AL13" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AM13" t="n">
         <v>500</v>
@@ -3762,13 +3762,13 @@
         <v>4.3</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT13" t="n">
         <v>4.1</v>
@@ -3777,40 +3777,40 @@
         <v>4.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AZ13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC13" t="n">
         <v>6.8</v>
       </c>
-      <c r="BA13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC13" t="n">
+      <c r="BD13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF13" t="n">
         <v>6.6</v>
       </c>
-      <c r="BD13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH13" t="n">
         <v>2.74</v>
@@ -3822,16 +3822,16 @@
         <v>13.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO13" t="n">
         <v>3.1</v>
@@ -3840,41 +3840,41 @@
         <v>16.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BT13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.08</v>
+        <v>2.46</v>
       </c>
       <c r="G14" t="n">
         <v>12</v>
@@ -3914,7 +3914,7 @@
         <v>2.08</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>4.1</v>
       </c>
       <c r="J14" t="n">
         <v>2.62</v>
@@ -3938,7 +3938,7 @@
         <v>1.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R14" t="n">
         <v>1.13</v>
@@ -3953,7 +3953,7 @@
         <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="W14" t="n">
         <v>1.32</v>
@@ -4007,58 +4007,58 @@
         <v>500</v>
       </c>
       <c r="AN14" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.23</v>
       </c>
       <c r="AR14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AS14" t="n">
         <v>1.24</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.25</v>
       </c>
       <c r="AT14" t="n">
         <v>1.23</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AV14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AW14" t="n">
         <v>1.24</v>
       </c>
-      <c r="AW14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AX14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AZ14" t="n">
         <v>1.23</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BF14" t="n">
         <v>1.55</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="G15" t="n">
         <v>4.6</v>
       </c>
       <c r="H15" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J15" t="n">
         <v>2.32</v>
@@ -4183,22 +4183,22 @@
         <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P15" t="n">
         <v>1.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.18</v>
+        <v>2.52</v>
       </c>
       <c r="R15" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S15" t="n">
-        <v>3.85</v>
+        <v>1.05</v>
       </c>
       <c r="T15" t="n">
         <v>1.11</v>
@@ -4210,7 +4210,7 @@
         <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X15" t="n">
         <v>970</v>
@@ -4261,58 +4261,58 @@
         <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="BF15" t="n">
         <v>1.55</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="G16" t="n">
         <v>4.1</v>
@@ -4437,22 +4437,22 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.35</v>
       </c>
       <c r="P16" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="R16" t="n">
         <v>1.12</v>
       </c>
       <c r="S16" t="n">
-        <v>1.59</v>
+        <v>1.05</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4464,16 +4464,16 @@
         <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y16" t="n">
         <v>950</v>
       </c>
       <c r="Z16" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AA16" t="n">
         <v>900</v>
@@ -4482,16 +4482,16 @@
         <v>950</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD16" t="n">
         <v>950</v>
       </c>
       <c r="AE16" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AF16" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AG16" t="n">
         <v>950</v>
@@ -4500,19 +4500,19 @@
         <v>950</v>
       </c>
       <c r="AI16" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK16" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AL16" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN16" t="n">
         <v>600</v>
@@ -4521,52 +4521,52 @@
         <v>600</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BF16" t="n">
         <v>1.55</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -4667,46 +4667,46 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
         <v>11.5</v>
       </c>
       <c r="H17" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
         <v>2.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>5.7</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O17" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="P17" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.18</v>
+        <v>1.58</v>
       </c>
       <c r="R17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S17" t="n">
-        <v>3.85</v>
+        <v>1.02</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4769,16 +4769,16 @@
         <v>500</v>
       </c>
       <c r="AN17" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
         <v>1.15</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AR17" t="n">
         <v>1.22</v>
@@ -4787,13 +4787,13 @@
         <v>1.23</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AW17" t="n">
         <v>1.23</v>
@@ -4802,7 +4802,7 @@
         <v>1.22</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AZ17" t="n">
         <v>1.21</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -4921,31 +4921,31 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G18" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="H18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K18" t="n">
         <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
         <v>1.29</v>
@@ -4954,46 +4954,46 @@
         <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R18" t="n">
         <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
         <v>1.79</v>
       </c>
       <c r="U18" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V18" t="n">
         <v>1.23</v>
       </c>
       <c r="W18" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="X18" t="n">
         <v>16</v>
       </c>
       <c r="Y18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA18" t="n">
         <v>700</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE18" t="n">
         <v>150</v>
@@ -5002,22 +5002,22 @@
         <v>12</v>
       </c>
       <c r="AG18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH18" t="n">
         <v>19.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AJ18" t="n">
         <v>21</v>
       </c>
       <c r="AK18" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM18" t="n">
         <v>500</v>
@@ -5035,22 +5035,22 @@
         <v>16</v>
       </c>
       <c r="AR18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS18" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="AT18" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
@@ -5059,34 +5059,34 @@
         <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB18" t="n">
         <v>16.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE18" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BF18" t="n">
         <v>9.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BJ18" t="n">
         <v>10.5</v>
@@ -5098,16 +5098,16 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN18" t="n">
         <v>4.7</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ18" t="n">
         <v>9.4</v>
@@ -5116,35 +5116,35 @@
         <v>27</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU18" t="n">
         <v>6.6</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ18" t="n">
         <v>22</v>
       </c>
       <c r="CA18" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -5175,19 +5175,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="G19" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="H19" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K19" t="n">
         <v>3.9</v>
@@ -5199,109 +5199,109 @@
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P19" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T19" t="n">
         <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V19" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W19" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AA19" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE19" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AF19" t="n">
         <v>11</v>
       </c>
       <c r="AG19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH19" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM19" t="n">
         <v>500</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>580</v>
       </c>
       <c r="AN19" t="n">
         <v>13.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>600</v>
+        <v>95</v>
       </c>
       <c r="AP19" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR19" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AS19" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="AT19" t="n">
         <v>7.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AW19" t="n">
         <v>46</v>
@@ -5310,28 +5310,28 @@
         <v>9.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB19" t="n">
         <v>17</v>
       </c>
       <c r="BC19" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BD19" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BE19" t="n">
-        <v>11.5</v>
+        <v>80</v>
       </c>
       <c r="BF19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG19" t="n">
         <v>50</v>
@@ -5340,65 +5340,65 @@
         <v>3.4</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BJ19" t="n">
         <v>10.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BP19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT19" t="n">
         <v>8.4</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -5429,25 +5429,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="G20" t="n">
         <v>1.78</v>
       </c>
       <c r="H20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J20" t="n">
         <v>4.4</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>4.9</v>
       </c>
-      <c r="J20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K20" t="n">
-        <v>5.1</v>
-      </c>
       <c r="L20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M20" t="n">
         <v>1.03</v>
@@ -5459,163 +5459,163 @@
         <v>1.15</v>
       </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="R20" t="n">
         <v>1.81</v>
       </c>
       <c r="S20" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="T20" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="U20" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X20" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="Y20" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="Z20" t="n">
         <v>500</v>
       </c>
       <c r="AA20" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB20" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AC20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE20" t="n">
         <v>500</v>
       </c>
       <c r="AF20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH20" t="n">
         <v>16</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>16.5</v>
       </c>
       <c r="AI20" t="n">
         <v>500</v>
       </c>
       <c r="AJ20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK20" t="n">
         <v>17</v>
       </c>
       <c r="AL20" t="n">
-        <v>160</v>
+        <v>28</v>
       </c>
       <c r="AM20" t="n">
-        <v>55</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AO20" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AP20" t="n">
-        <v>5.6</v>
+        <v>15.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="AV20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BH20" t="n">
         <v>5.1</v>
       </c>
-      <c r="AW20" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BI20" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="BJ20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BN20" t="n">
         <v>5.3</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="BP20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ20" t="n">
         <v>5.2</v>
@@ -5624,35 +5624,35 @@
         <v>19.5</v>
       </c>
       <c r="BS20" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT20" t="n">
         <v>9</v>
       </c>
       <c r="BU20" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX20" t="n">
         <v>34</v>
       </c>
       <c r="BY20" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CA20" t="n">
         <v>5.4</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -5683,16 +5683,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="G21" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="H21" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="I21" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
         <v>3.4</v>
@@ -5701,7 +5701,7 @@
         <v>3.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
         <v>1.08</v>
@@ -5719,7 +5719,7 @@
         <v>2.08</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
         <v>3.85</v>
@@ -5728,127 +5728,127 @@
         <v>1.85</v>
       </c>
       <c r="U21" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V21" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="X21" t="n">
         <v>13</v>
       </c>
       <c r="Y21" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AA21" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AB21" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC21" t="n">
         <v>8</v>
       </c>
       <c r="AD21" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AE21" t="n">
-        <v>320</v>
+        <v>60</v>
       </c>
       <c r="AF21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="AJ21" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK21" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="AM21" t="n">
         <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>55</v>
+        <v>230</v>
       </c>
       <c r="AP21" t="n">
         <v>11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AS21" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="AT21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU21" t="n">
         <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW21" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AX21" t="n">
         <v>11.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
         <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="BB21" t="n">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="BC21" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="BD21" t="n">
-        <v>10.5</v>
+        <v>29</v>
       </c>
       <c r="BE21" t="n">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="BF21" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="BJ21" t="n">
         <v>9.800000000000001</v>
@@ -5860,16 +5860,16 @@
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN21" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO21" t="n">
         <v>4.4</v>
       </c>
       <c r="BP21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ21" t="n">
         <v>8.199999999999999</v>
@@ -5878,35 +5878,35 @@
         <v>32</v>
       </c>
       <c r="BS21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT21" t="n">
         <v>7</v>
       </c>
       <c r="BU21" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BV21" t="n">
         <v>32</v>
       </c>
       <c r="BW21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ21" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="CA21" t="n">
         <v>10.5</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -5937,85 +5937,85 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I22" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J22" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K22" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="L22" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="P22" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S22" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="T22" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="U22" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="V22" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W22" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X22" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="Y22" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Z22" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AA22" t="n">
         <v>500</v>
       </c>
       <c r="AB22" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AC22" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE22" t="n">
         <v>55</v>
       </c>
       <c r="AF22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG22" t="n">
         <v>12</v>
@@ -6024,49 +6024,49 @@
         <v>17.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AJ22" t="n">
         <v>19.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM22" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AN22" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AO22" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AP22" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="AQ22" t="n">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="AR22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV22" t="n">
         <v>20</v>
       </c>
-      <c r="AS22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>18</v>
-      </c>
       <c r="AW22" t="n">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="AX22" t="n">
         <v>13.5</v>
@@ -6078,10 +6078,10 @@
         <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>18.5</v>
+        <v>32</v>
       </c>
       <c r="BB22" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC22" t="n">
         <v>12.5</v>
@@ -6090,22 +6090,22 @@
         <v>18.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="BH22" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BI22" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BJ22" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK22" t="n">
         <v>5.4</v>
@@ -6114,28 +6114,28 @@
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BN22" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BO22" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT22" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>10</v>
       </c>
       <c r="BU22" t="n">
         <v>5</v>
@@ -6150,17 +6150,17 @@
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BZ22" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA22" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -6194,10 +6194,10 @@
         <v>2.42</v>
       </c>
       <c r="G23" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H23" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="I23" t="n">
         <v>2.9</v>
@@ -6206,7 +6206,7 @@
         <v>4.1</v>
       </c>
       <c r="K23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.24</v>
@@ -6218,19 +6218,19 @@
         <v>7.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P23" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="R23" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="S23" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="T23" t="n">
         <v>1.43</v>
@@ -6242,7 +6242,7 @@
         <v>1.52</v>
       </c>
       <c r="W23" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X23" t="n">
         <v>36</v>
@@ -6254,7 +6254,7 @@
         <v>26</v>
       </c>
       <c r="AA23" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AB23" t="n">
         <v>21</v>
@@ -6272,7 +6272,7 @@
         <v>23</v>
       </c>
       <c r="AG23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH23" t="n">
         <v>14</v>
@@ -6281,7 +6281,7 @@
         <v>27</v>
       </c>
       <c r="AJ23" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK23" t="n">
         <v>22</v>
@@ -6296,19 +6296,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AO23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP23" t="n">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="AQ23" t="n">
         <v>20</v>
       </c>
       <c r="AR23" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AS23" t="n">
-        <v>9.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="AT23" t="n">
         <v>18.5</v>
@@ -6320,7 +6320,7 @@
         <v>12.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX23" t="n">
         <v>20</v>
@@ -6332,19 +6332,19 @@
         <v>12</v>
       </c>
       <c r="BA23" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BB23" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>19</v>
       </c>
       <c r="BD23" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BE23" t="n">
-        <v>9.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BF23" t="n">
         <v>8.6</v>
@@ -6356,7 +6356,7 @@
         <v>5.2</v>
       </c>
       <c r="BI23" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BJ23" t="n">
         <v>8.4</v>
@@ -6368,7 +6368,7 @@
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN23" t="n">
         <v>6.2</v>
@@ -6380,31 +6380,31 @@
         <v>15.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR23" t="n">
         <v>21</v>
       </c>
       <c r="BS23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT23" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU23" t="n">
         <v>4.7</v>
       </c>
       <c r="BV23" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX23" t="n">
         <v>22</v>
       </c>
       <c r="BY23" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ23" t="n">
         <v>12</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="G24" t="n">
         <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I24" t="n">
         <v>2.36</v>
@@ -6475,10 +6475,10 @@
         <v>1.11</v>
       </c>
       <c r="P24" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R24" t="n">
         <v>2.04</v>
@@ -6490,7 +6490,7 @@
         <v>1.38</v>
       </c>
       <c r="U24" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V24" t="n">
         <v>1.73</v>
@@ -6499,19 +6499,19 @@
         <v>1.5</v>
       </c>
       <c r="X24" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="Y24" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB24" t="n">
         <v>32</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>40</v>
       </c>
       <c r="AC24" t="n">
         <v>12.5</v>
@@ -6523,10 +6523,10 @@
         <v>21</v>
       </c>
       <c r="AF24" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AG24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH24" t="n">
         <v>14</v>
@@ -6538,34 +6538,34 @@
         <v>110</v>
       </c>
       <c r="AK24" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL24" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM24" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AN24" t="n">
         <v>11.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP24" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AQ24" t="n">
         <v>20</v>
       </c>
       <c r="AR24" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AS24" t="n">
         <v>28</v>
       </c>
       <c r="AT24" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AU24" t="n">
         <v>11</v>
@@ -6574,10 +6574,10 @@
         <v>11.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AY24" t="n">
         <v>13</v>
@@ -6586,19 +6586,19 @@
         <v>12</v>
       </c>
       <c r="BA24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC24" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BD24" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BE24" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BF24" t="n">
         <v>10.5</v>
@@ -6607,68 +6607,68 @@
         <v>7.2</v>
       </c>
       <c r="BH24" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BI24" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BJ24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BK24" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN24" t="n">
         <v>7.2</v>
       </c>
       <c r="BO24" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT24" t="n">
         <v>6.4</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV24" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CA24" t="n">
         <v>5.9</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G25" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H25" t="n">
         <v>4.8</v>
       </c>
       <c r="I25" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J25" t="n">
         <v>3.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L25" t="n">
         <v>1.46</v>
@@ -6732,19 +6732,19 @@
         <v>1.76</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R25" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T25" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U25" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V25" t="n">
         <v>1.22</v>
@@ -6756,7 +6756,7 @@
         <v>12</v>
       </c>
       <c r="Y25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z25" t="n">
         <v>90</v>
@@ -6771,7 +6771,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE25" t="n">
         <v>700</v>
@@ -6780,7 +6780,7 @@
         <v>11</v>
       </c>
       <c r="AG25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH25" t="n">
         <v>22</v>
@@ -6789,13 +6789,13 @@
         <v>320</v>
       </c>
       <c r="AJ25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK25" t="n">
         <v>23</v>
       </c>
       <c r="AL25" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AM25" t="n">
         <v>580</v>
@@ -6804,7 +6804,7 @@
         <v>16</v>
       </c>
       <c r="AO25" t="n">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="AP25" t="n">
         <v>10</v>
@@ -6813,10 +6813,10 @@
         <v>13.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT25" t="n">
         <v>6.8</v>
@@ -6828,7 +6828,7 @@
         <v>17.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX25" t="n">
         <v>9.4</v>
@@ -6840,7 +6840,7 @@
         <v>18</v>
       </c>
       <c r="BA25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB25" t="n">
         <v>18</v>
@@ -6849,22 +6849,22 @@
         <v>19</v>
       </c>
       <c r="BD25" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="BE25" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BF25" t="n">
         <v>13.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH25" t="n">
         <v>3.2</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ25" t="n">
         <v>11</v>
@@ -6876,7 +6876,7 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN25" t="n">
         <v>4.4</v>
@@ -6888,41 +6888,41 @@
         <v>13.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="BR25" t="n">
         <v>32</v>
       </c>
       <c r="BS25" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT25" t="n">
         <v>8.6</v>
       </c>
       <c r="BU25" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX25" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CA25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="O26" t="n">
         <v>1.13</v>
@@ -6986,19 +6986,19 @@
         <v>3.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R26" t="n">
         <v>1.9</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T26" t="n">
         <v>1.57</v>
       </c>
       <c r="U26" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V26" t="n">
         <v>1.16</v>
@@ -7136,7 +7136,7 @@
         <v>4.9</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="BP26" t="n">
         <v>9</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>
@@ -7207,19 +7207,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H27" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="I27" t="n">
         <v>2.98</v>
       </c>
       <c r="J27" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K27" t="n">
         <v>3.2</v>
@@ -7231,16 +7231,16 @@
         <v>1.11</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O27" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P27" t="n">
         <v>1.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R27" t="n">
         <v>1.22</v>
@@ -7249,7 +7249,7 @@
         <v>4.8</v>
       </c>
       <c r="T27" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U27" t="n">
         <v>1.87</v>
@@ -7258,16 +7258,16 @@
         <v>1.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X27" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y27" t="n">
         <v>9.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA27" t="n">
         <v>65</v>
@@ -7285,7 +7285,7 @@
         <v>50</v>
       </c>
       <c r="AF27" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AG27" t="n">
         <v>16</v>
@@ -7306,7 +7306,7 @@
         <v>75</v>
       </c>
       <c r="AM27" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN27" t="n">
         <v>55</v>
@@ -7324,7 +7324,7 @@
         <v>13.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT27" t="n">
         <v>6.6</v>
@@ -7354,19 +7354,19 @@
         <v>4.8</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BD27" t="n">
         <v>4.9</v>
       </c>
       <c r="BE27" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF27" t="n">
         <v>4.9</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH27" t="n">
         <v>2.86</v>
@@ -7384,10 +7384,10 @@
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN27" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BO27" t="n">
         <v>4.3</v>
@@ -7405,7 +7405,7 @@
         <v>11</v>
       </c>
       <c r="BT27" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU27" t="n">
         <v>4.4</v>
@@ -7414,7 +7414,7 @@
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-20 03:48:15</t>
+          <t>2026-07-20 05:58:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="I2" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -884,10 +884,10 @@
         <v>5.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q2" t="n">
         <v>1.67</v>
@@ -896,19 +896,19 @@
         <v>1.57</v>
       </c>
       <c r="S2" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U2" t="n">
         <v>2.62</v>
       </c>
       <c r="V2" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W2" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
         <v>21</v>
@@ -917,82 +917,82 @@
         <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC2" t="n">
         <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
         <v>25</v>
       </c>
       <c r="AF2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ2" t="n">
         <v>40</v>
       </c>
       <c r="AK2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL2" t="n">
         <v>32</v>
       </c>
       <c r="AM2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>14</v>
       </c>
       <c r="AR2" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS2" t="n">
         <v>36</v>
       </c>
       <c r="AT2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV2" t="n">
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>13.5</v>
@@ -1004,55 +1004,55 @@
         <v>34</v>
       </c>
       <c r="BC2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE2" t="n">
         <v>50</v>
       </c>
       <c r="BF2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BH2" t="n">
         <v>4.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL2" t="n">
         <v>80</v>
       </c>
       <c r="BM2" t="n">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="BN2" t="n">
         <v>5.9</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR2" t="n">
         <v>27</v>
       </c>
       <c r="BS2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT2" t="n">
         <v>6</v>
@@ -1061,16 +1061,16 @@
         <v>5.4</v>
       </c>
       <c r="BV2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -1111,220 +1111,220 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="G3" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="I3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L3" t="n">
         <v>1.28</v>
-      </c>
-      <c r="J3" t="n">
-        <v>7</v>
-      </c>
-      <c r="K3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.27</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="T3" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="U3" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="V3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Y3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AA3" t="n">
         <v>11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>10</v>
       </c>
       <c r="AB3" t="n">
         <v>100</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
         <v>13.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>540</v>
+        <v>120</v>
       </c>
       <c r="AG3" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AH3" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ3" t="n">
-        <v>520</v>
+        <v>570</v>
       </c>
       <c r="AK3" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="AL3" t="n">
-        <v>460</v>
+        <v>140</v>
       </c>
       <c r="AM3" t="n">
         <v>380</v>
       </c>
       <c r="AN3" t="n">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="AO3" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="AP3" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR3" t="n">
         <v>7.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AU3" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AW3" t="n">
         <v>12</v>
       </c>
       <c r="AX3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
         <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BF3" t="n">
         <v>15</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BH3" t="n">
         <v>4.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BV3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BW3" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BX3" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G4" t="n">
         <v>2.32</v>
       </c>
       <c r="H4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="n">
         <v>3.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.47</v>
@@ -1404,10 +1404,10 @@
         <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U4" t="n">
         <v>2</v>
@@ -1416,10 +1416,10 @@
         <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y4" t="n">
         <v>13.5</v>
@@ -1428,19 +1428,19 @@
         <v>27</v>
       </c>
       <c r="AA4" t="n">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="AB4" t="n">
         <v>9</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD4" t="n">
         <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
         <v>14</v>
@@ -1452,85 +1452,85 @@
         <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
         <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
         <v>50</v>
       </c>
       <c r="AT4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU4" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU4" t="n">
-        <v>6</v>
-      </c>
       <c r="AV4" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
         <v>44</v>
       </c>
       <c r="BB4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BC4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF4" t="n">
         <v>20</v>
       </c>
-      <c r="BD4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>17</v>
-      </c>
       <c r="BG4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH4" t="n">
         <v>3.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="BJ4" t="n">
         <v>10.5</v>
@@ -1542,13 +1542,13 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BN4" t="n">
         <v>5</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BP4" t="n">
         <v>17.5</v>
@@ -1560,7 +1560,7 @@
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT4" t="n">
         <v>7</v>
@@ -1572,13 +1572,13 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.44</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -1619,64 +1619,64 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="G5" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="I5" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O5" t="n">
         <v>1.39</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W5" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="X5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="Z5" t="n">
         <v>500</v>
@@ -1685,34 +1685,34 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI5" t="n">
         <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>27</v>
+        <v>15.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL5" t="n">
         <v>130</v>
@@ -1721,73 +1721,73 @@
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO5" t="n">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="AP5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR5" t="n">
         <v>10</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AS5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV5" t="n">
         <v>18.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AY5" t="n">
         <v>9</v>
       </c>
       <c r="AZ5" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>10.5</v>
+        <v>22</v>
       </c>
       <c r="BE5" t="n">
         <v>11.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK5" t="n">
         <v>6.8</v>
@@ -1796,43 +1796,43 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="BP5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT5" t="n">
         <v>11</v>
       </c>
-      <c r="BT5" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BU5" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -1882,37 +1882,37 @@
         <v>1.64</v>
       </c>
       <c r="I6" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R6" t="n">
         <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T6" t="n">
         <v>1.84</v>
@@ -1921,7 +1921,7 @@
         <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="W6" t="n">
         <v>1.19</v>
@@ -1939,7 +1939,7 @@
         <v>16</v>
       </c>
       <c r="AB6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC6" t="n">
         <v>9.800000000000001</v>
@@ -1978,7 +1978,7 @@
         <v>85</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP6" t="n">
         <v>16.5</v>
@@ -1999,7 +1999,7 @@
         <v>9</v>
       </c>
       <c r="AV6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
         <v>14.5</v>
@@ -2020,16 +2020,16 @@
         <v>44</v>
       </c>
       <c r="BC6" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BD6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BE6" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF6" t="n">
         <v>65</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>36</v>
       </c>
       <c r="BG6" t="n">
         <v>7.8</v>
@@ -2044,22 +2044,22 @@
         <v>10</v>
       </c>
       <c r="BK6" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>130</v>
       </c>
       <c r="BM6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BP6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BQ6" t="n">
         <v>12</v>
@@ -2068,25 +2068,25 @@
         <v>55</v>
       </c>
       <c r="BS6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BT6" t="n">
         <v>4.3</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BV6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BX6" t="n">
         <v>25</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -2127,31 +2127,31 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="H7" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="J7" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.39</v>
@@ -2166,7 +2166,7 @@
         <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
         <v>1.83</v>
@@ -2175,61 +2175,61 @@
         <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AA7" t="n">
         <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC7" t="n">
         <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF7" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AG7" t="n">
         <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK7" t="n">
         <v>90</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>36</v>
-      </c>
       <c r="AL7" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AM7" t="n">
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO7" t="n">
         <v>42</v>
@@ -2238,37 +2238,37 @@
         <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS7" t="n">
         <v>16.5</v>
       </c>
-      <c r="AS7" t="n">
-        <v>38</v>
-      </c>
       <c r="AT7" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU7" t="n">
         <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AX7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY7" t="n">
         <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="BB7" t="n">
         <v>18</v>
@@ -2277,16 +2277,16 @@
         <v>25</v>
       </c>
       <c r="BD7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE7" t="n">
         <v>24</v>
       </c>
       <c r="BF7" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BG7" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="BH7" t="n">
         <v>3.15</v>
@@ -2298,22 +2298,22 @@
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
         <v>7.4</v>
@@ -2325,16 +2325,16 @@
         <v>8.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BU7" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BV7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -2381,166 +2381,166 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="G8" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="J8" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P8" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="U8" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W8" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="X8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="n">
         <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AA8" t="n">
-        <v>900</v>
+        <v>250</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
         <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AF8" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI8" t="n">
-        <v>330</v>
+        <v>160</v>
       </c>
       <c r="AJ8" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AK8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.65</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.6</v>
+        <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.3</v>
+        <v>7.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.75</v>
+        <v>12.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.55</v>
+        <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.3</v>
+        <v>16</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.2</v>
+        <v>23</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.5</v>
+        <v>19.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.1</v>
+        <v>20</v>
       </c>
       <c r="BG8" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BH8" t="n">
         <v>3.4</v>
@@ -2558,37 +2558,37 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>2.32</v>
+        <v>7.2</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BR8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
         <v>6.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="BV8" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -2638,148 +2638,148 @@
         <v>7.6</v>
       </c>
       <c r="G9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="H9" t="n">
         <v>1.51</v>
       </c>
       <c r="I9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T9" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="W9" t="n">
         <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AA9" t="n">
         <v>13.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
         <v>10.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AG9" t="n">
         <v>32</v>
       </c>
       <c r="AH9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ9" t="n">
-        <v>340</v>
+        <v>260</v>
       </c>
       <c r="AK9" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AL9" t="n">
-        <v>260</v>
+        <v>150</v>
       </c>
       <c r="AM9" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AN9" t="n">
         <v>230</v>
       </c>
       <c r="AO9" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AY9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA9" t="n">
         <v>32</v>
       </c>
       <c r="BB9" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="BC9" t="n">
         <v>70</v>
@@ -2788,16 +2788,16 @@
         <v>60</v>
       </c>
       <c r="BE9" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="BF9" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="BG9" t="n">
         <v>7.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BI9" t="n">
         <v>2.9</v>
@@ -2806,59 +2806,59 @@
         <v>12</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BN9" t="n">
         <v>11.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BQ9" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BX9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BZ9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CA9" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="G10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="I10" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
         <v>1.25</v>
@@ -2919,31 +2919,31 @@
         <v>1.14</v>
       </c>
       <c r="P10" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S10" t="n">
         <v>2.16</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U10" t="n">
         <v>2.34</v>
       </c>
       <c r="V10" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y10" t="n">
         <v>14</v>
@@ -2958,16 +2958,16 @@
         <v>42</v>
       </c>
       <c r="AC10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
         <v>10.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AF10" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AG10" t="n">
         <v>30</v>
@@ -2979,10 +2979,10 @@
         <v>26</v>
       </c>
       <c r="AJ10" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AK10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AL10" t="n">
         <v>75</v>
@@ -2994,7 +2994,7 @@
         <v>85</v>
       </c>
       <c r="AO10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AP10" t="n">
         <v>32</v>
@@ -3006,28 +3006,28 @@
         <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AU10" t="n">
         <v>12</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW10" t="n">
         <v>12</v>
       </c>
       <c r="AX10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AY10" t="n">
         <v>27</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA10" t="n">
         <v>23</v>
@@ -3036,7 +3036,7 @@
         <v>65</v>
       </c>
       <c r="BC10" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="BD10" t="n">
         <v>65</v>
@@ -3045,7 +3045,7 @@
         <v>55</v>
       </c>
       <c r="BF10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BG10" t="n">
         <v>4.1</v>
@@ -3054,65 +3054,65 @@
         <v>5.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BL10" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BP10" t="n">
         <v>60</v>
       </c>
       <c r="BQ10" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BR10" t="n">
         <v>50</v>
       </c>
       <c r="BS10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BT10" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BV10" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BX10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BY10" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="G11" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I11" t="n">
         <v>2.58</v>
       </c>
-      <c r="I11" t="n">
-        <v>2.64</v>
-      </c>
       <c r="J11" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
         <v>1.34</v>
@@ -3188,37 +3188,37 @@
         <v>1.6</v>
       </c>
       <c r="U11" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V11" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W11" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB11" t="n">
         <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF11" t="n">
         <v>22</v>
@@ -3236,7 +3236,7 @@
         <v>42</v>
       </c>
       <c r="AK11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
         <v>34</v>
@@ -3245,28 +3245,28 @@
         <v>60</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AO11" t="n">
         <v>16</v>
       </c>
       <c r="AP11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT11" t="n">
         <v>14</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV11" t="n">
         <v>11</v>
@@ -3275,7 +3275,7 @@
         <v>22</v>
       </c>
       <c r="AX11" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY11" t="n">
         <v>11.5</v>
@@ -3287,16 +3287,16 @@
         <v>28</v>
       </c>
       <c r="BB11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD11" t="n">
         <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF11" t="n">
         <v>17</v>
@@ -3305,68 +3305,68 @@
         <v>14.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="BJ11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL11" t="n">
         <v>85</v>
       </c>
       <c r="BM11" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BN11" t="n">
         <v>6.2</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BP11" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BR11" t="n">
         <v>28</v>
       </c>
       <c r="BS11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT11" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU11" t="n">
         <v>5.2</v>
       </c>
       <c r="BV11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -3406,10 +3406,10 @@
         <v>3.95</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
         <v>3.8</v>
@@ -3421,10 +3421,10 @@
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
         <v>1.98</v>
@@ -3433,31 +3433,31 @@
         <v>1.98</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
         <v>1.78</v>
       </c>
       <c r="U12" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W12" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="X12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y12" t="n">
         <v>15</v>
       </c>
-      <c r="Y12" t="n">
-        <v>15.5</v>
-      </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA12" t="n">
         <v>85</v>
@@ -3490,13 +3490,13 @@
         <v>25</v>
       </c>
       <c r="AK12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM12" t="n">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="AN12" t="n">
         <v>15</v>
@@ -3508,16 +3508,16 @@
         <v>13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR12" t="n">
         <v>25</v>
       </c>
       <c r="AS12" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU12" t="n">
         <v>7.4</v>
@@ -3526,101 +3526,101 @@
         <v>14.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BB12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BF12" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BG12" t="n">
         <v>38</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="BJ12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL12" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM12" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="BR12" t="n">
         <v>29</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BT12" t="n">
         <v>7.6</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV12" t="n">
         <v>34</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX12" t="n">
         <v>44</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BZ12" t="n">
         <v>26</v>
       </c>
       <c r="CA12" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G13" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
         <v>6.2</v>
@@ -3666,22 +3666,22 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="M13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N13" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="O13" t="n">
         <v>1.56</v>
       </c>
       <c r="P13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q13" t="n">
         <v>2.66</v>
@@ -3702,7 +3702,7 @@
         <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="X13" t="n">
         <v>8.6</v>
@@ -3753,7 +3753,7 @@
         <v>500</v>
       </c>
       <c r="AN13" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AO13" t="n">
         <v>700</v>
@@ -3765,10 +3765,10 @@
         <v>5.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT13" t="n">
         <v>4.1</v>
@@ -3780,7 +3780,7 @@
         <v>6.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX13" t="n">
         <v>4.8</v>
@@ -3789,13 +3789,13 @@
         <v>5.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BA13" t="n">
         <v>8.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC13" t="n">
         <v>6.8</v>
@@ -3810,13 +3810,13 @@
         <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH13" t="n">
         <v>2.74</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="BJ13" t="n">
         <v>13.5</v>
@@ -3834,7 +3834,7 @@
         <v>4.5</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP13" t="n">
         <v>16.5</v>
@@ -3846,35 +3846,35 @@
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>2.06</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT13" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>2.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>2.06</v>
+        <v>8.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.46</v>
+        <v>2.06</v>
       </c>
       <c r="G14" t="n">
         <v>12</v>
@@ -3914,7 +3914,7 @@
         <v>2.08</v>
       </c>
       <c r="I14" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="J14" t="n">
         <v>2.62</v>
@@ -3929,16 +3929,16 @@
         <v>1.12</v>
       </c>
       <c r="N14" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="O14" t="n">
         <v>1.51</v>
       </c>
       <c r="P14" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="R14" t="n">
         <v>1.13</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -4162,37 +4162,37 @@
         <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H15" t="n">
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
         <v>2.32</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M15" t="n">
         <v>1.01</v>
       </c>
-      <c r="M15" t="n">
-        <v>1.13</v>
-      </c>
       <c r="N15" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="O15" t="n">
-        <v>1.54</v>
+        <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
         <v>1.12</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G16" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="H16" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="I16" t="n">
         <v>13.5</v>
@@ -4428,7 +4428,7 @@
         <v>2.6</v>
       </c>
       <c r="K16" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4437,7 +4437,7 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="O16" t="n">
         <v>1.35</v>
@@ -4452,7 +4452,7 @@
         <v>1.12</v>
       </c>
       <c r="S16" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4464,28 +4464,28 @@
         <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="X16" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Y16" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Z16" t="n">
         <v>500</v>
       </c>
       <c r="AA16" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB16" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AC16" t="n">
+        <v>95</v>
+      </c>
+      <c r="AD16" t="n">
         <v>500</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>950</v>
       </c>
       <c r="AE16" t="n">
         <v>500</v>
@@ -4494,85 +4494,85 @@
         <v>500</v>
       </c>
       <c r="AG16" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AH16" t="n">
         <v>950</v>
       </c>
       <c r="AI16" t="n">
+        <v>540</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>500</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>900</v>
       </c>
       <c r="AK16" t="n">
         <v>500</v>
       </c>
       <c r="AL16" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AM16" t="n">
         <v>500</v>
       </c>
       <c r="AN16" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.19</v>
+        <v>3.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.17</v>
+        <v>4.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.19</v>
+        <v>1.62</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.17</v>
+        <v>4.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.16</v>
+        <v>4.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.19</v>
+        <v>1.62</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.19</v>
+        <v>1.63</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.19</v>
+        <v>1.63</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.19</v>
+        <v>1.62</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.19</v>
+        <v>1.62</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.19</v>
+        <v>1.63</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="G17" t="n">
         <v>11.5</v>
@@ -4682,31 +4682,31 @@
         <v>2.6</v>
       </c>
       <c r="K17" t="n">
-        <v>5.7</v>
+        <v>3.65</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N17" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="O17" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="P17" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="R17" t="n">
         <v>1.12</v>
       </c>
       <c r="S17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -4921,19 +4921,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G18" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K18" t="n">
         <v>4.1</v>
@@ -4942,43 +4942,43 @@
         <v>1.39</v>
       </c>
       <c r="M18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T18" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U18" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V18" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W18" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X18" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z18" t="n">
         <v>46</v>
@@ -4996,7 +4996,7 @@
         <v>19.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AF18" t="n">
         <v>12</v>
@@ -5020,10 +5020,10 @@
         <v>46</v>
       </c>
       <c r="AM18" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AN18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO18" t="n">
         <v>280</v>
@@ -5041,7 +5041,7 @@
         <v>29</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU18" t="n">
         <v>7.8</v>
@@ -5050,7 +5050,7 @@
         <v>16.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
@@ -5062,43 +5062,43 @@
         <v>16.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BB18" t="n">
         <v>16.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE18" t="n">
         <v>28</v>
       </c>
       <c r="BF18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="BJ18" t="n">
         <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN18" t="n">
         <v>4.7</v>
@@ -5107,16 +5107,16 @@
         <v>3.95</v>
       </c>
       <c r="BP18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR18" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT18" t="n">
         <v>8.6</v>
@@ -5125,26 +5125,26 @@
         <v>6.6</v>
       </c>
       <c r="BV18" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
         <v>8.4</v>
       </c>
-      <c r="BX18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BZ18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CA18" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -5178,19 +5178,19 @@
         <v>1.79</v>
       </c>
       <c r="G19" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L19" t="n">
         <v>1.41</v>
@@ -5208,7 +5208,7 @@
         <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
         <v>1.36</v>
@@ -5220,19 +5220,19 @@
         <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z19" t="n">
         <v>40</v>
@@ -5247,7 +5247,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
         <v>75</v>
@@ -5256,28 +5256,28 @@
         <v>11</v>
       </c>
       <c r="AG19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH19" t="n">
         <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK19" t="n">
         <v>19.5</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>20</v>
       </c>
       <c r="AL19" t="n">
         <v>38</v>
       </c>
       <c r="AM19" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO19" t="n">
         <v>95</v>
@@ -5286,7 +5286,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR19" t="n">
         <v>34</v>
@@ -5307,7 +5307,7 @@
         <v>46</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY19" t="n">
         <v>9.199999999999999</v>
@@ -5319,7 +5319,7 @@
         <v>48</v>
       </c>
       <c r="BB19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC19" t="n">
         <v>17</v>
@@ -5328,7 +5328,7 @@
         <v>32</v>
       </c>
       <c r="BE19" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="BF19" t="n">
         <v>11</v>
@@ -5337,7 +5337,7 @@
         <v>50</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI19" t="n">
         <v>2.84</v>
@@ -5346,59 +5346,59 @@
         <v>10.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN19" t="n">
         <v>4.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="BP19" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BT19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -5429,52 +5429,52 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="G20" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="H20" t="n">
         <v>4.3</v>
       </c>
       <c r="I20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J20" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K20" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="M20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="O20" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P20" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="Q20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T20" t="n">
         <v>1.46</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.53</v>
-      </c>
       <c r="U20" t="n">
-        <v>2.58</v>
+        <v>2.86</v>
       </c>
       <c r="V20" t="n">
         <v>1.27</v>
@@ -5483,151 +5483,151 @@
         <v>2.28</v>
       </c>
       <c r="X20" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="Y20" t="n">
         <v>75</v>
       </c>
       <c r="Z20" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA20" t="n">
         <v>500</v>
       </c>
       <c r="AB20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF20" t="n">
         <v>18</v>
       </c>
-      <c r="AC20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD20" t="n">
+      <c r="AG20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP20" t="n">
         <v>19</v>
       </c>
-      <c r="AE20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF20" t="n">
+      <c r="AQ20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW20" t="n">
         <v>17.5</v>
       </c>
-      <c r="AG20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL20" t="n">
+      <c r="AX20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BE20" t="n">
         <v>28</v>
       </c>
-      <c r="AM20" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>260</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BF20" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.6</v>
+        <v>21</v>
       </c>
       <c r="BH20" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BJ20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL20" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM20" t="n">
         <v>8.4</v>
       </c>
       <c r="BN20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BP20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BR20" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BS20" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT20" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BU20" t="n">
         <v>6.8</v>
@@ -5639,20 +5639,20 @@
         <v>7.4</v>
       </c>
       <c r="BX20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY20" t="n">
         <v>7.4</v>
       </c>
       <c r="BZ20" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
         <v>2.12</v>
       </c>
       <c r="G21" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H21" t="n">
         <v>3.9</v>
@@ -5695,10 +5695,10 @@
         <v>4.1</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L21" t="n">
         <v>1.45</v>
@@ -5707,43 +5707,43 @@
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O21" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P21" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U21" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V21" t="n">
         <v>1.32</v>
       </c>
       <c r="W21" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z21" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA21" t="n">
         <v>170</v>
@@ -5755,10 +5755,10 @@
         <v>8</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF21" t="n">
         <v>13</v>
@@ -5773,28 +5773,28 @@
         <v>80</v>
       </c>
       <c r="AJ21" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AK21" t="n">
         <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM21" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AO21" t="n">
-        <v>230</v>
+        <v>90</v>
       </c>
       <c r="AP21" t="n">
         <v>11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR21" t="n">
         <v>22</v>
@@ -5803,19 +5803,19 @@
         <v>55</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU21" t="n">
         <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW21" t="n">
         <v>34</v>
       </c>
       <c r="AX21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY21" t="n">
         <v>9.199999999999999</v>
@@ -5836,19 +5836,19 @@
         <v>29</v>
       </c>
       <c r="BE21" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="BF21" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH21" t="n">
         <v>3.3</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BJ21" t="n">
         <v>9.800000000000001</v>
@@ -5860,53 +5860,53 @@
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BP21" t="n">
         <v>16</v>
       </c>
       <c r="BQ21" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BR21" t="n">
         <v>32</v>
       </c>
       <c r="BS21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT21" t="n">
         <v>7</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV21" t="n">
         <v>32</v>
       </c>
       <c r="BW21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX21" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY21" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ21" t="n">
         <v>28</v>
       </c>
       <c r="CA21" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -5940,94 +5940,94 @@
         <v>1.54</v>
       </c>
       <c r="G22" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" t="n">
         <v>5.3</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>5.8</v>
       </c>
-      <c r="J22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>5.9</v>
-      </c>
       <c r="L22" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="M22" t="n">
         <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="O22" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P22" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="R22" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="S22" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="T22" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="U22" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="V22" t="n">
         <v>1.2</v>
       </c>
       <c r="W22" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X22" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="Y22" t="n">
         <v>85</v>
       </c>
       <c r="Z22" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AA22" t="n">
         <v>500</v>
       </c>
       <c r="AB22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>21</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>19.5</v>
       </c>
       <c r="AK22" t="n">
         <v>15</v>
@@ -6036,106 +6036,106 @@
         <v>22</v>
       </c>
       <c r="AM22" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="AO22" t="n">
         <v>38</v>
       </c>
       <c r="AP22" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AQ22" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AR22" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT22" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AV22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
         <v>38</v>
       </c>
       <c r="AX22" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BB22" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD22" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BE22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="BG22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BH22" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BI22" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BJ22" t="n">
         <v>9</v>
       </c>
       <c r="BK22" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BN22" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BO22" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BP22" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BR22" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BS22" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BT22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU22" t="n">
         <v>5</v>
@@ -6144,23 +6144,23 @@
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ22" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="CA22" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -6191,16 +6191,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G23" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H23" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J23" t="n">
         <v>4.1</v>
@@ -6221,31 +6221,31 @@
         <v>1.14</v>
       </c>
       <c r="P23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R23" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="S23" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T23" t="n">
         <v>1.43</v>
       </c>
       <c r="U23" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W23" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X23" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="Y23" t="n">
         <v>24</v>
@@ -6254,16 +6254,16 @@
         <v>26</v>
       </c>
       <c r="AA23" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB23" t="n">
         <v>21</v>
       </c>
       <c r="AC23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD23" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE23" t="n">
         <v>25</v>
@@ -6275,7 +6275,7 @@
         <v>13</v>
       </c>
       <c r="AH23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI23" t="n">
         <v>27</v>
@@ -6290,16 +6290,16 @@
         <v>25</v>
       </c>
       <c r="AM23" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AN23" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP23" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AQ23" t="n">
         <v>20</v>
@@ -6308,7 +6308,7 @@
         <v>23</v>
       </c>
       <c r="AS23" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT23" t="n">
         <v>18.5</v>
@@ -6317,10 +6317,10 @@
         <v>10</v>
       </c>
       <c r="AV23" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW23" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AX23" t="n">
         <v>20</v>
@@ -6335,7 +6335,7 @@
         <v>22</v>
       </c>
       <c r="BB23" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BC23" t="n">
         <v>19</v>
@@ -6347,74 +6347,74 @@
         <v>34</v>
       </c>
       <c r="BF23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BJ23" t="n">
         <v>8.6</v>
       </c>
-      <c r="BG23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BK23" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BN23" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO23" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP23" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BR23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS23" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU23" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BV23" t="n">
         <v>17.5</v>
       </c>
       <c r="BW23" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX23" t="n">
         <v>22</v>
       </c>
       <c r="BY23" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ23" t="n">
         <v>12</v>
       </c>
       <c r="CA23" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="G24" t="n">
         <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I24" t="n">
         <v>2.36</v>
       </c>
       <c r="J24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K24" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L24" t="n">
         <v>1.21</v>
@@ -6469,7 +6469,7 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="O24" t="n">
         <v>1.11</v>
@@ -6478,13 +6478,13 @@
         <v>3.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R24" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S24" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="T24" t="n">
         <v>1.38</v>
@@ -6493,7 +6493,7 @@
         <v>3.4</v>
       </c>
       <c r="V24" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W24" t="n">
         <v>1.5</v>
@@ -6517,22 +6517,22 @@
         <v>12.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF24" t="n">
         <v>38</v>
       </c>
       <c r="AG24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ24" t="n">
         <v>110</v>
@@ -6541,7 +6541,7 @@
         <v>32</v>
       </c>
       <c r="AL24" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM24" t="n">
         <v>48</v>
@@ -6592,7 +6592,7 @@
         <v>34</v>
       </c>
       <c r="BC24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD24" t="n">
         <v>21</v>
@@ -6607,7 +6607,7 @@
         <v>7.2</v>
       </c>
       <c r="BH24" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BI24" t="n">
         <v>5.1</v>
@@ -6622,25 +6622,25 @@
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN24" t="n">
         <v>7.2</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ24" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS24" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT24" t="n">
         <v>6.4</v>
@@ -6649,16 +6649,16 @@
         <v>5.6</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW24" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ24" t="n">
         <v>10</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -6699,13 +6699,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G25" t="n">
         <v>1.92</v>
       </c>
       <c r="H25" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I25" t="n">
         <v>5.4</v>
@@ -6717,22 +6717,22 @@
         <v>3.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
         <v>1.38</v>
       </c>
       <c r="P25" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R25" t="n">
         <v>1.29</v>
@@ -6741,7 +6741,7 @@
         <v>3.95</v>
       </c>
       <c r="T25" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U25" t="n">
         <v>1.91</v>
@@ -6750,7 +6750,7 @@
         <v>1.22</v>
       </c>
       <c r="W25" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X25" t="n">
         <v>12</v>
@@ -6759,7 +6759,7 @@
         <v>15.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="AA25" t="n">
         <v>900</v>
@@ -6768,7 +6768,7 @@
         <v>8</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD25" t="n">
         <v>20</v>
@@ -6783,7 +6783,7 @@
         <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
         <v>320</v>
@@ -6792,7 +6792,7 @@
         <v>21</v>
       </c>
       <c r="AK25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL25" t="n">
         <v>160</v>
@@ -6801,7 +6801,7 @@
         <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO25" t="n">
         <v>600</v>
@@ -6813,7 +6813,7 @@
         <v>13.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AS25" t="n">
         <v>12</v>
@@ -6822,7 +6822,7 @@
         <v>6.8</v>
       </c>
       <c r="AU25" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV25" t="n">
         <v>17.5</v>
@@ -6882,7 +6882,7 @@
         <v>4.4</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP25" t="n">
         <v>13.5</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -6956,163 +6956,163 @@
         <v>1.47</v>
       </c>
       <c r="G26" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I26" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J26" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L26" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="O26" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P26" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="R26" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="S26" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="T26" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="U26" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V26" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W26" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="X26" t="n">
         <v>46</v>
       </c>
       <c r="Y26" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="Z26" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AA26" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AB26" t="n">
         <v>18.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE26" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF26" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG26" t="n">
         <v>11.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI26" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AJ26" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AM26" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AO26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP26" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ26" t="n">
         <v>6.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS26" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AV26" t="n">
         <v>6</v>
       </c>
       <c r="AW26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX26" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AY26" t="n">
         <v>4.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BA26" t="n">
         <v>6.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BC26" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BG26" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH26" t="n">
         <v>5.5</v>
@@ -7121,25 +7121,25 @@
         <v>3.65</v>
       </c>
       <c r="BJ26" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN26" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="BP26" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ26" t="n">
         <v>4.9</v>
@@ -7151,22 +7151,22 @@
         <v>6.8</v>
       </c>
       <c r="BT26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU26" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV26" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW26" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BX26" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY26" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>
@@ -7207,22 +7207,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="G27" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H27" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="I27" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K27" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L27" t="n">
         <v>1.54</v>
@@ -7234,7 +7234,7 @@
         <v>2.78</v>
       </c>
       <c r="O27" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P27" t="n">
         <v>1.6</v>
@@ -7246,19 +7246,19 @@
         <v>1.22</v>
       </c>
       <c r="S27" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T27" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
         <v>1.87</v>
       </c>
       <c r="V27" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W27" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X27" t="n">
         <v>11.5</v>
@@ -7270,7 +7270,7 @@
         <v>22</v>
       </c>
       <c r="AA27" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB27" t="n">
         <v>11</v>
@@ -7282,10 +7282,10 @@
         <v>14</v>
       </c>
       <c r="AE27" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF27" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
         <v>16</v>
@@ -7312,31 +7312,31 @@
         <v>55</v>
       </c>
       <c r="AO27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP27" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AR27" t="n">
         <v>13.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT27" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV27" t="n">
         <v>10</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX27" t="n">
         <v>13</v>
@@ -7345,31 +7345,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BA27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE27" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BF27" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH27" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BI27" t="n">
         <v>2.4</v>
@@ -7378,13 +7378,13 @@
         <v>11</v>
       </c>
       <c r="BK27" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN27" t="n">
         <v>5.8</v>
@@ -7396,13 +7396,13 @@
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT27" t="n">
         <v>5.8</v>
@@ -7414,23 +7414,23 @@
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ27" t="n">
         <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-20 05:58:07</t>
+          <t>2026-07-20 08:08:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="I2" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="J2" t="n">
         <v>3.8</v>
@@ -875,202 +875,202 @@
         <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="T2" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U2" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V2" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="W2" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="X2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
         <v>14.5</v>
       </c>
       <c r="AI2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK2" t="n">
         <v>32</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>26</v>
-      </c>
       <c r="AL2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM2" t="n">
         <v>60</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AO2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR2" t="n">
         <v>16</v>
       </c>
-      <c r="AP2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AS2" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AT2" t="n">
         <v>14.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AY2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG2" t="n">
         <v>13.5</v>
       </c>
-      <c r="BA2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BH2" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BJ2" t="n">
         <v>8.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BL2" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BM2" t="n">
         <v>65</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BP2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BS2" t="n">
-        <v>10.5</v>
+        <v>25</v>
       </c>
       <c r="BT2" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BW2" t="n">
         <v>9</v>
       </c>
       <c r="BX2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="G3" t="n">
         <v>12.5</v>
@@ -1120,10 +1120,10 @@
         <v>1.31</v>
       </c>
       <c r="I3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="J3" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="K3" t="n">
         <v>6.6</v>
@@ -1135,7 +1135,7 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.18</v>
@@ -1144,22 +1144,22 @@
         <v>2.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R3" t="n">
         <v>1.66</v>
       </c>
       <c r="S3" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="U3" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="V3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="W3" t="n">
         <v>1.08</v>
@@ -1174,16 +1174,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AA3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AC3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE3" t="n">
         <v>13.5</v>
@@ -1195,34 +1195,34 @@
         <v>42</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AI3" t="n">
         <v>36</v>
       </c>
       <c r="AJ3" t="n">
-        <v>570</v>
+        <v>480</v>
       </c>
       <c r="AK3" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AL3" t="n">
         <v>140</v>
       </c>
       <c r="AM3" t="n">
-        <v>380</v>
+        <v>150</v>
       </c>
       <c r="AN3" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AP3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR3" t="n">
         <v>7.8</v>
@@ -1231,19 +1231,19 @@
         <v>9.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AU3" t="n">
         <v>12.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW3" t="n">
         <v>12</v>
       </c>
       <c r="AX3" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY3" t="n">
         <v>34</v>
@@ -1252,22 +1252,22 @@
         <v>24</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>16.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BC3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BD3" t="n">
-        <v>13.5</v>
+        <v>29</v>
       </c>
       <c r="BE3" t="n">
-        <v>15.5</v>
+        <v>85</v>
       </c>
       <c r="BF3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BG3" t="n">
         <v>4.1</v>
@@ -1276,55 +1276,55 @@
         <v>4.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="BN3" t="n">
         <v>13.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BT3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BU3" t="n">
         <v>3.8</v>
       </c>
       <c r="BV3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G4" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1392,7 +1392,7 @@
         <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P4" t="n">
         <v>1.76</v>
@@ -1404,52 +1404,52 @@
         <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="X4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF4" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>14</v>
-      </c>
       <c r="AG4" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI4" t="n">
         <v>80</v>
@@ -1458,16 +1458,16 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AL4" t="n">
         <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AN4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO4" t="n">
         <v>65</v>
@@ -1476,119 +1476,119 @@
         <v>9.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT4" t="n">
         <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AV4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
         <v>18</v>
       </c>
       <c r="BA4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC4" t="n">
         <v>23</v>
       </c>
       <c r="BD4" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="BF4" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI4" t="n">
         <v>2.84</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.56</v>
+        <v>120</v>
       </c>
       <c r="BN4" t="n">
         <v>5</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP4" t="n">
         <v>17.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT4" t="n">
         <v>7</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
         <v>10.5</v>
       </c>
-      <c r="BZ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>2.4</v>
-      </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -1619,61 +1619,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="G5" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="H5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I5" t="n">
         <v>7.6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="M5" t="n">
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P5" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="V5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="X5" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="Y5" t="n">
         <v>25</v>
@@ -1685,37 +1685,37 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AI5" t="n">
         <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK5" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
@@ -1724,46 +1724,46 @@
         <v>12</v>
       </c>
       <c r="AO5" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AP5" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS5" t="n">
         <v>10</v>
       </c>
-      <c r="AS5" t="n">
-        <v>11</v>
-      </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV5" t="n">
         <v>18.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC5" t="n">
         <v>16.5</v>
@@ -1772,55 +1772,55 @@
         <v>22</v>
       </c>
       <c r="BE5" t="n">
-        <v>11.5</v>
+        <v>120</v>
       </c>
       <c r="BF5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG5" t="n">
         <v>10</v>
       </c>
-      <c r="BG5" t="n">
-        <v>11</v>
-      </c>
       <c r="BH5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="BN5" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="BP5" t="n">
         <v>11</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1832,7 +1832,7 @@
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -1873,220 +1873,220 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="I6" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="T6" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U6" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="W6" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y6" t="n">
         <v>9.4</v>
       </c>
       <c r="Z6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC6" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>10</v>
       </c>
       <c r="AE6" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AG6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
         <v>32</v>
       </c>
       <c r="AJ6" t="n">
-        <v>690</v>
+        <v>180</v>
       </c>
       <c r="AK6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL6" t="n">
         <v>80</v>
       </c>
-      <c r="AL6" t="n">
-        <v>75</v>
-      </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN6" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AO6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AP6" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AQ6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU6" t="n">
         <v>9.4</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>9</v>
       </c>
       <c r="AV6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AY6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA6" t="n">
         <v>28</v>
       </c>
       <c r="BB6" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="BC6" t="n">
+        <v>75</v>
+      </c>
+      <c r="BD6" t="n">
         <v>65</v>
       </c>
-      <c r="BD6" t="n">
-        <v>50</v>
-      </c>
       <c r="BE6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BF6" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BL6" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM6" t="n">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="BN6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO6" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BP6" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BQ6" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BR6" t="n">
         <v>55</v>
       </c>
       <c r="BS6" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BV6" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G7" t="n">
         <v>2.94</v>
@@ -2136,55 +2136,55 @@
         <v>2.74</v>
       </c>
       <c r="I7" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R7" t="n">
         <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U7" t="n">
         <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W7" t="n">
         <v>1.51</v>
       </c>
       <c r="X7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z7" t="n">
         <v>18.5</v>
@@ -2193,19 +2193,19 @@
         <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AE7" t="n">
         <v>44</v>
       </c>
       <c r="AF7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG7" t="n">
         <v>14</v>
@@ -2214,13 +2214,13 @@
         <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AJ7" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AK7" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="AL7" t="n">
         <v>55</v>
@@ -2229,10 +2229,10 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP7" t="n">
         <v>10</v>
@@ -2241,10 +2241,10 @@
         <v>8.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS7" t="n">
-        <v>16.5</v>
+        <v>34</v>
       </c>
       <c r="AT7" t="n">
         <v>9.4</v>
@@ -2253,10 +2253,10 @@
         <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX7" t="n">
         <v>16</v>
@@ -2268,25 +2268,25 @@
         <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BB7" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="BC7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BD7" t="n">
         <v>40</v>
       </c>
       <c r="BE7" t="n">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="BF7" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BG7" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="BH7" t="n">
         <v>3.15</v>
@@ -2304,16 +2304,16 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.800000000000001</v>
+        <v>120</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ7" t="n">
         <v>7.4</v>
@@ -2328,13 +2328,13 @@
         <v>5.9</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BV7" t="n">
         <v>24</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
@@ -2343,14 +2343,14 @@
         <v>8.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA7" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G8" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H8" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="I8" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
@@ -2420,22 +2420,22 @@
         <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T8" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U8" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V8" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y8" t="n">
         <v>13</v>
@@ -2444,10 +2444,10 @@
         <v>25</v>
       </c>
       <c r="AA8" t="n">
-        <v>250</v>
+        <v>65</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
         <v>8.4</v>
@@ -2456,7 +2456,7 @@
         <v>15.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AF8" t="n">
         <v>17.5</v>
@@ -2468,124 +2468,124 @@
         <v>20</v>
       </c>
       <c r="AI8" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AJ8" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AK8" t="n">
         <v>32</v>
       </c>
       <c r="AL8" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO8" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="AP8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR8" t="n">
         <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.2</v>
+        <v>38</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="AX8" t="n">
         <v>12.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
         <v>14.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="BB8" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="BC8" t="n">
         <v>23</v>
       </c>
       <c r="BD8" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF8" t="n">
         <v>19.5</v>
       </c>
-      <c r="BE8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>20</v>
-      </c>
       <c r="BG8" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="BJ8" t="n">
         <v>11</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>7.2</v>
+        <v>110</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BP8" t="n">
         <v>21</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT8" t="n">
         <v>6.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BV8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW8" t="n">
         <v>6</v>
@@ -2594,7 +2594,7 @@
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -2635,58 +2635,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="G9" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="J9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
         <v>4.7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
         <v>1.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="V9" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
         <v>16.5</v>
@@ -2695,16 +2695,16 @@
         <v>8.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AB9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
         <v>10.5</v>
@@ -2713,46 +2713,46 @@
         <v>16.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG9" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ9" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AK9" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AL9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM9" t="n">
         <v>150</v>
       </c>
-      <c r="AM9" t="n">
-        <v>160</v>
-      </c>
       <c r="AN9" t="n">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="AO9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AP9" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR9" t="n">
         <v>7.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT9" t="n">
         <v>20</v>
@@ -2767,98 +2767,98 @@
         <v>14.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AY9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ9" t="n">
         <v>22</v>
       </c>
       <c r="BA9" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BB9" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="BC9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BD9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BE9" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BF9" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BG9" t="n">
         <v>7.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="BJ9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>130</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO9" t="n">
         <v>5.7</v>
       </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>10</v>
       </c>
-      <c r="BN9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>75</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT9" t="n">
         <v>4.1</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BV9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BW9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>26</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="CA9" t="n">
         <v>7</v>
       </c>
-      <c r="BX9" t="n">
-        <v>27</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>18</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>6.6</v>
-      </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="G10" t="n">
         <v>8.800000000000001</v>
@@ -2904,37 +2904,37 @@
         <v>5.9</v>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M10" t="n">
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="R10" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="S10" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T10" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="U10" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
         <v>3.5</v>
@@ -2943,10 +2943,10 @@
         <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z10" t="n">
         <v>11</v>
@@ -2955,7 +2955,7 @@
         <v>12.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AC10" t="n">
         <v>14</v>
@@ -2976,7 +2976,7 @@
         <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ10" t="n">
         <v>230</v>
@@ -2994,13 +2994,13 @@
         <v>85</v>
       </c>
       <c r="AO10" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AP10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
         <v>10</v>
@@ -3012,16 +3012,16 @@
         <v>38</v>
       </c>
       <c r="AU10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW10" t="n">
         <v>12</v>
       </c>
       <c r="AX10" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AY10" t="n">
         <v>27</v>
@@ -3036,55 +3036,55 @@
         <v>65</v>
       </c>
       <c r="BC10" t="n">
+        <v>80</v>
+      </c>
+      <c r="BD10" t="n">
         <v>60</v>
       </c>
-      <c r="BD10" t="n">
-        <v>65</v>
-      </c>
       <c r="BE10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BF10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BH10" t="n">
         <v>5.1</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BL10" t="n">
         <v>90</v>
       </c>
       <c r="BM10" t="n">
-        <v>12.5</v>
+        <v>75</v>
       </c>
       <c r="BN10" t="n">
         <v>12.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BP10" t="n">
         <v>60</v>
       </c>
       <c r="BQ10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR10" t="n">
         <v>50</v>
       </c>
       <c r="BS10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT10" t="n">
         <v>4.3</v>
@@ -3093,26 +3093,26 @@
         <v>4</v>
       </c>
       <c r="BV10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BW10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX10" t="n">
         <v>19</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BZ10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="G11" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="H11" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="I11" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="J11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K11" t="n">
         <v>3.85</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.9</v>
       </c>
       <c r="L11" t="n">
         <v>1.34</v>
@@ -3173,55 +3173,55 @@
         <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U11" t="n">
         <v>2.56</v>
       </c>
       <c r="V11" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AA11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB11" t="n">
         <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
@@ -3236,7 +3236,7 @@
         <v>42</v>
       </c>
       <c r="AK11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL11" t="n">
         <v>34</v>
@@ -3245,19 +3245,19 @@
         <v>60</v>
       </c>
       <c r="AN11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP11" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>13</v>
       </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS11" t="n">
         <v>32</v>
@@ -3266,16 +3266,16 @@
         <v>14</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV11" t="n">
         <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY11" t="n">
         <v>11.5</v>
@@ -3284,31 +3284,31 @@
         <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BC11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD11" t="n">
         <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ11" t="n">
         <v>8.6</v>
@@ -3317,56 +3317,56 @@
         <v>7.6</v>
       </c>
       <c r="BL11" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BM11" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="BN11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BP11" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="BR11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BX11" t="n">
         <v>27</v>
       </c>
       <c r="BY11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>18.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -3400,22 +3400,22 @@
         <v>2.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I12" t="n">
         <v>4.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K12" t="n">
         <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
@@ -3427,22 +3427,22 @@
         <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U12" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V12" t="n">
         <v>1.32</v>
@@ -3454,25 +3454,25 @@
         <v>14.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z12" t="n">
         <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB12" t="n">
         <v>9.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>16.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF12" t="n">
         <v>13</v>
@@ -3484,22 +3484,22 @@
         <v>18.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK12" t="n">
         <v>23</v>
       </c>
       <c r="AL12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM12" t="n">
         <v>100</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO12" t="n">
         <v>55</v>
@@ -3508,10 +3508,10 @@
         <v>13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS12" t="n">
         <v>65</v>
@@ -3523,7 +3523,7 @@
         <v>7.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW12" t="n">
         <v>42</v>
@@ -3535,10 +3535,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB12" t="n">
         <v>22</v>
@@ -3547,34 +3547,34 @@
         <v>19.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE12" t="n">
         <v>75</v>
       </c>
       <c r="BF12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BL12" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BM12" t="n">
-        <v>11.5</v>
+        <v>90</v>
       </c>
       <c r="BN12" t="n">
         <v>4.9</v>
@@ -3583,44 +3583,44 @@
         <v>4.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BS12" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BT12" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV12" t="n">
         <v>34</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX12" t="n">
         <v>44</v>
       </c>
       <c r="BY12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>2.06</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
         <v>6.2</v>
@@ -3666,7 +3666,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L13" t="n">
         <v>1.58</v>
@@ -3675,13 +3675,13 @@
         <v>1.13</v>
       </c>
       <c r="N13" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P13" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="Q13" t="n">
         <v>2.66</v>
@@ -3690,7 +3690,7 @@
         <v>1.17</v>
       </c>
       <c r="S13" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="T13" t="n">
         <v>2.26</v>
@@ -3702,10 +3702,10 @@
         <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="X13" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y13" t="n">
         <v>14</v>
@@ -3759,31 +3759,31 @@
         <v>700</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AR13" t="n">
         <v>7.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT13" t="n">
         <v>4.1</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AY13" t="n">
         <v>5.2</v>
@@ -3792,25 +3792,25 @@
         <v>6.8</v>
       </c>
       <c r="BA13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE13" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BF13" t="n">
         <v>6.4</v>
       </c>
-      <c r="BC13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BG13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH13" t="n">
         <v>2.74</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>12</v>
       </c>
       <c r="H14" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I14" t="n">
         <v>4.7</v>
@@ -3926,22 +3926,22 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.46</v>
+        <v>1.02</v>
       </c>
       <c r="R14" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S14" t="n">
         <v>1.05</v>
@@ -3953,7 +3953,7 @@
         <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W14" t="n">
         <v>1.32</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -4162,13 +4162,13 @@
         <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4</v>
+        <v>990</v>
       </c>
       <c r="H15" t="n">
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>990</v>
       </c>
       <c r="J15" t="n">
         <v>2.32</v>
@@ -4183,16 +4183,16 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="O15" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="P15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="R15" t="n">
         <v>1.12</v>
@@ -4207,7 +4207,7 @@
         <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
         <v>1.3</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="G16" t="n">
         <v>3.6</v>
@@ -4437,16 +4437,16 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O16" t="n">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="P16" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R16" t="n">
         <v>1.12</v>
@@ -4527,7 +4527,7 @@
         <v>4.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.58</v>
+        <v>2.5</v>
       </c>
       <c r="AS16" t="n">
         <v>1.62</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
         <v>11.5</v>
@@ -4691,13 +4691,13 @@
         <v>1.13</v>
       </c>
       <c r="N17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O17" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Q17" t="n">
         <v>2.2</v>
@@ -4706,7 +4706,7 @@
         <v>1.12</v>
       </c>
       <c r="S17" t="n">
-        <v>1.05</v>
+        <v>3.85</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4715,7 +4715,7 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W17" t="n">
         <v>1.33</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="G18" t="n">
         <v>1.86</v>
@@ -4933,13 +4933,13 @@
         <v>5.3</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
@@ -4957,7 +4957,7 @@
         <v>1.91</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
         <v>3.35</v>
@@ -4969,13 +4969,13 @@
         <v>2.08</v>
       </c>
       <c r="V18" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W18" t="n">
         <v>2.16</v>
       </c>
       <c r="X18" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y18" t="n">
         <v>19.5</v>
@@ -4987,7 +4987,7 @@
         <v>700</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC18" t="n">
         <v>9.199999999999999</v>
@@ -4996,7 +4996,7 @@
         <v>19.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AF18" t="n">
         <v>12</v>
@@ -5008,7 +5008,7 @@
         <v>19.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AJ18" t="n">
         <v>21</v>
@@ -5020,7 +5020,7 @@
         <v>46</v>
       </c>
       <c r="AM18" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="n">
         <v>12</v>
@@ -5047,10 +5047,10 @@
         <v>7.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
@@ -5062,7 +5062,7 @@
         <v>16.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB18" t="n">
         <v>16.5</v>
@@ -5071,7 +5071,7 @@
         <v>16.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE18" t="n">
         <v>28</v>
@@ -5083,22 +5083,22 @@
         <v>44</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ18" t="n">
         <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN18" t="n">
         <v>4.7</v>
@@ -5107,44 +5107,44 @@
         <v>3.95</v>
       </c>
       <c r="BP18" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ18" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT18" t="n">
         <v>8.6</v>
       </c>
       <c r="BU18" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BZ18" t="n">
         <v>23</v>
       </c>
       <c r="CA18" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G19" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H19" t="n">
         <v>5.1</v>
@@ -5187,7 +5187,7 @@
         <v>5.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K19" t="n">
         <v>3.95</v>
@@ -5199,16 +5199,16 @@
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R19" t="n">
         <v>1.36</v>
@@ -5217,13 +5217,13 @@
         <v>3.55</v>
       </c>
       <c r="T19" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V19" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W19" t="n">
         <v>2.2</v>
@@ -5238,7 +5238,7 @@
         <v>40</v>
       </c>
       <c r="AA19" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AB19" t="n">
         <v>8.800000000000001</v>
@@ -5262,7 +5262,7 @@
         <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="n">
         <v>19</v>
@@ -5307,7 +5307,7 @@
         <v>46</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY19" t="n">
         <v>9.199999999999999</v>
@@ -5316,10 +5316,10 @@
         <v>18</v>
       </c>
       <c r="BA19" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB19" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC19" t="n">
         <v>17</v>
@@ -5331,16 +5331,16 @@
         <v>55</v>
       </c>
       <c r="BF19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ19" t="n">
         <v>10.5</v>
@@ -5352,19 +5352,19 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BN19" t="n">
         <v>4.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="BP19" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
@@ -5376,13 +5376,13 @@
         <v>8.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
@@ -5394,11 +5394,11 @@
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G20" t="n">
         <v>1.76</v>
@@ -5438,13 +5438,13 @@
         <v>4.3</v>
       </c>
       <c r="I20" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J20" t="n">
         <v>4.6</v>
       </c>
       <c r="K20" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L20" t="n">
         <v>1.22</v>
@@ -5456,46 +5456,46 @@
         <v>7.8</v>
       </c>
       <c r="O20" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="R20" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="S20" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="T20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U20" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="V20" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W20" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X20" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="Y20" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="Z20" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AA20" t="n">
         <v>500</v>
       </c>
       <c r="AB20" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AC20" t="n">
         <v>13.5</v>
@@ -5507,7 +5507,7 @@
         <v>120</v>
       </c>
       <c r="AF20" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG20" t="n">
         <v>12.5</v>
@@ -5516,37 +5516,37 @@
         <v>15.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK20" t="n">
         <v>16</v>
       </c>
       <c r="AL20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AM20" t="n">
         <v>200</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AO20" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="AP20" t="n">
         <v>19</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
         <v>18.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT20" t="n">
         <v>16</v>
@@ -5573,7 +5573,7 @@
         <v>18</v>
       </c>
       <c r="BB20" t="n">
-        <v>17.5</v>
+        <v>9.6</v>
       </c>
       <c r="BC20" t="n">
         <v>13</v>
@@ -5585,28 +5585,28 @@
         <v>28</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG20" t="n">
         <v>21</v>
       </c>
       <c r="BH20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BI20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ20" t="n">
         <v>9</v>
       </c>
       <c r="BK20" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BL20" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN20" t="n">
         <v>5.4</v>
@@ -5618,41 +5618,41 @@
         <v>11</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BR20" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BS20" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BT20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU20" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW20" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX20" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BZ20" t="n">
         <v>10.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G21" t="n">
         <v>2.18</v>
       </c>
       <c r="H21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I21" t="n">
         <v>4.1</v>
@@ -5698,10 +5698,10 @@
         <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M21" t="n">
         <v>1.08</v>
@@ -5710,22 +5710,22 @@
         <v>3.55</v>
       </c>
       <c r="O21" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
         <v>3.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U21" t="n">
         <v>2.02</v>
@@ -5740,16 +5740,16 @@
         <v>12.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA21" t="n">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC21" t="n">
         <v>8</v>
@@ -5758,7 +5758,7 @@
         <v>16.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF21" t="n">
         <v>13</v>
@@ -5770,55 +5770,55 @@
         <v>19</v>
       </c>
       <c r="AI21" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ21" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK21" t="n">
         <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AM21" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AN21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO21" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AP21" t="n">
         <v>11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS21" t="n">
         <v>55</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV21" t="n">
         <v>14.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX21" t="n">
         <v>11</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
         <v>17</v>
@@ -5827,19 +5827,19 @@
         <v>42</v>
       </c>
       <c r="BB21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC21" t="n">
         <v>21</v>
       </c>
       <c r="BD21" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BE21" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="BF21" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG21" t="n">
         <v>36</v>
@@ -5848,7 +5848,7 @@
         <v>3.3</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="BJ21" t="n">
         <v>9.800000000000001</v>
@@ -5863,10 +5863,10 @@
         <v>14.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BP21" t="n">
         <v>16</v>
@@ -5881,10 +5881,10 @@
         <v>10.5</v>
       </c>
       <c r="BT21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU21" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BV21" t="n">
         <v>32</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G22" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H22" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I22" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J22" t="n">
         <v>5.3</v>
       </c>
       <c r="K22" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L22" t="n">
         <v>1.17</v>
@@ -5982,49 +5982,49 @@
         <v>1.4</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V22" t="n">
         <v>1.2</v>
       </c>
       <c r="W22" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X22" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z22" t="n">
         <v>500</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>85</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>130</v>
       </c>
       <c r="AA22" t="n">
         <v>500</v>
       </c>
       <c r="AB22" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AC22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AD22" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE22" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF22" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH22" t="n">
         <v>18</v>
       </c>
       <c r="AI22" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AJ22" t="n">
         <v>21</v>
@@ -6033,31 +6033,31 @@
         <v>15</v>
       </c>
       <c r="AL22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM22" t="n">
         <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AO22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP22" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AQ22" t="n">
-        <v>30</v>
+        <v>14.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS22" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT22" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AU22" t="n">
         <v>14</v>
@@ -6066,10 +6066,10 @@
         <v>21</v>
       </c>
       <c r="AW22" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX22" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY22" t="n">
         <v>10.5</v>
@@ -6078,10 +6078,10 @@
         <v>14.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB22" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC22" t="n">
         <v>12</v>
@@ -6090,77 +6090,77 @@
         <v>17</v>
       </c>
       <c r="BE22" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BG22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH22" t="n">
         <v>7</v>
       </c>
       <c r="BI22" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BJ22" t="n">
         <v>9</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BN22" t="n">
         <v>5.7</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BP22" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ22" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BR22" t="n">
         <v>15.5</v>
       </c>
       <c r="BS22" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BT22" t="n">
         <v>11</v>
       </c>
       <c r="BU22" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BV22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW22" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BZ22" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="CA22" t="n">
         <v>5.7</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G23" t="n">
         <v>2.52</v>
@@ -6206,7 +6206,7 @@
         <v>4.1</v>
       </c>
       <c r="K23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L23" t="n">
         <v>1.24</v>
@@ -6215,7 +6215,7 @@
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.14</v>
@@ -6227,16 +6227,16 @@
         <v>1.43</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S23" t="n">
         <v>2.06</v>
       </c>
       <c r="T23" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="U23" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="V23" t="n">
         <v>1.53</v>
@@ -6245,7 +6245,7 @@
         <v>1.66</v>
       </c>
       <c r="X23" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="Y23" t="n">
         <v>24</v>
@@ -6281,7 +6281,7 @@
         <v>27</v>
       </c>
       <c r="AJ23" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK23" t="n">
         <v>22</v>
@@ -6290,7 +6290,7 @@
         <v>25</v>
       </c>
       <c r="AM23" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AN23" t="n">
         <v>10.5</v>
@@ -6341,7 +6341,7 @@
         <v>19</v>
       </c>
       <c r="BD23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE23" t="n">
         <v>34</v>
@@ -6350,7 +6350,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH23" t="n">
         <v>5.1</v>
@@ -6362,16 +6362,16 @@
         <v>8.6</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN23" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO23" t="n">
         <v>5.6</v>
@@ -6380,13 +6380,13 @@
         <v>15.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS23" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BT23" t="n">
         <v>6.8</v>
@@ -6398,23 +6398,23 @@
         <v>17.5</v>
       </c>
       <c r="BW23" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX23" t="n">
         <v>22</v>
       </c>
       <c r="BY23" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ23" t="n">
         <v>12</v>
       </c>
       <c r="CA23" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="G24" t="n">
         <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="I24" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K24" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L24" t="n">
         <v>1.21</v>
@@ -6469,49 +6469,49 @@
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="O24" t="n">
         <v>1.11</v>
       </c>
       <c r="P24" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T24" t="n">
         <v>1.37</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.38</v>
       </c>
       <c r="U24" t="n">
         <v>3.4</v>
       </c>
       <c r="V24" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="W24" t="n">
         <v>1.5</v>
       </c>
       <c r="X24" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="Y24" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Z24" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AA24" t="n">
         <v>38</v>
       </c>
       <c r="AB24" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AC24" t="n">
         <v>12.5</v>
@@ -6523,49 +6523,49 @@
         <v>20</v>
       </c>
       <c r="AF24" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AG24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH24" t="n">
         <v>13.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AJ24" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AK24" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AL24" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AM24" t="n">
         <v>48</v>
       </c>
       <c r="AN24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO24" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AP24" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AQ24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU24" t="n">
         <v>11</v>
@@ -6574,10 +6574,10 @@
         <v>11.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AY24" t="n">
         <v>13</v>
@@ -6586,43 +6586,43 @@
         <v>12</v>
       </c>
       <c r="BA24" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BC24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE24" t="n">
         <v>30</v>
       </c>
       <c r="BF24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG24" t="n">
         <v>7.2</v>
       </c>
       <c r="BH24" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BI24" t="n">
         <v>5.1</v>
       </c>
       <c r="BJ24" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL24" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM24" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN24" t="n">
         <v>7.2</v>
@@ -6631,16 +6631,16 @@
         <v>5.2</v>
       </c>
       <c r="BP24" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR24" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT24" t="n">
         <v>6.4</v>
@@ -6649,26 +6649,26 @@
         <v>5.6</v>
       </c>
       <c r="BV24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BW24" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ24" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA24" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -6699,16 +6699,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G25" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H25" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="I25" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J25" t="n">
         <v>3.6</v>
@@ -6720,10 +6720,10 @@
         <v>1.45</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
         <v>1.38</v>
@@ -6738,7 +6738,7 @@
         <v>1.29</v>
       </c>
       <c r="S25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
         <v>1.96</v>
@@ -6747,16 +6747,16 @@
         <v>1.91</v>
       </c>
       <c r="V25" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W25" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z25" t="n">
         <v>40</v>
@@ -6771,7 +6771,7 @@
         <v>8.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE25" t="n">
         <v>700</v>
@@ -6795,7 +6795,7 @@
         <v>22</v>
       </c>
       <c r="AL25" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AM25" t="n">
         <v>580</v>
@@ -6810,13 +6810,13 @@
         <v>10</v>
       </c>
       <c r="AQ25" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR25" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT25" t="n">
         <v>6.8</v>
@@ -6825,10 +6825,10 @@
         <v>7.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX25" t="n">
         <v>9.4</v>
@@ -6837,10 +6837,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB25" t="n">
         <v>18</v>
@@ -6852,19 +6852,19 @@
         <v>20</v>
       </c>
       <c r="BE25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG25" t="n">
         <v>12</v>
       </c>
-      <c r="BF25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BH25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ25" t="n">
         <v>11</v>
@@ -6876,53 +6876,53 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN25" t="n">
         <v>4.4</v>
       </c>
       <c r="BO25" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="BP25" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ25" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BR25" t="n">
         <v>32</v>
       </c>
       <c r="BS25" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BT25" t="n">
         <v>8.6</v>
       </c>
       <c r="BU25" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
         <v>11</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>11.5</v>
       </c>
       <c r="BZ25" t="n">
         <v>28</v>
       </c>
       <c r="CA25" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="G26" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="H26" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I26" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J26" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="K26" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L26" t="n">
         <v>1.23</v>
@@ -6977,55 +6977,55 @@
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="O26" t="n">
         <v>1.14</v>
       </c>
       <c r="P26" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="R26" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="S26" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="T26" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U26" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V26" t="n">
         <v>1.15</v>
       </c>
       <c r="W26" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="X26" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Y26" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Z26" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA26" t="n">
         <v>200</v>
       </c>
       <c r="AB26" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC26" t="n">
         <v>17</v>
       </c>
       <c r="AD26" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AE26" t="n">
         <v>75</v>
@@ -7040,7 +7040,7 @@
         <v>20</v>
       </c>
       <c r="AI26" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ26" t="n">
         <v>15.5</v>
@@ -7049,124 +7049,124 @@
         <v>14.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AM26" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AN26" t="n">
         <v>4.6</v>
       </c>
       <c r="AO26" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP26" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ26" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR26" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA26" t="n">
         <v>7.2</v>
       </c>
-      <c r="AT26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU26" t="n">
+      <c r="BB26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC26" t="n">
         <v>5.2</v>
       </c>
-      <c r="AV26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY26" t="n">
+      <c r="BD26" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>24</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>38</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN26" t="n">
         <v>4.6</v>
       </c>
-      <c r="AZ26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG26" t="n">
+      <c r="BO26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU26" t="n">
         <v>6.6</v>
       </c>
-      <c r="BH26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BI26" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BJ26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BQ26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BR26" t="n">
-        <v>18</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BT26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BX26" t="n">
         <v>42</v>
       </c>
       <c r="BY26" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BZ26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="G27" t="n">
         <v>3.05</v>
       </c>
       <c r="H27" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I27" t="n">
         <v>2.9</v>
@@ -7222,7 +7222,7 @@
         <v>3.2</v>
       </c>
       <c r="K27" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L27" t="n">
         <v>1.54</v>
@@ -7237,7 +7237,7 @@
         <v>1.5</v>
       </c>
       <c r="P27" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Q27" t="n">
         <v>2.46</v>
@@ -7249,7 +7249,7 @@
         <v>4.9</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U27" t="n">
         <v>1.87</v>
@@ -7258,10 +7258,10 @@
         <v>1.52</v>
       </c>
       <c r="W27" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X27" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y27" t="n">
         <v>9.6</v>
@@ -7288,13 +7288,13 @@
         <v>23</v>
       </c>
       <c r="AG27" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH27" t="n">
         <v>25</v>
       </c>
       <c r="AI27" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ27" t="n">
         <v>60</v>
@@ -7315,13 +7315,13 @@
         <v>55</v>
       </c>
       <c r="AP27" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ27" t="n">
         <v>7.8</v>
       </c>
       <c r="AR27" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS27" t="n">
         <v>5</v>
@@ -7339,13 +7339,13 @@
         <v>5.2</v>
       </c>
       <c r="AX27" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>18</v>
+        <v>5.3</v>
       </c>
       <c r="BA27" t="n">
         <v>4.7</v>
@@ -7354,19 +7354,19 @@
         <v>5</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BE27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG27" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>5</v>
       </c>
       <c r="BH27" t="n">
         <v>2.84</v>
@@ -7390,7 +7390,7 @@
         <v>5.8</v>
       </c>
       <c r="BO27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-20 08:08:17</t>
+          <t>2026-07-20 10:18:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N2" t="n">
         <v>3.1</v>
       </c>
-      <c r="G2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5.1</v>
-      </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="P2" t="n">
-        <v>2.38</v>
+        <v>1.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.7</v>
+        <v>2.44</v>
       </c>
       <c r="R2" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>2.74</v>
+        <v>4.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="W2" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE2" t="n">
         <v>34</v>
       </c>
-      <c r="AB2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>23</v>
-      </c>
       <c r="AF2" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
         <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AI2" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA2" t="n">
         <v>48</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>26</v>
       </c>
       <c r="BB2" t="n">
         <v>44</v>
       </c>
       <c r="BC2" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>120</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG2" t="n">
         <v>30</v>
       </c>
-      <c r="BD2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG2" t="n">
+      <c r="BH2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>18</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
         <v>13.5</v>
       </c>
-      <c r="BH2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>85</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>65</v>
-      </c>
       <c r="BN2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="BQ2" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="BR2" t="n">
-        <v>29</v>
+        <v>160</v>
       </c>
       <c r="BS2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW2" t="n">
         <v>25</v>
       </c>
-      <c r="BT2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>9</v>
-      </c>
       <c r="BX2" t="n">
-        <v>28</v>
+        <v>160</v>
       </c>
       <c r="BY2" t="n">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -1111,220 +1111,220 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="G3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="I3" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="J3" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.28</v>
+        <v>1.84</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>5.9</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>2.68</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="R3" t="n">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="U3" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="V3" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
-        <v>28</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AA3" t="n">
         <v>11.5</v>
       </c>
       <c r="AB3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>490</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>200</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>190</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>310</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>360</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX3" t="n">
         <v>50</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AY3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>28</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>270</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>130</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>160</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>200</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>260</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>170</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>910</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BV3" t="n">
         <v>14</v>
       </c>
-      <c r="AD3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>480</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>170</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>170</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>85</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BJ3" t="n">
+      <c r="BW3" t="n">
         <v>11.5</v>
       </c>
-      <c r="BK3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>110</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.4</v>
+        <v>38</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="G4" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
         <v>1.09</v>
@@ -1392,10 +1392,10 @@
         <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
         <v>2.24</v>
@@ -1407,136 +1407,136 @@
         <v>4.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.54</v>
+        <v>1.98</v>
       </c>
       <c r="U4" t="n">
-        <v>1.66</v>
+        <v>1.99</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="X4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AA4" t="n">
-        <v>95</v>
+        <v>990</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF4" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>980</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK4" t="n">
         <v>24</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>36</v>
       </c>
       <c r="AL4" t="n">
         <v>60</v>
       </c>
       <c r="AM4" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>65</v>
+        <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AS4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW4" t="n">
         <v>55</v>
       </c>
-      <c r="AT4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>38</v>
-      </c>
       <c r="AX4" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BB4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BE4" t="n">
         <v>95</v>
       </c>
       <c r="BF4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG4" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1545,50 +1545,50 @@
         <v>120</v>
       </c>
       <c r="BN4" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BT4" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -1619,178 +1619,178 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="G5" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="H5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="V5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W5" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="X5" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>980</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AC5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AE5" t="n">
         <v>700</v>
       </c>
       <c r="AF5" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AI5" t="n">
         <v>700</v>
       </c>
       <c r="AJ5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK5" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO5" t="n">
         <v>240</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="AS5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AT5" t="n">
         <v>6.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BB5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD5" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="BE5" t="n">
         <v>120</v>
       </c>
       <c r="BF5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="BJ5" t="n">
         <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1799,40 +1799,40 @@
         <v>150</v>
       </c>
       <c r="BN5" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BP5" t="n">
         <v>11</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS5" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BT5" t="n">
         <v>10.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -1876,79 +1876,79 @@
         <v>6.4</v>
       </c>
       <c r="G6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H6" t="n">
         <v>1.57</v>
       </c>
       <c r="I6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="J6" t="n">
         <v>4.6</v>
       </c>
       <c r="K6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S6" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="T6" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V6" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="W6" t="n">
         <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AB6" t="n">
         <v>25</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AE6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AF6" t="n">
         <v>55</v>
@@ -1957,34 +1957,34 @@
         <v>24</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AJ6" t="n">
         <v>180</v>
       </c>
       <c r="AK6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL6" t="n">
         <v>80</v>
       </c>
       <c r="AM6" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AN6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AO6" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AP6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR6" t="n">
         <v>9.6</v>
@@ -1993,34 +1993,34 @@
         <v>13</v>
       </c>
       <c r="AT6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV6" t="n">
         <v>9.4</v>
       </c>
-      <c r="AV6" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AW6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX6" t="n">
         <v>48</v>
       </c>
       <c r="AY6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BB6" t="n">
         <v>60</v>
       </c>
       <c r="BC6" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BD6" t="n">
         <v>65</v>
@@ -2029,22 +2029,22 @@
         <v>75</v>
       </c>
       <c r="BF6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BG6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL6" t="n">
         <v>120</v>
@@ -2053,7 +2053,7 @@
         <v>90</v>
       </c>
       <c r="BN6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BO6" t="n">
         <v>8.800000000000001</v>
@@ -2062,31 +2062,31 @@
         <v>55</v>
       </c>
       <c r="BQ6" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR6" t="n">
         <v>55</v>
       </c>
       <c r="BS6" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT6" t="n">
         <v>4.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX6" t="n">
         <v>24</v>
       </c>
       <c r="BY6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -2127,25 +2127,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="G7" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="H7" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="I7" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
         <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
@@ -2154,10 +2154,10 @@
         <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
         <v>2.26</v>
@@ -2166,88 +2166,88 @@
         <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U7" t="n">
         <v>2</v>
       </c>
       <c r="V7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.54</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.51</v>
-      </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB7" t="n">
         <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AD7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AF7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ7" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AK7" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AL7" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>580</v>
+        <v>390</v>
       </c>
       <c r="AN7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO7" t="n">
         <v>34</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>40</v>
       </c>
       <c r="AP7" t="n">
         <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR7" t="n">
         <v>15</v>
       </c>
       <c r="AS7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AU7" t="n">
         <v>6.6</v>
@@ -2256,7 +2256,7 @@
         <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AX7" t="n">
         <v>16</v>
@@ -2268,37 +2268,37 @@
         <v>16.5</v>
       </c>
       <c r="BA7" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD7" t="n">
         <v>36</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>29</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>40</v>
       </c>
       <c r="BE7" t="n">
         <v>95</v>
       </c>
       <c r="BF7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BG7" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BH7" t="n">
         <v>3.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ7" t="n">
         <v>10.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2307,50 +2307,50 @@
         <v>120</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BO7" t="n">
         <v>5</v>
       </c>
       <c r="BP7" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT7" t="n">
         <v>5.9</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV7" t="n">
         <v>24</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -2381,31 +2381,31 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="G8" t="n">
         <v>2.64</v>
       </c>
       <c r="H8" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J8" t="n">
         <v>3.4</v>
       </c>
-      <c r="J8" t="n">
-        <v>3.15</v>
-      </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
         <v>1.36</v>
@@ -2414,121 +2414,121 @@
         <v>1.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U8" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W8" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="X8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y8" t="n">
         <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA8" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB8" t="n">
         <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE8" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AF8" t="n">
         <v>17.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI8" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ8" t="n">
         <v>42</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL8" t="n">
         <v>60</v>
       </c>
       <c r="AM8" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AO8" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AP8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>9.6</v>
       </c>
       <c r="AR8" t="n">
         <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW8" t="n">
         <v>25</v>
       </c>
       <c r="AX8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BC8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD8" t="n">
         <v>30</v>
@@ -2537,22 +2537,22 @@
         <v>85</v>
       </c>
       <c r="BF8" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BG8" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2561,40 +2561,40 @@
         <v>110</v>
       </c>
       <c r="BN8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>5.8</v>
       </c>
-      <c r="BO8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BT8" t="n">
         <v>6.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -2638,52 +2638,52 @@
         <v>7.2</v>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="I9" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="J9" t="n">
         <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U9" t="n">
         <v>2</v>
       </c>
-      <c r="U9" t="n">
-        <v>1.89</v>
-      </c>
       <c r="V9" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="W9" t="n">
         <v>1.14</v>
@@ -2695,19 +2695,19 @@
         <v>8.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA9" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
         <v>16.5</v>
@@ -2719,40 +2719,40 @@
         <v>29</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="AK9" t="n">
         <v>120</v>
       </c>
       <c r="AL9" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM9" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN9" t="n">
         <v>150</v>
       </c>
-      <c r="AN9" t="n">
-        <v>180</v>
-      </c>
       <c r="AO9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AP9" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT9" t="n">
         <v>20</v>
@@ -2761,49 +2761,49 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW9" t="n">
         <v>14.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AY9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BB9" t="n">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="BC9" t="n">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="BD9" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="BE9" t="n">
         <v>100</v>
       </c>
       <c r="BF9" t="n">
-        <v>85</v>
+        <v>15.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="BJ9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK9" t="n">
         <v>5.8</v>
@@ -2815,10 +2815,10 @@
         <v>130</v>
       </c>
       <c r="BN9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
@@ -2827,38 +2827,38 @@
         <v>10</v>
       </c>
       <c r="BR9" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
         <v>10</v>
       </c>
       <c r="BT9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BV9" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BX9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="CA9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="H10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I10" t="n">
         <v>1.39</v>
       </c>
-      <c r="I10" t="n">
-        <v>1.4</v>
-      </c>
       <c r="J10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
         <v>6.2</v>
@@ -2913,43 +2913,43 @@
         <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1.13</v>
       </c>
       <c r="P10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R10" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="S10" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="T10" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="W10" t="n">
         <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AA10" t="n">
         <v>12.5</v>
@@ -2958,7 +2958,7 @@
         <v>46</v>
       </c>
       <c r="AC10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AD10" t="n">
         <v>10.5</v>
@@ -2970,7 +2970,7 @@
         <v>85</v>
       </c>
       <c r="AG10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AH10" t="n">
         <v>21</v>
@@ -2979,10 +2979,10 @@
         <v>25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AK10" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AL10" t="n">
         <v>75</v>
@@ -3000,7 +3000,7 @@
         <v>34</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR10" t="n">
         <v>10</v>
@@ -3009,10 +3009,10 @@
         <v>11.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AU10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AV10" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
         <v>12</v>
       </c>
       <c r="AX10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AY10" t="n">
         <v>27</v>
@@ -3039,22 +3039,22 @@
         <v>80</v>
       </c>
       <c r="BD10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BE10" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="BF10" t="n">
         <v>60</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BH10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BJ10" t="n">
         <v>10.5</v>
@@ -3069,7 +3069,7 @@
         <v>75</v>
       </c>
       <c r="BN10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BO10" t="n">
         <v>10.5</v>
@@ -3078,16 +3078,16 @@
         <v>60</v>
       </c>
       <c r="BQ10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BR10" t="n">
         <v>50</v>
       </c>
       <c r="BS10" t="n">
-        <v>11.5</v>
+        <v>25</v>
       </c>
       <c r="BT10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BU10" t="n">
         <v>4</v>
@@ -3096,23 +3096,23 @@
         <v>7.8</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BY10" t="n">
         <v>15</v>
       </c>
       <c r="BZ10" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA10" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
         <v>2.74</v>
       </c>
       <c r="G11" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H11" t="n">
         <v>2.64</v>
@@ -3155,40 +3155,40 @@
         <v>2.68</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="R11" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="S11" t="n">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="T11" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="U11" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="V11" t="n">
         <v>1.6</v>
@@ -3197,10 +3197,10 @@
         <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z11" t="n">
         <v>20</v>
@@ -3209,112 +3209,112 @@
         <v>38</v>
       </c>
       <c r="AB11" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
         <v>12</v>
       </c>
       <c r="AE11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF11" t="n">
         <v>21</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL11" t="n">
         <v>32</v>
       </c>
-      <c r="AJ11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>34</v>
-      </c>
       <c r="AM11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR11" t="n">
         <v>18</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>17.5</v>
       </c>
       <c r="AS11" t="n">
         <v>32</v>
       </c>
       <c r="AT11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV11" t="n">
         <v>11</v>
       </c>
       <c r="AW11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC11" t="n">
         <v>23</v>
       </c>
-      <c r="AX11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA11" t="n">
+      <c r="BD11" t="n">
         <v>29</v>
       </c>
-      <c r="BB11" t="n">
-        <v>36</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>30</v>
-      </c>
       <c r="BE11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF11" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BJ11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL11" t="n">
         <v>80</v>
@@ -3326,47 +3326,47 @@
         <v>6</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP11" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ11" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BR11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS11" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BT11" t="n">
         <v>5.9</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV11" t="n">
         <v>18</v>
       </c>
       <c r="BW11" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BX11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ11" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
         <v>3.65</v>
@@ -3421,49 +3421,49 @@
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
         <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
         <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="U12" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V12" t="n">
         <v>1.32</v>
       </c>
       <c r="W12" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="X12" t="n">
         <v>14.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z12" t="n">
         <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC12" t="n">
         <v>8.199999999999999</v>
@@ -3472,7 +3472,7 @@
         <v>16.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF12" t="n">
         <v>13</v>
@@ -3484,7 +3484,7 @@
         <v>18.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ12" t="n">
         <v>26</v>
@@ -3499,13 +3499,13 @@
         <v>100</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>13.5</v>
@@ -3514,10 +3514,10 @@
         <v>24</v>
       </c>
       <c r="AS12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU12" t="n">
         <v>7.4</v>
@@ -3532,13 +3532,13 @@
         <v>11.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB12" t="n">
         <v>22</v>
@@ -3556,7 +3556,7 @@
         <v>14</v>
       </c>
       <c r="BG12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH12" t="n">
         <v>3.45</v>
@@ -3583,10 +3583,10 @@
         <v>4.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR12" t="n">
         <v>30</v>
@@ -3595,32 +3595,32 @@
         <v>9.4</v>
       </c>
       <c r="BT12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BV12" t="n">
         <v>34</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX12" t="n">
         <v>44</v>
       </c>
       <c r="BY12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CA12" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="G13" t="n">
         <v>2.06</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L13" t="n">
         <v>1.58</v>
@@ -3675,28 +3675,28 @@
         <v>1.13</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="O13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="R13" t="n">
         <v>1.17</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="T13" t="n">
         <v>2.26</v>
       </c>
       <c r="U13" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V13" t="n">
         <v>1.2</v>
@@ -3723,19 +3723,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE13" t="n">
         <v>700</v>
       </c>
       <c r="AF13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG13" t="n">
         <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI13" t="n">
         <v>700</v>
@@ -3759,10 +3759,10 @@
         <v>700</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="AR13" t="n">
         <v>7.2</v>
@@ -3771,34 +3771,34 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV13" t="n">
         <v>6.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BA13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.6</v>
+        <v>19.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD13" t="n">
         <v>7.6</v>
@@ -3807,74 +3807,74 @@
         <v>8.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>2.14</v>
+        <v>10.5</v>
       </c>
       <c r="BN13" t="n">
         <v>4.5</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BP13" t="n">
         <v>16.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BU13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA13" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>8.4</v>
-      </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -3929,22 +3929,22 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O14" t="n">
         <v>1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="R14" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S14" t="n">
-        <v>1.05</v>
+        <v>5.5</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>990</v>
+        <v>5.2</v>
       </c>
       <c r="H15" t="n">
         <v>2</v>
@@ -4180,22 +4180,22 @@
         <v>1.68</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N15" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="O15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P15" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S15" t="n">
         <v>1.05</v>
@@ -4207,7 +4207,7 @@
         <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
         <v>1.3</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G16" t="n">
         <v>3.6</v>
@@ -4437,22 +4437,22 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P16" t="n">
         <v>1.32</v>
       </c>
-      <c r="O16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.31</v>
-      </c>
       <c r="Q16" t="n">
-        <v>1.86</v>
+        <v>2.26</v>
       </c>
       <c r="R16" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="S16" t="n">
-        <v>1.06</v>
+        <v>5.7</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4464,7 +4464,7 @@
         <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="X16" t="n">
         <v>970</v>
@@ -4527,7 +4527,7 @@
         <v>4.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.5</v>
+        <v>7.6</v>
       </c>
       <c r="AS16" t="n">
         <v>1.62</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -4673,40 +4673,40 @@
         <v>11.5</v>
       </c>
       <c r="H17" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="J17" t="n">
         <v>2.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
         <v>1.32</v>
       </c>
       <c r="O17" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="P17" t="n">
         <v>1.32</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="R17" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S17" t="n">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4715,7 +4715,7 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
         <v>1.33</v>
@@ -4736,7 +4736,7 @@
         <v>950</v>
       </c>
       <c r="AC17" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AD17" t="n">
         <v>950</v>
@@ -4775,52 +4775,52 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AU17" t="n">
         <v>1.19</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="BF17" t="n">
         <v>1.55</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="G18" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H18" t="n">
         <v>5</v>
@@ -4933,7 +4933,7 @@
         <v>5.3</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K18" t="n">
         <v>4</v>
@@ -4942,37 +4942,37 @@
         <v>1.4</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U18" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V18" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W18" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X18" t="n">
         <v>16</v>
@@ -4987,37 +4987,37 @@
         <v>700</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD18" t="n">
         <v>19.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AF18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH18" t="n">
         <v>19.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AJ18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK18" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL18" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM18" t="n">
         <v>200</v>
@@ -5029,64 +5029,64 @@
         <v>280</v>
       </c>
       <c r="AP18" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
         <v>29</v>
       </c>
       <c r="AS18" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="AT18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU18" t="n">
         <v>7.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AW18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
       </c>
       <c r="AY18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB18" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC18" t="n">
         <v>16.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BE18" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH18" t="n">
         <v>3.6</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BJ18" t="n">
         <v>10.5</v>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN18" t="n">
         <v>4.7</v>
@@ -5113,10 +5113,10 @@
         <v>8.4</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS18" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT18" t="n">
         <v>8.6</v>
@@ -5125,26 +5125,26 @@
         <v>5.6</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX18" t="n">
         <v>55</v>
       </c>
       <c r="BY18" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -5175,19 +5175,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="G19" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="H19" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I19" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J19" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
         <v>3.95</v>
@@ -5199,64 +5199,64 @@
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P19" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U19" t="n">
         <v>2.02</v>
       </c>
       <c r="V19" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA19" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD19" t="n">
         <v>21</v>
       </c>
       <c r="AE19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF19" t="n">
         <v>11</v>
       </c>
       <c r="AG19" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AH19" t="n">
         <v>21</v>
@@ -5268,7 +5268,7 @@
         <v>19</v>
       </c>
       <c r="AK19" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL19" t="n">
         <v>38</v>
@@ -5277,31 +5277,31 @@
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO19" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AP19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ19" t="n">
         <v>16</v>
       </c>
       <c r="AR19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS19" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU19" t="n">
         <v>7.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW19" t="n">
         <v>46</v>
@@ -5310,28 +5310,28 @@
         <v>9.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
         <v>18</v>
       </c>
       <c r="BA19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE19" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="BF19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG19" t="n">
         <v>55</v>
@@ -5340,19 +5340,19 @@
         <v>3.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="BJ19" t="n">
         <v>10.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN19" t="n">
         <v>4.4</v>
@@ -5361,7 +5361,7 @@
         <v>3.95</v>
       </c>
       <c r="BP19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ19" t="n">
         <v>6.6</v>
@@ -5370,35 +5370,35 @@
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU19" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="G20" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="H20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I20" t="n">
         <v>4.3</v>
       </c>
-      <c r="I20" t="n">
-        <v>4.9</v>
-      </c>
       <c r="J20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K20" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
         <v>1.22</v>
@@ -5453,100 +5453,100 @@
         <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="O20" t="n">
         <v>1.13</v>
       </c>
       <c r="P20" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="S20" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="T20" t="n">
         <v>1.47</v>
       </c>
       <c r="U20" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="W20" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="X20" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="Y20" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="Z20" t="n">
         <v>500</v>
       </c>
       <c r="AA20" t="n">
-        <v>500</v>
+        <v>340</v>
       </c>
       <c r="AB20" t="n">
         <v>19.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
         <v>120</v>
       </c>
       <c r="AF20" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
         <v>15.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="AK20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM20" t="n">
         <v>200</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AO20" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AP20" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AQ20" t="n">
         <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>18.5</v>
+        <v>7.8</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT20" t="n">
         <v>16</v>
@@ -5555,104 +5555,104 @@
         <v>11</v>
       </c>
       <c r="AV20" t="n">
-        <v>17</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW20" t="n">
-        <v>17.5</v>
+        <v>7.8</v>
       </c>
       <c r="AX20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
         <v>12.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD20" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE20" t="n">
         <v>28</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BH20" t="n">
         <v>5.6</v>
       </c>
       <c r="BI20" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BJ20" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK20" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BN20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ20" t="n">
         <v>5.4</v>
       </c>
-      <c r="BO20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>11</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BR20" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BS20" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BT20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BU20" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="BV20" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BW20" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY20" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ20" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CA20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -5683,139 +5683,139 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="G21" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="H21" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L21" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
         <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="U21" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="V21" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W21" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="X21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y21" t="n">
         <v>14.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA21" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC21" t="n">
         <v>8</v>
       </c>
       <c r="AD21" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG21" t="n">
         <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AJ21" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AK21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM21" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN21" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AP21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>12.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AS21" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AT21" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU21" t="n">
         <v>7.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY21" t="n">
         <v>9.4</v>
@@ -5824,34 +5824,34 @@
         <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BB21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BC21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BE21" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="BF21" t="n">
         <v>16.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BI21" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ21" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BK21" t="n">
         <v>7.8</v>
@@ -5860,53 +5860,53 @@
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP21" t="n">
         <v>14.5</v>
       </c>
-      <c r="BN21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>16</v>
-      </c>
       <c r="BQ21" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR21" t="n">
         <v>32</v>
       </c>
       <c r="BS21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT21" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BU21" t="n">
         <v>6</v>
       </c>
       <c r="BV21" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BW21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>29</v>
+      </c>
+      <c r="CA21" t="n">
         <v>10.5</v>
       </c>
-      <c r="BX21" t="n">
-        <v>44</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BZ21" t="n">
-        <v>28</v>
-      </c>
-      <c r="CA21" t="n">
-        <v>10</v>
-      </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -5937,19 +5937,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="G22" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I22" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="J22" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K22" t="n">
         <v>5.9</v>
@@ -5958,103 +5958,103 @@
         <v>1.17</v>
       </c>
       <c r="M22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O22" t="n">
         <v>1.09</v>
       </c>
       <c r="P22" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="R22" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S22" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="T22" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="U22" t="n">
         <v>3.05</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W22" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="X22" t="n">
+        <v>65</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z22" t="n">
         <v>100</v>
       </c>
-      <c r="Y22" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>500</v>
-      </c>
       <c r="AA22" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AB22" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AC22" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AD22" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AE22" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AF22" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH22" t="n">
         <v>18</v>
       </c>
       <c r="AI22" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ22" t="n">
         <v>21</v>
       </c>
       <c r="AK22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM22" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AN22" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AO22" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AP22" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14.5</v>
+        <v>42</v>
       </c>
       <c r="AR22" t="n">
         <v>55</v>
       </c>
       <c r="AS22" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="AT22" t="n">
         <v>19</v>
@@ -6063,58 +6063,58 @@
         <v>14</v>
       </c>
       <c r="AV22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW22" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AX22" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY22" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BB22" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD22" t="n">
         <v>17</v>
       </c>
       <c r="BE22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BF22" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BG22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BH22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BI22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BJ22" t="n">
         <v>9</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL22" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BM22" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN22" t="n">
         <v>5.7</v>
@@ -6123,16 +6123,16 @@
         <v>4.7</v>
       </c>
       <c r="BP22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BQ22" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BR22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BS22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT22" t="n">
         <v>11</v>
@@ -6141,26 +6141,26 @@
         <v>6.6</v>
       </c>
       <c r="BV22" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ22" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CA22" t="n">
         <v>5.7</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -6194,22 +6194,22 @@
         <v>2.42</v>
       </c>
       <c r="G23" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I23" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
         <v>4.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
@@ -6218,22 +6218,22 @@
         <v>7.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P23" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Q23" t="n">
         <v>1.43</v>
       </c>
       <c r="R23" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="S23" t="n">
         <v>2.06</v>
       </c>
       <c r="T23" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="U23" t="n">
         <v>3.15</v>
@@ -6242,7 +6242,7 @@
         <v>1.53</v>
       </c>
       <c r="W23" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X23" t="n">
         <v>40</v>
@@ -6254,7 +6254,7 @@
         <v>26</v>
       </c>
       <c r="AA23" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB23" t="n">
         <v>21</v>
@@ -6290,7 +6290,7 @@
         <v>25</v>
       </c>
       <c r="AM23" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AN23" t="n">
         <v>10.5</v>
@@ -6314,7 +6314,7 @@
         <v>18.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV23" t="n">
         <v>12</v>
@@ -6338,7 +6338,7 @@
         <v>30</v>
       </c>
       <c r="BC23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD23" t="n">
         <v>20</v>
@@ -6347,7 +6347,7 @@
         <v>34</v>
       </c>
       <c r="BF23" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG23" t="n">
         <v>11</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -6445,230 +6445,230 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G24" t="n">
         <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="J24" t="n">
         <v>4.3</v>
       </c>
       <c r="K24" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M24" t="n">
         <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P24" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="R24" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="S24" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="T24" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="U24" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="V24" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W24" t="n">
         <v>1.5</v>
       </c>
       <c r="X24" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Y24" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB24" t="n">
         <v>25</v>
       </c>
-      <c r="Z24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="AC24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL24" t="n">
         <v>29</v>
       </c>
-      <c r="AC24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE24" t="n">
+      <c r="AM24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT24" t="n">
         <v>20</v>
       </c>
-      <c r="AF24" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>48</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>24</v>
-      </c>
       <c r="AU24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV24" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW24" t="n">
         <v>17.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AY24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BB24" t="n">
         <v>40</v>
       </c>
       <c r="BC24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE24" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BF24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BG24" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH24" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BI24" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BJ24" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BK24" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL24" t="n">
         <v>65</v>
       </c>
       <c r="BM24" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN24" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BO24" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BP24" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="BQ24" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>26</v>
+      </c>
+      <c r="BY24" t="n">
         <v>9</v>
       </c>
-      <c r="BT24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV24" t="n">
-        <v>14</v>
-      </c>
-      <c r="BW24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BX24" t="n">
-        <v>19</v>
-      </c>
-      <c r="BY24" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BZ24" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="CA24" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -6699,10 +6699,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G25" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H25" t="n">
         <v>5.1</v>
@@ -6771,7 +6771,7 @@
         <v>8.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE25" t="n">
         <v>700</v>
@@ -6804,7 +6804,7 @@
         <v>15.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="AP25" t="n">
         <v>10</v>
@@ -6840,7 +6840,7 @@
         <v>19.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB25" t="n">
         <v>18</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -6953,58 +6953,58 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="G26" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="H26" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I26" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K26" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L26" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M26" t="n">
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O26" t="n">
         <v>1.14</v>
       </c>
       <c r="P26" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="R26" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S26" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="U26" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W26" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="X26" t="n">
         <v>38</v>
@@ -7013,7 +7013,7 @@
         <v>40</v>
       </c>
       <c r="Z26" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AA26" t="n">
         <v>200</v>
@@ -7028,7 +7028,7 @@
         <v>34</v>
       </c>
       <c r="AE26" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AF26" t="n">
         <v>13.5</v>
@@ -7037,55 +7037,55 @@
         <v>11.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ26" t="n">
         <v>15.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR26" t="n">
         <v>25</v>
       </c>
-      <c r="AM26" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AS26" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AT26" t="n">
         <v>13</v>
       </c>
       <c r="AU26" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="AV26" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AX26" t="n">
-        <v>5.1</v>
+        <v>11</v>
       </c>
       <c r="AY26" t="n">
         <v>9.6</v>
@@ -7094,34 +7094,34 @@
         <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BB26" t="n">
         <v>12.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="BD26" t="n">
         <v>20</v>
       </c>
       <c r="BE26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BF26" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BG26" t="n">
-        <v>38</v>
+        <v>8.4</v>
       </c>
       <c r="BH26" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BI26" t="n">
         <v>4.2</v>
       </c>
       <c r="BJ26" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK26" t="n">
         <v>7.2</v>
@@ -7130,10 +7130,10 @@
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO26" t="n">
         <v>4.1</v>
@@ -7142,31 +7142,31 @@
         <v>8.6</v>
       </c>
       <c r="BQ26" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR26" t="n">
         <v>17.5</v>
       </c>
       <c r="BS26" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BT26" t="n">
         <v>11</v>
       </c>
       <c r="BU26" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BX26" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ26" t="n">
         <v>0</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>
@@ -7213,13 +7213,13 @@
         <v>3.05</v>
       </c>
       <c r="H27" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="J27" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K27" t="n">
         <v>3.4</v>
@@ -7231,7 +7231,7 @@
         <v>1.11</v>
       </c>
       <c r="N27" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="O27" t="n">
         <v>1.5</v>
@@ -7243,19 +7243,19 @@
         <v>2.46</v>
       </c>
       <c r="R27" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S27" t="n">
         <v>4.9</v>
       </c>
       <c r="T27" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
         <v>1.87</v>
       </c>
       <c r="V27" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W27" t="n">
         <v>1.5</v>
@@ -7285,7 +7285,7 @@
         <v>48</v>
       </c>
       <c r="AF27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG27" t="n">
         <v>16.5</v>
@@ -7324,7 +7324,7 @@
         <v>15.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AT27" t="n">
         <v>8</v>
@@ -7336,7 +7336,7 @@
         <v>10</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX27" t="n">
         <v>16</v>
@@ -7345,25 +7345,25 @@
         <v>11.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB27" t="n">
         <v>5</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BG27" t="n">
         <v>4.9</v>
@@ -7372,19 +7372,19 @@
         <v>2.84</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ27" t="n">
         <v>11</v>
       </c>
       <c r="BK27" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN27" t="n">
         <v>5.8</v>
@@ -7396,16 +7396,16 @@
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT27" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU27" t="n">
         <v>4.4</v>
@@ -7414,23 +7414,23 @@
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ27" t="n">
         <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-07-20 10:18:32</t>
+          <t>2026-07-20 12:28:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="108">
   <si>
     <t>League</t>
   </si>
@@ -262,18 +262,12 @@
     <t>Bulgarian A League</t>
   </si>
   <si>
+    <t>Uruguayan Primera Division</t>
+  </si>
+  <si>
     <t>Bolivian Liga de Futbol Profesional</t>
   </si>
   <si>
-    <t>Icelandic 1 Deild</t>
-  </si>
-  <si>
-    <t>Icelandic Urvalsdeild</t>
-  </si>
-  <si>
-    <t>Uruguayan Primera Division</t>
-  </si>
-  <si>
     <t>2026-07-20</t>
   </si>
   <si>
@@ -283,12 +277,6 @@
     <t>18:30:00</t>
   </si>
   <si>
-    <t>19:00:00</t>
-  </si>
-  <si>
-    <t>19:15:00</t>
-  </si>
-  <si>
     <t>20:00:00</t>
   </si>
   <si>
@@ -313,18 +301,6 @@
     <t>Botev Plovdiv</t>
   </si>
   <si>
-    <t>San Antonio Bulo Bulo</t>
-  </si>
-  <si>
-    <t>HK Kopavogur</t>
-  </si>
-  <si>
-    <t>Keflavik</t>
-  </si>
-  <si>
-    <t>Hafnarfjordur</t>
-  </si>
-  <si>
     <t>Torque</t>
   </si>
   <si>
@@ -352,18 +328,6 @@
     <t>Lokomotiv Sofia</t>
   </si>
   <si>
-    <t>Academia de Balompie Boli</t>
-  </si>
-  <si>
-    <t>IF Vestri</t>
-  </si>
-  <si>
-    <t>IA Akranes</t>
-  </si>
-  <si>
-    <t>Breidablik</t>
-  </si>
-  <si>
     <t>Danubio</t>
   </si>
   <si>
@@ -373,7 +337,7 @@
     <t>Liverpool Montevideo</t>
   </si>
   <si>
-    <t>2026-07-20 18:05:15</t>
+    <t>2026-07-20 18:26:24</t>
   </si>
 </sst>
 </file>
@@ -705,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -955,16 +919,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F2">
         <v>2.8</v>
@@ -1189,7 +1153,7 @@
         <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1197,16 +1161,16 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F3">
         <v>2.82</v>
@@ -1431,7 +1395,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1439,16 +1403,16 @@
         <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>2.8</v>
@@ -1673,7 +1637,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1681,16 +1645,16 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F5">
         <v>2.78</v>
@@ -1915,7 +1879,7 @@
         <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1923,16 +1887,16 @@
         <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F6">
         <v>1.79</v>
@@ -2157,7 +2121,7 @@
         <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2165,16 +2129,16 @@
         <v>81</v>
       </c>
       <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
         <v>86</v>
       </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="F7">
         <v>1.25</v>
@@ -2186,13 +2150,13 @@
         <v>4.4</v>
       </c>
       <c r="I7">
-        <v>38</v>
+        <v>680</v>
       </c>
       <c r="J7">
         <v>2.12</v>
       </c>
       <c r="K7">
-        <v>12</v>
+        <v>250</v>
       </c>
       <c r="L7">
         <v>1.41</v>
@@ -2210,7 +2174,7 @@
         <v>1.82</v>
       </c>
       <c r="Q7">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="R7">
         <v>1.18</v>
@@ -2399,7 +2363,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2407,241 +2371,241 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="F8">
-        <v>1.16</v>
+        <v>1.73</v>
       </c>
       <c r="G8">
+        <v>1.96</v>
+      </c>
+      <c r="H8">
+        <v>1.04</v>
+      </c>
+      <c r="I8">
+        <v>960</v>
+      </c>
+      <c r="J8">
+        <v>3.6</v>
+      </c>
+      <c r="K8">
+        <v>950</v>
+      </c>
+      <c r="L8">
         <v>1.17</v>
       </c>
-      <c r="H8">
-        <v>48</v>
-      </c>
-      <c r="I8">
+      <c r="M8">
+        <v>1.08</v>
+      </c>
+      <c r="N8">
+        <v>3.25</v>
+      </c>
+      <c r="O8">
+        <v>1.03</v>
+      </c>
+      <c r="P8">
+        <v>1.44</v>
+      </c>
+      <c r="Q8">
+        <v>1.75</v>
+      </c>
+      <c r="R8">
+        <v>1.21</v>
+      </c>
+      <c r="S8">
+        <v>1.05</v>
+      </c>
+      <c r="T8">
+        <v>1.83</v>
+      </c>
+      <c r="U8">
+        <v>1.92</v>
+      </c>
+      <c r="V8">
+        <v>1.03</v>
+      </c>
+      <c r="W8">
+        <v>1.03</v>
+      </c>
+      <c r="X8">
+        <v>970</v>
+      </c>
+      <c r="Y8">
+        <v>970</v>
+      </c>
+      <c r="Z8">
+        <v>65</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>970</v>
+      </c>
+      <c r="AC8">
+        <v>10</v>
+      </c>
+      <c r="AD8">
+        <v>1000</v>
+      </c>
+      <c r="AE8">
+        <v>130</v>
+      </c>
+      <c r="AF8">
+        <v>12.5</v>
+      </c>
+      <c r="AG8">
+        <v>11</v>
+      </c>
+      <c r="AH8">
         <v>950</v>
       </c>
-      <c r="J8">
-        <v>7.4</v>
-      </c>
-      <c r="K8">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>1.18</v>
-      </c>
-      <c r="S8">
-        <v>6.2</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>1.01</v>
-      </c>
-      <c r="W8">
-        <v>7.4</v>
-      </c>
-      <c r="X8">
-        <v>1000</v>
-      </c>
-      <c r="Y8">
-        <v>1000</v>
-      </c>
-      <c r="Z8">
-        <v>1000</v>
-      </c>
-      <c r="AA8">
-        <v>1000</v>
-      </c>
-      <c r="AB8">
-        <v>1000</v>
-      </c>
-      <c r="AC8">
-        <v>1000</v>
-      </c>
-      <c r="AD8">
-        <v>1000</v>
-      </c>
-      <c r="AE8">
-        <v>1000</v>
-      </c>
-      <c r="AF8">
-        <v>1000</v>
-      </c>
-      <c r="AG8">
-        <v>1.21</v>
-      </c>
-      <c r="AH8">
-        <v>1000</v>
-      </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK8">
-        <v>850</v>
+        <v>27</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM8">
         <v>1000</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO8">
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="AQ8">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="AR8">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="AS8">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="AT8">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="AU8">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AV8">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="AW8">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="AX8">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AY8">
-        <v>1.18</v>
+        <v>7.6</v>
       </c>
       <c r="AZ8">
-        <v>7.4</v>
+        <v>2.92</v>
       </c>
       <c r="BA8">
-        <v>8.199999999999999</v>
+        <v>3.25</v>
       </c>
       <c r="BB8">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BC8">
-        <v>5.8</v>
+        <v>2.84</v>
       </c>
       <c r="BD8">
-        <v>8.199999999999999</v>
+        <v>3.15</v>
       </c>
       <c r="BE8">
-        <v>6.2</v>
+        <v>2.48</v>
       </c>
       <c r="BF8">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="BG8">
-        <v>8</v>
+        <v>2.48</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2649,232 +2613,232 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F9">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="G9">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="H9">
-        <v>55</v>
+        <v>5.3</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="J9">
+        <v>5.2</v>
+      </c>
+      <c r="K9">
+        <v>5.4</v>
+      </c>
+      <c r="L9">
+        <v>1.25</v>
+      </c>
+      <c r="M9">
+        <v>1.02</v>
+      </c>
+      <c r="N9">
+        <v>7.4</v>
+      </c>
+      <c r="O9">
+        <v>1.13</v>
+      </c>
+      <c r="P9">
+        <v>3.1</v>
+      </c>
+      <c r="Q9">
+        <v>1.44</v>
+      </c>
+      <c r="R9">
+        <v>1.86</v>
+      </c>
+      <c r="S9">
+        <v>2.14</v>
+      </c>
+      <c r="T9">
+        <v>1.52</v>
+      </c>
+      <c r="U9">
+        <v>2.64</v>
+      </c>
+      <c r="V9">
+        <v>1.22</v>
+      </c>
+      <c r="W9">
+        <v>2.68</v>
+      </c>
+      <c r="X9">
+        <v>44</v>
+      </c>
+      <c r="Y9">
+        <v>38</v>
+      </c>
+      <c r="Z9">
+        <v>60</v>
+      </c>
+      <c r="AA9">
+        <v>160</v>
+      </c>
+      <c r="AB9">
+        <v>18.5</v>
+      </c>
+      <c r="AC9">
+        <v>13.5</v>
+      </c>
+      <c r="AD9">
+        <v>22</v>
+      </c>
+      <c r="AE9">
+        <v>70</v>
+      </c>
+      <c r="AF9">
+        <v>14</v>
+      </c>
+      <c r="AG9">
+        <v>10.5</v>
+      </c>
+      <c r="AH9">
+        <v>22</v>
+      </c>
+      <c r="AI9">
+        <v>48</v>
+      </c>
+      <c r="AJ9">
+        <v>18</v>
+      </c>
+      <c r="AK9">
+        <v>15</v>
+      </c>
+      <c r="AL9">
+        <v>23</v>
+      </c>
+      <c r="AM9">
+        <v>70</v>
+      </c>
+      <c r="AN9">
+        <v>5.5</v>
+      </c>
+      <c r="AO9">
+        <v>40</v>
+      </c>
+      <c r="AP9">
+        <v>32</v>
+      </c>
+      <c r="AQ9">
+        <v>30</v>
+      </c>
+      <c r="AR9">
+        <v>44</v>
+      </c>
+      <c r="AS9">
+        <v>10.5</v>
+      </c>
+      <c r="AT9">
+        <v>13.5</v>
+      </c>
+      <c r="AU9">
+        <v>10.5</v>
+      </c>
+      <c r="AV9">
+        <v>20</v>
+      </c>
+      <c r="AW9">
+        <v>46</v>
+      </c>
+      <c r="AX9">
+        <v>11.5</v>
+      </c>
+      <c r="AY9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ9">
+        <v>15</v>
+      </c>
+      <c r="BA9">
+        <v>32</v>
+      </c>
+      <c r="BB9">
+        <v>16</v>
+      </c>
+      <c r="BC9">
+        <v>12.5</v>
+      </c>
+      <c r="BD9">
+        <v>18.5</v>
+      </c>
+      <c r="BE9">
+        <v>11</v>
+      </c>
+      <c r="BF9">
+        <v>4.8</v>
+      </c>
+      <c r="BG9">
+        <v>29</v>
+      </c>
+      <c r="BH9">
+        <v>5.3</v>
+      </c>
+      <c r="BI9">
+        <v>4.7</v>
+      </c>
+      <c r="BJ9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK9">
+        <v>5.8</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
         <v>12</v>
       </c>
-      <c r="K9">
-        <v>1000</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>1.01</v>
-      </c>
-      <c r="W9">
-        <v>50</v>
-      </c>
-      <c r="X9">
-        <v>1000</v>
-      </c>
-      <c r="Y9">
-        <v>1000</v>
-      </c>
-      <c r="Z9">
-        <v>1000</v>
-      </c>
-      <c r="AA9">
-        <v>1000</v>
-      </c>
-      <c r="AB9">
-        <v>1000</v>
-      </c>
-      <c r="AC9">
-        <v>1000</v>
-      </c>
-      <c r="AD9">
-        <v>1000</v>
-      </c>
-      <c r="AE9">
-        <v>1000</v>
-      </c>
-      <c r="AF9">
-        <v>1000</v>
-      </c>
-      <c r="AG9">
-        <v>1000</v>
-      </c>
-      <c r="AH9">
-        <v>1000</v>
-      </c>
-      <c r="AI9">
-        <v>1000</v>
-      </c>
-      <c r="AJ9">
-        <v>1000</v>
-      </c>
-      <c r="AK9">
-        <v>1000</v>
-      </c>
-      <c r="AL9">
-        <v>1000</v>
-      </c>
-      <c r="AM9">
-        <v>1000</v>
-      </c>
-      <c r="AN9">
-        <v>1.01</v>
-      </c>
-      <c r="AO9">
-        <v>1000</v>
-      </c>
-      <c r="AP9">
-        <v>220</v>
-      </c>
-      <c r="AQ9">
-        <v>220</v>
-      </c>
-      <c r="AR9">
-        <v>220</v>
-      </c>
-      <c r="AS9">
-        <v>220</v>
-      </c>
-      <c r="AT9">
-        <v>220</v>
-      </c>
-      <c r="AU9">
-        <v>220</v>
-      </c>
-      <c r="AV9">
-        <v>220</v>
-      </c>
-      <c r="AW9">
-        <v>220</v>
-      </c>
-      <c r="AX9">
-        <v>28</v>
-      </c>
-      <c r="AY9">
-        <v>28</v>
-      </c>
-      <c r="AZ9">
-        <v>28</v>
-      </c>
-      <c r="BA9">
-        <v>50</v>
-      </c>
-      <c r="BB9">
-        <v>28</v>
-      </c>
-      <c r="BC9">
-        <v>28</v>
-      </c>
-      <c r="BD9">
-        <v>28</v>
-      </c>
-      <c r="BE9">
-        <v>28</v>
-      </c>
-      <c r="BF9">
-        <v>1.01</v>
-      </c>
-      <c r="BG9">
+      <c r="BN9">
+        <v>4.8</v>
+      </c>
+      <c r="BO9">
+        <v>4.2</v>
+      </c>
+      <c r="BP9">
+        <v>9.4</v>
+      </c>
+      <c r="BQ9">
+        <v>5.9</v>
+      </c>
+      <c r="BR9">
+        <v>17.5</v>
+      </c>
+      <c r="BS9">
         <v>7.8</v>
       </c>
-      <c r="BH9">
-        <v>0</v>
-      </c>
-      <c r="BI9">
-        <v>0</v>
-      </c>
-      <c r="BJ9">
-        <v>0</v>
-      </c>
-      <c r="BK9">
-        <v>0</v>
-      </c>
-      <c r="BL9">
-        <v>0</v>
-      </c>
-      <c r="BM9">
-        <v>0</v>
-      </c>
-      <c r="BN9">
-        <v>0</v>
-      </c>
-      <c r="BO9">
-        <v>0</v>
-      </c>
-      <c r="BP9">
-        <v>0</v>
-      </c>
-      <c r="BQ9">
-        <v>0</v>
-      </c>
-      <c r="BR9">
-        <v>0</v>
-      </c>
-      <c r="BS9">
-        <v>0</v>
-      </c>
       <c r="BT9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9">
         <v>0</v>
@@ -2883,120 +2847,120 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" t="s">
         <v>84</v>
       </c>
-      <c r="B10" t="s">
-        <v>86</v>
-      </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F10">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="G10">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="H10">
-        <v>80</v>
+        <v>2.82</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="K10">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V10">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI10">
         <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL10">
         <v>1000</v>
@@ -3005,1095 +2969,127 @@
         <v>1000</v>
       </c>
       <c r="AN10">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP10">
+        <v>7.6</v>
+      </c>
+      <c r="AQ10">
+        <v>7.8</v>
+      </c>
+      <c r="AR10">
+        <v>15</v>
+      </c>
+      <c r="AS10">
+        <v>27</v>
+      </c>
+      <c r="AT10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU10">
+        <v>6.6</v>
+      </c>
+      <c r="AV10">
+        <v>11.5</v>
+      </c>
+      <c r="AW10">
+        <v>32</v>
+      </c>
+      <c r="AX10">
+        <v>15.5</v>
+      </c>
+      <c r="AY10">
+        <v>12</v>
+      </c>
+      <c r="AZ10">
+        <v>19.5</v>
+      </c>
+      <c r="BA10">
+        <v>48</v>
+      </c>
+      <c r="BB10">
+        <v>26</v>
+      </c>
+      <c r="BC10">
+        <v>24</v>
+      </c>
+      <c r="BD10">
+        <v>48</v>
+      </c>
+      <c r="BE10">
+        <v>46</v>
+      </c>
+      <c r="BF10">
+        <v>26</v>
+      </c>
+      <c r="BG10">
+        <v>32</v>
+      </c>
+      <c r="BH10">
+        <v>2.76</v>
+      </c>
+      <c r="BI10">
+        <v>2.54</v>
+      </c>
+      <c r="BJ10">
+        <v>11</v>
+      </c>
+      <c r="BK10">
+        <v>6.6</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>15.5</v>
+      </c>
+      <c r="BN10">
+        <v>5.8</v>
+      </c>
+      <c r="BO10">
+        <v>5.1</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
         <v>10</v>
       </c>
-      <c r="AQ10">
-        <v>28</v>
-      </c>
-      <c r="AR10">
-        <v>28</v>
-      </c>
-      <c r="AS10">
-        <v>28</v>
-      </c>
-      <c r="AT10">
-        <v>4.3</v>
-      </c>
-      <c r="AU10">
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>12.5</v>
+      </c>
+      <c r="BT10">
+        <v>5.8</v>
+      </c>
+      <c r="BU10">
+        <v>5.1</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
         <v>10</v>
       </c>
-      <c r="AV10">
-        <v>28</v>
-      </c>
-      <c r="AW10">
-        <v>28</v>
-      </c>
-      <c r="AX10">
-        <v>4.3</v>
-      </c>
-      <c r="AY10">
-        <v>4.3</v>
-      </c>
-      <c r="AZ10">
-        <v>10</v>
-      </c>
-      <c r="BA10">
-        <v>12</v>
-      </c>
-      <c r="BB10">
-        <v>4.3</v>
-      </c>
-      <c r="BC10">
-        <v>4.3</v>
-      </c>
-      <c r="BD10">
-        <v>4.3</v>
-      </c>
-      <c r="BE10">
-        <v>10</v>
-      </c>
-      <c r="BF10">
-        <v>1.01</v>
-      </c>
-      <c r="BG10">
-        <v>4.3</v>
-      </c>
-      <c r="BH10">
-        <v>0</v>
-      </c>
-      <c r="BI10">
-        <v>0</v>
-      </c>
-      <c r="BJ10">
-        <v>0</v>
-      </c>
-      <c r="BK10">
-        <v>0</v>
-      </c>
-      <c r="BL10">
-        <v>0</v>
-      </c>
-      <c r="BM10">
-        <v>0</v>
-      </c>
-      <c r="BN10">
-        <v>0</v>
-      </c>
-      <c r="BO10">
-        <v>0</v>
-      </c>
-      <c r="BP10">
-        <v>0</v>
-      </c>
-      <c r="BQ10">
-        <v>0</v>
-      </c>
-      <c r="BR10">
-        <v>0</v>
-      </c>
-      <c r="BS10">
-        <v>0</v>
-      </c>
-      <c r="BT10">
-        <v>0</v>
-      </c>
-      <c r="BU10">
-        <v>0</v>
-      </c>
-      <c r="BV10">
-        <v>0</v>
-      </c>
-      <c r="BW10">
-        <v>0</v>
-      </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="CB10" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11" spans="1:80">
-      <c r="A11" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" t="s">
-        <v>115</v>
-      </c>
-      <c r="F11">
-        <v>8.6</v>
-      </c>
-      <c r="G11">
-        <v>22</v>
-      </c>
-      <c r="H11">
-        <v>10</v>
-      </c>
-      <c r="I11">
-        <v>18.5</v>
-      </c>
-      <c r="J11">
-        <v>1.14</v>
-      </c>
-      <c r="K11">
-        <v>1.16</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>6.2</v>
-      </c>
-      <c r="N11">
-        <v>1.01</v>
-      </c>
-      <c r="O11">
-        <v>150</v>
-      </c>
-      <c r="P11">
-        <v>1.01</v>
-      </c>
-      <c r="Q11">
-        <v>150</v>
-      </c>
-      <c r="R11">
-        <v>1.01</v>
-      </c>
-      <c r="S11">
-        <v>17.5</v>
-      </c>
-      <c r="T11">
-        <v>1.56</v>
-      </c>
-      <c r="U11">
-        <v>1.01</v>
-      </c>
-      <c r="V11">
-        <v>1.05</v>
-      </c>
-      <c r="W11">
-        <v>1.05</v>
-      </c>
-      <c r="X11">
-        <v>1.11</v>
-      </c>
-      <c r="Y11">
-        <v>850</v>
-      </c>
-      <c r="Z11">
-        <v>1000</v>
-      </c>
-      <c r="AA11">
-        <v>1000</v>
-      </c>
-      <c r="AB11">
-        <v>850</v>
-      </c>
-      <c r="AC11">
-        <v>1000</v>
-      </c>
-      <c r="AD11">
-        <v>1000</v>
-      </c>
-      <c r="AE11">
-        <v>1000</v>
-      </c>
-      <c r="AF11">
-        <v>1000</v>
-      </c>
-      <c r="AG11">
-        <v>1000</v>
-      </c>
-      <c r="AH11">
-        <v>1000</v>
-      </c>
-      <c r="AI11">
-        <v>1000</v>
-      </c>
-      <c r="AJ11">
-        <v>1000</v>
-      </c>
-      <c r="AK11">
-        <v>1000</v>
-      </c>
-      <c r="AL11">
-        <v>1000</v>
-      </c>
-      <c r="AM11">
-        <v>1000</v>
-      </c>
-      <c r="AN11">
-        <v>1000</v>
-      </c>
-      <c r="AO11">
-        <v>1000</v>
-      </c>
-      <c r="AP11">
-        <v>1.07</v>
-      </c>
-      <c r="AQ11">
-        <v>10.5</v>
-      </c>
-      <c r="AR11">
-        <v>15.5</v>
-      </c>
-      <c r="AS11">
-        <v>3.75</v>
-      </c>
-      <c r="AT11">
-        <v>10.5</v>
-      </c>
-      <c r="AU11">
-        <v>100</v>
-      </c>
-      <c r="AV11">
-        <v>3.75</v>
-      </c>
-      <c r="AW11">
-        <v>3.75</v>
-      </c>
-      <c r="AX11">
-        <v>15.5</v>
-      </c>
-      <c r="AY11">
-        <v>3.75</v>
-      </c>
-      <c r="AZ11">
-        <v>5.4</v>
-      </c>
-      <c r="BA11">
-        <v>3.75</v>
-      </c>
-      <c r="BB11">
-        <v>3.75</v>
-      </c>
-      <c r="BC11">
-        <v>3.75</v>
-      </c>
-      <c r="BD11">
-        <v>3.75</v>
-      </c>
-      <c r="BE11">
-        <v>3.75</v>
-      </c>
-      <c r="BF11">
-        <v>11</v>
-      </c>
-      <c r="BG11">
-        <v>3.75</v>
-      </c>
-      <c r="BH11">
-        <v>0</v>
-      </c>
-      <c r="BI11">
-        <v>0</v>
-      </c>
-      <c r="BJ11">
-        <v>0</v>
-      </c>
-      <c r="BK11">
-        <v>0</v>
-      </c>
-      <c r="BL11">
-        <v>0</v>
-      </c>
-      <c r="BM11">
-        <v>0</v>
-      </c>
-      <c r="BN11">
-        <v>0</v>
-      </c>
-      <c r="BO11">
-        <v>0</v>
-      </c>
-      <c r="BP11">
-        <v>0</v>
-      </c>
-      <c r="BQ11">
-        <v>0</v>
-      </c>
-      <c r="BR11">
-        <v>0</v>
-      </c>
-      <c r="BS11">
-        <v>0</v>
-      </c>
-      <c r="BT11">
-        <v>0</v>
-      </c>
-      <c r="BU11">
-        <v>0</v>
-      </c>
-      <c r="BV11">
-        <v>0</v>
-      </c>
-      <c r="BW11">
-        <v>0</v>
-      </c>
-      <c r="BX11">
-        <v>0</v>
-      </c>
-      <c r="BY11">
-        <v>0</v>
-      </c>
-      <c r="BZ11">
-        <v>0</v>
-      </c>
-      <c r="CA11">
-        <v>0</v>
-      </c>
-      <c r="CB11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="12" spans="1:80">
-      <c r="A12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" t="s">
-        <v>116</v>
-      </c>
-      <c r="F12">
-        <v>1.73</v>
-      </c>
-      <c r="G12">
-        <v>1.96</v>
-      </c>
-      <c r="H12">
-        <v>1.04</v>
-      </c>
-      <c r="I12">
-        <v>46</v>
-      </c>
-      <c r="J12">
-        <v>3.6</v>
-      </c>
-      <c r="K12">
-        <v>14.5</v>
-      </c>
-      <c r="L12">
-        <v>1.17</v>
-      </c>
-      <c r="M12">
-        <v>1.08</v>
-      </c>
-      <c r="N12">
-        <v>3.25</v>
-      </c>
-      <c r="O12">
-        <v>1.03</v>
-      </c>
-      <c r="P12">
-        <v>1.44</v>
-      </c>
-      <c r="Q12">
-        <v>1.75</v>
-      </c>
-      <c r="R12">
-        <v>1.22</v>
-      </c>
-      <c r="S12">
-        <v>1.05</v>
-      </c>
-      <c r="T12">
-        <v>1.83</v>
-      </c>
-      <c r="U12">
-        <v>1.92</v>
-      </c>
-      <c r="V12">
-        <v>1.03</v>
-      </c>
-      <c r="W12">
-        <v>1.03</v>
-      </c>
-      <c r="X12">
-        <v>970</v>
-      </c>
-      <c r="Y12">
-        <v>970</v>
-      </c>
-      <c r="Z12">
-        <v>65</v>
-      </c>
-      <c r="AA12">
-        <v>1000</v>
-      </c>
-      <c r="AB12">
-        <v>970</v>
-      </c>
-      <c r="AC12">
-        <v>10</v>
-      </c>
-      <c r="AD12">
-        <v>1000</v>
-      </c>
-      <c r="AE12">
-        <v>130</v>
-      </c>
-      <c r="AF12">
-        <v>12.5</v>
-      </c>
-      <c r="AG12">
-        <v>11</v>
-      </c>
-      <c r="AH12">
-        <v>950</v>
-      </c>
-      <c r="AI12">
-        <v>150</v>
-      </c>
-      <c r="AJ12">
-        <v>27</v>
-      </c>
-      <c r="AK12">
-        <v>27</v>
-      </c>
-      <c r="AL12">
-        <v>70</v>
-      </c>
-      <c r="AM12">
-        <v>1000</v>
-      </c>
-      <c r="AN12">
-        <v>970</v>
-      </c>
-      <c r="AO12">
-        <v>1000</v>
-      </c>
-      <c r="AP12">
-        <v>2.88</v>
-      </c>
-      <c r="AQ12">
-        <v>2.96</v>
-      </c>
-      <c r="AR12">
-        <v>3.15</v>
-      </c>
-      <c r="AS12">
-        <v>3.15</v>
-      </c>
-      <c r="AT12">
-        <v>5.7</v>
-      </c>
-      <c r="AU12">
-        <v>6.6</v>
-      </c>
-      <c r="AV12">
-        <v>3.3</v>
-      </c>
-      <c r="AW12">
-        <v>3.25</v>
-      </c>
-      <c r="AX12">
-        <v>8.4</v>
-      </c>
-      <c r="AY12">
-        <v>7.6</v>
-      </c>
-      <c r="AZ12">
-        <v>2.92</v>
-      </c>
-      <c r="BA12">
-        <v>3.25</v>
-      </c>
-      <c r="BB12">
-        <v>3.3</v>
-      </c>
-      <c r="BC12">
-        <v>2.84</v>
-      </c>
-      <c r="BD12">
-        <v>3.15</v>
-      </c>
-      <c r="BE12">
-        <v>2.48</v>
-      </c>
-      <c r="BF12">
-        <v>3</v>
-      </c>
-      <c r="BG12">
-        <v>2.48</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.04</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>1.04</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.04</v>
-      </c>
-      <c r="BN12">
-        <v>1000</v>
-      </c>
-      <c r="BO12">
-        <v>1.04</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>1.04</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>1.04</v>
-      </c>
-      <c r="BT12">
-        <v>1000</v>
-      </c>
-      <c r="BU12">
-        <v>1.04</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>1.04</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
-      <c r="BY12">
-        <v>1.04</v>
-      </c>
-      <c r="BZ12">
-        <v>1000</v>
-      </c>
-      <c r="CA12">
-        <v>1.04</v>
-      </c>
-      <c r="CB12" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="13" spans="1:80">
-      <c r="A13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" t="s">
-        <v>104</v>
-      </c>
-      <c r="E13" t="s">
-        <v>117</v>
-      </c>
-      <c r="F13">
-        <v>1.52</v>
-      </c>
-      <c r="G13">
-        <v>1.56</v>
-      </c>
-      <c r="H13">
-        <v>6</v>
-      </c>
-      <c r="I13">
-        <v>7</v>
-      </c>
-      <c r="J13">
-        <v>5</v>
-      </c>
-      <c r="K13">
-        <v>5.5</v>
-      </c>
-      <c r="L13">
-        <v>1.23</v>
-      </c>
-      <c r="M13">
-        <v>1.02</v>
-      </c>
-      <c r="N13">
-        <v>7.4</v>
-      </c>
-      <c r="O13">
-        <v>1.13</v>
-      </c>
-      <c r="P13">
-        <v>3.15</v>
-      </c>
-      <c r="Q13">
-        <v>1.45</v>
-      </c>
-      <c r="R13">
-        <v>1.87</v>
-      </c>
-      <c r="S13">
-        <v>2.08</v>
-      </c>
-      <c r="T13">
-        <v>1.53</v>
-      </c>
-      <c r="U13">
-        <v>2.62</v>
-      </c>
-      <c r="V13">
-        <v>1.17</v>
-      </c>
-      <c r="W13">
-        <v>2.78</v>
-      </c>
-      <c r="X13">
-        <v>38</v>
-      </c>
-      <c r="Y13">
-        <v>38</v>
-      </c>
-      <c r="Z13">
-        <v>70</v>
-      </c>
-      <c r="AA13">
-        <v>210</v>
-      </c>
-      <c r="AB13">
-        <v>18.5</v>
-      </c>
-      <c r="AC13">
-        <v>17</v>
-      </c>
-      <c r="AD13">
-        <v>28</v>
-      </c>
-      <c r="AE13">
-        <v>80</v>
-      </c>
-      <c r="AF13">
-        <v>14</v>
-      </c>
-      <c r="AG13">
-        <v>11</v>
-      </c>
-      <c r="AH13">
-        <v>18</v>
-      </c>
-      <c r="AI13">
-        <v>95</v>
-      </c>
-      <c r="AJ13">
-        <v>17</v>
-      </c>
-      <c r="AK13">
-        <v>14</v>
-      </c>
-      <c r="AL13">
-        <v>23</v>
-      </c>
-      <c r="AM13">
-        <v>65</v>
-      </c>
-      <c r="AN13">
-        <v>4.9</v>
-      </c>
-      <c r="AO13">
-        <v>46</v>
-      </c>
-      <c r="AP13">
-        <v>29</v>
-      </c>
-      <c r="AQ13">
-        <v>16</v>
-      </c>
-      <c r="AR13">
-        <v>11</v>
-      </c>
-      <c r="AS13">
-        <v>9.4</v>
-      </c>
-      <c r="AT13">
-        <v>13</v>
-      </c>
-      <c r="AU13">
-        <v>11.5</v>
-      </c>
-      <c r="AV13">
-        <v>20</v>
-      </c>
-      <c r="AW13">
-        <v>11</v>
-      </c>
-      <c r="AX13">
-        <v>12</v>
-      </c>
-      <c r="AY13">
-        <v>9.4</v>
-      </c>
-      <c r="AZ13">
-        <v>15</v>
-      </c>
-      <c r="BA13">
-        <v>21</v>
-      </c>
-      <c r="BB13">
-        <v>14.5</v>
-      </c>
-      <c r="BC13">
-        <v>12</v>
-      </c>
-      <c r="BD13">
-        <v>19.5</v>
-      </c>
-      <c r="BE13">
-        <v>24</v>
-      </c>
-      <c r="BF13">
-        <v>4.4</v>
-      </c>
-      <c r="BG13">
-        <v>19</v>
-      </c>
-      <c r="BH13">
-        <v>5.3</v>
-      </c>
-      <c r="BI13">
-        <v>4.7</v>
-      </c>
-      <c r="BJ13">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK13">
-        <v>5.7</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>12.5</v>
-      </c>
-      <c r="BN13">
-        <v>4.8</v>
-      </c>
-      <c r="BO13">
-        <v>4.2</v>
-      </c>
-      <c r="BP13">
-        <v>9</v>
-      </c>
-      <c r="BQ13">
-        <v>5.7</v>
-      </c>
-      <c r="BR13">
-        <v>17.5</v>
-      </c>
-      <c r="BS13">
-        <v>8</v>
-      </c>
-      <c r="BT13">
-        <v>10.5</v>
-      </c>
-      <c r="BU13">
-        <v>6.2</v>
-      </c>
-      <c r="BV13">
-        <v>980</v>
-      </c>
-      <c r="BW13">
-        <v>11</v>
-      </c>
-      <c r="BX13">
-        <v>40</v>
-      </c>
-      <c r="BY13">
-        <v>11</v>
-      </c>
-      <c r="BZ13">
-        <v>0</v>
-      </c>
-      <c r="CA13">
-        <v>0</v>
-      </c>
-      <c r="CB13" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="14" spans="1:80">
-      <c r="A14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" t="s">
-        <v>105</v>
-      </c>
-      <c r="E14" t="s">
-        <v>118</v>
-      </c>
-      <c r="F14">
-        <v>2.88</v>
-      </c>
-      <c r="G14">
-        <v>2.98</v>
-      </c>
-      <c r="H14">
-        <v>2.82</v>
-      </c>
-      <c r="I14">
-        <v>2.9</v>
-      </c>
-      <c r="J14">
-        <v>3.15</v>
-      </c>
-      <c r="K14">
-        <v>3.35</v>
-      </c>
-      <c r="L14">
-        <v>1.54</v>
-      </c>
-      <c r="M14">
-        <v>1.11</v>
-      </c>
-      <c r="N14">
-        <v>2.82</v>
-      </c>
-      <c r="O14">
-        <v>1.51</v>
-      </c>
-      <c r="P14">
-        <v>1.6</v>
-      </c>
-      <c r="Q14">
-        <v>2.5</v>
-      </c>
-      <c r="R14">
-        <v>1.22</v>
-      </c>
-      <c r="S14">
-        <v>5</v>
-      </c>
-      <c r="T14">
-        <v>2.06</v>
-      </c>
-      <c r="U14">
-        <v>1.85</v>
-      </c>
-      <c r="V14">
-        <v>1.52</v>
-      </c>
-      <c r="W14">
-        <v>1.5</v>
-      </c>
-      <c r="X14">
-        <v>10.5</v>
-      </c>
-      <c r="Y14">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z14">
-        <v>17.5</v>
-      </c>
-      <c r="AA14">
-        <v>140</v>
-      </c>
-      <c r="AB14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC14">
-        <v>7.8</v>
-      </c>
-      <c r="AD14">
-        <v>13.5</v>
-      </c>
-      <c r="AE14">
-        <v>46</v>
-      </c>
-      <c r="AF14">
-        <v>19</v>
-      </c>
-      <c r="AG14">
-        <v>14.5</v>
-      </c>
-      <c r="AH14">
-        <v>25</v>
-      </c>
-      <c r="AI14">
-        <v>1000</v>
-      </c>
-      <c r="AJ14">
-        <v>65</v>
-      </c>
-      <c r="AK14">
-        <v>46</v>
-      </c>
-      <c r="AL14">
-        <v>75</v>
-      </c>
-      <c r="AM14">
-        <v>1000</v>
-      </c>
-      <c r="AN14">
-        <v>55</v>
-      </c>
-      <c r="AO14">
-        <v>55</v>
-      </c>
-      <c r="AP14">
-        <v>8.4</v>
-      </c>
-      <c r="AQ14">
-        <v>7.8</v>
-      </c>
-      <c r="AR14">
-        <v>15.5</v>
-      </c>
-      <c r="AS14">
-        <v>32</v>
-      </c>
-      <c r="AT14">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU14">
-        <v>6.6</v>
-      </c>
-      <c r="AV14">
-        <v>11.5</v>
-      </c>
-      <c r="AW14">
-        <v>23</v>
-      </c>
-      <c r="AX14">
-        <v>15.5</v>
-      </c>
-      <c r="AY14">
-        <v>12</v>
-      </c>
-      <c r="AZ14">
-        <v>19.5</v>
-      </c>
-      <c r="BA14">
-        <v>48</v>
-      </c>
-      <c r="BB14">
-        <v>32</v>
-      </c>
-      <c r="BC14">
-        <v>23</v>
-      </c>
-      <c r="BD14">
-        <v>48</v>
-      </c>
-      <c r="BE14">
-        <v>46</v>
-      </c>
-      <c r="BF14">
-        <v>25</v>
-      </c>
-      <c r="BG14">
-        <v>29</v>
-      </c>
-      <c r="BH14">
-        <v>2.82</v>
-      </c>
-      <c r="BI14">
-        <v>2.58</v>
-      </c>
-      <c r="BJ14">
-        <v>11</v>
-      </c>
-      <c r="BK14">
-        <v>6.4</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>14.5</v>
-      </c>
-      <c r="BN14">
-        <v>5.8</v>
-      </c>
-      <c r="BO14">
-        <v>5.1</v>
-      </c>
-      <c r="BP14">
-        <v>1000</v>
-      </c>
-      <c r="BQ14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BR14">
-        <v>1000</v>
-      </c>
-      <c r="BS14">
-        <v>11.5</v>
-      </c>
-      <c r="BT14">
-        <v>5.8</v>
-      </c>
-      <c r="BU14">
-        <v>5.1</v>
-      </c>
-      <c r="BV14">
-        <v>1000</v>
-      </c>
-      <c r="BW14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BX14">
-        <v>1000</v>
-      </c>
-      <c r="BY14">
-        <v>11.5</v>
-      </c>
-      <c r="BZ14">
-        <v>1000</v>
-      </c>
-      <c r="CA14">
-        <v>11.5</v>
-      </c>
-      <c r="CB14" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
